--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5322,13 +5322,13 @@
         <v>2406.91</v>
       </c>
       <c r="E58" t="n">
-        <v>2474.37</v>
+        <v>2493.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-40.18</v>
+        <v>-21.45</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.016</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>256.14</v>
@@ -5365,9 +5365,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5402,19 +5402,19 @@
         <v>2150.76</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2187.92</v>
+        <v>2216.02</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2346.3</v>
+        <v>2365.03</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2504.67</v>
+        <v>2514.04</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2602.44</v>
+        <v>2621.17</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2700.21</v>
+        <v>2728.3</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2919.19</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4254.23</v>
+        <v>4473.33</v>
       </c>
       <c r="C2" t="n">
-        <v>4788.55</v>
+        <v>4953.73</v>
       </c>
       <c r="D2" t="n">
-        <v>4168.88</v>
+        <v>4064.97</v>
       </c>
       <c r="E2" t="n">
-        <v>4473.27</v>
+        <v>4779.65</v>
       </c>
       <c r="F2" t="n">
-        <v>219.05</v>
+        <v>306.38</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0515</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>619.6799999999999</v>
+        <v>888.77</v>
       </c>
       <c r="I2" t="n">
-        <v>3995.67</v>
+        <v>3549.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4089.02</v>
+        <v>3850.87</v>
       </c>
       <c r="K2" t="n">
-        <v>4170.08</v>
+        <v>4163.43</v>
       </c>
       <c r="L2" t="n">
-        <v>4251.15</v>
+        <v>4475.99</v>
       </c>
       <c r="M2" t="n">
-        <v>4338.35</v>
+        <v>4783.11</v>
       </c>
       <c r="N2" t="n">
-        <v>4425.56</v>
+        <v>5090.23</v>
       </c>
       <c r="O2" t="n">
-        <v>4500.48</v>
+        <v>5408.23</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -704,73 +704,73 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4473.33</v>
+        <v>4779.77</v>
       </c>
       <c r="C3" t="n">
-        <v>4953.73</v>
+        <v>4796.35</v>
       </c>
       <c r="D3" t="n">
-        <v>4064.97</v>
+        <v>4264.2</v>
       </c>
       <c r="E3" t="n">
-        <v>4779.65</v>
+        <v>4390.02</v>
       </c>
       <c r="F3" t="n">
-        <v>306.38</v>
+        <v>-389.63</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.0815</v>
       </c>
       <c r="H3" t="n">
-        <v>888.77</v>
+        <v>532.15</v>
       </c>
       <c r="I3" t="n">
-        <v>3549.2</v>
+        <v>3176.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3850.87</v>
+        <v>4026.03</v>
       </c>
       <c r="K3" t="n">
-        <v>4163.43</v>
+        <v>4335.26</v>
       </c>
       <c r="L3" t="n">
-        <v>4475.99</v>
+        <v>4644.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4783.11</v>
+        <v>5224.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5090.23</v>
+        <v>5803.56</v>
       </c>
       <c r="O3" t="n">
-        <v>5408.23</v>
+        <v>5842.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -780,19 +780,17 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -806,57 +804,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4779.77</v>
+        <v>4389.63</v>
       </c>
       <c r="C4" t="n">
-        <v>4796.35</v>
+        <v>4490.35</v>
       </c>
       <c r="D4" t="n">
-        <v>4264.2</v>
+        <v>4221.25</v>
       </c>
       <c r="E4" t="n">
-        <v>4390.02</v>
+        <v>4305.35</v>
       </c>
       <c r="F4" t="n">
-        <v>-389.63</v>
+        <v>-84.67</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0815</v>
+        <v>-0.0193</v>
       </c>
       <c r="H4" t="n">
-        <v>532.15</v>
+        <v>269.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3176.2</v>
+        <v>3732.04</v>
       </c>
       <c r="J4" t="n">
-        <v>4026.03</v>
+        <v>3787.74</v>
       </c>
       <c r="K4" t="n">
-        <v>4335.26</v>
+        <v>4123.94</v>
       </c>
       <c r="L4" t="n">
-        <v>4644.5</v>
+        <v>4460.15</v>
       </c>
       <c r="M4" t="n">
-        <v>5224.03</v>
+        <v>4656.1</v>
       </c>
       <c r="N4" t="n">
-        <v>5803.56</v>
+        <v>4852.05</v>
       </c>
       <c r="O4" t="n">
-        <v>5842.5</v>
+        <v>5328.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -864,14 +862,12 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -890,57 +886,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4389.63</v>
+        <v>4305.38</v>
       </c>
       <c r="C5" t="n">
-        <v>4490.35</v>
+        <v>4763.36</v>
       </c>
       <c r="D5" t="n">
-        <v>4221.25</v>
+        <v>4277.85</v>
       </c>
       <c r="E5" t="n">
-        <v>4305.35</v>
+        <v>4609.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-84.67</v>
+        <v>304.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0193</v>
+        <v>0.0707</v>
       </c>
       <c r="H5" t="n">
-        <v>269.1</v>
+        <v>485.51</v>
       </c>
       <c r="I5" t="n">
-        <v>3732.04</v>
+        <v>3952.15</v>
       </c>
       <c r="J5" t="n">
-        <v>3787.74</v>
+        <v>4011.02</v>
       </c>
       <c r="K5" t="n">
-        <v>4123.94</v>
+        <v>4170.8</v>
       </c>
       <c r="L5" t="n">
-        <v>4460.15</v>
+        <v>4330.57</v>
       </c>
       <c r="M5" t="n">
-        <v>4656.1</v>
+        <v>4439.9</v>
       </c>
       <c r="N5" t="n">
-        <v>4852.05</v>
+        <v>4549.22</v>
       </c>
       <c r="O5" t="n">
-        <v>5328.5</v>
+        <v>4759.45</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -951,78 +947,80 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4305.38</v>
+        <v>4609.72</v>
       </c>
       <c r="C6" t="n">
-        <v>4763.36</v>
+        <v>4670.53</v>
       </c>
       <c r="D6" t="n">
-        <v>4277.85</v>
+        <v>4428.33</v>
       </c>
       <c r="E6" t="n">
-        <v>4609.6</v>
+        <v>4451.33</v>
       </c>
       <c r="F6" t="n">
-        <v>304.25</v>
+        <v>-158.27</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0707</v>
+        <v>-0.0343</v>
       </c>
       <c r="H6" t="n">
-        <v>485.51</v>
+        <v>242.2</v>
       </c>
       <c r="I6" t="n">
-        <v>3952.15</v>
+        <v>3792.34</v>
       </c>
       <c r="J6" t="n">
-        <v>4011.02</v>
+        <v>4168.58</v>
       </c>
       <c r="K6" t="n">
-        <v>4170.8</v>
+        <v>4366.84</v>
       </c>
       <c r="L6" t="n">
-        <v>4330.57</v>
+        <v>4565.1</v>
       </c>
       <c r="M6" t="n">
-        <v>4439.9</v>
+        <v>4852.35</v>
       </c>
       <c r="N6" t="n">
-        <v>4549.22</v>
+        <v>5139.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4759.45</v>
+        <v>5248.87</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1030,93 +1028,97 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4609.72</v>
+        <v>4451.58</v>
       </c>
       <c r="C7" t="n">
-        <v>4670.53</v>
+        <v>4457.08</v>
       </c>
       <c r="D7" t="n">
-        <v>4428.33</v>
+        <v>3829.01</v>
       </c>
       <c r="E7" t="n">
-        <v>4451.33</v>
+        <v>4141.48</v>
       </c>
       <c r="F7" t="n">
-        <v>-158.27</v>
+        <v>-309.85</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0343</v>
+        <v>-0.0696</v>
       </c>
       <c r="H7" t="n">
-        <v>242.2</v>
+        <v>628.0700000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>3792.34</v>
+        <v>4186.13</v>
       </c>
       <c r="J7" t="n">
-        <v>4168.58</v>
+        <v>4160.08</v>
       </c>
       <c r="K7" t="n">
-        <v>4366.84</v>
+        <v>4330.23</v>
       </c>
       <c r="L7" t="n">
-        <v>4565.1</v>
+        <v>4500.38</v>
       </c>
       <c r="M7" t="n">
-        <v>4852.35</v>
+        <v>4572.43</v>
       </c>
       <c r="N7" t="n">
-        <v>5139.6</v>
+        <v>4644.48</v>
       </c>
       <c r="O7" t="n">
-        <v>5248.87</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+        <v>4912.73</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
@@ -1133,88 +1135,80 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4451.58</v>
+        <v>4141.36</v>
       </c>
       <c r="C8" t="n">
-        <v>4457.08</v>
+        <v>4616.53</v>
       </c>
       <c r="D8" t="n">
-        <v>3829.01</v>
+        <v>4087.93</v>
       </c>
       <c r="E8" t="n">
-        <v>4141.48</v>
+        <v>4515.42</v>
       </c>
       <c r="F8" t="n">
-        <v>-309.85</v>
+        <v>373.95</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0696</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>628.0700000000001</v>
+        <v>528.61</v>
       </c>
       <c r="I8" t="n">
-        <v>4186.13</v>
+        <v>3200.94</v>
       </c>
       <c r="J8" t="n">
-        <v>4160.08</v>
+        <v>3512.62</v>
       </c>
       <c r="K8" t="n">
-        <v>4330.23</v>
+        <v>3827.44</v>
       </c>
       <c r="L8" t="n">
-        <v>4500.38</v>
+        <v>4142.26</v>
       </c>
       <c r="M8" t="n">
-        <v>4572.43</v>
+        <v>4455.51</v>
       </c>
       <c r="N8" t="n">
-        <v>4644.48</v>
+        <v>4768.76</v>
       </c>
       <c r="O8" t="n">
-        <v>4912.73</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>5085.15</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1226,75 +1220,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4141.36</v>
+        <v>4515.3</v>
       </c>
       <c r="C9" t="n">
-        <v>4616.53</v>
+        <v>4755.22</v>
       </c>
       <c r="D9" t="n">
-        <v>4087.93</v>
+        <v>3460.22</v>
       </c>
       <c r="E9" t="n">
-        <v>4515.42</v>
+        <v>4164.43</v>
       </c>
       <c r="F9" t="n">
-        <v>373.95</v>
+        <v>-351</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>528.61</v>
+        <v>1295</v>
       </c>
       <c r="I9" t="n">
-        <v>3200.94</v>
+        <v>3559.32</v>
       </c>
       <c r="J9" t="n">
-        <v>3512.62</v>
+        <v>4068.41</v>
       </c>
       <c r="K9" t="n">
-        <v>3827.44</v>
+        <v>4251.12</v>
       </c>
       <c r="L9" t="n">
-        <v>4142.26</v>
+        <v>4433.83</v>
       </c>
       <c r="M9" t="n">
-        <v>4455.51</v>
+        <v>4779.73</v>
       </c>
       <c r="N9" t="n">
-        <v>4768.76</v>
+        <v>5125.63</v>
       </c>
       <c r="O9" t="n">
-        <v>5085.15</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+        <v>5145.14</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1308,76 +1310,70 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4515.3</v>
+        <v>4164.05</v>
       </c>
       <c r="C10" t="n">
-        <v>4755.22</v>
+        <v>4292.85</v>
       </c>
       <c r="D10" t="n">
-        <v>3460.22</v>
+        <v>3678.62</v>
       </c>
       <c r="E10" t="n">
-        <v>4164.43</v>
+        <v>3984.65</v>
       </c>
       <c r="F10" t="n">
-        <v>-351</v>
+        <v>-179.78</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0432</v>
       </c>
       <c r="H10" t="n">
-        <v>1295</v>
+        <v>614.23</v>
       </c>
       <c r="I10" t="n">
-        <v>3559.32</v>
+        <v>2165.22</v>
       </c>
       <c r="J10" t="n">
-        <v>4068.41</v>
+        <v>2897.78</v>
       </c>
       <c r="K10" t="n">
-        <v>4251.12</v>
+        <v>3516.93</v>
       </c>
       <c r="L10" t="n">
-        <v>4433.83</v>
+        <v>4136.07</v>
       </c>
       <c r="M10" t="n">
-        <v>4779.73</v>
+        <v>4811.93</v>
       </c>
       <c r="N10" t="n">
-        <v>5125.63</v>
+        <v>5487.78</v>
       </c>
       <c r="O10" t="n">
-        <v>5145.14</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>6050.22</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1403,50 +1399,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4164.05</v>
+        <v>3984.7</v>
       </c>
       <c r="C11" t="n">
-        <v>4292.85</v>
+        <v>4177.31</v>
       </c>
       <c r="D11" t="n">
-        <v>3678.62</v>
+        <v>3718.08</v>
       </c>
       <c r="E11" t="n">
-        <v>3984.65</v>
+        <v>4157.99</v>
       </c>
       <c r="F11" t="n">
-        <v>-179.78</v>
+        <v>173.34</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0432</v>
+        <v>0.0435</v>
       </c>
       <c r="H11" t="n">
-        <v>614.23</v>
+        <v>459.23</v>
       </c>
       <c r="I11" t="n">
-        <v>2165.22</v>
+        <v>3064.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2897.78</v>
+        <v>3369.88</v>
       </c>
       <c r="K11" t="n">
-        <v>3516.93</v>
+        <v>3677.54</v>
       </c>
       <c r="L11" t="n">
-        <v>4136.07</v>
+        <v>3985.19</v>
       </c>
       <c r="M11" t="n">
-        <v>4811.93</v>
+        <v>4291.76</v>
       </c>
       <c r="N11" t="n">
-        <v>5487.78</v>
+        <v>4598.33</v>
       </c>
       <c r="O11" t="n">
-        <v>6050.22</v>
+        <v>4907.07</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1457,13 +1453,15 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1478,77 +1476,79 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3984.7</v>
+        <v>4158.01</v>
       </c>
       <c r="C12" t="n">
-        <v>4177.31</v>
+        <v>4250.67</v>
       </c>
       <c r="D12" t="n">
-        <v>3718.08</v>
+        <v>3681.91</v>
       </c>
       <c r="E12" t="n">
-        <v>4157.99</v>
+        <v>3911.06</v>
       </c>
       <c r="F12" t="n">
-        <v>173.34</v>
+        <v>-246.93</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0435</v>
+        <v>-0.0594</v>
       </c>
       <c r="H12" t="n">
-        <v>459.23</v>
+        <v>568.76</v>
       </c>
       <c r="I12" t="n">
-        <v>3064.4</v>
+        <v>3258.84</v>
       </c>
       <c r="J12" t="n">
-        <v>3369.88</v>
+        <v>3803.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3677.54</v>
+        <v>3928.37</v>
       </c>
       <c r="L12" t="n">
-        <v>3985.19</v>
+        <v>4052.84</v>
       </c>
       <c r="M12" t="n">
-        <v>4291.76</v>
+        <v>4387.61</v>
       </c>
       <c r="N12" t="n">
-        <v>4598.33</v>
+        <v>4722.37</v>
       </c>
       <c r="O12" t="n">
-        <v>4907.07</v>
+        <v>4636.54</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1562,60 +1562,62 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4158.01</v>
+        <v>3911.75</v>
       </c>
       <c r="C13" t="n">
-        <v>4250.67</v>
+        <v>3912.63</v>
       </c>
       <c r="D13" t="n">
-        <v>3681.91</v>
+        <v>3063.09</v>
       </c>
       <c r="E13" t="n">
-        <v>3911.06</v>
+        <v>3582.62</v>
       </c>
       <c r="F13" t="n">
-        <v>-246.93</v>
+        <v>-328.44</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>568.76</v>
+        <v>849.55</v>
       </c>
       <c r="I13" t="n">
-        <v>3258.84</v>
+        <v>3113.15</v>
       </c>
       <c r="J13" t="n">
-        <v>3803.9</v>
+        <v>3314.69</v>
       </c>
       <c r="K13" t="n">
-        <v>3928.37</v>
+        <v>3626.68</v>
       </c>
       <c r="L13" t="n">
-        <v>4052.84</v>
+        <v>3938.68</v>
       </c>
       <c r="M13" t="n">
-        <v>4387.61</v>
+        <v>4195.44</v>
       </c>
       <c r="N13" t="n">
-        <v>4722.37</v>
+        <v>4452.21</v>
       </c>
       <c r="O13" t="n">
-        <v>4636.54</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
+        <v>4819.43</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
@@ -1646,69 +1648,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3911.75</v>
+        <v>3583.44</v>
       </c>
       <c r="C14" t="n">
-        <v>3912.63</v>
+        <v>3656.15</v>
       </c>
       <c r="D14" t="n">
-        <v>3063.09</v>
+        <v>3007.07</v>
       </c>
       <c r="E14" t="n">
-        <v>3582.62</v>
+        <v>3092.85</v>
       </c>
       <c r="F14" t="n">
-        <v>-328.44</v>
+        <v>-489.77</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1367</v>
       </c>
       <c r="H14" t="n">
-        <v>849.55</v>
+        <v>649.08</v>
       </c>
       <c r="I14" t="n">
-        <v>3113.15</v>
+        <v>2213.54</v>
       </c>
       <c r="J14" t="n">
-        <v>3314.69</v>
+        <v>2780.46</v>
       </c>
       <c r="K14" t="n">
-        <v>3626.68</v>
+        <v>3157.85</v>
       </c>
       <c r="L14" t="n">
-        <v>3938.68</v>
+        <v>3535.24</v>
       </c>
       <c r="M14" t="n">
-        <v>4195.44</v>
+        <v>4007.39</v>
       </c>
       <c r="N14" t="n">
-        <v>4452.21</v>
+        <v>4479.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4819.43</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4762.18</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
@@ -1739,50 +1733,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3583.44</v>
+        <v>3092.94</v>
       </c>
       <c r="C15" t="n">
-        <v>3656.15</v>
+        <v>3218.13</v>
       </c>
       <c r="D15" t="n">
-        <v>3007.07</v>
+        <v>2626.87</v>
       </c>
       <c r="E15" t="n">
-        <v>3092.85</v>
+        <v>2801.68</v>
       </c>
       <c r="F15" t="n">
-        <v>-489.77</v>
+        <v>-291.17</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.1367</v>
+        <v>-0.0941</v>
       </c>
       <c r="H15" t="n">
-        <v>649.08</v>
+        <v>591.26</v>
       </c>
       <c r="I15" t="n">
-        <v>2213.54</v>
+        <v>2358</v>
       </c>
       <c r="J15" t="n">
-        <v>2780.46</v>
+        <v>2324.39</v>
       </c>
       <c r="K15" t="n">
-        <v>3157.85</v>
+        <v>2768.31</v>
       </c>
       <c r="L15" t="n">
-        <v>3535.24</v>
+        <v>3212.23</v>
       </c>
       <c r="M15" t="n">
-        <v>4007.39</v>
+        <v>3417.39</v>
       </c>
       <c r="N15" t="n">
-        <v>4479.55</v>
+        <v>3622.54</v>
       </c>
       <c r="O15" t="n">
-        <v>4762.18</v>
+        <v>4305.23</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1819,50 +1813,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3092.94</v>
+        <v>2801.2</v>
       </c>
       <c r="C16" t="n">
-        <v>3218.13</v>
+        <v>3095.03</v>
       </c>
       <c r="D16" t="n">
-        <v>2626.87</v>
+        <v>2763.38</v>
       </c>
       <c r="E16" t="n">
-        <v>2801.68</v>
+        <v>2992.11</v>
       </c>
       <c r="F16" t="n">
-        <v>-291.17</v>
+        <v>190.44</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0941</v>
+        <v>0.068</v>
       </c>
       <c r="H16" t="n">
-        <v>591.26</v>
+        <v>331.66</v>
       </c>
       <c r="I16" t="n">
-        <v>2358</v>
+        <v>2035.61</v>
       </c>
       <c r="J16" t="n">
-        <v>2324.39</v>
+        <v>2150</v>
       </c>
       <c r="K16" t="n">
-        <v>2768.31</v>
+        <v>2506.05</v>
       </c>
       <c r="L16" t="n">
-        <v>3212.23</v>
+        <v>2862.09</v>
       </c>
       <c r="M16" t="n">
-        <v>3417.39</v>
+        <v>3097.31</v>
       </c>
       <c r="N16" t="n">
-        <v>3622.54</v>
+        <v>3332.52</v>
       </c>
       <c r="O16" t="n">
-        <v>4305.23</v>
+        <v>3809.39</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1870,19 +1864,19 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1894,55 +1888,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2801.2</v>
+        <v>2991.92</v>
       </c>
       <c r="C17" t="n">
-        <v>3095.03</v>
+        <v>3238.56</v>
       </c>
       <c r="D17" t="n">
-        <v>2763.38</v>
+        <v>2720.44</v>
       </c>
       <c r="E17" t="n">
-        <v>2992.11</v>
+        <v>3061.3</v>
       </c>
       <c r="F17" t="n">
-        <v>190.44</v>
+        <v>69.19</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.068</v>
+        <v>0.0231</v>
       </c>
       <c r="H17" t="n">
-        <v>331.66</v>
+        <v>518.12</v>
       </c>
       <c r="I17" t="n">
-        <v>2035.61</v>
+        <v>2431.72</v>
       </c>
       <c r="J17" t="n">
-        <v>2150</v>
+        <v>2691.91</v>
       </c>
       <c r="K17" t="n">
-        <v>2506.05</v>
+        <v>2826.28</v>
       </c>
       <c r="L17" t="n">
-        <v>2862.09</v>
+        <v>2960.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3097.31</v>
+        <v>3157.94</v>
       </c>
       <c r="N17" t="n">
-        <v>3332.52</v>
+        <v>3355.22</v>
       </c>
       <c r="O17" t="n">
-        <v>3809.39</v>
+        <v>3426.69</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1950,8 +1948,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
@@ -1983,50 +1983,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2991.92</v>
+        <v>3061.01</v>
       </c>
       <c r="C18" t="n">
-        <v>3238.56</v>
+        <v>3446.62</v>
       </c>
       <c r="D18" t="n">
-        <v>2720.44</v>
+        <v>3034.69</v>
       </c>
       <c r="E18" t="n">
-        <v>3061.3</v>
+        <v>3060.59</v>
       </c>
       <c r="F18" t="n">
-        <v>69.19</v>
+        <v>-0.71</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0231</v>
+        <v>-0.0002</v>
       </c>
       <c r="H18" t="n">
-        <v>518.12</v>
+        <v>411.93</v>
       </c>
       <c r="I18" t="n">
-        <v>2431.72</v>
+        <v>2202.32</v>
       </c>
       <c r="J18" t="n">
-        <v>2691.91</v>
+        <v>2584.09</v>
       </c>
       <c r="K18" t="n">
-        <v>2826.28</v>
+        <v>2802.24</v>
       </c>
       <c r="L18" t="n">
-        <v>2960.66</v>
+        <v>3020.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3157.94</v>
+        <v>3320.36</v>
       </c>
       <c r="N18" t="n">
-        <v>3355.22</v>
+        <v>3620.32</v>
       </c>
       <c r="O18" t="n">
-        <v>3426.69</v>
+        <v>3756.67</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2034,19 +2034,17 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2069,50 +2067,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3061.01</v>
+        <v>3060.48</v>
       </c>
       <c r="C19" t="n">
-        <v>3446.62</v>
+        <v>3175.12</v>
       </c>
       <c r="D19" t="n">
-        <v>3034.69</v>
+        <v>2777.12</v>
       </c>
       <c r="E19" t="n">
-        <v>3060.59</v>
+        <v>3001.61</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.71</v>
+        <v>-58.98</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H19" t="n">
-        <v>411.93</v>
+        <v>398</v>
       </c>
       <c r="I19" t="n">
-        <v>2202.32</v>
+        <v>2622.76</v>
       </c>
       <c r="J19" t="n">
-        <v>2584.09</v>
+        <v>2558.63</v>
       </c>
       <c r="K19" t="n">
-        <v>2802.24</v>
+        <v>2854.63</v>
       </c>
       <c r="L19" t="n">
-        <v>3020.4</v>
+        <v>3150.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3320.36</v>
+        <v>3266.56</v>
       </c>
       <c r="N19" t="n">
-        <v>3620.32</v>
+        <v>3382.49</v>
       </c>
       <c r="O19" t="n">
-        <v>3756.67</v>
+        <v>3858.55</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2120,18 +2118,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2144,59 +2142,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3060.48</v>
+        <v>3001.61</v>
       </c>
       <c r="C20" t="n">
-        <v>3175.12</v>
+        <v>3073.35</v>
       </c>
       <c r="D20" t="n">
-        <v>2777.12</v>
+        <v>2888.99</v>
       </c>
       <c r="E20" t="n">
-        <v>3001.61</v>
+        <v>2948.57</v>
       </c>
       <c r="F20" t="n">
-        <v>-58.98</v>
+        <v>-53.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0177</v>
       </c>
       <c r="H20" t="n">
-        <v>398</v>
+        <v>184.37</v>
       </c>
       <c r="I20" t="n">
-        <v>2622.76</v>
+        <v>2379.12</v>
       </c>
       <c r="J20" t="n">
-        <v>2558.63</v>
+        <v>2616.36</v>
       </c>
       <c r="K20" t="n">
-        <v>2854.63</v>
+        <v>2802.61</v>
       </c>
       <c r="L20" t="n">
-        <v>3150.63</v>
+        <v>2988.87</v>
       </c>
       <c r="M20" t="n">
-        <v>3266.56</v>
+        <v>3200.61</v>
       </c>
       <c r="N20" t="n">
-        <v>3382.49</v>
+        <v>3412.36</v>
       </c>
       <c r="O20" t="n">
-        <v>3858.55</v>
+        <v>3573.12</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2204,14 +2198,12 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2228,55 +2220,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3001.61</v>
+        <v>2948.56</v>
       </c>
       <c r="C21" t="n">
-        <v>3073.35</v>
+        <v>3160.55</v>
       </c>
       <c r="D21" t="n">
-        <v>2888.99</v>
+        <v>2908.75</v>
       </c>
       <c r="E21" t="n">
-        <v>2948.57</v>
+        <v>3140.71</v>
       </c>
       <c r="F21" t="n">
-        <v>-53.05</v>
+        <v>192.14</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0177</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>184.37</v>
+        <v>251.8</v>
       </c>
       <c r="I21" t="n">
-        <v>2379.12</v>
+        <v>2704.62</v>
       </c>
       <c r="J21" t="n">
-        <v>2616.36</v>
+        <v>2747.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2802.61</v>
+        <v>2856.39</v>
       </c>
       <c r="L21" t="n">
-        <v>2988.87</v>
+        <v>2964.87</v>
       </c>
       <c r="M21" t="n">
-        <v>3200.61</v>
+        <v>3040.75</v>
       </c>
       <c r="N21" t="n">
-        <v>3412.36</v>
+        <v>3116.63</v>
       </c>
       <c r="O21" t="n">
-        <v>3573.12</v>
+        <v>3257.72</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2287,78 +2283,78 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2948.56</v>
+        <v>3141.49</v>
       </c>
       <c r="C22" t="n">
-        <v>3160.55</v>
+        <v>3303.56</v>
       </c>
       <c r="D22" t="n">
-        <v>2908.75</v>
+        <v>3052.51</v>
       </c>
       <c r="E22" t="n">
-        <v>3140.71</v>
+        <v>3118.89</v>
       </c>
       <c r="F22" t="n">
-        <v>192.14</v>
+        <v>-21.83</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="H22" t="n">
-        <v>251.8</v>
+        <v>251.05</v>
       </c>
       <c r="I22" t="n">
-        <v>2704.62</v>
+        <v>2656.95</v>
       </c>
       <c r="J22" t="n">
-        <v>2747.9</v>
+        <v>2941.94</v>
       </c>
       <c r="K22" t="n">
-        <v>2856.39</v>
+        <v>3014.81</v>
       </c>
       <c r="L22" t="n">
-        <v>2964.87</v>
+        <v>3087.68</v>
       </c>
       <c r="M22" t="n">
-        <v>3040.75</v>
+        <v>3266.61</v>
       </c>
       <c r="N22" t="n">
-        <v>3116.63</v>
+        <v>3445.54</v>
       </c>
       <c r="O22" t="n">
-        <v>3257.72</v>
+        <v>3412.35</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2371,7 +2367,7 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2379,10 +2375,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2392,55 +2386,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3141.49</v>
+        <v>3118.83</v>
       </c>
       <c r="C23" t="n">
-        <v>3303.56</v>
+        <v>3397.9</v>
       </c>
       <c r="D23" t="n">
-        <v>3052.51</v>
+        <v>3068.07</v>
       </c>
       <c r="E23" t="n">
-        <v>3118.89</v>
+        <v>3281.16</v>
       </c>
       <c r="F23" t="n">
-        <v>-21.83</v>
+        <v>162.27</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.052</v>
       </c>
       <c r="H23" t="n">
-        <v>251.05</v>
+        <v>329.82</v>
       </c>
       <c r="I23" t="n">
-        <v>2656.95</v>
+        <v>2801.46</v>
       </c>
       <c r="J23" t="n">
-        <v>2941.94</v>
+        <v>2838.26</v>
       </c>
       <c r="K23" t="n">
-        <v>3014.81</v>
+        <v>2993.36</v>
       </c>
       <c r="L23" t="n">
-        <v>3087.68</v>
+        <v>3148.46</v>
       </c>
       <c r="M23" t="n">
-        <v>3266.61</v>
+        <v>3244.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3445.54</v>
+        <v>3340.36</v>
       </c>
       <c r="O23" t="n">
-        <v>3412.35</v>
+        <v>3554.62</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2453,17 +2451,19 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2472,90 +2472,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3118.83</v>
+        <v>3282.2</v>
       </c>
       <c r="C24" t="n">
-        <v>3397.9</v>
+        <v>3282.65</v>
       </c>
       <c r="D24" t="n">
-        <v>3068.07</v>
+        <v>2785.9</v>
       </c>
       <c r="E24" t="n">
-        <v>3281.16</v>
+        <v>2815.9</v>
       </c>
       <c r="F24" t="n">
-        <v>162.27</v>
+        <v>-465.26</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.052</v>
+        <v>-0.1418</v>
       </c>
       <c r="H24" t="n">
-        <v>329.82</v>
+        <v>496.76</v>
       </c>
       <c r="I24" t="n">
-        <v>2801.46</v>
+        <v>2738.25</v>
       </c>
       <c r="J24" t="n">
-        <v>2838.26</v>
+        <v>2975.42</v>
       </c>
       <c r="K24" t="n">
-        <v>2993.36</v>
+        <v>3116.25</v>
       </c>
       <c r="L24" t="n">
-        <v>3148.46</v>
+        <v>3257.07</v>
       </c>
       <c r="M24" t="n">
-        <v>3244.41</v>
+        <v>3446.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3340.36</v>
+        <v>3635.07</v>
       </c>
       <c r="O24" t="n">
-        <v>3554.62</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+        <v>3727.72</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2563,60 +2561,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3282.2</v>
+        <v>2815.77</v>
       </c>
       <c r="C25" t="n">
-        <v>3282.65</v>
+        <v>3040.72</v>
       </c>
       <c r="D25" t="n">
-        <v>2785.9</v>
+        <v>2224.12</v>
       </c>
       <c r="E25" t="n">
-        <v>2815.9</v>
+        <v>2267.96</v>
       </c>
       <c r="F25" t="n">
-        <v>-465.26</v>
+        <v>-547.9400000000001</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.1418</v>
+        <v>-0.1946</v>
       </c>
       <c r="H25" t="n">
-        <v>496.76</v>
+        <v>816.6</v>
       </c>
       <c r="I25" t="n">
-        <v>2738.25</v>
+        <v>2289.14</v>
       </c>
       <c r="J25" t="n">
-        <v>2975.42</v>
+        <v>2209.96</v>
       </c>
       <c r="K25" t="n">
-        <v>3116.25</v>
+        <v>2567.52</v>
       </c>
       <c r="L25" t="n">
-        <v>3257.07</v>
+        <v>2925.09</v>
       </c>
       <c r="M25" t="n">
-        <v>3446.07</v>
+        <v>3064.28</v>
       </c>
       <c r="N25" t="n">
-        <v>3635.07</v>
+        <v>3203.47</v>
       </c>
       <c r="O25" t="n">
-        <v>3727.72</v>
+        <v>3779.41</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2647,62 +2643,60 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2815.77</v>
+        <v>2267.56</v>
       </c>
       <c r="C26" t="n">
-        <v>3040.72</v>
+        <v>2393.06</v>
       </c>
       <c r="D26" t="n">
-        <v>2224.12</v>
+        <v>1748.63</v>
       </c>
       <c r="E26" t="n">
-        <v>2267.96</v>
+        <v>2088.76</v>
       </c>
       <c r="F26" t="n">
-        <v>-547.9400000000001</v>
+        <v>-179.2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.1946</v>
+        <v>-0.079</v>
       </c>
       <c r="H26" t="n">
-        <v>816.6</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>2289.14</v>
+        <v>1407.52</v>
       </c>
       <c r="J26" t="n">
-        <v>2209.96</v>
+        <v>1269.14</v>
       </c>
       <c r="K26" t="n">
-        <v>2567.52</v>
+        <v>1859.66</v>
       </c>
       <c r="L26" t="n">
-        <v>2925.09</v>
+        <v>2450.19</v>
       </c>
       <c r="M26" t="n">
-        <v>3064.28</v>
+        <v>2676.27</v>
       </c>
       <c r="N26" t="n">
-        <v>3203.47</v>
+        <v>2902.34</v>
       </c>
       <c r="O26" t="n">
-        <v>3779.41</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>3857.32</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2729,50 +2723,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2267.56</v>
+        <v>2087.92</v>
       </c>
       <c r="C27" t="n">
-        <v>2393.06</v>
+        <v>2144.98</v>
       </c>
       <c r="D27" t="n">
-        <v>1748.63</v>
+        <v>1897.33</v>
       </c>
       <c r="E27" t="n">
-        <v>2088.76</v>
+        <v>1966.04</v>
       </c>
       <c r="F27" t="n">
-        <v>-179.2</v>
+        <v>-122.72</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.0588</v>
       </c>
       <c r="H27" t="n">
-        <v>644.4400000000001</v>
+        <v>247.64</v>
       </c>
       <c r="I27" t="n">
-        <v>1407.52</v>
+        <v>1104.19</v>
       </c>
       <c r="J27" t="n">
-        <v>1269.14</v>
+        <v>1453.29</v>
       </c>
       <c r="K27" t="n">
-        <v>1859.66</v>
+        <v>1766.55</v>
       </c>
       <c r="L27" t="n">
-        <v>2450.19</v>
+        <v>2079.8</v>
       </c>
       <c r="M27" t="n">
-        <v>2676.27</v>
+        <v>2410.98</v>
       </c>
       <c r="N27" t="n">
-        <v>2902.34</v>
+        <v>2742.16</v>
       </c>
       <c r="O27" t="n">
-        <v>3857.32</v>
+        <v>3037.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2780,14 +2774,12 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2804,55 +2796,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2087.92</v>
+        <v>1965.92</v>
       </c>
       <c r="C28" t="n">
-        <v>2144.98</v>
+        <v>2037.16</v>
       </c>
       <c r="D28" t="n">
-        <v>1897.33</v>
+        <v>1906.82</v>
       </c>
       <c r="E28" t="n">
-        <v>1966.04</v>
+        <v>1957.81</v>
       </c>
       <c r="F28" t="n">
-        <v>-122.72</v>
+        <v>-8.24</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0042</v>
       </c>
       <c r="H28" t="n">
-        <v>247.64</v>
+        <v>130.34</v>
       </c>
       <c r="I28" t="n">
-        <v>1104.19</v>
+        <v>1649.69</v>
       </c>
       <c r="J28" t="n">
-        <v>1453.29</v>
+        <v>1690.85</v>
       </c>
       <c r="K28" t="n">
-        <v>1766.55</v>
+        <v>1842.22</v>
       </c>
       <c r="L28" t="n">
-        <v>2079.8</v>
+        <v>1993.6</v>
       </c>
       <c r="M28" t="n">
-        <v>2410.98</v>
+        <v>2089.86</v>
       </c>
       <c r="N28" t="n">
-        <v>2742.16</v>
+        <v>2186.13</v>
       </c>
       <c r="O28" t="n">
-        <v>3037.5</v>
+        <v>2392.62</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2891,70 +2887,78 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1965.92</v>
+        <v>1958.14</v>
       </c>
       <c r="C29" t="n">
-        <v>2037.16</v>
+        <v>2145.51</v>
       </c>
       <c r="D29" t="n">
-        <v>1906.82</v>
+        <v>1804.11</v>
       </c>
       <c r="E29" t="n">
-        <v>1957.81</v>
+        <v>1939.07</v>
       </c>
       <c r="F29" t="n">
-        <v>-8.24</v>
+        <v>-18.74</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>130.34</v>
+        <v>341.39</v>
       </c>
       <c r="I29" t="n">
-        <v>1649.69</v>
+        <v>1776.49</v>
       </c>
       <c r="J29" t="n">
-        <v>1690.85</v>
+        <v>1820.38</v>
       </c>
       <c r="K29" t="n">
-        <v>1842.22</v>
+        <v>1892.64</v>
       </c>
       <c r="L29" t="n">
-        <v>1993.6</v>
+        <v>1964.9</v>
       </c>
       <c r="M29" t="n">
-        <v>2089.86</v>
+        <v>2022.97</v>
       </c>
       <c r="N29" t="n">
-        <v>2186.13</v>
+        <v>2081.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2392.62</v>
+        <v>2167.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2973,78 +2977,72 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1958.14</v>
+        <v>1939.06</v>
       </c>
       <c r="C30" t="n">
-        <v>2145.51</v>
+        <v>2198.66</v>
       </c>
       <c r="D30" t="n">
-        <v>1804.11</v>
+        <v>1915.3</v>
       </c>
       <c r="E30" t="n">
-        <v>1939.07</v>
+        <v>1936.6</v>
       </c>
       <c r="F30" t="n">
-        <v>-18.74</v>
+        <v>-2.46</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0013</v>
       </c>
       <c r="H30" t="n">
-        <v>341.39</v>
+        <v>283.36</v>
       </c>
       <c r="I30" t="n">
-        <v>1776.49</v>
+        <v>1462.72</v>
       </c>
       <c r="J30" t="n">
-        <v>1820.38</v>
+        <v>1579.8</v>
       </c>
       <c r="K30" t="n">
-        <v>1892.64</v>
+        <v>1768.37</v>
       </c>
       <c r="L30" t="n">
-        <v>1964.9</v>
+        <v>1956.94</v>
       </c>
       <c r="M30" t="n">
-        <v>2022.97</v>
+        <v>2109.76</v>
       </c>
       <c r="N30" t="n">
-        <v>2081.05</v>
+        <v>2262.59</v>
       </c>
       <c r="O30" t="n">
-        <v>2167.5</v>
+        <v>2486.9</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3056,57 +3054,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1939.06</v>
+        <v>1936.64</v>
       </c>
       <c r="C31" t="n">
-        <v>2198.66</v>
+        <v>2206.81</v>
       </c>
       <c r="D31" t="n">
-        <v>1915.3</v>
+        <v>1930.6</v>
       </c>
       <c r="E31" t="n">
-        <v>1936.6</v>
+        <v>2177.48</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.46</v>
+        <v>240.87</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.1244</v>
       </c>
       <c r="H31" t="n">
-        <v>283.36</v>
+        <v>276.21</v>
       </c>
       <c r="I31" t="n">
-        <v>1462.72</v>
+        <v>1631.95</v>
       </c>
       <c r="J31" t="n">
-        <v>1579.8</v>
+        <v>1593.06</v>
       </c>
       <c r="K31" t="n">
-        <v>1768.37</v>
+        <v>1794.93</v>
       </c>
       <c r="L31" t="n">
-        <v>1956.94</v>
+        <v>1996.79</v>
       </c>
       <c r="M31" t="n">
-        <v>2109.76</v>
+        <v>2078.28</v>
       </c>
       <c r="N31" t="n">
-        <v>2262.59</v>
+        <v>2159.77</v>
       </c>
       <c r="O31" t="n">
-        <v>2486.9</v>
+        <v>2482.01</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,9 +3115,9 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3127,70 +3125,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1936.64</v>
+        <v>2177.78</v>
       </c>
       <c r="C32" t="n">
-        <v>2206.81</v>
+        <v>2384.47</v>
       </c>
       <c r="D32" t="n">
-        <v>1930.6</v>
+        <v>2027.05</v>
       </c>
       <c r="E32" t="n">
-        <v>2177.48</v>
+        <v>2053.05</v>
       </c>
       <c r="F32" t="n">
-        <v>240.87</v>
+        <v>-124.43</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.1244</v>
+        <v>-0.0571</v>
       </c>
       <c r="H32" t="n">
-        <v>276.21</v>
+        <v>357.42</v>
       </c>
       <c r="I32" t="n">
-        <v>1631.95</v>
+        <v>1654.39</v>
       </c>
       <c r="J32" t="n">
-        <v>1593.06</v>
+        <v>1955.65</v>
       </c>
       <c r="K32" t="n">
-        <v>1794.93</v>
+        <v>2039.37</v>
       </c>
       <c r="L32" t="n">
-        <v>1996.79</v>
+        <v>2123.09</v>
       </c>
       <c r="M32" t="n">
-        <v>2078.28</v>
+        <v>2315.58</v>
       </c>
       <c r="N32" t="n">
-        <v>2159.77</v>
+        <v>2508.08</v>
       </c>
       <c r="O32" t="n">
-        <v>2482.01</v>
+        <v>2483.03</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3198,12 +3194,14 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3211,10 +3209,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3224,55 +3220,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2177.78</v>
+        <v>2052.95</v>
       </c>
       <c r="C33" t="n">
-        <v>2384.47</v>
+        <v>2198.37</v>
       </c>
       <c r="D33" t="n">
-        <v>2027.05</v>
+        <v>1939.53</v>
       </c>
       <c r="E33" t="n">
-        <v>2053.05</v>
+        <v>1982.56</v>
       </c>
       <c r="F33" t="n">
-        <v>-124.43</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0571</v>
+        <v>-0.0343</v>
       </c>
       <c r="H33" t="n">
-        <v>357.42</v>
+        <v>258.84</v>
       </c>
       <c r="I33" t="n">
-        <v>1654.39</v>
+        <v>1669.63</v>
       </c>
       <c r="J33" t="n">
-        <v>1955.65</v>
+        <v>1619.28</v>
       </c>
       <c r="K33" t="n">
-        <v>2039.37</v>
+        <v>1874.34</v>
       </c>
       <c r="L33" t="n">
-        <v>2123.09</v>
+        <v>2129.4</v>
       </c>
       <c r="M33" t="n">
-        <v>2315.58</v>
+        <v>2231.76</v>
       </c>
       <c r="N33" t="n">
-        <v>2508.08</v>
+        <v>2334.11</v>
       </c>
       <c r="O33" t="n">
-        <v>2483.03</v>
+        <v>2741.89</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3290,10 +3290,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3308,57 +3306,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2052.95</v>
+        <v>1982.55</v>
       </c>
       <c r="C34" t="n">
-        <v>2198.37</v>
+        <v>2165.67</v>
       </c>
       <c r="D34" t="n">
-        <v>1939.53</v>
+        <v>1979.08</v>
       </c>
       <c r="E34" t="n">
-        <v>1982.56</v>
+        <v>2109</v>
       </c>
       <c r="F34" t="n">
-        <v>-70.48999999999999</v>
+        <v>126.44</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0343</v>
+        <v>0.0638</v>
       </c>
       <c r="H34" t="n">
-        <v>258.84</v>
+        <v>186.59</v>
       </c>
       <c r="I34" t="n">
-        <v>1669.63</v>
+        <v>1680.69</v>
       </c>
       <c r="J34" t="n">
-        <v>1619.28</v>
+        <v>1680.52</v>
       </c>
       <c r="K34" t="n">
-        <v>1874.34</v>
+        <v>1853.14</v>
       </c>
       <c r="L34" t="n">
-        <v>2129.4</v>
+        <v>2025.75</v>
       </c>
       <c r="M34" t="n">
-        <v>2231.76</v>
+        <v>2111.98</v>
       </c>
       <c r="N34" t="n">
-        <v>2334.11</v>
+        <v>2198.21</v>
       </c>
       <c r="O34" t="n">
-        <v>2741.89</v>
+        <v>2457.21</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3366,19 +3364,19 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3392,57 +3390,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1982.55</v>
+        <v>2108.94</v>
       </c>
       <c r="C35" t="n">
-        <v>2165.67</v>
+        <v>2327.46</v>
       </c>
       <c r="D35" t="n">
-        <v>1979.08</v>
+        <v>2061.47</v>
       </c>
       <c r="E35" t="n">
-        <v>2109</v>
+        <v>2192.2</v>
       </c>
       <c r="F35" t="n">
-        <v>126.44</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0638</v>
+        <v>0.0395</v>
       </c>
       <c r="H35" t="n">
-        <v>186.59</v>
+        <v>265.99</v>
       </c>
       <c r="I35" t="n">
-        <v>1680.69</v>
+        <v>1792.49</v>
       </c>
       <c r="J35" t="n">
-        <v>1680.52</v>
+        <v>1940.72</v>
       </c>
       <c r="K35" t="n">
-        <v>1853.14</v>
+        <v>2015.7</v>
       </c>
       <c r="L35" t="n">
-        <v>2025.75</v>
+        <v>2090.68</v>
       </c>
       <c r="M35" t="n">
-        <v>2111.98</v>
+        <v>2202.29</v>
       </c>
       <c r="N35" t="n">
-        <v>2198.21</v>
+        <v>2313.9</v>
       </c>
       <c r="O35" t="n">
-        <v>2457.21</v>
+        <v>2352.26</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3463,8 +3461,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3474,59 +3474,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2108.94</v>
+        <v>2192.33</v>
       </c>
       <c r="C36" t="n">
-        <v>2327.46</v>
+        <v>2464.78</v>
       </c>
       <c r="D36" t="n">
-        <v>2061.47</v>
+        <v>2176.32</v>
       </c>
       <c r="E36" t="n">
-        <v>2192.2</v>
+        <v>2264.92</v>
       </c>
       <c r="F36" t="n">
-        <v>83.20999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0332</v>
       </c>
       <c r="H36" t="n">
-        <v>265.99</v>
+        <v>288.46</v>
       </c>
       <c r="I36" t="n">
-        <v>1792.49</v>
+        <v>1795.48</v>
       </c>
       <c r="J36" t="n">
-        <v>1940.72</v>
+        <v>1925.08</v>
       </c>
       <c r="K36" t="n">
-        <v>2015.7</v>
+        <v>2059.21</v>
       </c>
       <c r="L36" t="n">
-        <v>2090.68</v>
+        <v>2193.33</v>
       </c>
       <c r="M36" t="n">
-        <v>2202.29</v>
+        <v>2325.2</v>
       </c>
       <c r="N36" t="n">
-        <v>2313.9</v>
+        <v>2457.06</v>
       </c>
       <c r="O36" t="n">
-        <v>2352.26</v>
+        <v>2593.45</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3565,50 +3561,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2192.33</v>
+        <v>2264.87</v>
       </c>
       <c r="C37" t="n">
-        <v>2464.78</v>
+        <v>2422.86</v>
       </c>
       <c r="D37" t="n">
-        <v>2176.32</v>
+        <v>2262.05</v>
       </c>
       <c r="E37" t="n">
-        <v>2264.92</v>
+        <v>2369.73</v>
       </c>
       <c r="F37" t="n">
-        <v>72.72</v>
+        <v>104.81</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0463</v>
       </c>
       <c r="H37" t="n">
-        <v>288.46</v>
+        <v>160.81</v>
       </c>
       <c r="I37" t="n">
-        <v>1795.48</v>
+        <v>1887.87</v>
       </c>
       <c r="J37" t="n">
-        <v>1925.08</v>
+        <v>1948.64</v>
       </c>
       <c r="K37" t="n">
-        <v>2059.21</v>
+        <v>2120.69</v>
       </c>
       <c r="L37" t="n">
-        <v>2193.33</v>
+        <v>2292.74</v>
       </c>
       <c r="M37" t="n">
-        <v>2325.2</v>
+        <v>2409.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2457.06</v>
+        <v>2525.56</v>
       </c>
       <c r="O37" t="n">
-        <v>2593.45</v>
+        <v>2753.24</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3629,10 +3625,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3642,75 +3636,81 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2264.87</v>
+        <v>2369.84</v>
       </c>
       <c r="C38" t="n">
-        <v>2422.86</v>
+        <v>2403.73</v>
       </c>
       <c r="D38" t="n">
-        <v>2262.05</v>
+        <v>2221.22</v>
       </c>
       <c r="E38" t="n">
-        <v>2369.73</v>
+        <v>2321.64</v>
       </c>
       <c r="F38" t="n">
-        <v>104.81</v>
+        <v>-48.09</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0463</v>
+        <v>-0.0203</v>
       </c>
       <c r="H38" t="n">
-        <v>160.81</v>
+        <v>182.5</v>
       </c>
       <c r="I38" t="n">
-        <v>1887.87</v>
+        <v>2101.25</v>
       </c>
       <c r="J38" t="n">
-        <v>1948.64</v>
+        <v>2222.56</v>
       </c>
       <c r="K38" t="n">
-        <v>2120.69</v>
+        <v>2289.33</v>
       </c>
       <c r="L38" t="n">
-        <v>2292.74</v>
+        <v>2356.09</v>
       </c>
       <c r="M38" t="n">
-        <v>2409.15</v>
+        <v>2450.13</v>
       </c>
       <c r="N38" t="n">
-        <v>2525.56</v>
+        <v>2544.17</v>
       </c>
       <c r="O38" t="n">
-        <v>2753.24</v>
+        <v>2583.67</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3724,79 +3724,77 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2369.84</v>
+        <v>2321.82</v>
       </c>
       <c r="C39" t="n">
-        <v>2403.73</v>
+        <v>2423.04</v>
       </c>
       <c r="D39" t="n">
-        <v>2221.22</v>
+        <v>2265.83</v>
       </c>
       <c r="E39" t="n">
-        <v>2321.64</v>
+        <v>2369.04</v>
       </c>
       <c r="F39" t="n">
-        <v>-48.09</v>
+        <v>47.41</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="H39" t="n">
-        <v>182.5</v>
+        <v>157.21</v>
       </c>
       <c r="I39" t="n">
-        <v>2101.25</v>
+        <v>2038.72</v>
       </c>
       <c r="J39" t="n">
-        <v>2222.56</v>
+        <v>2143.71</v>
       </c>
       <c r="K39" t="n">
-        <v>2289.33</v>
+        <v>2230.38</v>
       </c>
       <c r="L39" t="n">
-        <v>2356.09</v>
+        <v>2317.06</v>
       </c>
       <c r="M39" t="n">
-        <v>2450.13</v>
+        <v>2412.89</v>
       </c>
       <c r="N39" t="n">
-        <v>2544.17</v>
+        <v>2508.72</v>
       </c>
       <c r="O39" t="n">
-        <v>2583.67</v>
+        <v>2586.23</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3808,88 +3806,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2321.82</v>
+        <v>2369.19</v>
       </c>
       <c r="C40" t="n">
-        <v>2423.04</v>
+        <v>2374.3</v>
       </c>
       <c r="D40" t="n">
-        <v>2265.83</v>
+        <v>2097.02</v>
       </c>
       <c r="E40" t="n">
-        <v>2369.04</v>
+        <v>2127.65</v>
       </c>
       <c r="F40" t="n">
-        <v>47.41</v>
+        <v>-241.4</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.1019</v>
       </c>
       <c r="H40" t="n">
-        <v>157.21</v>
+        <v>277.28</v>
       </c>
       <c r="I40" t="n">
-        <v>2038.72</v>
+        <v>2108.63</v>
       </c>
       <c r="J40" t="n">
-        <v>2143.71</v>
+        <v>2224.14</v>
       </c>
       <c r="K40" t="n">
-        <v>2230.38</v>
+        <v>2290.44</v>
       </c>
       <c r="L40" t="n">
-        <v>2317.06</v>
+        <v>2356.74</v>
       </c>
       <c r="M40" t="n">
-        <v>2412.89</v>
+        <v>2447.65</v>
       </c>
       <c r="N40" t="n">
-        <v>2508.72</v>
+        <v>2538.55</v>
       </c>
       <c r="O40" t="n">
-        <v>2586.23</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+        <v>2580.25</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3897,69 +3895,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2369.19</v>
+        <v>2127.68</v>
       </c>
       <c r="C41" t="n">
-        <v>2374.3</v>
+        <v>2155.96</v>
       </c>
       <c r="D41" t="n">
-        <v>2097.02</v>
+        <v>2010.55</v>
       </c>
       <c r="E41" t="n">
-        <v>2127.65</v>
+        <v>2097.99</v>
       </c>
       <c r="F41" t="n">
-        <v>-241.4</v>
+        <v>-29.65</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.1019</v>
+        <v>-0.0139</v>
       </c>
       <c r="H41" t="n">
-        <v>277.28</v>
+        <v>145.41</v>
       </c>
       <c r="I41" t="n">
-        <v>2108.63</v>
+        <v>1819.74</v>
       </c>
       <c r="J41" t="n">
-        <v>2224.14</v>
+        <v>1796.35</v>
       </c>
       <c r="K41" t="n">
-        <v>2290.44</v>
+        <v>1989</v>
       </c>
       <c r="L41" t="n">
-        <v>2356.74</v>
+        <v>2181.65</v>
       </c>
       <c r="M41" t="n">
-        <v>2447.65</v>
+        <v>2266.29</v>
       </c>
       <c r="N41" t="n">
-        <v>2538.55</v>
+        <v>2350.92</v>
       </c>
       <c r="O41" t="n">
-        <v>2580.25</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>2651.59</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3981,50 +3973,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2127.68</v>
+        <v>2097.99</v>
       </c>
       <c r="C42" t="n">
-        <v>2155.96</v>
+        <v>2138.41</v>
       </c>
       <c r="D42" t="n">
-        <v>2010.55</v>
+        <v>1966.28</v>
       </c>
       <c r="E42" t="n">
-        <v>2097.99</v>
+        <v>2004.34</v>
       </c>
       <c r="F42" t="n">
-        <v>-29.65</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.0446</v>
       </c>
       <c r="H42" t="n">
-        <v>145.41</v>
+        <v>172.13</v>
       </c>
       <c r="I42" t="n">
-        <v>1819.74</v>
+        <v>1865.14</v>
       </c>
       <c r="J42" t="n">
-        <v>1796.35</v>
+        <v>1959.95</v>
       </c>
       <c r="K42" t="n">
-        <v>1989</v>
+        <v>2025.29</v>
       </c>
       <c r="L42" t="n">
-        <v>2181.65</v>
+        <v>2090.63</v>
       </c>
       <c r="M42" t="n">
-        <v>2266.29</v>
+        <v>2170.7</v>
       </c>
       <c r="N42" t="n">
-        <v>2350.92</v>
+        <v>2250.78</v>
       </c>
       <c r="O42" t="n">
-        <v>2651.59</v>
+        <v>2301.38</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4032,12 +4024,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4059,60 +4053,64 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2097.99</v>
+        <v>2004.24</v>
       </c>
       <c r="C43" t="n">
-        <v>2138.41</v>
+        <v>2017.61</v>
       </c>
       <c r="D43" t="n">
-        <v>1966.28</v>
+        <v>1506.51</v>
       </c>
       <c r="E43" t="n">
-        <v>2004.34</v>
+        <v>1686.4</v>
       </c>
       <c r="F43" t="n">
-        <v>-93.65000000000001</v>
+        <v>-317.95</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0446</v>
+        <v>-0.1586</v>
       </c>
       <c r="H43" t="n">
-        <v>172.13</v>
+        <v>511.1</v>
       </c>
       <c r="I43" t="n">
-        <v>1865.14</v>
+        <v>1794.15</v>
       </c>
       <c r="J43" t="n">
-        <v>1959.95</v>
+        <v>1808.21</v>
       </c>
       <c r="K43" t="n">
-        <v>2025.29</v>
+        <v>1918.28</v>
       </c>
       <c r="L43" t="n">
-        <v>2090.63</v>
+        <v>2028.34</v>
       </c>
       <c r="M43" t="n">
-        <v>2170.7</v>
+        <v>2090.41</v>
       </c>
       <c r="N43" t="n">
-        <v>2250.78</v>
+        <v>2152.47</v>
       </c>
       <c r="O43" t="n">
-        <v>2301.38</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>2310.54</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -4139,69 +4137,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2004.24</v>
+        <v>1686.25</v>
       </c>
       <c r="C44" t="n">
-        <v>2017.61</v>
+        <v>1729.35</v>
       </c>
       <c r="D44" t="n">
-        <v>1506.51</v>
+        <v>1603.83</v>
       </c>
       <c r="E44" t="n">
-        <v>1686.4</v>
+        <v>1724.61</v>
       </c>
       <c r="F44" t="n">
-        <v>-317.95</v>
+        <v>38.22</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.1586</v>
+        <v>0.0227</v>
       </c>
       <c r="H44" t="n">
-        <v>511.1</v>
+        <v>125.53</v>
       </c>
       <c r="I44" t="n">
-        <v>1794.15</v>
+        <v>995.4</v>
       </c>
       <c r="J44" t="n">
-        <v>1808.21</v>
+        <v>1137.46</v>
       </c>
       <c r="K44" t="n">
-        <v>1918.28</v>
+        <v>1430.85</v>
       </c>
       <c r="L44" t="n">
-        <v>2028.34</v>
+        <v>1724.23</v>
       </c>
       <c r="M44" t="n">
-        <v>2090.41</v>
+        <v>1941.95</v>
       </c>
       <c r="N44" t="n">
-        <v>2152.47</v>
+        <v>2159.67</v>
       </c>
       <c r="O44" t="n">
-        <v>2310.54</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>2528.71</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4218,55 +4210,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1686.25</v>
+        <v>1724.57</v>
       </c>
       <c r="C45" t="n">
-        <v>1729.35</v>
+        <v>1847.77</v>
       </c>
       <c r="D45" t="n">
-        <v>1603.83</v>
+        <v>1670.1</v>
       </c>
       <c r="E45" t="n">
-        <v>1724.61</v>
+        <v>1704.58</v>
       </c>
       <c r="F45" t="n">
-        <v>38.22</v>
+        <v>-20.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0227</v>
+        <v>-0.0116</v>
       </c>
       <c r="H45" t="n">
-        <v>125.53</v>
+        <v>177.67</v>
       </c>
       <c r="I45" t="n">
-        <v>995.4</v>
+        <v>1478.3</v>
       </c>
       <c r="J45" t="n">
-        <v>1137.46</v>
+        <v>1628.1</v>
       </c>
       <c r="K45" t="n">
-        <v>1430.85</v>
+        <v>1661.85</v>
       </c>
       <c r="L45" t="n">
-        <v>1724.23</v>
+        <v>1695.6</v>
       </c>
       <c r="M45" t="n">
-        <v>1941.95</v>
+        <v>1787.38</v>
       </c>
       <c r="N45" t="n">
-        <v>2159.67</v>
+        <v>1879.15</v>
       </c>
       <c r="O45" t="n">
-        <v>2528.71</v>
+        <v>1854.88</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4282,8 +4278,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4305,50 +4303,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1724.57</v>
+        <v>1704.63</v>
       </c>
       <c r="C46" t="n">
-        <v>1847.77</v>
+        <v>1776.83</v>
       </c>
       <c r="D46" t="n">
-        <v>1670.1</v>
+        <v>1510.51</v>
       </c>
       <c r="E46" t="n">
-        <v>1704.58</v>
+        <v>1570.36</v>
       </c>
       <c r="F46" t="n">
-        <v>-20.03</v>
+        <v>-134.22</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>177.67</v>
+        <v>266.33</v>
       </c>
       <c r="I46" t="n">
-        <v>1478.3</v>
+        <v>1492.44</v>
       </c>
       <c r="J46" t="n">
-        <v>1628.1</v>
+        <v>1499.74</v>
       </c>
       <c r="K46" t="n">
-        <v>1661.85</v>
+        <v>1615.75</v>
       </c>
       <c r="L46" t="n">
-        <v>1695.6</v>
+        <v>1731.76</v>
       </c>
       <c r="M46" t="n">
-        <v>1787.38</v>
+        <v>1793.41</v>
       </c>
       <c r="N46" t="n">
-        <v>1879.15</v>
+        <v>1855.07</v>
       </c>
       <c r="O46" t="n">
-        <v>1854.88</v>
+        <v>2025.44</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4356,18 +4354,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4380,59 +4378,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1704.63</v>
+        <v>1569.99</v>
       </c>
       <c r="C47" t="n">
-        <v>1776.83</v>
+        <v>1805.91</v>
       </c>
       <c r="D47" t="n">
-        <v>1510.51</v>
+        <v>1549.25</v>
       </c>
       <c r="E47" t="n">
-        <v>1570.36</v>
+        <v>1783.01</v>
       </c>
       <c r="F47" t="n">
-        <v>-134.22</v>
+        <v>212.64</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.1354</v>
       </c>
       <c r="H47" t="n">
-        <v>266.33</v>
+        <v>256.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1492.44</v>
+        <v>1244.18</v>
       </c>
       <c r="J47" t="n">
-        <v>1499.74</v>
+        <v>1267.38</v>
       </c>
       <c r="K47" t="n">
-        <v>1615.75</v>
+        <v>1437.2</v>
       </c>
       <c r="L47" t="n">
-        <v>1731.76</v>
+        <v>1607.02</v>
       </c>
       <c r="M47" t="n">
-        <v>1793.41</v>
+        <v>1703.52</v>
       </c>
       <c r="N47" t="n">
-        <v>1855.07</v>
+        <v>1800.03</v>
       </c>
       <c r="O47" t="n">
-        <v>2025.44</v>
+        <v>2043.16</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4440,22 +4434,24 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4464,55 +4460,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1569.99</v>
+        <v>1783</v>
       </c>
       <c r="C48" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D48" t="n">
-        <v>1549.25</v>
+        <v>1711.9</v>
       </c>
       <c r="E48" t="n">
-        <v>1783.01</v>
+        <v>1805.79</v>
       </c>
       <c r="F48" t="n">
-        <v>212.64</v>
+        <v>22.78</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.1354</v>
+        <v>0.0128</v>
       </c>
       <c r="H48" t="n">
-        <v>256.66</v>
+        <v>117.61</v>
       </c>
       <c r="I48" t="n">
-        <v>1244.18</v>
+        <v>1292.59</v>
       </c>
       <c r="J48" t="n">
-        <v>1267.38</v>
+        <v>1579.06</v>
       </c>
       <c r="K48" t="n">
-        <v>1437.2</v>
+        <v>1654.67</v>
       </c>
       <c r="L48" t="n">
-        <v>1607.02</v>
+        <v>1730.29</v>
       </c>
       <c r="M48" t="n">
-        <v>1703.52</v>
+        <v>1911.34</v>
       </c>
       <c r="N48" t="n">
-        <v>1800.03</v>
+        <v>2092.38</v>
       </c>
       <c r="O48" t="n">
-        <v>2043.16</v>
+        <v>2062.58</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4525,18 +4525,14 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4555,50 +4551,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1783</v>
+        <v>1805.76</v>
       </c>
       <c r="C49" t="n">
-        <v>1829.51</v>
+        <v>1944.16</v>
       </c>
       <c r="D49" t="n">
-        <v>1711.9</v>
+        <v>1749.35</v>
       </c>
       <c r="E49" t="n">
-        <v>1805.79</v>
+        <v>1871.51</v>
       </c>
       <c r="F49" t="n">
-        <v>22.78</v>
+        <v>65.72</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0364</v>
       </c>
       <c r="H49" t="n">
-        <v>117.61</v>
+        <v>194.81</v>
       </c>
       <c r="I49" t="n">
-        <v>1292.59</v>
+        <v>1594.29</v>
       </c>
       <c r="J49" t="n">
-        <v>1579.06</v>
+        <v>1705.72</v>
       </c>
       <c r="K49" t="n">
-        <v>1654.67</v>
+        <v>1746.98</v>
       </c>
       <c r="L49" t="n">
-        <v>1730.29</v>
+        <v>1788.25</v>
       </c>
       <c r="M49" t="n">
-        <v>1911.34</v>
+        <v>1864.59</v>
       </c>
       <c r="N49" t="n">
-        <v>2092.38</v>
+        <v>1940.94</v>
       </c>
       <c r="O49" t="n">
-        <v>2062.58</v>
+        <v>1947.13</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4611,14 +4607,18 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4637,50 +4637,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1805.76</v>
+        <v>1871.28</v>
       </c>
       <c r="C50" t="n">
-        <v>1944.16</v>
+        <v>1963.25</v>
       </c>
       <c r="D50" t="n">
-        <v>1749.35</v>
+        <v>1842.82</v>
       </c>
       <c r="E50" t="n">
-        <v>1871.51</v>
+        <v>1953.41</v>
       </c>
       <c r="F50" t="n">
-        <v>65.72</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0364</v>
+        <v>0.0438</v>
       </c>
       <c r="H50" t="n">
-        <v>194.81</v>
+        <v>120.43</v>
       </c>
       <c r="I50" t="n">
-        <v>1594.29</v>
+        <v>1554.53</v>
       </c>
       <c r="J50" t="n">
-        <v>1705.72</v>
+        <v>1689.07</v>
       </c>
       <c r="K50" t="n">
-        <v>1746.98</v>
+        <v>1774.1</v>
       </c>
       <c r="L50" t="n">
-        <v>1788.25</v>
+        <v>1859.13</v>
       </c>
       <c r="M50" t="n">
-        <v>1864.59</v>
+        <v>1968.92</v>
       </c>
       <c r="N50" t="n">
-        <v>1940.94</v>
+        <v>2078.7</v>
       </c>
       <c r="O50" t="n">
-        <v>1947.13</v>
+        <v>2138.97</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4701,10 +4701,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4723,70 +4721,72 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1871.28</v>
+        <v>1953.41</v>
       </c>
       <c r="C51" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D51" t="n">
-        <v>1842.82</v>
+        <v>1821.49</v>
       </c>
       <c r="E51" t="n">
-        <v>1953.41</v>
+        <v>1882.52</v>
       </c>
       <c r="F51" t="n">
-        <v>81.90000000000001</v>
+        <v>-70.89</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0363</v>
       </c>
       <c r="H51" t="n">
-        <v>120.43</v>
+        <v>154.98</v>
       </c>
       <c r="I51" t="n">
-        <v>1554.53</v>
+        <v>1722.39</v>
       </c>
       <c r="J51" t="n">
-        <v>1689.07</v>
+        <v>1858.17</v>
       </c>
       <c r="K51" t="n">
-        <v>1774.1</v>
+        <v>1893.2</v>
       </c>
       <c r="L51" t="n">
-        <v>1859.13</v>
+        <v>1928.22</v>
       </c>
       <c r="M51" t="n">
-        <v>1968.92</v>
+        <v>2013.63</v>
       </c>
       <c r="N51" t="n">
-        <v>2078.7</v>
+        <v>2099.03</v>
       </c>
       <c r="O51" t="n">
-        <v>2138.97</v>
+        <v>2083.68</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4800,74 +4800,70 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1953.41</v>
+        <v>1882.78</v>
       </c>
       <c r="C52" t="n">
-        <v>1976.46</v>
+        <v>1937.17</v>
       </c>
       <c r="D52" t="n">
-        <v>1821.49</v>
+        <v>1827.7</v>
       </c>
       <c r="E52" t="n">
-        <v>1882.52</v>
+        <v>1908.68</v>
       </c>
       <c r="F52" t="n">
-        <v>-70.89</v>
+        <v>26.16</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0363</v>
+        <v>0.0139</v>
       </c>
       <c r="H52" t="n">
-        <v>154.98</v>
+        <v>109.47</v>
       </c>
       <c r="I52" t="n">
-        <v>1722.39</v>
+        <v>1666.51</v>
       </c>
       <c r="J52" t="n">
-        <v>1858.17</v>
+        <v>1719.32</v>
       </c>
       <c r="K52" t="n">
-        <v>1893.2</v>
+        <v>1805.03</v>
       </c>
       <c r="L52" t="n">
-        <v>1928.22</v>
+        <v>1890.75</v>
       </c>
       <c r="M52" t="n">
-        <v>2013.63</v>
+        <v>1960.01</v>
       </c>
       <c r="N52" t="n">
-        <v>2099.03</v>
+        <v>2029.27</v>
       </c>
       <c r="O52" t="n">
-        <v>2083.68</v>
+        <v>2131.44</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4886,57 +4882,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1882.78</v>
+        <v>1908.72</v>
       </c>
       <c r="C53" t="n">
-        <v>1937.17</v>
+        <v>1928.99</v>
       </c>
       <c r="D53" t="n">
-        <v>1827.7</v>
+        <v>1852.84</v>
       </c>
       <c r="E53" t="n">
-        <v>1908.68</v>
+        <v>1873.94</v>
       </c>
       <c r="F53" t="n">
-        <v>26.16</v>
+        <v>-34.74</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0182</v>
       </c>
       <c r="H53" t="n">
-        <v>109.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>1666.51</v>
+        <v>1718.23</v>
       </c>
       <c r="J53" t="n">
-        <v>1719.32</v>
+        <v>1812.34</v>
       </c>
       <c r="K53" t="n">
-        <v>1805.03</v>
+        <v>1853.95</v>
       </c>
       <c r="L53" t="n">
-        <v>1890.75</v>
+        <v>1895.56</v>
       </c>
       <c r="M53" t="n">
-        <v>1960.01</v>
+        <v>1963.42</v>
       </c>
       <c r="N53" t="n">
-        <v>2029.27</v>
+        <v>2031.28</v>
       </c>
       <c r="O53" t="n">
-        <v>2131.44</v>
+        <v>2046.64</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4944,12 +4940,14 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4968,57 +4966,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1908.72</v>
+        <v>1873.97</v>
       </c>
       <c r="C54" t="n">
-        <v>1928.99</v>
+        <v>2545.88</v>
       </c>
       <c r="D54" t="n">
-        <v>1852.84</v>
+        <v>1870.75</v>
       </c>
       <c r="E54" t="n">
-        <v>1873.94</v>
+        <v>2463.82</v>
       </c>
       <c r="F54" t="n">
-        <v>-34.74</v>
+        <v>589.87</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.3148</v>
       </c>
       <c r="H54" t="n">
-        <v>76.15000000000001</v>
+        <v>675.13</v>
       </c>
       <c r="I54" t="n">
-        <v>1718.23</v>
+        <v>1776.69</v>
       </c>
       <c r="J54" t="n">
-        <v>1812.34</v>
+        <v>1789.3</v>
       </c>
       <c r="K54" t="n">
-        <v>1853.95</v>
+        <v>1835.87</v>
       </c>
       <c r="L54" t="n">
-        <v>1895.56</v>
+        <v>1882.43</v>
       </c>
       <c r="M54" t="n">
-        <v>1963.42</v>
+        <v>1912.02</v>
       </c>
       <c r="N54" t="n">
-        <v>2031.28</v>
+        <v>1941.61</v>
       </c>
       <c r="O54" t="n">
-        <v>2046.64</v>
+        <v>2005.15</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5026,83 +5024,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1873.97</v>
+        <v>2463.64</v>
       </c>
       <c r="C55" t="n">
-        <v>2545.88</v>
+        <v>2564.27</v>
       </c>
       <c r="D55" t="n">
-        <v>1870.75</v>
+        <v>2389.47</v>
       </c>
       <c r="E55" t="n">
-        <v>2463.82</v>
+        <v>2417.94</v>
       </c>
       <c r="F55" t="n">
-        <v>589.87</v>
+        <v>-45.88</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.3148</v>
+        <v>-0.0186</v>
       </c>
       <c r="H55" t="n">
-        <v>675.13</v>
+        <v>174.81</v>
       </c>
       <c r="I55" t="n">
-        <v>1776.69</v>
+        <v>1195.61</v>
       </c>
       <c r="J55" t="n">
-        <v>1789.3</v>
+        <v>1916.43</v>
       </c>
       <c r="K55" t="n">
-        <v>1835.87</v>
+        <v>2126.25</v>
       </c>
       <c r="L55" t="n">
-        <v>1882.43</v>
+        <v>2336.07</v>
       </c>
       <c r="M55" t="n">
-        <v>1912.02</v>
+        <v>2801.38</v>
       </c>
       <c r="N55" t="n">
-        <v>1941.61</v>
+        <v>3266.7</v>
       </c>
       <c r="O55" t="n">
-        <v>2005.15</v>
+        <v>3221.01</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5115,78 +5113,76 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2463.64</v>
+        <v>2417.9</v>
       </c>
       <c r="C56" t="n">
-        <v>2564.27</v>
+        <v>2545.62</v>
       </c>
       <c r="D56" t="n">
-        <v>2389.47</v>
+        <v>2356.19</v>
       </c>
       <c r="E56" t="n">
-        <v>2417.94</v>
+        <v>2514.55</v>
       </c>
       <c r="F56" t="n">
-        <v>-45.88</v>
+        <v>96.61</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0186</v>
+        <v>0.04</v>
       </c>
       <c r="H56" t="n">
-        <v>174.81</v>
+        <v>189.44</v>
       </c>
       <c r="I56" t="n">
-        <v>1195.61</v>
+        <v>2214.66</v>
       </c>
       <c r="J56" t="n">
-        <v>1916.43</v>
+        <v>2213.67</v>
       </c>
       <c r="K56" t="n">
-        <v>2126.25</v>
+        <v>2330.54</v>
       </c>
       <c r="L56" t="n">
-        <v>2336.07</v>
+        <v>2447.41</v>
       </c>
       <c r="M56" t="n">
-        <v>2801.38</v>
+        <v>2505.34</v>
       </c>
       <c r="N56" t="n">
-        <v>3266.7</v>
+        <v>2563.28</v>
       </c>
       <c r="O56" t="n">
-        <v>3221.01</v>
+        <v>2739.08</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5199,11 +5195,13 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5218,57 +5216,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2417.9</v>
+        <v>2514.58</v>
       </c>
       <c r="C57" t="n">
-        <v>2545.62</v>
+        <v>2663.05</v>
       </c>
       <c r="D57" t="n">
-        <v>2356.19</v>
+        <v>2406.91</v>
       </c>
       <c r="E57" t="n">
-        <v>2514.55</v>
+        <v>2477.02</v>
       </c>
       <c r="F57" t="n">
-        <v>96.61</v>
+        <v>-37.53</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.0149</v>
       </c>
       <c r="H57" t="n">
-        <v>189.44</v>
+        <v>256.14</v>
       </c>
       <c r="I57" t="n">
-        <v>2214.66</v>
+        <v>2166.75</v>
       </c>
       <c r="J57" t="n">
-        <v>2213.67</v>
+        <v>2356.93</v>
       </c>
       <c r="K57" t="n">
-        <v>2330.54</v>
+        <v>2419.83</v>
       </c>
       <c r="L57" t="n">
-        <v>2447.41</v>
+        <v>2482.73</v>
       </c>
       <c r="M57" t="n">
-        <v>2505.34</v>
+        <v>2609.27</v>
       </c>
       <c r="N57" t="n">
-        <v>2563.28</v>
+        <v>2735.81</v>
       </c>
       <c r="O57" t="n">
-        <v>2739.08</v>
+        <v>2735.06</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5276,17 +5274,19 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5302,57 +5302,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2514.58</v>
+        <v>2475.82</v>
       </c>
       <c r="C58" t="n">
-        <v>2663.05</v>
+        <v>2605.78</v>
       </c>
       <c r="D58" t="n">
-        <v>2406.91</v>
+        <v>2468.6</v>
       </c>
       <c r="E58" t="n">
-        <v>2493.1</v>
+        <v>2548.83</v>
       </c>
       <c r="F58" t="n">
-        <v>-21.45</v>
+        <v>71.81</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.029</v>
       </c>
       <c r="H58" t="n">
-        <v>256.14</v>
+        <v>137.18</v>
       </c>
       <c r="I58" t="n">
-        <v>2166.75</v>
+        <v>2150.76</v>
       </c>
       <c r="J58" t="n">
-        <v>2356.93</v>
+        <v>2191.9</v>
       </c>
       <c r="K58" t="n">
-        <v>2419.83</v>
+        <v>2348.95</v>
       </c>
       <c r="L58" t="n">
-        <v>2482.73</v>
+        <v>2506</v>
       </c>
       <c r="M58" t="n">
-        <v>2609.27</v>
+        <v>2605.09</v>
       </c>
       <c r="N58" t="n">
-        <v>2735.81</v>
+        <v>2704.19</v>
       </c>
       <c r="O58" t="n">
-        <v>2735.06</v>
+        <v>2919.19</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5360,10 +5360,8 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
@@ -5399,25 +5397,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2150.76</v>
+        <v>2331.42</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2216.02</v>
+        <v>2417.47</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2365.03</v>
+        <v>2480.24</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2514.04</v>
+        <v>2543.01</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2621.17</v>
+        <v>2617.42</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2728.3</v>
+        <v>2691.83</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2919.19</v>
+        <v>2742.96</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>888.77</v>
       </c>
       <c r="I2" t="n">
-        <v>3549.2</v>
+        <v>3656.17</v>
       </c>
       <c r="J2" t="n">
-        <v>3850.87</v>
+        <v>3890.99</v>
       </c>
       <c r="K2" t="n">
-        <v>4163.43</v>
+        <v>4190.18</v>
       </c>
       <c r="L2" t="n">
-        <v>4475.99</v>
+        <v>4489.36</v>
       </c>
       <c r="M2" t="n">
-        <v>4783.11</v>
+        <v>4756.37</v>
       </c>
       <c r="N2" t="n">
-        <v>5090.23</v>
+        <v>5023.37</v>
       </c>
       <c r="O2" t="n">
-        <v>5408.23</v>
+        <v>5354.74</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5313,25 +5313,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2475.82</v>
+        <v>2515.17</v>
       </c>
       <c r="C58" t="n">
-        <v>2605.78</v>
+        <v>2517.18</v>
       </c>
       <c r="D58" t="n">
-        <v>2468.6</v>
+        <v>2508.21</v>
       </c>
       <c r="E58" t="n">
-        <v>2548.83</v>
+        <v>2516.14</v>
       </c>
       <c r="F58" t="n">
-        <v>71.81</v>
+        <v>39.12</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0158</v>
       </c>
       <c r="H58" t="n">
-        <v>137.18</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5368,10 +5368,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5397,25 +5395,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2331.42</v>
+        <v>2499.24</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2417.47</v>
+        <v>2508.89</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2480.24</v>
+        <v>2511.65</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2543.01</v>
+        <v>2514.42</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2617.42</v>
+        <v>2520.63</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2691.83</v>
+        <v>2526.83</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2742.96</v>
+        <v>2526.16</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5316,22 +5316,22 @@
         <v>2515.17</v>
       </c>
       <c r="C58" t="n">
-        <v>2517.18</v>
+        <v>2518.69</v>
       </c>
       <c r="D58" t="n">
         <v>2508.21</v>
       </c>
       <c r="E58" t="n">
-        <v>2516.14</v>
+        <v>2516.7</v>
       </c>
       <c r="F58" t="n">
-        <v>39.12</v>
+        <v>39.68</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
       <c r="H58" t="n">
-        <v>8.970000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5395,25 +5395,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2499.24</v>
+        <v>2497.74</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2508.89</v>
+        <v>2507.85</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2511.65</v>
+        <v>2511.46</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2514.42</v>
+        <v>2515.07</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2520.63</v>
+        <v>2521.94</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2526.83</v>
+        <v>2528.8</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2526.16</v>
+        <v>2529.16</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5319,19 +5319,19 @@
         <v>2518.69</v>
       </c>
       <c r="D58" t="n">
-        <v>2508.21</v>
+        <v>2497.06</v>
       </c>
       <c r="E58" t="n">
-        <v>2516.7</v>
+        <v>2498.84</v>
       </c>
       <c r="F58" t="n">
-        <v>39.68</v>
+        <v>21.82</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.016</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>10.47</v>
+        <v>21.63</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5363,9 +5363,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5395,25 +5395,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2497.74</v>
+        <v>2475.43</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2507.85</v>
+        <v>2472.69</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2511.46</v>
+        <v>2488.02</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2515.07</v>
+        <v>2503.36</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2521.94</v>
+        <v>2509.66</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2528.8</v>
+        <v>2515.95</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2529.16</v>
+        <v>2540.32</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5319,19 +5319,19 @@
         <v>2518.69</v>
       </c>
       <c r="D58" t="n">
-        <v>2497.06</v>
+        <v>2497.89</v>
       </c>
       <c r="E58" t="n">
-        <v>2498.84</v>
+        <v>2498.33</v>
       </c>
       <c r="F58" t="n">
-        <v>21.82</v>
+        <v>21.31</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="H58" t="n">
-        <v>21.63</v>
+        <v>20.79</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5395,25 +5395,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2475.43</v>
+        <v>2477.1</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2472.69</v>
+        <v>2472.56</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2488.02</v>
+        <v>2487.93</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2503.36</v>
+        <v>2503.31</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2509.66</v>
+        <v>2508.73</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2515.95</v>
+        <v>2514.14</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2540.32</v>
+        <v>2539.48</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5313,25 +5313,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2515.17</v>
+        <v>2476.6</v>
       </c>
       <c r="C58" t="n">
-        <v>2518.69</v>
+        <v>2612.4</v>
       </c>
       <c r="D58" t="n">
-        <v>2497.89</v>
+        <v>2358.66</v>
       </c>
       <c r="E58" t="n">
-        <v>2498.33</v>
+        <v>2387.94</v>
       </c>
       <c r="F58" t="n">
-        <v>21.31</v>
+        <v>-89.08</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.036</v>
       </c>
       <c r="H58" t="n">
-        <v>20.79</v>
+        <v>253.75</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5360,16 +5360,20 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5384,7 +5388,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5395,25 +5399,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2477.1</v>
+        <v>2104.91</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2472.56</v>
+        <v>2085.4</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2487.93</v>
+        <v>2261.07</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2503.31</v>
+        <v>2436.73</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2508.73</v>
+        <v>2514.81</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2514.14</v>
+        <v>2592.89</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2539.48</v>
+        <v>2866.15</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>888.77</v>
       </c>
       <c r="I2" t="n">
-        <v>3656.17</v>
+        <v>3962.54</v>
       </c>
       <c r="J2" t="n">
-        <v>3890.99</v>
+        <v>4005.88</v>
       </c>
       <c r="K2" t="n">
-        <v>4190.18</v>
+        <v>4266.77</v>
       </c>
       <c r="L2" t="n">
-        <v>4489.36</v>
+        <v>4527.66</v>
       </c>
       <c r="M2" t="n">
-        <v>4756.37</v>
+        <v>4679.77</v>
       </c>
       <c r="N2" t="n">
-        <v>5023.37</v>
+        <v>4831.89</v>
       </c>
       <c r="O2" t="n">
-        <v>5354.74</v>
+        <v>5201.56</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -704,11 +704,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5319,19 +5321,19 @@
         <v>2612.4</v>
       </c>
       <c r="D58" t="n">
-        <v>2358.66</v>
+        <v>2389.14</v>
       </c>
       <c r="E58" t="n">
-        <v>2387.94</v>
+        <v>2390.21</v>
       </c>
       <c r="F58" t="n">
-        <v>-89.08</v>
+        <v>-86.81</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.036</v>
+        <v>-0.035</v>
       </c>
       <c r="H58" t="n">
-        <v>253.75</v>
+        <v>223.27</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5399,25 +5401,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2104.91</v>
+        <v>2165.87</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2085.4</v>
+        <v>2111.66</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2261.07</v>
+        <v>2278.58</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2436.73</v>
+        <v>2445.49</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2514.81</v>
+        <v>2501.84</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2592.89</v>
+        <v>2558.2</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2866.15</v>
+        <v>2835.67</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5321,19 +5321,19 @@
         <v>2612.4</v>
       </c>
       <c r="D58" t="n">
-        <v>2389.14</v>
+        <v>2389.89</v>
       </c>
       <c r="E58" t="n">
-        <v>2390.21</v>
+        <v>2405.93</v>
       </c>
       <c r="F58" t="n">
-        <v>-86.81</v>
+        <v>-71.09</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.035</v>
+        <v>-0.0287</v>
       </c>
       <c r="H58" t="n">
-        <v>223.27</v>
+        <v>222.51</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5401,25 +5401,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2165.87</v>
+        <v>2167.37</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2111.66</v>
+        <v>2135.81</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2278.58</v>
+        <v>2294.67</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2445.49</v>
+        <v>2453.54</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2501.84</v>
+        <v>2517.19</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2558.2</v>
+        <v>2580.84</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2835.67</v>
+        <v>2834.92</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5321,19 +5321,19 @@
         <v>2612.4</v>
       </c>
       <c r="D58" t="n">
-        <v>2389.89</v>
+        <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2405.93</v>
+        <v>2411.88</v>
       </c>
       <c r="F58" t="n">
-        <v>-71.09</v>
+        <v>-65.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0287</v>
+        <v>-0.0263</v>
       </c>
       <c r="H58" t="n">
-        <v>222.51</v>
+        <v>254.44</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5401,25 +5401,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>2167.37</v>
+        <v>2103.52</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2135.81</v>
+        <v>2120.79</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2294.67</v>
+        <v>2284.66</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2453.54</v>
+        <v>2448.53</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2517.19</v>
+        <v>2539.1</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2580.84</v>
+        <v>2629.67</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>2834.92</v>
+        <v>2866.85</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5324,13 +5324,13 @@
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2411.88</v>
+        <v>2417.66</v>
       </c>
       <c r="F58" t="n">
-        <v>-65.14</v>
+        <v>-59.36</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0263</v>
+        <v>-0.024</v>
       </c>
       <c r="H58" t="n">
         <v>254.44</v>
@@ -5404,19 +5404,19 @@
         <v>2103.52</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2120.79</v>
+        <v>2129.46</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2284.66</v>
+        <v>2290.44</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2448.53</v>
+        <v>2451.42</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2539.1</v>
+        <v>2544.88</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2629.67</v>
+        <v>2638.34</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2866.85</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5324,13 +5324,13 @@
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2417.66</v>
+        <v>2412.24</v>
       </c>
       <c r="F58" t="n">
-        <v>-59.36</v>
+        <v>-64.78</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.0262</v>
       </c>
       <c r="H58" t="n">
         <v>254.44</v>
@@ -5404,19 +5404,19 @@
         <v>2103.52</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2129.46</v>
+        <v>2121.33</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2290.44</v>
+        <v>2285.02</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2451.42</v>
+        <v>2448.71</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2544.88</v>
+        <v>2539.46</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2638.34</v>
+        <v>2630.21</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2866.85</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5324,13 +5324,13 @@
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2412.24</v>
+        <v>2396.95</v>
       </c>
       <c r="F58" t="n">
-        <v>-64.78</v>
+        <v>-80.06999999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0262</v>
+        <v>-0.0323</v>
       </c>
       <c r="H58" t="n">
         <v>254.44</v>
@@ -5404,19 +5404,19 @@
         <v>2103.52</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2121.33</v>
+        <v>2098.39</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2285.02</v>
+        <v>2269.73</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2448.71</v>
+        <v>2441.07</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2539.46</v>
+        <v>2524.17</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2630.21</v>
+        <v>2607.28</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2866.85</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5324,13 +5324,13 @@
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2396.95</v>
+        <v>2412.33</v>
       </c>
       <c r="F58" t="n">
-        <v>-80.06999999999999</v>
+        <v>-64.69</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0323</v>
+        <v>-0.0261</v>
       </c>
       <c r="H58" t="n">
         <v>254.44</v>
@@ -5404,19 +5404,19 @@
         <v>2103.52</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2098.39</v>
+        <v>2121.46</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2269.73</v>
+        <v>2285.11</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2441.07</v>
+        <v>2448.76</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2524.17</v>
+        <v>2539.55</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2607.28</v>
+        <v>2630.35</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2866.85</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5324,13 +5324,13 @@
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2412.33</v>
+        <v>2441.68</v>
       </c>
       <c r="F58" t="n">
-        <v>-64.69</v>
+        <v>-35.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0261</v>
+        <v>-0.0143</v>
       </c>
       <c r="H58" t="n">
         <v>254.44</v>
@@ -5362,14 +5362,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5404,19 +5402,19 @@
         <v>2103.52</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2121.46</v>
+        <v>2165.49</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2285.11</v>
+        <v>2314.46</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2448.76</v>
+        <v>2463.43</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2539.55</v>
+        <v>2568.9</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2630.35</v>
+        <v>2674.37</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2866.85</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5324,13 +5324,13 @@
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2441.68</v>
+        <v>2445.47</v>
       </c>
       <c r="F58" t="n">
-        <v>-35.34</v>
+        <v>-31.55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0127</v>
       </c>
       <c r="H58" t="n">
         <v>254.44</v>
@@ -5402,19 +5402,19 @@
         <v>2103.52</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>2165.49</v>
+        <v>2171.17</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>2314.46</v>
+        <v>2318.25</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>2463.43</v>
+        <v>2465.33</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2568.9</v>
+        <v>2572.69</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>2674.37</v>
+        <v>2680.06</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>2866.85</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,31 +659,35 @@
         <v>888.77</v>
       </c>
       <c r="I2" t="n">
-        <v>3962.54</v>
+        <v>4083.36</v>
       </c>
       <c r="J2" t="n">
-        <v>4005.88</v>
+        <v>4156.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4266.77</v>
+        <v>4327.18</v>
       </c>
       <c r="L2" t="n">
-        <v>4527.66</v>
+        <v>4497.45</v>
       </c>
       <c r="M2" t="n">
-        <v>4679.77</v>
+        <v>4619.36</v>
       </c>
       <c r="N2" t="n">
-        <v>4831.89</v>
+        <v>4741.27</v>
       </c>
       <c r="O2" t="n">
-        <v>5201.56</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>4959.91</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5324,13 +5321,13 @@
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2445.47</v>
+        <v>2438.11</v>
       </c>
       <c r="F58" t="n">
-        <v>-31.55</v>
+        <v>-38.91</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.0157</v>
       </c>
       <c r="H58" t="n">
         <v>254.44</v>
@@ -5390,34 +5387,6 @@
         <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>2103.52</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>2171.17</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>2318.25</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>2465.33</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>2572.69</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>2680.06</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>2866.85</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5321,13 +5321,13 @@
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2438.11</v>
+        <v>2445.52</v>
       </c>
       <c r="F58" t="n">
-        <v>-38.91</v>
+        <v>-31.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0127</v>
       </c>
       <c r="H58" t="n">
         <v>254.44</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>888.77</v>
       </c>
       <c r="I2" t="n">
-        <v>4083.36</v>
+        <v>4225.55</v>
       </c>
       <c r="J2" t="n">
-        <v>4156.9</v>
+        <v>4290.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4327.18</v>
+        <v>4385.69</v>
       </c>
       <c r="L2" t="n">
-        <v>4497.45</v>
+        <v>4480.78</v>
       </c>
       <c r="M2" t="n">
-        <v>4619.36</v>
+        <v>4560.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4741.27</v>
+        <v>4640.92</v>
       </c>
       <c r="O2" t="n">
-        <v>4959.91</v>
+        <v>4751.04</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -706,11 +706,13 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5315,22 +5317,22 @@
         <v>2476.6</v>
       </c>
       <c r="C58" t="n">
-        <v>2612.4</v>
+        <v>2659.72</v>
       </c>
       <c r="D58" t="n">
         <v>2357.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2445.52</v>
+        <v>2644.05</v>
       </c>
       <c r="F58" t="n">
-        <v>-31.5</v>
+        <v>167.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0674</v>
       </c>
       <c r="H58" t="n">
-        <v>254.44</v>
+        <v>301.76</v>
       </c>
       <c r="I58" t="n">
         <v>2150.76</v>
@@ -5362,14 +5364,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5385,7 +5387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,85 +634,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4473.33</v>
+        <v>4779.77</v>
       </c>
       <c r="C2" t="n">
-        <v>4953.73</v>
+        <v>4796.35</v>
       </c>
       <c r="D2" t="n">
-        <v>4064.97</v>
+        <v>4264.2</v>
       </c>
       <c r="E2" t="n">
-        <v>4779.65</v>
+        <v>4390.02</v>
       </c>
       <c r="F2" t="n">
-        <v>306.38</v>
+        <v>-389.63</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.0815</v>
       </c>
       <c r="H2" t="n">
-        <v>888.77</v>
+        <v>532.15</v>
       </c>
       <c r="I2" t="n">
-        <v>4225.55</v>
+        <v>3176.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4290.6</v>
+        <v>4026.03</v>
       </c>
       <c r="K2" t="n">
-        <v>4385.69</v>
+        <v>4335.26</v>
       </c>
       <c r="L2" t="n">
-        <v>4480.78</v>
+        <v>4644.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4560.85</v>
+        <v>5224.03</v>
       </c>
       <c r="N2" t="n">
-        <v>4640.92</v>
+        <v>5803.56</v>
       </c>
       <c r="O2" t="n">
-        <v>4751.04</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>5842.5</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -721,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4779.77</v>
+        <v>4389.63</v>
       </c>
       <c r="C3" t="n">
-        <v>4796.35</v>
+        <v>4490.35</v>
       </c>
       <c r="D3" t="n">
-        <v>4264.2</v>
+        <v>4221.25</v>
       </c>
       <c r="E3" t="n">
-        <v>4390.02</v>
+        <v>4305.35</v>
       </c>
       <c r="F3" t="n">
-        <v>-389.63</v>
+        <v>-84.67</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0815</v>
+        <v>-0.0193</v>
       </c>
       <c r="H3" t="n">
-        <v>532.15</v>
+        <v>269.1</v>
       </c>
       <c r="I3" t="n">
-        <v>3176.2</v>
+        <v>3732.04</v>
       </c>
       <c r="J3" t="n">
-        <v>4026.03</v>
+        <v>3787.74</v>
       </c>
       <c r="K3" t="n">
-        <v>4335.26</v>
+        <v>4123.94</v>
       </c>
       <c r="L3" t="n">
-        <v>4644.5</v>
+        <v>4460.15</v>
       </c>
       <c r="M3" t="n">
-        <v>5224.03</v>
+        <v>4656.1</v>
       </c>
       <c r="N3" t="n">
-        <v>5803.56</v>
+        <v>4852.05</v>
       </c>
       <c r="O3" t="n">
-        <v>5842.5</v>
+        <v>5328.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,14 +769,12 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -805,57 +793,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4389.63</v>
+        <v>4305.38</v>
       </c>
       <c r="C4" t="n">
-        <v>4490.35</v>
+        <v>4763.36</v>
       </c>
       <c r="D4" t="n">
-        <v>4221.25</v>
+        <v>4277.85</v>
       </c>
       <c r="E4" t="n">
-        <v>4305.35</v>
+        <v>4609.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-84.67</v>
+        <v>304.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0193</v>
+        <v>0.0707</v>
       </c>
       <c r="H4" t="n">
-        <v>269.1</v>
+        <v>485.51</v>
       </c>
       <c r="I4" t="n">
-        <v>3732.04</v>
+        <v>3952.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3787.74</v>
+        <v>4011.02</v>
       </c>
       <c r="K4" t="n">
-        <v>4123.94</v>
+        <v>4170.8</v>
       </c>
       <c r="L4" t="n">
-        <v>4460.15</v>
+        <v>4330.57</v>
       </c>
       <c r="M4" t="n">
-        <v>4656.1</v>
+        <v>4439.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4852.05</v>
+        <v>4549.22</v>
       </c>
       <c r="O4" t="n">
-        <v>5328.5</v>
+        <v>4759.45</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -868,76 +856,78 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4305.38</v>
+        <v>4609.72</v>
       </c>
       <c r="C5" t="n">
-        <v>4763.36</v>
+        <v>4670.53</v>
       </c>
       <c r="D5" t="n">
-        <v>4277.85</v>
+        <v>4428.33</v>
       </c>
       <c r="E5" t="n">
-        <v>4609.6</v>
+        <v>4451.33</v>
       </c>
       <c r="F5" t="n">
-        <v>304.25</v>
+        <v>-158.27</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0707</v>
+        <v>-0.0343</v>
       </c>
       <c r="H5" t="n">
-        <v>485.51</v>
+        <v>242.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3952.15</v>
+        <v>3792.34</v>
       </c>
       <c r="J5" t="n">
-        <v>4011.02</v>
+        <v>4168.58</v>
       </c>
       <c r="K5" t="n">
-        <v>4170.8</v>
+        <v>4366.84</v>
       </c>
       <c r="L5" t="n">
-        <v>4330.57</v>
+        <v>4565.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4439.9</v>
+        <v>4852.35</v>
       </c>
       <c r="N5" t="n">
-        <v>4549.22</v>
+        <v>5139.6</v>
       </c>
       <c r="O5" t="n">
-        <v>4759.45</v>
+        <v>5248.87</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,96 +935,100 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4609.72</v>
+        <v>4451.58</v>
       </c>
       <c r="C6" t="n">
-        <v>4670.53</v>
+        <v>4457.08</v>
       </c>
       <c r="D6" t="n">
-        <v>4428.33</v>
+        <v>3829.01</v>
       </c>
       <c r="E6" t="n">
-        <v>4451.33</v>
+        <v>4141.48</v>
       </c>
       <c r="F6" t="n">
-        <v>-158.27</v>
+        <v>-309.85</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0343</v>
+        <v>-0.0696</v>
       </c>
       <c r="H6" t="n">
-        <v>242.2</v>
+        <v>628.0700000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3792.34</v>
+        <v>4186.13</v>
       </c>
       <c r="J6" t="n">
-        <v>4168.58</v>
+        <v>4160.08</v>
       </c>
       <c r="K6" t="n">
-        <v>4366.84</v>
+        <v>4330.23</v>
       </c>
       <c r="L6" t="n">
-        <v>4565.1</v>
+        <v>4500.38</v>
       </c>
       <c r="M6" t="n">
-        <v>4852.35</v>
+        <v>4572.43</v>
       </c>
       <c r="N6" t="n">
-        <v>5139.6</v>
+        <v>4644.48</v>
       </c>
       <c r="O6" t="n">
-        <v>5248.87</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+        <v>4912.73</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1048,88 +1042,80 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4451.58</v>
+        <v>4141.36</v>
       </c>
       <c r="C7" t="n">
-        <v>4457.08</v>
+        <v>4616.53</v>
       </c>
       <c r="D7" t="n">
-        <v>3829.01</v>
+        <v>4087.93</v>
       </c>
       <c r="E7" t="n">
-        <v>4141.48</v>
+        <v>4515.42</v>
       </c>
       <c r="F7" t="n">
-        <v>-309.85</v>
+        <v>373.95</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0696</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>628.0700000000001</v>
+        <v>528.61</v>
       </c>
       <c r="I7" t="n">
-        <v>4186.13</v>
+        <v>3200.94</v>
       </c>
       <c r="J7" t="n">
-        <v>4160.08</v>
+        <v>3512.62</v>
       </c>
       <c r="K7" t="n">
-        <v>4330.23</v>
+        <v>3827.44</v>
       </c>
       <c r="L7" t="n">
-        <v>4500.38</v>
+        <v>4142.26</v>
       </c>
       <c r="M7" t="n">
-        <v>4572.43</v>
+        <v>4455.51</v>
       </c>
       <c r="N7" t="n">
-        <v>4644.48</v>
+        <v>4768.76</v>
       </c>
       <c r="O7" t="n">
-        <v>4912.73</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
+        <v>5085.15</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1141,74 +1127,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4141.36</v>
+        <v>4515.3</v>
       </c>
       <c r="C8" t="n">
-        <v>4616.53</v>
+        <v>4755.22</v>
       </c>
       <c r="D8" t="n">
-        <v>4087.93</v>
+        <v>3460.22</v>
       </c>
       <c r="E8" t="n">
-        <v>4515.42</v>
+        <v>4164.43</v>
       </c>
       <c r="F8" t="n">
-        <v>373.95</v>
+        <v>-351</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>528.61</v>
+        <v>1295</v>
       </c>
       <c r="I8" t="n">
-        <v>3200.94</v>
+        <v>3559.32</v>
       </c>
       <c r="J8" t="n">
-        <v>3512.62</v>
+        <v>4068.41</v>
       </c>
       <c r="K8" t="n">
-        <v>3827.44</v>
+        <v>4251.12</v>
       </c>
       <c r="L8" t="n">
-        <v>4142.26</v>
+        <v>4433.83</v>
       </c>
       <c r="M8" t="n">
-        <v>4455.51</v>
+        <v>4779.73</v>
       </c>
       <c r="N8" t="n">
-        <v>4768.76</v>
+        <v>5125.63</v>
       </c>
       <c r="O8" t="n">
-        <v>5085.15</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>5145.14</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1223,76 +1217,70 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4515.3</v>
+        <v>4164.05</v>
       </c>
       <c r="C9" t="n">
-        <v>4755.22</v>
+        <v>4292.85</v>
       </c>
       <c r="D9" t="n">
-        <v>3460.22</v>
+        <v>3678.62</v>
       </c>
       <c r="E9" t="n">
-        <v>4164.43</v>
+        <v>3984.65</v>
       </c>
       <c r="F9" t="n">
-        <v>-351</v>
+        <v>-179.78</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0432</v>
       </c>
       <c r="H9" t="n">
-        <v>1295</v>
+        <v>614.23</v>
       </c>
       <c r="I9" t="n">
-        <v>3559.32</v>
+        <v>2165.22</v>
       </c>
       <c r="J9" t="n">
-        <v>4068.41</v>
+        <v>2897.78</v>
       </c>
       <c r="K9" t="n">
-        <v>4251.12</v>
+        <v>3516.93</v>
       </c>
       <c r="L9" t="n">
-        <v>4433.83</v>
+        <v>4136.07</v>
       </c>
       <c r="M9" t="n">
-        <v>4779.73</v>
+        <v>4811.93</v>
       </c>
       <c r="N9" t="n">
-        <v>5125.63</v>
+        <v>5487.78</v>
       </c>
       <c r="O9" t="n">
-        <v>5145.14</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>6050.22</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1318,50 +1306,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4164.05</v>
+        <v>3984.7</v>
       </c>
       <c r="C10" t="n">
-        <v>4292.85</v>
+        <v>4177.31</v>
       </c>
       <c r="D10" t="n">
-        <v>3678.62</v>
+        <v>3718.08</v>
       </c>
       <c r="E10" t="n">
-        <v>3984.65</v>
+        <v>4157.99</v>
       </c>
       <c r="F10" t="n">
-        <v>-179.78</v>
+        <v>173.34</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0432</v>
+        <v>0.0435</v>
       </c>
       <c r="H10" t="n">
-        <v>614.23</v>
+        <v>459.23</v>
       </c>
       <c r="I10" t="n">
-        <v>2165.22</v>
+        <v>3064.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2897.78</v>
+        <v>3369.88</v>
       </c>
       <c r="K10" t="n">
-        <v>3516.93</v>
+        <v>3677.54</v>
       </c>
       <c r="L10" t="n">
-        <v>4136.07</v>
+        <v>3985.19</v>
       </c>
       <c r="M10" t="n">
-        <v>4811.93</v>
+        <v>4291.76</v>
       </c>
       <c r="N10" t="n">
-        <v>5487.78</v>
+        <v>4598.33</v>
       </c>
       <c r="O10" t="n">
-        <v>6050.22</v>
+        <v>4907.07</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1374,11 +1362,13 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1393,76 +1383,78 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3984.7</v>
+        <v>4158.01</v>
       </c>
       <c r="C11" t="n">
-        <v>4177.31</v>
+        <v>4250.67</v>
       </c>
       <c r="D11" t="n">
-        <v>3718.08</v>
+        <v>3681.91</v>
       </c>
       <c r="E11" t="n">
-        <v>4157.99</v>
+        <v>3911.06</v>
       </c>
       <c r="F11" t="n">
-        <v>173.34</v>
+        <v>-246.93</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0435</v>
+        <v>-0.0594</v>
       </c>
       <c r="H11" t="n">
-        <v>459.23</v>
+        <v>568.76</v>
       </c>
       <c r="I11" t="n">
-        <v>3064.4</v>
+        <v>3258.84</v>
       </c>
       <c r="J11" t="n">
-        <v>3369.88</v>
+        <v>3803.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3677.54</v>
+        <v>3928.37</v>
       </c>
       <c r="L11" t="n">
-        <v>3985.19</v>
+        <v>4052.84</v>
       </c>
       <c r="M11" t="n">
-        <v>4291.76</v>
+        <v>4387.61</v>
       </c>
       <c r="N11" t="n">
-        <v>4598.33</v>
+        <v>4722.37</v>
       </c>
       <c r="O11" t="n">
-        <v>4907.07</v>
+        <v>4636.54</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1477,60 +1469,62 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4158.01</v>
+        <v>3911.75</v>
       </c>
       <c r="C12" t="n">
-        <v>4250.67</v>
+        <v>3912.63</v>
       </c>
       <c r="D12" t="n">
-        <v>3681.91</v>
+        <v>3063.09</v>
       </c>
       <c r="E12" t="n">
-        <v>3911.06</v>
+        <v>3582.62</v>
       </c>
       <c r="F12" t="n">
-        <v>-246.93</v>
+        <v>-328.44</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>568.76</v>
+        <v>849.55</v>
       </c>
       <c r="I12" t="n">
-        <v>3258.84</v>
+        <v>3113.15</v>
       </c>
       <c r="J12" t="n">
-        <v>3803.9</v>
+        <v>3314.69</v>
       </c>
       <c r="K12" t="n">
-        <v>3928.37</v>
+        <v>3626.68</v>
       </c>
       <c r="L12" t="n">
-        <v>4052.84</v>
+        <v>3938.68</v>
       </c>
       <c r="M12" t="n">
-        <v>4387.61</v>
+        <v>4195.44</v>
       </c>
       <c r="N12" t="n">
-        <v>4722.37</v>
+        <v>4452.21</v>
       </c>
       <c r="O12" t="n">
-        <v>4636.54</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
+        <v>4819.43</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
@@ -1542,7 +1536,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1561,76 +1555,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3911.75</v>
+        <v>3583.44</v>
       </c>
       <c r="C13" t="n">
-        <v>3912.63</v>
+        <v>3656.15</v>
       </c>
       <c r="D13" t="n">
-        <v>3063.09</v>
+        <v>3007.07</v>
       </c>
       <c r="E13" t="n">
-        <v>3582.62</v>
+        <v>3092.85</v>
       </c>
       <c r="F13" t="n">
-        <v>-328.44</v>
+        <v>-489.77</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1367</v>
       </c>
       <c r="H13" t="n">
-        <v>849.55</v>
+        <v>649.08</v>
       </c>
       <c r="I13" t="n">
-        <v>3113.15</v>
+        <v>2213.54</v>
       </c>
       <c r="J13" t="n">
-        <v>3314.69</v>
+        <v>2780.46</v>
       </c>
       <c r="K13" t="n">
-        <v>3626.68</v>
+        <v>3157.85</v>
       </c>
       <c r="L13" t="n">
-        <v>3938.68</v>
+        <v>3535.24</v>
       </c>
       <c r="M13" t="n">
-        <v>4195.44</v>
+        <v>4007.39</v>
       </c>
       <c r="N13" t="n">
-        <v>4452.21</v>
+        <v>4479.55</v>
       </c>
       <c r="O13" t="n">
-        <v>4819.43</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4762.18</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1654,50 +1640,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3583.44</v>
+        <v>3092.94</v>
       </c>
       <c r="C14" t="n">
-        <v>3656.15</v>
+        <v>3218.13</v>
       </c>
       <c r="D14" t="n">
-        <v>3007.07</v>
+        <v>2626.87</v>
       </c>
       <c r="E14" t="n">
-        <v>3092.85</v>
+        <v>2801.68</v>
       </c>
       <c r="F14" t="n">
-        <v>-489.77</v>
+        <v>-291.17</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.1367</v>
+        <v>-0.0941</v>
       </c>
       <c r="H14" t="n">
-        <v>649.08</v>
+        <v>591.26</v>
       </c>
       <c r="I14" t="n">
-        <v>2213.54</v>
+        <v>2358</v>
       </c>
       <c r="J14" t="n">
-        <v>2780.46</v>
+        <v>2324.39</v>
       </c>
       <c r="K14" t="n">
-        <v>3157.85</v>
+        <v>2768.31</v>
       </c>
       <c r="L14" t="n">
-        <v>3535.24</v>
+        <v>3212.23</v>
       </c>
       <c r="M14" t="n">
-        <v>4007.39</v>
+        <v>3417.39</v>
       </c>
       <c r="N14" t="n">
-        <v>4479.55</v>
+        <v>3622.54</v>
       </c>
       <c r="O14" t="n">
-        <v>4762.18</v>
+        <v>4305.23</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1710,7 +1696,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1734,50 +1720,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3092.94</v>
+        <v>2801.2</v>
       </c>
       <c r="C15" t="n">
-        <v>3218.13</v>
+        <v>3095.03</v>
       </c>
       <c r="D15" t="n">
-        <v>2626.87</v>
+        <v>2763.38</v>
       </c>
       <c r="E15" t="n">
-        <v>2801.68</v>
+        <v>2992.11</v>
       </c>
       <c r="F15" t="n">
-        <v>-291.17</v>
+        <v>190.44</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0941</v>
+        <v>0.068</v>
       </c>
       <c r="H15" t="n">
-        <v>591.26</v>
+        <v>331.66</v>
       </c>
       <c r="I15" t="n">
-        <v>2358</v>
+        <v>2035.61</v>
       </c>
       <c r="J15" t="n">
-        <v>2324.39</v>
+        <v>2150</v>
       </c>
       <c r="K15" t="n">
-        <v>2768.31</v>
+        <v>2506.05</v>
       </c>
       <c r="L15" t="n">
-        <v>3212.23</v>
+        <v>2862.09</v>
       </c>
       <c r="M15" t="n">
-        <v>3417.39</v>
+        <v>3097.31</v>
       </c>
       <c r="N15" t="n">
-        <v>3622.54</v>
+        <v>3332.52</v>
       </c>
       <c r="O15" t="n">
-        <v>4305.23</v>
+        <v>3809.39</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,19 +1771,19 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1809,55 +1795,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2801.2</v>
+        <v>2991.92</v>
       </c>
       <c r="C16" t="n">
-        <v>3095.03</v>
+        <v>3238.56</v>
       </c>
       <c r="D16" t="n">
-        <v>2763.38</v>
+        <v>2720.44</v>
       </c>
       <c r="E16" t="n">
-        <v>2992.11</v>
+        <v>3061.3</v>
       </c>
       <c r="F16" t="n">
-        <v>190.44</v>
+        <v>69.19</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.068</v>
+        <v>0.0231</v>
       </c>
       <c r="H16" t="n">
-        <v>331.66</v>
+        <v>518.12</v>
       </c>
       <c r="I16" t="n">
-        <v>2035.61</v>
+        <v>2431.72</v>
       </c>
       <c r="J16" t="n">
-        <v>2150</v>
+        <v>2691.91</v>
       </c>
       <c r="K16" t="n">
-        <v>2506.05</v>
+        <v>2826.28</v>
       </c>
       <c r="L16" t="n">
-        <v>2862.09</v>
+        <v>2960.66</v>
       </c>
       <c r="M16" t="n">
-        <v>3097.31</v>
+        <v>3157.94</v>
       </c>
       <c r="N16" t="n">
-        <v>3332.52</v>
+        <v>3355.22</v>
       </c>
       <c r="O16" t="n">
-        <v>3809.39</v>
+        <v>3426.69</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,10 +1855,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1898,50 +1890,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2991.92</v>
+        <v>3061.01</v>
       </c>
       <c r="C17" t="n">
-        <v>3238.56</v>
+        <v>3446.62</v>
       </c>
       <c r="D17" t="n">
-        <v>2720.44</v>
+        <v>3034.69</v>
       </c>
       <c r="E17" t="n">
-        <v>3061.3</v>
+        <v>3060.59</v>
       </c>
       <c r="F17" t="n">
-        <v>69.19</v>
+        <v>-0.71</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0231</v>
+        <v>-0.0002</v>
       </c>
       <c r="H17" t="n">
-        <v>518.12</v>
+        <v>411.93</v>
       </c>
       <c r="I17" t="n">
-        <v>2431.72</v>
+        <v>2202.32</v>
       </c>
       <c r="J17" t="n">
-        <v>2691.91</v>
+        <v>2584.09</v>
       </c>
       <c r="K17" t="n">
-        <v>2826.28</v>
+        <v>2802.24</v>
       </c>
       <c r="L17" t="n">
-        <v>2960.66</v>
+        <v>3020.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3157.94</v>
+        <v>3320.36</v>
       </c>
       <c r="N17" t="n">
-        <v>3355.22</v>
+        <v>3620.32</v>
       </c>
       <c r="O17" t="n">
-        <v>3426.69</v>
+        <v>3756.67</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,19 +1941,17 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1984,50 +1974,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3061.01</v>
+        <v>3060.48</v>
       </c>
       <c r="C18" t="n">
-        <v>3446.62</v>
+        <v>3175.12</v>
       </c>
       <c r="D18" t="n">
-        <v>3034.69</v>
+        <v>2777.12</v>
       </c>
       <c r="E18" t="n">
-        <v>3060.59</v>
+        <v>3001.61</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.71</v>
+        <v>-58.98</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H18" t="n">
-        <v>411.93</v>
+        <v>398</v>
       </c>
       <c r="I18" t="n">
-        <v>2202.32</v>
+        <v>2622.76</v>
       </c>
       <c r="J18" t="n">
-        <v>2584.09</v>
+        <v>2558.63</v>
       </c>
       <c r="K18" t="n">
-        <v>2802.24</v>
+        <v>2854.63</v>
       </c>
       <c r="L18" t="n">
-        <v>3020.4</v>
+        <v>3150.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3320.36</v>
+        <v>3266.56</v>
       </c>
       <c r="N18" t="n">
-        <v>3620.32</v>
+        <v>3382.49</v>
       </c>
       <c r="O18" t="n">
-        <v>3756.67</v>
+        <v>3858.55</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2035,18 +2025,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2059,59 +2049,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3060.48</v>
+        <v>3001.61</v>
       </c>
       <c r="C19" t="n">
-        <v>3175.12</v>
+        <v>3073.35</v>
       </c>
       <c r="D19" t="n">
-        <v>2777.12</v>
+        <v>2888.99</v>
       </c>
       <c r="E19" t="n">
-        <v>3001.61</v>
+        <v>2948.57</v>
       </c>
       <c r="F19" t="n">
-        <v>-58.98</v>
+        <v>-53.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0177</v>
       </c>
       <c r="H19" t="n">
-        <v>398</v>
+        <v>184.37</v>
       </c>
       <c r="I19" t="n">
-        <v>2622.76</v>
+        <v>2379.12</v>
       </c>
       <c r="J19" t="n">
-        <v>2558.63</v>
+        <v>2616.36</v>
       </c>
       <c r="K19" t="n">
-        <v>2854.63</v>
+        <v>2802.61</v>
       </c>
       <c r="L19" t="n">
-        <v>3150.63</v>
+        <v>2988.87</v>
       </c>
       <c r="M19" t="n">
-        <v>3266.56</v>
+        <v>3200.61</v>
       </c>
       <c r="N19" t="n">
-        <v>3382.49</v>
+        <v>3412.36</v>
       </c>
       <c r="O19" t="n">
-        <v>3858.55</v>
+        <v>3573.12</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2119,14 +2105,12 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2143,55 +2127,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3001.61</v>
+        <v>2948.56</v>
       </c>
       <c r="C20" t="n">
-        <v>3073.35</v>
+        <v>3160.55</v>
       </c>
       <c r="D20" t="n">
-        <v>2888.99</v>
+        <v>2908.75</v>
       </c>
       <c r="E20" t="n">
-        <v>2948.57</v>
+        <v>3140.71</v>
       </c>
       <c r="F20" t="n">
-        <v>-53.05</v>
+        <v>192.14</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0177</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>184.37</v>
+        <v>251.8</v>
       </c>
       <c r="I20" t="n">
-        <v>2379.12</v>
+        <v>2704.62</v>
       </c>
       <c r="J20" t="n">
-        <v>2616.36</v>
+        <v>2747.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2802.61</v>
+        <v>2856.39</v>
       </c>
       <c r="L20" t="n">
-        <v>2988.87</v>
+        <v>2964.87</v>
       </c>
       <c r="M20" t="n">
-        <v>3200.61</v>
+        <v>3040.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3412.36</v>
+        <v>3116.63</v>
       </c>
       <c r="O20" t="n">
-        <v>3573.12</v>
+        <v>3257.72</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2204,76 +2192,76 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2948.56</v>
+        <v>3141.49</v>
       </c>
       <c r="C21" t="n">
-        <v>3160.55</v>
+        <v>3303.56</v>
       </c>
       <c r="D21" t="n">
-        <v>2908.75</v>
+        <v>3052.51</v>
       </c>
       <c r="E21" t="n">
-        <v>3140.71</v>
+        <v>3118.89</v>
       </c>
       <c r="F21" t="n">
-        <v>192.14</v>
+        <v>-21.83</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="H21" t="n">
-        <v>251.8</v>
+        <v>251.05</v>
       </c>
       <c r="I21" t="n">
-        <v>2704.62</v>
+        <v>2656.95</v>
       </c>
       <c r="J21" t="n">
-        <v>2747.9</v>
+        <v>2941.94</v>
       </c>
       <c r="K21" t="n">
-        <v>2856.39</v>
+        <v>3014.81</v>
       </c>
       <c r="L21" t="n">
-        <v>2964.87</v>
+        <v>3087.68</v>
       </c>
       <c r="M21" t="n">
-        <v>3040.75</v>
+        <v>3266.61</v>
       </c>
       <c r="N21" t="n">
-        <v>3116.63</v>
+        <v>3445.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3257.72</v>
+        <v>3412.35</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2284,9 +2272,9 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2294,10 +2282,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2307,55 +2293,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3141.49</v>
+        <v>3118.83</v>
       </c>
       <c r="C22" t="n">
-        <v>3303.56</v>
+        <v>3397.9</v>
       </c>
       <c r="D22" t="n">
-        <v>3052.51</v>
+        <v>3068.07</v>
       </c>
       <c r="E22" t="n">
-        <v>3118.89</v>
+        <v>3281.16</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.83</v>
+        <v>162.27</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.052</v>
       </c>
       <c r="H22" t="n">
-        <v>251.05</v>
+        <v>329.82</v>
       </c>
       <c r="I22" t="n">
-        <v>2656.95</v>
+        <v>2801.46</v>
       </c>
       <c r="J22" t="n">
-        <v>2941.94</v>
+        <v>2838.26</v>
       </c>
       <c r="K22" t="n">
-        <v>3014.81</v>
+        <v>2993.36</v>
       </c>
       <c r="L22" t="n">
-        <v>3087.68</v>
+        <v>3148.46</v>
       </c>
       <c r="M22" t="n">
-        <v>3266.61</v>
+        <v>3244.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3445.54</v>
+        <v>3340.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3412.35</v>
+        <v>3554.62</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2366,19 +2356,21 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2387,90 +2379,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3118.83</v>
+        <v>3282.2</v>
       </c>
       <c r="C23" t="n">
-        <v>3397.9</v>
+        <v>3282.65</v>
       </c>
       <c r="D23" t="n">
-        <v>3068.07</v>
+        <v>2785.9</v>
       </c>
       <c r="E23" t="n">
-        <v>3281.16</v>
+        <v>2815.9</v>
       </c>
       <c r="F23" t="n">
-        <v>162.27</v>
+        <v>-465.26</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.052</v>
+        <v>-0.1418</v>
       </c>
       <c r="H23" t="n">
-        <v>329.82</v>
+        <v>496.76</v>
       </c>
       <c r="I23" t="n">
-        <v>2801.46</v>
+        <v>2738.25</v>
       </c>
       <c r="J23" t="n">
-        <v>2838.26</v>
+        <v>2975.42</v>
       </c>
       <c r="K23" t="n">
-        <v>2993.36</v>
+        <v>3116.25</v>
       </c>
       <c r="L23" t="n">
-        <v>3148.46</v>
+        <v>3257.07</v>
       </c>
       <c r="M23" t="n">
-        <v>3244.41</v>
+        <v>3446.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3340.36</v>
+        <v>3635.07</v>
       </c>
       <c r="O23" t="n">
-        <v>3554.62</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>3727.72</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2478,67 +2468,65 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3282.2</v>
+        <v>2815.77</v>
       </c>
       <c r="C24" t="n">
-        <v>3282.65</v>
+        <v>3040.72</v>
       </c>
       <c r="D24" t="n">
-        <v>2785.9</v>
+        <v>2224.12</v>
       </c>
       <c r="E24" t="n">
-        <v>2815.9</v>
+        <v>2267.96</v>
       </c>
       <c r="F24" t="n">
-        <v>-465.26</v>
+        <v>-547.9400000000001</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.1418</v>
+        <v>-0.1946</v>
       </c>
       <c r="H24" t="n">
-        <v>496.76</v>
+        <v>816.6</v>
       </c>
       <c r="I24" t="n">
-        <v>2738.25</v>
+        <v>2289.14</v>
       </c>
       <c r="J24" t="n">
-        <v>2975.42</v>
+        <v>2209.96</v>
       </c>
       <c r="K24" t="n">
-        <v>3116.25</v>
+        <v>2567.52</v>
       </c>
       <c r="L24" t="n">
-        <v>3257.07</v>
+        <v>2925.09</v>
       </c>
       <c r="M24" t="n">
-        <v>3446.07</v>
+        <v>3064.28</v>
       </c>
       <c r="N24" t="n">
-        <v>3635.07</v>
+        <v>3203.47</v>
       </c>
       <c r="O24" t="n">
-        <v>3727.72</v>
+        <v>3779.41</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2562,65 +2550,63 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2815.77</v>
+        <v>2267.56</v>
       </c>
       <c r="C25" t="n">
-        <v>3040.72</v>
+        <v>2393.06</v>
       </c>
       <c r="D25" t="n">
-        <v>2224.12</v>
+        <v>1748.63</v>
       </c>
       <c r="E25" t="n">
-        <v>2267.96</v>
+        <v>2088.76</v>
       </c>
       <c r="F25" t="n">
-        <v>-547.9400000000001</v>
+        <v>-179.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.1946</v>
+        <v>-0.079</v>
       </c>
       <c r="H25" t="n">
-        <v>816.6</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>2289.14</v>
+        <v>1407.52</v>
       </c>
       <c r="J25" t="n">
-        <v>2209.96</v>
+        <v>1269.14</v>
       </c>
       <c r="K25" t="n">
-        <v>2567.52</v>
+        <v>1859.66</v>
       </c>
       <c r="L25" t="n">
-        <v>2925.09</v>
+        <v>2450.19</v>
       </c>
       <c r="M25" t="n">
-        <v>3064.28</v>
+        <v>2676.27</v>
       </c>
       <c r="N25" t="n">
-        <v>3203.47</v>
+        <v>2902.34</v>
       </c>
       <c r="O25" t="n">
-        <v>3779.41</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>3857.32</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2644,50 +2630,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2267.56</v>
+        <v>2087.92</v>
       </c>
       <c r="C26" t="n">
-        <v>2393.06</v>
+        <v>2144.98</v>
       </c>
       <c r="D26" t="n">
-        <v>1748.63</v>
+        <v>1897.33</v>
       </c>
       <c r="E26" t="n">
-        <v>2088.76</v>
+        <v>1966.04</v>
       </c>
       <c r="F26" t="n">
-        <v>-179.2</v>
+        <v>-122.72</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.0588</v>
       </c>
       <c r="H26" t="n">
-        <v>644.4400000000001</v>
+        <v>247.64</v>
       </c>
       <c r="I26" t="n">
-        <v>1407.52</v>
+        <v>1104.19</v>
       </c>
       <c r="J26" t="n">
-        <v>1269.14</v>
+        <v>1453.29</v>
       </c>
       <c r="K26" t="n">
-        <v>1859.66</v>
+        <v>1766.55</v>
       </c>
       <c r="L26" t="n">
-        <v>2450.19</v>
+        <v>2079.8</v>
       </c>
       <c r="M26" t="n">
-        <v>2676.27</v>
+        <v>2410.98</v>
       </c>
       <c r="N26" t="n">
-        <v>2902.34</v>
+        <v>2742.16</v>
       </c>
       <c r="O26" t="n">
-        <v>3857.32</v>
+        <v>3037.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,14 +2681,12 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2719,55 +2703,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2087.92</v>
+        <v>1965.92</v>
       </c>
       <c r="C27" t="n">
-        <v>2144.98</v>
+        <v>2037.16</v>
       </c>
       <c r="D27" t="n">
-        <v>1897.33</v>
+        <v>1906.82</v>
       </c>
       <c r="E27" t="n">
-        <v>1966.04</v>
+        <v>1957.81</v>
       </c>
       <c r="F27" t="n">
-        <v>-122.72</v>
+        <v>-8.24</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0042</v>
       </c>
       <c r="H27" t="n">
-        <v>247.64</v>
+        <v>130.34</v>
       </c>
       <c r="I27" t="n">
-        <v>1104.19</v>
+        <v>1649.69</v>
       </c>
       <c r="J27" t="n">
-        <v>1453.29</v>
+        <v>1690.85</v>
       </c>
       <c r="K27" t="n">
-        <v>1766.55</v>
+        <v>1842.22</v>
       </c>
       <c r="L27" t="n">
-        <v>2079.8</v>
+        <v>1993.6</v>
       </c>
       <c r="M27" t="n">
-        <v>2410.98</v>
+        <v>2089.86</v>
       </c>
       <c r="N27" t="n">
-        <v>2742.16</v>
+        <v>2186.13</v>
       </c>
       <c r="O27" t="n">
-        <v>3037.5</v>
+        <v>2392.62</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2778,7 +2766,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2806,70 +2794,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1965.92</v>
+        <v>1958.14</v>
       </c>
       <c r="C28" t="n">
-        <v>2037.16</v>
+        <v>2145.51</v>
       </c>
       <c r="D28" t="n">
-        <v>1906.82</v>
+        <v>1804.11</v>
       </c>
       <c r="E28" t="n">
-        <v>1957.81</v>
+        <v>1939.07</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.24</v>
+        <v>-18.74</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>130.34</v>
+        <v>341.39</v>
       </c>
       <c r="I28" t="n">
-        <v>1649.69</v>
+        <v>1776.49</v>
       </c>
       <c r="J28" t="n">
-        <v>1690.85</v>
+        <v>1820.38</v>
       </c>
       <c r="K28" t="n">
-        <v>1842.22</v>
+        <v>1892.64</v>
       </c>
       <c r="L28" t="n">
-        <v>1993.6</v>
+        <v>1964.9</v>
       </c>
       <c r="M28" t="n">
-        <v>2089.86</v>
+        <v>2022.97</v>
       </c>
       <c r="N28" t="n">
-        <v>2186.13</v>
+        <v>2081.05</v>
       </c>
       <c r="O28" t="n">
-        <v>2392.62</v>
+        <v>2167.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2888,78 +2884,72 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1958.14</v>
+        <v>1939.06</v>
       </c>
       <c r="C29" t="n">
-        <v>2145.51</v>
+        <v>2198.66</v>
       </c>
       <c r="D29" t="n">
-        <v>1804.11</v>
+        <v>1915.3</v>
       </c>
       <c r="E29" t="n">
-        <v>1939.07</v>
+        <v>1936.6</v>
       </c>
       <c r="F29" t="n">
-        <v>-18.74</v>
+        <v>-2.46</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0013</v>
       </c>
       <c r="H29" t="n">
-        <v>341.39</v>
+        <v>283.36</v>
       </c>
       <c r="I29" t="n">
-        <v>1776.49</v>
+        <v>1462.72</v>
       </c>
       <c r="J29" t="n">
-        <v>1820.38</v>
+        <v>1579.8</v>
       </c>
       <c r="K29" t="n">
-        <v>1892.64</v>
+        <v>1768.37</v>
       </c>
       <c r="L29" t="n">
-        <v>1964.9</v>
+        <v>1956.94</v>
       </c>
       <c r="M29" t="n">
-        <v>2022.97</v>
+        <v>2109.76</v>
       </c>
       <c r="N29" t="n">
-        <v>2081.05</v>
+        <v>2262.59</v>
       </c>
       <c r="O29" t="n">
-        <v>2167.5</v>
+        <v>2486.9</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2971,57 +2961,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1939.06</v>
+        <v>1936.64</v>
       </c>
       <c r="C30" t="n">
-        <v>2198.66</v>
+        <v>2206.81</v>
       </c>
       <c r="D30" t="n">
-        <v>1915.3</v>
+        <v>1930.6</v>
       </c>
       <c r="E30" t="n">
-        <v>1936.6</v>
+        <v>2177.48</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.46</v>
+        <v>240.87</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.1244</v>
       </c>
       <c r="H30" t="n">
-        <v>283.36</v>
+        <v>276.21</v>
       </c>
       <c r="I30" t="n">
-        <v>1462.72</v>
+        <v>1631.95</v>
       </c>
       <c r="J30" t="n">
-        <v>1579.8</v>
+        <v>1593.06</v>
       </c>
       <c r="K30" t="n">
-        <v>1768.37</v>
+        <v>1794.93</v>
       </c>
       <c r="L30" t="n">
-        <v>1956.94</v>
+        <v>1996.79</v>
       </c>
       <c r="M30" t="n">
-        <v>2109.76</v>
+        <v>2078.28</v>
       </c>
       <c r="N30" t="n">
-        <v>2262.59</v>
+        <v>2159.77</v>
       </c>
       <c r="O30" t="n">
-        <v>2486.9</v>
+        <v>2482.01</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3034,7 +3024,7 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3042,70 +3032,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1936.64</v>
+        <v>2177.78</v>
       </c>
       <c r="C31" t="n">
-        <v>2206.81</v>
+        <v>2384.47</v>
       </c>
       <c r="D31" t="n">
-        <v>1930.6</v>
+        <v>2027.05</v>
       </c>
       <c r="E31" t="n">
-        <v>2177.48</v>
+        <v>2053.05</v>
       </c>
       <c r="F31" t="n">
-        <v>240.87</v>
+        <v>-124.43</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.1244</v>
+        <v>-0.0571</v>
       </c>
       <c r="H31" t="n">
-        <v>276.21</v>
+        <v>357.42</v>
       </c>
       <c r="I31" t="n">
-        <v>1631.95</v>
+        <v>1654.39</v>
       </c>
       <c r="J31" t="n">
-        <v>1593.06</v>
+        <v>1955.65</v>
       </c>
       <c r="K31" t="n">
-        <v>1794.93</v>
+        <v>2039.37</v>
       </c>
       <c r="L31" t="n">
-        <v>1996.79</v>
+        <v>2123.09</v>
       </c>
       <c r="M31" t="n">
-        <v>2078.28</v>
+        <v>2315.58</v>
       </c>
       <c r="N31" t="n">
-        <v>2159.77</v>
+        <v>2508.08</v>
       </c>
       <c r="O31" t="n">
-        <v>2482.01</v>
+        <v>2483.03</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3113,12 +3101,14 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3126,10 +3116,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3139,55 +3127,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2177.78</v>
+        <v>2052.95</v>
       </c>
       <c r="C32" t="n">
-        <v>2384.47</v>
+        <v>2198.37</v>
       </c>
       <c r="D32" t="n">
-        <v>2027.05</v>
+        <v>1939.53</v>
       </c>
       <c r="E32" t="n">
-        <v>2053.05</v>
+        <v>1982.56</v>
       </c>
       <c r="F32" t="n">
-        <v>-124.43</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0571</v>
+        <v>-0.0343</v>
       </c>
       <c r="H32" t="n">
-        <v>357.42</v>
+        <v>258.84</v>
       </c>
       <c r="I32" t="n">
-        <v>1654.39</v>
+        <v>1669.63</v>
       </c>
       <c r="J32" t="n">
-        <v>1955.65</v>
+        <v>1619.28</v>
       </c>
       <c r="K32" t="n">
-        <v>2039.37</v>
+        <v>1874.34</v>
       </c>
       <c r="L32" t="n">
-        <v>2123.09</v>
+        <v>2129.4</v>
       </c>
       <c r="M32" t="n">
-        <v>2315.58</v>
+        <v>2231.76</v>
       </c>
       <c r="N32" t="n">
-        <v>2508.08</v>
+        <v>2334.11</v>
       </c>
       <c r="O32" t="n">
-        <v>2483.03</v>
+        <v>2741.89</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3200,15 +3192,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3223,57 +3213,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2052.95</v>
+        <v>1982.55</v>
       </c>
       <c r="C33" t="n">
-        <v>2198.37</v>
+        <v>2165.67</v>
       </c>
       <c r="D33" t="n">
-        <v>1939.53</v>
+        <v>1979.08</v>
       </c>
       <c r="E33" t="n">
-        <v>1982.56</v>
+        <v>2109</v>
       </c>
       <c r="F33" t="n">
-        <v>-70.48999999999999</v>
+        <v>126.44</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0343</v>
+        <v>0.0638</v>
       </c>
       <c r="H33" t="n">
-        <v>258.84</v>
+        <v>186.59</v>
       </c>
       <c r="I33" t="n">
-        <v>1669.63</v>
+        <v>1680.69</v>
       </c>
       <c r="J33" t="n">
-        <v>1619.28</v>
+        <v>1680.52</v>
       </c>
       <c r="K33" t="n">
-        <v>1874.34</v>
+        <v>1853.14</v>
       </c>
       <c r="L33" t="n">
-        <v>2129.4</v>
+        <v>2025.75</v>
       </c>
       <c r="M33" t="n">
-        <v>2231.76</v>
+        <v>2111.98</v>
       </c>
       <c r="N33" t="n">
-        <v>2334.11</v>
+        <v>2198.21</v>
       </c>
       <c r="O33" t="n">
-        <v>2741.89</v>
+        <v>2457.21</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3281,19 +3271,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3307,57 +3297,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1982.55</v>
+        <v>2108.94</v>
       </c>
       <c r="C34" t="n">
-        <v>2165.67</v>
+        <v>2327.46</v>
       </c>
       <c r="D34" t="n">
-        <v>1979.08</v>
+        <v>2061.47</v>
       </c>
       <c r="E34" t="n">
-        <v>2109</v>
+        <v>2192.2</v>
       </c>
       <c r="F34" t="n">
-        <v>126.44</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0638</v>
+        <v>0.0395</v>
       </c>
       <c r="H34" t="n">
-        <v>186.59</v>
+        <v>265.99</v>
       </c>
       <c r="I34" t="n">
-        <v>1680.69</v>
+        <v>1792.49</v>
       </c>
       <c r="J34" t="n">
-        <v>1680.52</v>
+        <v>1940.72</v>
       </c>
       <c r="K34" t="n">
-        <v>1853.14</v>
+        <v>2015.7</v>
       </c>
       <c r="L34" t="n">
-        <v>2025.75</v>
+        <v>2090.68</v>
       </c>
       <c r="M34" t="n">
-        <v>2111.98</v>
+        <v>2202.29</v>
       </c>
       <c r="N34" t="n">
-        <v>2198.21</v>
+        <v>2313.9</v>
       </c>
       <c r="O34" t="n">
-        <v>2457.21</v>
+        <v>2352.26</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3368,7 +3358,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3378,8 +3368,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3389,59 +3381,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2108.94</v>
+        <v>2192.33</v>
       </c>
       <c r="C35" t="n">
-        <v>2327.46</v>
+        <v>2464.78</v>
       </c>
       <c r="D35" t="n">
-        <v>2061.47</v>
+        <v>2176.32</v>
       </c>
       <c r="E35" t="n">
-        <v>2192.2</v>
+        <v>2264.92</v>
       </c>
       <c r="F35" t="n">
-        <v>83.20999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0332</v>
       </c>
       <c r="H35" t="n">
-        <v>265.99</v>
+        <v>288.46</v>
       </c>
       <c r="I35" t="n">
-        <v>1792.49</v>
+        <v>1795.48</v>
       </c>
       <c r="J35" t="n">
-        <v>1940.72</v>
+        <v>1925.08</v>
       </c>
       <c r="K35" t="n">
-        <v>2015.7</v>
+        <v>2059.21</v>
       </c>
       <c r="L35" t="n">
-        <v>2090.68</v>
+        <v>2193.33</v>
       </c>
       <c r="M35" t="n">
-        <v>2202.29</v>
+        <v>2325.2</v>
       </c>
       <c r="N35" t="n">
-        <v>2313.9</v>
+        <v>2457.06</v>
       </c>
       <c r="O35" t="n">
-        <v>2352.26</v>
+        <v>2593.45</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3452,7 +3440,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3480,50 +3468,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2192.33</v>
+        <v>2264.87</v>
       </c>
       <c r="C36" t="n">
-        <v>2464.78</v>
+        <v>2422.86</v>
       </c>
       <c r="D36" t="n">
-        <v>2176.32</v>
+        <v>2262.05</v>
       </c>
       <c r="E36" t="n">
-        <v>2264.92</v>
+        <v>2369.73</v>
       </c>
       <c r="F36" t="n">
-        <v>72.72</v>
+        <v>104.81</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0463</v>
       </c>
       <c r="H36" t="n">
-        <v>288.46</v>
+        <v>160.81</v>
       </c>
       <c r="I36" t="n">
-        <v>1795.48</v>
+        <v>1887.87</v>
       </c>
       <c r="J36" t="n">
-        <v>1925.08</v>
+        <v>1948.64</v>
       </c>
       <c r="K36" t="n">
-        <v>2059.21</v>
+        <v>2120.69</v>
       </c>
       <c r="L36" t="n">
-        <v>2193.33</v>
+        <v>2292.74</v>
       </c>
       <c r="M36" t="n">
-        <v>2325.2</v>
+        <v>2409.15</v>
       </c>
       <c r="N36" t="n">
-        <v>2457.06</v>
+        <v>2525.56</v>
       </c>
       <c r="O36" t="n">
-        <v>2593.45</v>
+        <v>2753.24</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3534,7 +3522,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3544,10 +3532,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3557,74 +3543,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2264.87</v>
+        <v>2369.84</v>
       </c>
       <c r="C37" t="n">
-        <v>2422.86</v>
+        <v>2403.73</v>
       </c>
       <c r="D37" t="n">
-        <v>2262.05</v>
+        <v>2221.22</v>
       </c>
       <c r="E37" t="n">
-        <v>2369.73</v>
+        <v>2321.64</v>
       </c>
       <c r="F37" t="n">
-        <v>104.81</v>
+        <v>-48.09</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0463</v>
+        <v>-0.0203</v>
       </c>
       <c r="H37" t="n">
-        <v>160.81</v>
+        <v>182.5</v>
       </c>
       <c r="I37" t="n">
-        <v>1887.87</v>
+        <v>2101.25</v>
       </c>
       <c r="J37" t="n">
-        <v>1948.64</v>
+        <v>2222.56</v>
       </c>
       <c r="K37" t="n">
-        <v>2120.69</v>
+        <v>2289.33</v>
       </c>
       <c r="L37" t="n">
-        <v>2292.74</v>
+        <v>2356.09</v>
       </c>
       <c r="M37" t="n">
-        <v>2409.15</v>
+        <v>2450.13</v>
       </c>
       <c r="N37" t="n">
-        <v>2525.56</v>
+        <v>2544.17</v>
       </c>
       <c r="O37" t="n">
-        <v>2753.24</v>
+        <v>2583.67</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3639,79 +3631,77 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2369.84</v>
+        <v>2321.82</v>
       </c>
       <c r="C38" t="n">
-        <v>2403.73</v>
+        <v>2423.04</v>
       </c>
       <c r="D38" t="n">
-        <v>2221.22</v>
+        <v>2265.83</v>
       </c>
       <c r="E38" t="n">
-        <v>2321.64</v>
+        <v>2369.04</v>
       </c>
       <c r="F38" t="n">
-        <v>-48.09</v>
+        <v>47.41</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="H38" t="n">
-        <v>182.5</v>
+        <v>157.21</v>
       </c>
       <c r="I38" t="n">
-        <v>2101.25</v>
+        <v>2038.72</v>
       </c>
       <c r="J38" t="n">
-        <v>2222.56</v>
+        <v>2143.71</v>
       </c>
       <c r="K38" t="n">
-        <v>2289.33</v>
+        <v>2230.38</v>
       </c>
       <c r="L38" t="n">
-        <v>2356.09</v>
+        <v>2317.06</v>
       </c>
       <c r="M38" t="n">
-        <v>2450.13</v>
+        <v>2412.89</v>
       </c>
       <c r="N38" t="n">
-        <v>2544.17</v>
+        <v>2508.72</v>
       </c>
       <c r="O38" t="n">
-        <v>2583.67</v>
+        <v>2586.23</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3723,78 +3713,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2321.82</v>
+        <v>2369.19</v>
       </c>
       <c r="C39" t="n">
-        <v>2423.04</v>
+        <v>2374.3</v>
       </c>
       <c r="D39" t="n">
-        <v>2265.83</v>
+        <v>2097.02</v>
       </c>
       <c r="E39" t="n">
-        <v>2369.04</v>
+        <v>2127.65</v>
       </c>
       <c r="F39" t="n">
-        <v>47.41</v>
+        <v>-241.4</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.1019</v>
       </c>
       <c r="H39" t="n">
-        <v>157.21</v>
+        <v>277.28</v>
       </c>
       <c r="I39" t="n">
-        <v>2038.72</v>
+        <v>2108.63</v>
       </c>
       <c r="J39" t="n">
-        <v>2143.71</v>
+        <v>2224.14</v>
       </c>
       <c r="K39" t="n">
-        <v>2230.38</v>
+        <v>2290.44</v>
       </c>
       <c r="L39" t="n">
-        <v>2317.06</v>
+        <v>2356.74</v>
       </c>
       <c r="M39" t="n">
-        <v>2412.89</v>
+        <v>2447.65</v>
       </c>
       <c r="N39" t="n">
-        <v>2508.72</v>
+        <v>2538.55</v>
       </c>
       <c r="O39" t="n">
-        <v>2586.23</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+        <v>2580.25</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3802,9 +3792,9 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3812,69 +3802,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2369.19</v>
+        <v>2127.68</v>
       </c>
       <c r="C40" t="n">
-        <v>2374.3</v>
+        <v>2155.96</v>
       </c>
       <c r="D40" t="n">
-        <v>2097.02</v>
+        <v>2010.55</v>
       </c>
       <c r="E40" t="n">
-        <v>2127.65</v>
+        <v>2097.99</v>
       </c>
       <c r="F40" t="n">
-        <v>-241.4</v>
+        <v>-29.65</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.1019</v>
+        <v>-0.0139</v>
       </c>
       <c r="H40" t="n">
-        <v>277.28</v>
+        <v>145.41</v>
       </c>
       <c r="I40" t="n">
-        <v>2108.63</v>
+        <v>1819.74</v>
       </c>
       <c r="J40" t="n">
-        <v>2224.14</v>
+        <v>1796.35</v>
       </c>
       <c r="K40" t="n">
-        <v>2290.44</v>
+        <v>1989</v>
       </c>
       <c r="L40" t="n">
-        <v>2356.74</v>
+        <v>2181.65</v>
       </c>
       <c r="M40" t="n">
-        <v>2447.65</v>
+        <v>2266.29</v>
       </c>
       <c r="N40" t="n">
-        <v>2538.55</v>
+        <v>2350.92</v>
       </c>
       <c r="O40" t="n">
-        <v>2580.25</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>2651.59</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3896,50 +3880,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2127.68</v>
+        <v>2097.99</v>
       </c>
       <c r="C41" t="n">
-        <v>2155.96</v>
+        <v>2138.41</v>
       </c>
       <c r="D41" t="n">
-        <v>2010.55</v>
+        <v>1966.28</v>
       </c>
       <c r="E41" t="n">
-        <v>2097.99</v>
+        <v>2004.34</v>
       </c>
       <c r="F41" t="n">
-        <v>-29.65</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.0446</v>
       </c>
       <c r="H41" t="n">
-        <v>145.41</v>
+        <v>172.13</v>
       </c>
       <c r="I41" t="n">
-        <v>1819.74</v>
+        <v>1865.14</v>
       </c>
       <c r="J41" t="n">
-        <v>1796.35</v>
+        <v>1959.95</v>
       </c>
       <c r="K41" t="n">
-        <v>1989</v>
+        <v>2025.29</v>
       </c>
       <c r="L41" t="n">
-        <v>2181.65</v>
+        <v>2090.63</v>
       </c>
       <c r="M41" t="n">
-        <v>2266.29</v>
+        <v>2170.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2350.92</v>
+        <v>2250.78</v>
       </c>
       <c r="O41" t="n">
-        <v>2651.59</v>
+        <v>2301.38</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3947,12 +3931,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3974,63 +3960,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2097.99</v>
+        <v>2004.24</v>
       </c>
       <c r="C42" t="n">
-        <v>2138.41</v>
+        <v>2017.61</v>
       </c>
       <c r="D42" t="n">
-        <v>1966.28</v>
+        <v>1506.51</v>
       </c>
       <c r="E42" t="n">
-        <v>2004.34</v>
+        <v>1686.4</v>
       </c>
       <c r="F42" t="n">
-        <v>-93.65000000000001</v>
+        <v>-317.95</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0446</v>
+        <v>-0.1586</v>
       </c>
       <c r="H42" t="n">
-        <v>172.13</v>
+        <v>511.1</v>
       </c>
       <c r="I42" t="n">
-        <v>1865.14</v>
+        <v>1794.15</v>
       </c>
       <c r="J42" t="n">
-        <v>1959.95</v>
+        <v>1808.21</v>
       </c>
       <c r="K42" t="n">
-        <v>2025.29</v>
+        <v>1918.28</v>
       </c>
       <c r="L42" t="n">
-        <v>2090.63</v>
+        <v>2028.34</v>
       </c>
       <c r="M42" t="n">
-        <v>2170.7</v>
+        <v>2090.41</v>
       </c>
       <c r="N42" t="n">
-        <v>2250.78</v>
+        <v>2152.47</v>
       </c>
       <c r="O42" t="n">
-        <v>2301.38</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>2310.54</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4054,69 +4044,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2004.24</v>
+        <v>1686.25</v>
       </c>
       <c r="C43" t="n">
-        <v>2017.61</v>
+        <v>1729.35</v>
       </c>
       <c r="D43" t="n">
-        <v>1506.51</v>
+        <v>1603.83</v>
       </c>
       <c r="E43" t="n">
-        <v>1686.4</v>
+        <v>1724.61</v>
       </c>
       <c r="F43" t="n">
-        <v>-317.95</v>
+        <v>38.22</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.1586</v>
+        <v>0.0227</v>
       </c>
       <c r="H43" t="n">
-        <v>511.1</v>
+        <v>125.53</v>
       </c>
       <c r="I43" t="n">
-        <v>1794.15</v>
+        <v>995.4</v>
       </c>
       <c r="J43" t="n">
-        <v>1808.21</v>
+        <v>1137.46</v>
       </c>
       <c r="K43" t="n">
-        <v>1918.28</v>
+        <v>1430.85</v>
       </c>
       <c r="L43" t="n">
-        <v>2028.34</v>
+        <v>1724.23</v>
       </c>
       <c r="M43" t="n">
-        <v>2090.41</v>
+        <v>1941.95</v>
       </c>
       <c r="N43" t="n">
-        <v>2152.47</v>
+        <v>2159.67</v>
       </c>
       <c r="O43" t="n">
-        <v>2310.54</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>2528.71</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4133,55 +4117,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1686.25</v>
+        <v>1724.57</v>
       </c>
       <c r="C44" t="n">
-        <v>1729.35</v>
+        <v>1847.77</v>
       </c>
       <c r="D44" t="n">
-        <v>1603.83</v>
+        <v>1670.1</v>
       </c>
       <c r="E44" t="n">
-        <v>1724.61</v>
+        <v>1704.58</v>
       </c>
       <c r="F44" t="n">
-        <v>38.22</v>
+        <v>-20.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0227</v>
+        <v>-0.0116</v>
       </c>
       <c r="H44" t="n">
-        <v>125.53</v>
+        <v>177.67</v>
       </c>
       <c r="I44" t="n">
-        <v>995.4</v>
+        <v>1478.3</v>
       </c>
       <c r="J44" t="n">
-        <v>1137.46</v>
+        <v>1628.1</v>
       </c>
       <c r="K44" t="n">
-        <v>1430.85</v>
+        <v>1661.85</v>
       </c>
       <c r="L44" t="n">
-        <v>1724.23</v>
+        <v>1695.6</v>
       </c>
       <c r="M44" t="n">
-        <v>1941.95</v>
+        <v>1787.38</v>
       </c>
       <c r="N44" t="n">
-        <v>2159.67</v>
+        <v>1879.15</v>
       </c>
       <c r="O44" t="n">
-        <v>2528.71</v>
+        <v>1854.88</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4192,13 +4180,15 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4220,50 +4210,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1724.57</v>
+        <v>1704.63</v>
       </c>
       <c r="C45" t="n">
-        <v>1847.77</v>
+        <v>1776.83</v>
       </c>
       <c r="D45" t="n">
-        <v>1670.1</v>
+        <v>1510.51</v>
       </c>
       <c r="E45" t="n">
-        <v>1704.58</v>
+        <v>1570.36</v>
       </c>
       <c r="F45" t="n">
-        <v>-20.03</v>
+        <v>-134.22</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>177.67</v>
+        <v>266.33</v>
       </c>
       <c r="I45" t="n">
-        <v>1478.3</v>
+        <v>1492.44</v>
       </c>
       <c r="J45" t="n">
-        <v>1628.1</v>
+        <v>1499.74</v>
       </c>
       <c r="K45" t="n">
-        <v>1661.85</v>
+        <v>1615.75</v>
       </c>
       <c r="L45" t="n">
-        <v>1695.6</v>
+        <v>1731.76</v>
       </c>
       <c r="M45" t="n">
-        <v>1787.38</v>
+        <v>1793.41</v>
       </c>
       <c r="N45" t="n">
-        <v>1879.15</v>
+        <v>1855.07</v>
       </c>
       <c r="O45" t="n">
-        <v>1854.88</v>
+        <v>2025.44</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4271,18 +4261,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4295,59 +4285,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1704.63</v>
+        <v>1569.99</v>
       </c>
       <c r="C46" t="n">
-        <v>1776.83</v>
+        <v>1805.91</v>
       </c>
       <c r="D46" t="n">
-        <v>1510.51</v>
+        <v>1549.25</v>
       </c>
       <c r="E46" t="n">
-        <v>1570.36</v>
+        <v>1783.01</v>
       </c>
       <c r="F46" t="n">
-        <v>-134.22</v>
+        <v>212.64</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.1354</v>
       </c>
       <c r="H46" t="n">
-        <v>266.33</v>
+        <v>256.66</v>
       </c>
       <c r="I46" t="n">
-        <v>1492.44</v>
+        <v>1244.18</v>
       </c>
       <c r="J46" t="n">
-        <v>1499.74</v>
+        <v>1267.38</v>
       </c>
       <c r="K46" t="n">
-        <v>1615.75</v>
+        <v>1437.2</v>
       </c>
       <c r="L46" t="n">
-        <v>1731.76</v>
+        <v>1607.02</v>
       </c>
       <c r="M46" t="n">
-        <v>1793.41</v>
+        <v>1703.52</v>
       </c>
       <c r="N46" t="n">
-        <v>1855.07</v>
+        <v>1800.03</v>
       </c>
       <c r="O46" t="n">
-        <v>2025.44</v>
+        <v>2043.16</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4355,22 +4341,24 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4379,55 +4367,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1569.99</v>
+        <v>1783</v>
       </c>
       <c r="C47" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D47" t="n">
-        <v>1549.25</v>
+        <v>1711.9</v>
       </c>
       <c r="E47" t="n">
-        <v>1783.01</v>
+        <v>1805.79</v>
       </c>
       <c r="F47" t="n">
-        <v>212.64</v>
+        <v>22.78</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.1354</v>
+        <v>0.0128</v>
       </c>
       <c r="H47" t="n">
-        <v>256.66</v>
+        <v>117.61</v>
       </c>
       <c r="I47" t="n">
-        <v>1244.18</v>
+        <v>1292.59</v>
       </c>
       <c r="J47" t="n">
-        <v>1267.38</v>
+        <v>1579.06</v>
       </c>
       <c r="K47" t="n">
-        <v>1437.2</v>
+        <v>1654.67</v>
       </c>
       <c r="L47" t="n">
-        <v>1607.02</v>
+        <v>1730.29</v>
       </c>
       <c r="M47" t="n">
-        <v>1703.52</v>
+        <v>1911.34</v>
       </c>
       <c r="N47" t="n">
-        <v>1800.03</v>
+        <v>2092.38</v>
       </c>
       <c r="O47" t="n">
-        <v>2043.16</v>
+        <v>2062.58</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4438,20 +4430,16 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4470,50 +4458,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1783</v>
+        <v>1805.76</v>
       </c>
       <c r="C48" t="n">
-        <v>1829.51</v>
+        <v>1944.16</v>
       </c>
       <c r="D48" t="n">
-        <v>1711.9</v>
+        <v>1749.35</v>
       </c>
       <c r="E48" t="n">
-        <v>1805.79</v>
+        <v>1871.51</v>
       </c>
       <c r="F48" t="n">
-        <v>22.78</v>
+        <v>65.72</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0364</v>
       </c>
       <c r="H48" t="n">
-        <v>117.61</v>
+        <v>194.81</v>
       </c>
       <c r="I48" t="n">
-        <v>1292.59</v>
+        <v>1594.29</v>
       </c>
       <c r="J48" t="n">
-        <v>1579.06</v>
+        <v>1705.72</v>
       </c>
       <c r="K48" t="n">
-        <v>1654.67</v>
+        <v>1746.98</v>
       </c>
       <c r="L48" t="n">
-        <v>1730.29</v>
+        <v>1788.25</v>
       </c>
       <c r="M48" t="n">
-        <v>1911.34</v>
+        <v>1864.59</v>
       </c>
       <c r="N48" t="n">
-        <v>2092.38</v>
+        <v>1940.94</v>
       </c>
       <c r="O48" t="n">
-        <v>2062.58</v>
+        <v>1947.13</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4524,16 +4512,20 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4552,50 +4544,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1805.76</v>
+        <v>1871.28</v>
       </c>
       <c r="C49" t="n">
-        <v>1944.16</v>
+        <v>1963.25</v>
       </c>
       <c r="D49" t="n">
-        <v>1749.35</v>
+        <v>1842.82</v>
       </c>
       <c r="E49" t="n">
-        <v>1871.51</v>
+        <v>1953.41</v>
       </c>
       <c r="F49" t="n">
-        <v>65.72</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0364</v>
+        <v>0.0438</v>
       </c>
       <c r="H49" t="n">
-        <v>194.81</v>
+        <v>120.43</v>
       </c>
       <c r="I49" t="n">
-        <v>1594.29</v>
+        <v>1554.53</v>
       </c>
       <c r="J49" t="n">
-        <v>1705.72</v>
+        <v>1689.07</v>
       </c>
       <c r="K49" t="n">
-        <v>1746.98</v>
+        <v>1774.1</v>
       </c>
       <c r="L49" t="n">
-        <v>1788.25</v>
+        <v>1859.13</v>
       </c>
       <c r="M49" t="n">
-        <v>1864.59</v>
+        <v>1968.92</v>
       </c>
       <c r="N49" t="n">
-        <v>1940.94</v>
+        <v>2078.7</v>
       </c>
       <c r="O49" t="n">
-        <v>1947.13</v>
+        <v>2138.97</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4606,7 +4598,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4616,10 +4608,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4638,69 +4628,71 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1871.28</v>
+        <v>1953.41</v>
       </c>
       <c r="C50" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D50" t="n">
-        <v>1842.82</v>
+        <v>1821.49</v>
       </c>
       <c r="E50" t="n">
-        <v>1953.41</v>
+        <v>1882.52</v>
       </c>
       <c r="F50" t="n">
-        <v>81.90000000000001</v>
+        <v>-70.89</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0363</v>
       </c>
       <c r="H50" t="n">
-        <v>120.43</v>
+        <v>154.98</v>
       </c>
       <c r="I50" t="n">
-        <v>1554.53</v>
+        <v>1722.39</v>
       </c>
       <c r="J50" t="n">
-        <v>1689.07</v>
+        <v>1858.17</v>
       </c>
       <c r="K50" t="n">
-        <v>1774.1</v>
+        <v>1893.2</v>
       </c>
       <c r="L50" t="n">
-        <v>1859.13</v>
+        <v>1928.22</v>
       </c>
       <c r="M50" t="n">
-        <v>1968.92</v>
+        <v>2013.63</v>
       </c>
       <c r="N50" t="n">
-        <v>2078.7</v>
+        <v>2099.03</v>
       </c>
       <c r="O50" t="n">
-        <v>2138.97</v>
+        <v>2083.68</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4715,74 +4707,70 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1953.41</v>
+        <v>1882.78</v>
       </c>
       <c r="C51" t="n">
-        <v>1976.46</v>
+        <v>1937.17</v>
       </c>
       <c r="D51" t="n">
-        <v>1821.49</v>
+        <v>1827.7</v>
       </c>
       <c r="E51" t="n">
-        <v>1882.52</v>
+        <v>1908.68</v>
       </c>
       <c r="F51" t="n">
-        <v>-70.89</v>
+        <v>26.16</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0363</v>
+        <v>0.0139</v>
       </c>
       <c r="H51" t="n">
-        <v>154.98</v>
+        <v>109.47</v>
       </c>
       <c r="I51" t="n">
-        <v>1722.39</v>
+        <v>1666.51</v>
       </c>
       <c r="J51" t="n">
-        <v>1858.17</v>
+        <v>1719.32</v>
       </c>
       <c r="K51" t="n">
-        <v>1893.2</v>
+        <v>1805.03</v>
       </c>
       <c r="L51" t="n">
-        <v>1928.22</v>
+        <v>1890.75</v>
       </c>
       <c r="M51" t="n">
-        <v>2013.63</v>
+        <v>1960.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2099.03</v>
+        <v>2029.27</v>
       </c>
       <c r="O51" t="n">
-        <v>2083.68</v>
+        <v>2131.44</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4801,57 +4789,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1882.78</v>
+        <v>1908.72</v>
       </c>
       <c r="C52" t="n">
-        <v>1937.17</v>
+        <v>1928.99</v>
       </c>
       <c r="D52" t="n">
-        <v>1827.7</v>
+        <v>1852.84</v>
       </c>
       <c r="E52" t="n">
-        <v>1908.68</v>
+        <v>1873.94</v>
       </c>
       <c r="F52" t="n">
-        <v>26.16</v>
+        <v>-34.74</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0182</v>
       </c>
       <c r="H52" t="n">
-        <v>109.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>1666.51</v>
+        <v>1718.23</v>
       </c>
       <c r="J52" t="n">
-        <v>1719.32</v>
+        <v>1812.34</v>
       </c>
       <c r="K52" t="n">
-        <v>1805.03</v>
+        <v>1853.95</v>
       </c>
       <c r="L52" t="n">
-        <v>1890.75</v>
+        <v>1895.56</v>
       </c>
       <c r="M52" t="n">
-        <v>1960.01</v>
+        <v>1963.42</v>
       </c>
       <c r="N52" t="n">
-        <v>2029.27</v>
+        <v>2031.28</v>
       </c>
       <c r="O52" t="n">
-        <v>2131.44</v>
+        <v>2046.64</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4859,12 +4847,14 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4883,57 +4873,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1908.72</v>
+        <v>1873.97</v>
       </c>
       <c r="C53" t="n">
-        <v>1928.99</v>
+        <v>2545.88</v>
       </c>
       <c r="D53" t="n">
-        <v>1852.84</v>
+        <v>1870.75</v>
       </c>
       <c r="E53" t="n">
-        <v>1873.94</v>
+        <v>2463.82</v>
       </c>
       <c r="F53" t="n">
-        <v>-34.74</v>
+        <v>589.87</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.3148</v>
       </c>
       <c r="H53" t="n">
-        <v>76.15000000000001</v>
+        <v>675.13</v>
       </c>
       <c r="I53" t="n">
-        <v>1718.23</v>
+        <v>1776.69</v>
       </c>
       <c r="J53" t="n">
-        <v>1812.34</v>
+        <v>1789.3</v>
       </c>
       <c r="K53" t="n">
-        <v>1853.95</v>
+        <v>1835.87</v>
       </c>
       <c r="L53" t="n">
-        <v>1895.56</v>
+        <v>1882.43</v>
       </c>
       <c r="M53" t="n">
-        <v>1963.42</v>
+        <v>1912.02</v>
       </c>
       <c r="N53" t="n">
-        <v>2031.28</v>
+        <v>1941.61</v>
       </c>
       <c r="O53" t="n">
-        <v>2046.64</v>
+        <v>2005.15</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4941,83 +4931,83 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1873.97</v>
+        <v>2463.64</v>
       </c>
       <c r="C54" t="n">
-        <v>2545.88</v>
+        <v>2564.27</v>
       </c>
       <c r="D54" t="n">
-        <v>1870.75</v>
+        <v>2389.47</v>
       </c>
       <c r="E54" t="n">
-        <v>2463.82</v>
+        <v>2417.94</v>
       </c>
       <c r="F54" t="n">
-        <v>589.87</v>
+        <v>-45.88</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.3148</v>
+        <v>-0.0186</v>
       </c>
       <c r="H54" t="n">
-        <v>675.13</v>
+        <v>174.81</v>
       </c>
       <c r="I54" t="n">
-        <v>1776.69</v>
+        <v>1195.61</v>
       </c>
       <c r="J54" t="n">
-        <v>1789.3</v>
+        <v>1916.43</v>
       </c>
       <c r="K54" t="n">
-        <v>1835.87</v>
+        <v>2126.25</v>
       </c>
       <c r="L54" t="n">
-        <v>1882.43</v>
+        <v>2336.07</v>
       </c>
       <c r="M54" t="n">
-        <v>1912.02</v>
+        <v>2801.38</v>
       </c>
       <c r="N54" t="n">
-        <v>1941.61</v>
+        <v>3266.7</v>
       </c>
       <c r="O54" t="n">
-        <v>2005.15</v>
+        <v>3221.01</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5028,80 +5018,78 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2463.64</v>
+        <v>2417.9</v>
       </c>
       <c r="C55" t="n">
-        <v>2564.27</v>
+        <v>2545.62</v>
       </c>
       <c r="D55" t="n">
-        <v>2389.47</v>
+        <v>2356.19</v>
       </c>
       <c r="E55" t="n">
-        <v>2417.94</v>
+        <v>2514.55</v>
       </c>
       <c r="F55" t="n">
-        <v>-45.88</v>
+        <v>96.61</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0186</v>
+        <v>0.04</v>
       </c>
       <c r="H55" t="n">
-        <v>174.81</v>
+        <v>189.44</v>
       </c>
       <c r="I55" t="n">
-        <v>1195.61</v>
+        <v>2214.66</v>
       </c>
       <c r="J55" t="n">
-        <v>1916.43</v>
+        <v>2213.67</v>
       </c>
       <c r="K55" t="n">
-        <v>2126.25</v>
+        <v>2330.54</v>
       </c>
       <c r="L55" t="n">
-        <v>2336.07</v>
+        <v>2447.41</v>
       </c>
       <c r="M55" t="n">
-        <v>2801.38</v>
+        <v>2505.34</v>
       </c>
       <c r="N55" t="n">
-        <v>3266.7</v>
+        <v>2563.28</v>
       </c>
       <c r="O55" t="n">
-        <v>3221.01</v>
+        <v>2739.08</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5112,13 +5100,15 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5133,57 +5123,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2417.9</v>
+        <v>2514.58</v>
       </c>
       <c r="C56" t="n">
-        <v>2545.62</v>
+        <v>2663.05</v>
       </c>
       <c r="D56" t="n">
-        <v>2356.19</v>
+        <v>2406.91</v>
       </c>
       <c r="E56" t="n">
-        <v>2514.55</v>
+        <v>2477.02</v>
       </c>
       <c r="F56" t="n">
-        <v>96.61</v>
+        <v>-37.53</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.0149</v>
       </c>
       <c r="H56" t="n">
-        <v>189.44</v>
+        <v>256.14</v>
       </c>
       <c r="I56" t="n">
-        <v>2214.66</v>
+        <v>2166.75</v>
       </c>
       <c r="J56" t="n">
-        <v>2213.67</v>
+        <v>2356.93</v>
       </c>
       <c r="K56" t="n">
-        <v>2330.54</v>
+        <v>2419.83</v>
       </c>
       <c r="L56" t="n">
-        <v>2447.41</v>
+        <v>2482.73</v>
       </c>
       <c r="M56" t="n">
-        <v>2505.34</v>
+        <v>2609.27</v>
       </c>
       <c r="N56" t="n">
-        <v>2563.28</v>
+        <v>2735.81</v>
       </c>
       <c r="O56" t="n">
-        <v>2739.08</v>
+        <v>2735.06</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5191,17 +5181,19 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5217,57 +5209,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2514.58</v>
+        <v>2476.6</v>
       </c>
       <c r="C57" t="n">
-        <v>2663.05</v>
+        <v>2659.72</v>
       </c>
       <c r="D57" t="n">
-        <v>2406.91</v>
+        <v>2357.96</v>
       </c>
       <c r="E57" t="n">
-        <v>2477.02</v>
+        <v>2643</v>
       </c>
       <c r="F57" t="n">
-        <v>-37.53</v>
+        <v>165.98</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.067</v>
       </c>
       <c r="H57" t="n">
-        <v>256.14</v>
+        <v>301.76</v>
       </c>
       <c r="I57" t="n">
-        <v>2166.75</v>
+        <v>2150.76</v>
       </c>
       <c r="J57" t="n">
-        <v>2356.93</v>
+        <v>2191.9</v>
       </c>
       <c r="K57" t="n">
-        <v>2419.83</v>
+        <v>2348.95</v>
       </c>
       <c r="L57" t="n">
-        <v>2482.73</v>
+        <v>2506</v>
       </c>
       <c r="M57" t="n">
-        <v>2609.27</v>
+        <v>2605.09</v>
       </c>
       <c r="N57" t="n">
-        <v>2735.81</v>
+        <v>2704.19</v>
       </c>
       <c r="O57" t="n">
-        <v>2735.06</v>
+        <v>2919.19</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5275,19 +5267,17 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5303,57 +5293,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2476.6</v>
+        <v>2644.8</v>
       </c>
       <c r="C58" t="n">
-        <v>2659.72</v>
+        <v>2804.96</v>
       </c>
       <c r="D58" t="n">
-        <v>2357.96</v>
+        <v>2644.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2644.05</v>
+        <v>2770.86</v>
       </c>
       <c r="F58" t="n">
-        <v>167.03</v>
+        <v>127.86</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0674</v>
+        <v>0.0484</v>
       </c>
       <c r="H58" t="n">
-        <v>301.76</v>
+        <v>160.17</v>
       </c>
       <c r="I58" t="n">
-        <v>2150.76</v>
+        <v>2056.2</v>
       </c>
       <c r="J58" t="n">
-        <v>2191.9</v>
+        <v>2408.32</v>
       </c>
       <c r="K58" t="n">
-        <v>2348.95</v>
+        <v>2492.12</v>
       </c>
       <c r="L58" t="n">
-        <v>2506</v>
+        <v>2575.92</v>
       </c>
       <c r="M58" t="n">
-        <v>2605.09</v>
+        <v>2793.88</v>
       </c>
       <c r="N58" t="n">
-        <v>2704.19</v>
+        <v>3011.84</v>
       </c>
       <c r="O58" t="n">
-        <v>2919.19</v>
+        <v>2961.48</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5364,7 +5354,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5385,11 +5375,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5304,25 +5304,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2644.8</v>
+        <v>2642.78</v>
       </c>
       <c r="C58" t="n">
-        <v>2804.96</v>
+        <v>2805.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2644.8</v>
+        <v>2642.78</v>
       </c>
       <c r="E58" t="n">
-        <v>2770.86</v>
+        <v>2752.99</v>
       </c>
       <c r="F58" t="n">
-        <v>127.86</v>
+        <v>109.99</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0416</v>
       </c>
       <c r="H58" t="n">
-        <v>160.17</v>
+        <v>162.72</v>
       </c>
       <c r="I58" t="n">
         <v>2056.2</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>2642.78</v>
       </c>
       <c r="E58" t="n">
-        <v>2752.99</v>
+        <v>2739.44</v>
       </c>
       <c r="F58" t="n">
-        <v>109.99</v>
+        <v>96.44</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0416</v>
+        <v>0.0365</v>
       </c>
       <c r="H58" t="n">
         <v>162.72</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>2642.78</v>
       </c>
       <c r="E58" t="n">
-        <v>2739.44</v>
+        <v>2756.74</v>
       </c>
       <c r="F58" t="n">
-        <v>96.44</v>
+        <v>113.74</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0365</v>
+        <v>0.043</v>
       </c>
       <c r="H58" t="n">
         <v>162.72</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>2642.78</v>
       </c>
       <c r="E58" t="n">
-        <v>2756.74</v>
+        <v>2746.42</v>
       </c>
       <c r="F58" t="n">
-        <v>113.74</v>
+        <v>103.42</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.043</v>
+        <v>0.0391</v>
       </c>
       <c r="H58" t="n">
         <v>162.72</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>2642.78</v>
       </c>
       <c r="E58" t="n">
-        <v>2746.42</v>
+        <v>2759.37</v>
       </c>
       <c r="F58" t="n">
-        <v>103.42</v>
+        <v>116.37</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0391</v>
+        <v>0.044</v>
       </c>
       <c r="H58" t="n">
         <v>162.72</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>2642.78</v>
       </c>
       <c r="E58" t="n">
-        <v>2759.37</v>
+        <v>2768.48</v>
       </c>
       <c r="F58" t="n">
-        <v>116.37</v>
+        <v>125.48</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.044</v>
+        <v>0.0475</v>
       </c>
       <c r="H58" t="n">
         <v>162.72</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>2642.78</v>
       </c>
       <c r="E58" t="n">
-        <v>2768.48</v>
+        <v>2712.68</v>
       </c>
       <c r="F58" t="n">
-        <v>125.48</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0475</v>
+        <v>0.0264</v>
       </c>
       <c r="H58" t="n">
         <v>162.72</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5313,13 +5313,13 @@
         <v>2642.78</v>
       </c>
       <c r="E58" t="n">
-        <v>2712.68</v>
+        <v>2688.5</v>
       </c>
       <c r="F58" t="n">
-        <v>69.68000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0264</v>
+        <v>0.0172</v>
       </c>
       <c r="H58" t="n">
         <v>162.72</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>532.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3176.2</v>
+        <v>3457.82</v>
       </c>
       <c r="J2" t="n">
-        <v>4026.03</v>
+        <v>4131.64</v>
       </c>
       <c r="K2" t="n">
-        <v>4335.26</v>
+        <v>4405.67</v>
       </c>
       <c r="L2" t="n">
-        <v>4644.5</v>
+        <v>4679.7</v>
       </c>
       <c r="M2" t="n">
-        <v>5224.03</v>
+        <v>5153.63</v>
       </c>
       <c r="N2" t="n">
-        <v>5803.56</v>
+        <v>5627.55</v>
       </c>
       <c r="O2" t="n">
-        <v>5842.5</v>
+        <v>5701.69</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5310,19 +5310,19 @@
         <v>2805.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2642.78</v>
+        <v>2635.16</v>
       </c>
       <c r="E58" t="n">
-        <v>2688.5</v>
+        <v>2685.44</v>
       </c>
       <c r="F58" t="n">
-        <v>45.5</v>
+        <v>42.44</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0161</v>
       </c>
       <c r="H58" t="n">
-        <v>162.72</v>
+        <v>170.34</v>
       </c>
       <c r="I58" t="n">
         <v>2056.2</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,35 +659,39 @@
         <v>532.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3457.82</v>
+        <v>4475.21</v>
       </c>
       <c r="J2" t="n">
-        <v>4131.64</v>
+        <v>4513.16</v>
       </c>
       <c r="K2" t="n">
-        <v>4405.67</v>
+        <v>4660.02</v>
       </c>
       <c r="L2" t="n">
-        <v>4679.7</v>
+        <v>4806.88</v>
       </c>
       <c r="M2" t="n">
-        <v>5153.63</v>
+        <v>4899.28</v>
       </c>
       <c r="N2" t="n">
-        <v>5627.55</v>
+        <v>4991.68</v>
       </c>
       <c r="O2" t="n">
-        <v>5701.69</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>5192.99</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -706,14 +710,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -788,14 +788,10 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -874,7 +870,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -954,7 +950,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1042,7 +1038,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1122,7 +1118,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1210,7 +1206,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1292,7 +1288,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1376,7 +1372,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1462,7 +1458,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1550,7 +1546,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1630,7 +1626,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1710,7 +1706,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1790,7 +1786,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1876,7 +1872,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1960,7 +1956,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2044,7 +2040,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2122,7 +2118,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2208,7 +2204,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2288,7 +2284,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2374,7 +2370,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2458,7 +2454,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2540,7 +2536,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2620,7 +2616,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2698,7 +2694,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2780,7 +2776,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2870,7 +2866,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2954,7 +2950,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3040,7 +3036,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3122,7 +3118,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3206,7 +3202,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3290,7 +3286,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3376,7 +3372,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3458,7 +3454,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3538,7 +3534,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3624,7 +3620,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3708,7 +3704,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3792,7 +3788,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3870,7 +3866,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3950,7 +3946,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4034,7 +4030,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4112,7 +4108,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4196,7 +4192,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4280,7 +4276,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4362,7 +4358,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4444,7 +4440,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4530,7 +4526,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4614,7 +4610,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4700,7 +4696,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4782,7 +4778,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4866,7 +4862,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4954,7 +4950,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5032,7 +5028,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5116,7 +5112,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5202,7 +5198,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5286,7 +5282,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5310,19 +5306,19 @@
         <v>2805.5</v>
       </c>
       <c r="D58" t="n">
-        <v>2635.16</v>
+        <v>2628.69</v>
       </c>
       <c r="E58" t="n">
-        <v>2685.44</v>
+        <v>2673</v>
       </c>
       <c r="F58" t="n">
-        <v>42.44</v>
+        <v>30</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0161</v>
+        <v>0.0114</v>
       </c>
       <c r="H58" t="n">
-        <v>170.34</v>
+        <v>176.81</v>
       </c>
       <c r="I58" t="n">
         <v>2056.2</v>
@@ -5356,12 +5352,12 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5370,7 +5366,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,69 +634,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4779.77</v>
+        <v>4389.63</v>
       </c>
       <c r="C2" t="n">
-        <v>4796.35</v>
+        <v>4490.35</v>
       </c>
       <c r="D2" t="n">
-        <v>4264.2</v>
+        <v>4221.25</v>
       </c>
       <c r="E2" t="n">
-        <v>4390.02</v>
+        <v>4305.35</v>
       </c>
       <c r="F2" t="n">
-        <v>-389.63</v>
+        <v>-84.67</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0815</v>
+        <v>-0.0193</v>
       </c>
       <c r="H2" t="n">
-        <v>532.15</v>
+        <v>269.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4475.21</v>
+        <v>3732.04</v>
       </c>
       <c r="J2" t="n">
-        <v>4513.16</v>
+        <v>3787.74</v>
       </c>
       <c r="K2" t="n">
-        <v>4660.02</v>
+        <v>4123.94</v>
       </c>
       <c r="L2" t="n">
-        <v>4806.88</v>
+        <v>4460.15</v>
       </c>
       <c r="M2" t="n">
-        <v>4899.28</v>
+        <v>4656.1</v>
       </c>
       <c r="N2" t="n">
-        <v>4991.68</v>
+        <v>4852.05</v>
       </c>
       <c r="O2" t="n">
-        <v>5192.99</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>5328.5</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -710,58 +704,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4389.63</v>
+        <v>4305.38</v>
       </c>
       <c r="C3" t="n">
-        <v>4490.35</v>
+        <v>4763.36</v>
       </c>
       <c r="D3" t="n">
-        <v>4221.25</v>
+        <v>4277.85</v>
       </c>
       <c r="E3" t="n">
-        <v>4305.35</v>
+        <v>4609.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-84.67</v>
+        <v>304.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0193</v>
+        <v>0.0707</v>
       </c>
       <c r="H3" t="n">
-        <v>269.1</v>
+        <v>485.51</v>
       </c>
       <c r="I3" t="n">
-        <v>3732.04</v>
+        <v>3952.15</v>
       </c>
       <c r="J3" t="n">
-        <v>3787.74</v>
+        <v>4011.02</v>
       </c>
       <c r="K3" t="n">
-        <v>4123.94</v>
+        <v>4170.8</v>
       </c>
       <c r="L3" t="n">
-        <v>4460.15</v>
+        <v>4330.57</v>
       </c>
       <c r="M3" t="n">
-        <v>4656.1</v>
+        <v>4439.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4852.05</v>
+        <v>4549.22</v>
       </c>
       <c r="O3" t="n">
-        <v>5328.5</v>
+        <v>4759.45</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,23 +770,29 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -796,50 +800,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4305.38</v>
+        <v>4609.72</v>
       </c>
       <c r="C4" t="n">
-        <v>4763.36</v>
+        <v>4670.53</v>
       </c>
       <c r="D4" t="n">
-        <v>4277.85</v>
+        <v>4428.33</v>
       </c>
       <c r="E4" t="n">
-        <v>4609.6</v>
+        <v>4451.33</v>
       </c>
       <c r="F4" t="n">
-        <v>304.25</v>
+        <v>-158.27</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0707</v>
+        <v>-0.0343</v>
       </c>
       <c r="H4" t="n">
-        <v>485.51</v>
+        <v>242.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3952.15</v>
+        <v>3792.34</v>
       </c>
       <c r="J4" t="n">
-        <v>4011.02</v>
+        <v>4168.58</v>
       </c>
       <c r="K4" t="n">
-        <v>4170.8</v>
+        <v>4366.84</v>
       </c>
       <c r="L4" t="n">
-        <v>4330.57</v>
+        <v>4565.1</v>
       </c>
       <c r="M4" t="n">
-        <v>4439.9</v>
+        <v>4852.35</v>
       </c>
       <c r="N4" t="n">
-        <v>4549.22</v>
+        <v>5139.6</v>
       </c>
       <c r="O4" t="n">
-        <v>4759.45</v>
+        <v>5248.87</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,93 +851,97 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4609.72</v>
+        <v>4451.58</v>
       </c>
       <c r="C5" t="n">
-        <v>4670.53</v>
+        <v>4457.08</v>
       </c>
       <c r="D5" t="n">
-        <v>4428.33</v>
+        <v>3829.01</v>
       </c>
       <c r="E5" t="n">
-        <v>4451.33</v>
+        <v>4141.48</v>
       </c>
       <c r="F5" t="n">
-        <v>-158.27</v>
+        <v>-309.85</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0343</v>
+        <v>-0.0696</v>
       </c>
       <c r="H5" t="n">
-        <v>242.2</v>
+        <v>628.0700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>3792.34</v>
+        <v>4186.13</v>
       </c>
       <c r="J5" t="n">
-        <v>4168.58</v>
+        <v>4160.08</v>
       </c>
       <c r="K5" t="n">
-        <v>4366.84</v>
+        <v>4330.23</v>
       </c>
       <c r="L5" t="n">
-        <v>4565.1</v>
+        <v>4500.38</v>
       </c>
       <c r="M5" t="n">
-        <v>4852.35</v>
+        <v>4572.43</v>
       </c>
       <c r="N5" t="n">
-        <v>5139.6</v>
+        <v>4644.48</v>
       </c>
       <c r="O5" t="n">
-        <v>5248.87</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+        <v>4912.73</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
@@ -952,249 +960,243 @@
       </c>
       <c r="W5" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4451.58</v>
+        <v>4141.36</v>
       </c>
       <c r="C6" t="n">
-        <v>4457.08</v>
+        <v>4616.53</v>
       </c>
       <c r="D6" t="n">
-        <v>3829.01</v>
+        <v>4087.93</v>
       </c>
       <c r="E6" t="n">
-        <v>4141.48</v>
+        <v>4515.42</v>
       </c>
       <c r="F6" t="n">
-        <v>-309.85</v>
+        <v>373.95</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0696</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>628.0700000000001</v>
+        <v>528.61</v>
       </c>
       <c r="I6" t="n">
-        <v>4186.13</v>
+        <v>3200.94</v>
       </c>
       <c r="J6" t="n">
-        <v>4160.08</v>
+        <v>3512.62</v>
       </c>
       <c r="K6" t="n">
-        <v>4330.23</v>
+        <v>3827.44</v>
       </c>
       <c r="L6" t="n">
-        <v>4500.38</v>
+        <v>4142.26</v>
       </c>
       <c r="M6" t="n">
-        <v>4572.43</v>
+        <v>4455.51</v>
       </c>
       <c r="N6" t="n">
-        <v>4644.48</v>
+        <v>4768.76</v>
       </c>
       <c r="O6" t="n">
-        <v>4912.73</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
+        <v>5085.15</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4141.36</v>
+        <v>4515.3</v>
       </c>
       <c r="C7" t="n">
-        <v>4616.53</v>
+        <v>4755.22</v>
       </c>
       <c r="D7" t="n">
-        <v>4087.93</v>
+        <v>3460.22</v>
       </c>
       <c r="E7" t="n">
-        <v>4515.42</v>
+        <v>4164.43</v>
       </c>
       <c r="F7" t="n">
-        <v>373.95</v>
+        <v>-351</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>528.61</v>
+        <v>1295</v>
       </c>
       <c r="I7" t="n">
-        <v>3200.94</v>
+        <v>3559.32</v>
       </c>
       <c r="J7" t="n">
-        <v>3512.62</v>
+        <v>4068.41</v>
       </c>
       <c r="K7" t="n">
-        <v>3827.44</v>
+        <v>4251.12</v>
       </c>
       <c r="L7" t="n">
-        <v>4142.26</v>
+        <v>4433.83</v>
       </c>
       <c r="M7" t="n">
-        <v>4455.51</v>
+        <v>4779.73</v>
       </c>
       <c r="N7" t="n">
-        <v>4768.76</v>
+        <v>5125.63</v>
       </c>
       <c r="O7" t="n">
-        <v>5085.15</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+        <v>5145.14</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4515.3</v>
+        <v>4164.05</v>
       </c>
       <c r="C8" t="n">
-        <v>4755.22</v>
+        <v>4292.85</v>
       </c>
       <c r="D8" t="n">
-        <v>3460.22</v>
+        <v>3678.62</v>
       </c>
       <c r="E8" t="n">
-        <v>4164.43</v>
+        <v>3984.65</v>
       </c>
       <c r="F8" t="n">
-        <v>-351</v>
+        <v>-179.78</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0432</v>
       </c>
       <c r="H8" t="n">
-        <v>1295</v>
+        <v>614.23</v>
       </c>
       <c r="I8" t="n">
-        <v>3559.32</v>
+        <v>2165.22</v>
       </c>
       <c r="J8" t="n">
-        <v>4068.41</v>
+        <v>2897.78</v>
       </c>
       <c r="K8" t="n">
-        <v>4251.12</v>
+        <v>3516.93</v>
       </c>
       <c r="L8" t="n">
-        <v>4433.83</v>
+        <v>4136.07</v>
       </c>
       <c r="M8" t="n">
-        <v>4779.73</v>
+        <v>4811.93</v>
       </c>
       <c r="N8" t="n">
-        <v>5125.63</v>
+        <v>5487.78</v>
       </c>
       <c r="O8" t="n">
-        <v>5145.14</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>6050.22</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1206,7 +1208,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1220,50 +1222,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4164.05</v>
+        <v>3984.7</v>
       </c>
       <c r="C9" t="n">
-        <v>4292.85</v>
+        <v>4177.31</v>
       </c>
       <c r="D9" t="n">
-        <v>3678.62</v>
+        <v>3718.08</v>
       </c>
       <c r="E9" t="n">
-        <v>3984.65</v>
+        <v>4157.99</v>
       </c>
       <c r="F9" t="n">
-        <v>-179.78</v>
+        <v>173.34</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0432</v>
+        <v>0.0435</v>
       </c>
       <c r="H9" t="n">
-        <v>614.23</v>
+        <v>459.23</v>
       </c>
       <c r="I9" t="n">
-        <v>2165.22</v>
+        <v>3064.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2897.78</v>
+        <v>3369.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3516.93</v>
+        <v>3677.54</v>
       </c>
       <c r="L9" t="n">
-        <v>4136.07</v>
+        <v>3985.19</v>
       </c>
       <c r="M9" t="n">
-        <v>4811.93</v>
+        <v>4291.76</v>
       </c>
       <c r="N9" t="n">
-        <v>5487.78</v>
+        <v>4598.33</v>
       </c>
       <c r="O9" t="n">
-        <v>6050.22</v>
+        <v>4907.07</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,13 +1276,15 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1288,151 +1292,155 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3984.7</v>
+        <v>4158.01</v>
       </c>
       <c r="C10" t="n">
-        <v>4177.31</v>
+        <v>4250.67</v>
       </c>
       <c r="D10" t="n">
-        <v>3718.08</v>
+        <v>3681.91</v>
       </c>
       <c r="E10" t="n">
-        <v>4157.99</v>
+        <v>3911.06</v>
       </c>
       <c r="F10" t="n">
-        <v>173.34</v>
+        <v>-246.93</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0435</v>
+        <v>-0.0594</v>
       </c>
       <c r="H10" t="n">
-        <v>459.23</v>
+        <v>568.76</v>
       </c>
       <c r="I10" t="n">
-        <v>3064.4</v>
+        <v>3258.84</v>
       </c>
       <c r="J10" t="n">
-        <v>3369.88</v>
+        <v>3803.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3677.54</v>
+        <v>3928.37</v>
       </c>
       <c r="L10" t="n">
-        <v>3985.19</v>
+        <v>4052.84</v>
       </c>
       <c r="M10" t="n">
-        <v>4291.76</v>
+        <v>4387.61</v>
       </c>
       <c r="N10" t="n">
-        <v>4598.33</v>
+        <v>4722.37</v>
       </c>
       <c r="O10" t="n">
-        <v>4907.07</v>
+        <v>4636.54</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4158.01</v>
+        <v>3911.75</v>
       </c>
       <c r="C11" t="n">
-        <v>4250.67</v>
+        <v>3912.63</v>
       </c>
       <c r="D11" t="n">
-        <v>3681.91</v>
+        <v>3063.09</v>
       </c>
       <c r="E11" t="n">
-        <v>3911.06</v>
+        <v>3582.62</v>
       </c>
       <c r="F11" t="n">
-        <v>-246.93</v>
+        <v>-328.44</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>568.76</v>
+        <v>849.55</v>
       </c>
       <c r="I11" t="n">
-        <v>3258.84</v>
+        <v>3113.15</v>
       </c>
       <c r="J11" t="n">
-        <v>3803.9</v>
+        <v>3314.69</v>
       </c>
       <c r="K11" t="n">
-        <v>3928.37</v>
+        <v>3626.68</v>
       </c>
       <c r="L11" t="n">
-        <v>4052.84</v>
+        <v>3938.68</v>
       </c>
       <c r="M11" t="n">
-        <v>4387.61</v>
+        <v>4195.44</v>
       </c>
       <c r="N11" t="n">
-        <v>4722.37</v>
+        <v>4452.21</v>
       </c>
       <c r="O11" t="n">
-        <v>4636.54</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
+        <v>4819.43</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
@@ -1458,74 +1466,66 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3911.75</v>
+        <v>3583.44</v>
       </c>
       <c r="C12" t="n">
-        <v>3912.63</v>
+        <v>3656.15</v>
       </c>
       <c r="D12" t="n">
-        <v>3063.09</v>
+        <v>3007.07</v>
       </c>
       <c r="E12" t="n">
-        <v>3582.62</v>
+        <v>3092.85</v>
       </c>
       <c r="F12" t="n">
-        <v>-328.44</v>
+        <v>-489.77</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1367</v>
       </c>
       <c r="H12" t="n">
-        <v>849.55</v>
+        <v>649.08</v>
       </c>
       <c r="I12" t="n">
-        <v>3113.15</v>
+        <v>2213.54</v>
       </c>
       <c r="J12" t="n">
-        <v>3314.69</v>
+        <v>2780.46</v>
       </c>
       <c r="K12" t="n">
-        <v>3626.68</v>
+        <v>3157.85</v>
       </c>
       <c r="L12" t="n">
-        <v>3938.68</v>
+        <v>3535.24</v>
       </c>
       <c r="M12" t="n">
-        <v>4195.44</v>
+        <v>4007.39</v>
       </c>
       <c r="N12" t="n">
-        <v>4452.21</v>
+        <v>4479.55</v>
       </c>
       <c r="O12" t="n">
-        <v>4819.43</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4762.18</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1556,50 +1556,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3583.44</v>
+        <v>3092.94</v>
       </c>
       <c r="C13" t="n">
-        <v>3656.15</v>
+        <v>3218.13</v>
       </c>
       <c r="D13" t="n">
-        <v>3007.07</v>
+        <v>2626.87</v>
       </c>
       <c r="E13" t="n">
-        <v>3092.85</v>
+        <v>2801.68</v>
       </c>
       <c r="F13" t="n">
-        <v>-489.77</v>
+        <v>-291.17</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.1367</v>
+        <v>-0.0941</v>
       </c>
       <c r="H13" t="n">
-        <v>649.08</v>
+        <v>591.26</v>
       </c>
       <c r="I13" t="n">
-        <v>2213.54</v>
+        <v>2358</v>
       </c>
       <c r="J13" t="n">
-        <v>2780.46</v>
+        <v>2324.39</v>
       </c>
       <c r="K13" t="n">
-        <v>3157.85</v>
+        <v>2768.31</v>
       </c>
       <c r="L13" t="n">
-        <v>3535.24</v>
+        <v>3212.23</v>
       </c>
       <c r="M13" t="n">
-        <v>4007.39</v>
+        <v>3417.39</v>
       </c>
       <c r="N13" t="n">
-        <v>4479.55</v>
+        <v>3622.54</v>
       </c>
       <c r="O13" t="n">
-        <v>4762.18</v>
+        <v>4305.23</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1626,7 +1626,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1636,50 +1636,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3092.94</v>
+        <v>2801.2</v>
       </c>
       <c r="C14" t="n">
-        <v>3218.13</v>
+        <v>3095.03</v>
       </c>
       <c r="D14" t="n">
-        <v>2626.87</v>
+        <v>2763.38</v>
       </c>
       <c r="E14" t="n">
-        <v>2801.68</v>
+        <v>2992.11</v>
       </c>
       <c r="F14" t="n">
-        <v>-291.17</v>
+        <v>190.44</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0941</v>
+        <v>0.068</v>
       </c>
       <c r="H14" t="n">
-        <v>591.26</v>
+        <v>331.66</v>
       </c>
       <c r="I14" t="n">
-        <v>2358</v>
+        <v>2035.61</v>
       </c>
       <c r="J14" t="n">
-        <v>2324.39</v>
+        <v>2150</v>
       </c>
       <c r="K14" t="n">
-        <v>2768.31</v>
+        <v>2506.05</v>
       </c>
       <c r="L14" t="n">
-        <v>3212.23</v>
+        <v>2862.09</v>
       </c>
       <c r="M14" t="n">
-        <v>3417.39</v>
+        <v>3097.31</v>
       </c>
       <c r="N14" t="n">
-        <v>3622.54</v>
+        <v>3332.52</v>
       </c>
       <c r="O14" t="n">
-        <v>4305.23</v>
+        <v>3809.39</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,79 +1687,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2801.2</v>
+        <v>2991.92</v>
       </c>
       <c r="C15" t="n">
-        <v>3095.03</v>
+        <v>3238.56</v>
       </c>
       <c r="D15" t="n">
-        <v>2763.38</v>
+        <v>2720.44</v>
       </c>
       <c r="E15" t="n">
-        <v>2992.11</v>
+        <v>3061.3</v>
       </c>
       <c r="F15" t="n">
-        <v>190.44</v>
+        <v>69.19</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.068</v>
+        <v>0.0231</v>
       </c>
       <c r="H15" t="n">
-        <v>331.66</v>
+        <v>518.12</v>
       </c>
       <c r="I15" t="n">
-        <v>2035.61</v>
+        <v>2431.72</v>
       </c>
       <c r="J15" t="n">
-        <v>2150</v>
+        <v>2691.91</v>
       </c>
       <c r="K15" t="n">
-        <v>2506.05</v>
+        <v>2826.28</v>
       </c>
       <c r="L15" t="n">
-        <v>2862.09</v>
+        <v>2960.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3097.31</v>
+        <v>3157.94</v>
       </c>
       <c r="N15" t="n">
-        <v>3332.52</v>
+        <v>3355.22</v>
       </c>
       <c r="O15" t="n">
-        <v>3809.39</v>
+        <v>3426.69</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,8 +1771,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
@@ -1786,7 +1792,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1800,50 +1806,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2991.92</v>
+        <v>3061.01</v>
       </c>
       <c r="C16" t="n">
-        <v>3238.56</v>
+        <v>3446.62</v>
       </c>
       <c r="D16" t="n">
-        <v>2720.44</v>
+        <v>3034.69</v>
       </c>
       <c r="E16" t="n">
-        <v>3061.3</v>
+        <v>3060.59</v>
       </c>
       <c r="F16" t="n">
-        <v>69.19</v>
+        <v>-0.71</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0231</v>
+        <v>-0.0002</v>
       </c>
       <c r="H16" t="n">
-        <v>518.12</v>
+        <v>411.93</v>
       </c>
       <c r="I16" t="n">
-        <v>2431.72</v>
+        <v>2202.32</v>
       </c>
       <c r="J16" t="n">
-        <v>2691.91</v>
+        <v>2584.09</v>
       </c>
       <c r="K16" t="n">
-        <v>2826.28</v>
+        <v>2802.24</v>
       </c>
       <c r="L16" t="n">
-        <v>2960.66</v>
+        <v>3020.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3157.94</v>
+        <v>3320.36</v>
       </c>
       <c r="N16" t="n">
-        <v>3355.22</v>
+        <v>3620.32</v>
       </c>
       <c r="O16" t="n">
-        <v>3426.69</v>
+        <v>3756.67</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1851,28 +1857,26 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1886,50 +1890,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3061.01</v>
+        <v>3060.48</v>
       </c>
       <c r="C17" t="n">
-        <v>3446.62</v>
+        <v>3175.12</v>
       </c>
       <c r="D17" t="n">
-        <v>3034.69</v>
+        <v>2777.12</v>
       </c>
       <c r="E17" t="n">
-        <v>3060.59</v>
+        <v>3001.61</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.71</v>
+        <v>-58.98</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H17" t="n">
-        <v>411.93</v>
+        <v>398</v>
       </c>
       <c r="I17" t="n">
-        <v>2202.32</v>
+        <v>2622.76</v>
       </c>
       <c r="J17" t="n">
-        <v>2584.09</v>
+        <v>2558.63</v>
       </c>
       <c r="K17" t="n">
-        <v>2802.24</v>
+        <v>2854.63</v>
       </c>
       <c r="L17" t="n">
-        <v>3020.4</v>
+        <v>3150.63</v>
       </c>
       <c r="M17" t="n">
-        <v>3320.36</v>
+        <v>3266.56</v>
       </c>
       <c r="N17" t="n">
-        <v>3620.32</v>
+        <v>3382.49</v>
       </c>
       <c r="O17" t="n">
-        <v>3756.67</v>
+        <v>3858.55</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,18 +1941,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1956,64 +1960,60 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3060.48</v>
+        <v>3001.61</v>
       </c>
       <c r="C18" t="n">
-        <v>3175.12</v>
+        <v>3073.35</v>
       </c>
       <c r="D18" t="n">
-        <v>2777.12</v>
+        <v>2888.99</v>
       </c>
       <c r="E18" t="n">
-        <v>3001.61</v>
+        <v>2948.57</v>
       </c>
       <c r="F18" t="n">
-        <v>-58.98</v>
+        <v>-53.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0177</v>
       </c>
       <c r="H18" t="n">
-        <v>398</v>
+        <v>184.37</v>
       </c>
       <c r="I18" t="n">
-        <v>2622.76</v>
+        <v>2379.12</v>
       </c>
       <c r="J18" t="n">
-        <v>2558.63</v>
+        <v>2616.36</v>
       </c>
       <c r="K18" t="n">
-        <v>2854.63</v>
+        <v>2802.61</v>
       </c>
       <c r="L18" t="n">
-        <v>3150.63</v>
+        <v>2988.87</v>
       </c>
       <c r="M18" t="n">
-        <v>3266.56</v>
+        <v>3200.61</v>
       </c>
       <c r="N18" t="n">
-        <v>3382.49</v>
+        <v>3412.36</v>
       </c>
       <c r="O18" t="n">
-        <v>3858.55</v>
+        <v>3573.12</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2021,14 +2021,12 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2040,60 +2038,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3001.61</v>
+        <v>2948.56</v>
       </c>
       <c r="C19" t="n">
-        <v>3073.35</v>
+        <v>3160.55</v>
       </c>
       <c r="D19" t="n">
-        <v>2888.99</v>
+        <v>2908.75</v>
       </c>
       <c r="E19" t="n">
-        <v>2948.57</v>
+        <v>3140.71</v>
       </c>
       <c r="F19" t="n">
-        <v>-53.05</v>
+        <v>192.14</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0177</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>184.37</v>
+        <v>251.8</v>
       </c>
       <c r="I19" t="n">
-        <v>2379.12</v>
+        <v>2704.62</v>
       </c>
       <c r="J19" t="n">
-        <v>2616.36</v>
+        <v>2747.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2802.61</v>
+        <v>2856.39</v>
       </c>
       <c r="L19" t="n">
-        <v>2988.87</v>
+        <v>2964.87</v>
       </c>
       <c r="M19" t="n">
-        <v>3200.61</v>
+        <v>3040.75</v>
       </c>
       <c r="N19" t="n">
-        <v>3412.36</v>
+        <v>3116.63</v>
       </c>
       <c r="O19" t="n">
-        <v>3573.12</v>
+        <v>3257.72</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2104,78 +2106,78 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2948.56</v>
+        <v>3141.49</v>
       </c>
       <c r="C20" t="n">
-        <v>3160.55</v>
+        <v>3303.56</v>
       </c>
       <c r="D20" t="n">
-        <v>2908.75</v>
+        <v>3052.51</v>
       </c>
       <c r="E20" t="n">
-        <v>3140.71</v>
+        <v>3118.89</v>
       </c>
       <c r="F20" t="n">
-        <v>192.14</v>
+        <v>-21.83</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="H20" t="n">
-        <v>251.8</v>
+        <v>251.05</v>
       </c>
       <c r="I20" t="n">
-        <v>2704.62</v>
+        <v>2656.95</v>
       </c>
       <c r="J20" t="n">
-        <v>2747.9</v>
+        <v>2941.94</v>
       </c>
       <c r="K20" t="n">
-        <v>2856.39</v>
+        <v>3014.81</v>
       </c>
       <c r="L20" t="n">
-        <v>2964.87</v>
+        <v>3087.68</v>
       </c>
       <c r="M20" t="n">
-        <v>3040.75</v>
+        <v>3266.61</v>
       </c>
       <c r="N20" t="n">
-        <v>3116.63</v>
+        <v>3445.54</v>
       </c>
       <c r="O20" t="n">
-        <v>3257.72</v>
+        <v>3412.35</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,7 +2190,7 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2196,68 +2198,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3141.49</v>
+        <v>3118.83</v>
       </c>
       <c r="C21" t="n">
-        <v>3303.56</v>
+        <v>3397.9</v>
       </c>
       <c r="D21" t="n">
-        <v>3052.51</v>
+        <v>3068.07</v>
       </c>
       <c r="E21" t="n">
-        <v>3118.89</v>
+        <v>3281.16</v>
       </c>
       <c r="F21" t="n">
-        <v>-21.83</v>
+        <v>162.27</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.052</v>
       </c>
       <c r="H21" t="n">
-        <v>251.05</v>
+        <v>329.82</v>
       </c>
       <c r="I21" t="n">
-        <v>2656.95</v>
+        <v>2801.46</v>
       </c>
       <c r="J21" t="n">
-        <v>2941.94</v>
+        <v>2838.26</v>
       </c>
       <c r="K21" t="n">
-        <v>3014.81</v>
+        <v>2993.36</v>
       </c>
       <c r="L21" t="n">
-        <v>3087.68</v>
+        <v>3148.46</v>
       </c>
       <c r="M21" t="n">
-        <v>3266.61</v>
+        <v>3244.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3445.54</v>
+        <v>3340.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3412.35</v>
+        <v>3554.62</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2270,109 +2274,109 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3118.83</v>
+        <v>3282.2</v>
       </c>
       <c r="C22" t="n">
-        <v>3397.9</v>
+        <v>3282.65</v>
       </c>
       <c r="D22" t="n">
-        <v>3068.07</v>
+        <v>2785.9</v>
       </c>
       <c r="E22" t="n">
-        <v>3281.16</v>
+        <v>2815.9</v>
       </c>
       <c r="F22" t="n">
-        <v>162.27</v>
+        <v>-465.26</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.052</v>
+        <v>-0.1418</v>
       </c>
       <c r="H22" t="n">
-        <v>329.82</v>
+        <v>496.76</v>
       </c>
       <c r="I22" t="n">
-        <v>2801.46</v>
+        <v>2738.25</v>
       </c>
       <c r="J22" t="n">
-        <v>2838.26</v>
+        <v>2975.42</v>
       </c>
       <c r="K22" t="n">
-        <v>2993.36</v>
+        <v>3116.25</v>
       </c>
       <c r="L22" t="n">
-        <v>3148.46</v>
+        <v>3257.07</v>
       </c>
       <c r="M22" t="n">
-        <v>3244.41</v>
+        <v>3446.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3340.36</v>
+        <v>3635.07</v>
       </c>
       <c r="O22" t="n">
-        <v>3554.62</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+        <v>3727.72</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2380,66 +2384,64 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3282.2</v>
+        <v>2815.77</v>
       </c>
       <c r="C23" t="n">
-        <v>3282.65</v>
+        <v>3040.72</v>
       </c>
       <c r="D23" t="n">
-        <v>2785.9</v>
+        <v>2224.12</v>
       </c>
       <c r="E23" t="n">
-        <v>2815.9</v>
+        <v>2267.96</v>
       </c>
       <c r="F23" t="n">
-        <v>-465.26</v>
+        <v>-547.9400000000001</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.1418</v>
+        <v>-0.1946</v>
       </c>
       <c r="H23" t="n">
-        <v>496.76</v>
+        <v>816.6</v>
       </c>
       <c r="I23" t="n">
-        <v>2738.25</v>
+        <v>2289.14</v>
       </c>
       <c r="J23" t="n">
-        <v>2975.42</v>
+        <v>2209.96</v>
       </c>
       <c r="K23" t="n">
-        <v>3116.25</v>
+        <v>2567.52</v>
       </c>
       <c r="L23" t="n">
-        <v>3257.07</v>
+        <v>2925.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3446.07</v>
+        <v>3064.28</v>
       </c>
       <c r="N23" t="n">
-        <v>3635.07</v>
+        <v>3203.47</v>
       </c>
       <c r="O23" t="n">
-        <v>3727.72</v>
+        <v>3779.41</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2454,7 +2456,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2464,64 +2466,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2815.77</v>
+        <v>2267.56</v>
       </c>
       <c r="C24" t="n">
-        <v>3040.72</v>
+        <v>2393.06</v>
       </c>
       <c r="D24" t="n">
-        <v>2224.12</v>
+        <v>1748.63</v>
       </c>
       <c r="E24" t="n">
-        <v>2267.96</v>
+        <v>2088.76</v>
       </c>
       <c r="F24" t="n">
-        <v>-547.9400000000001</v>
+        <v>-179.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.1946</v>
+        <v>-0.079</v>
       </c>
       <c r="H24" t="n">
-        <v>816.6</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>2289.14</v>
+        <v>1407.52</v>
       </c>
       <c r="J24" t="n">
-        <v>2209.96</v>
+        <v>1269.14</v>
       </c>
       <c r="K24" t="n">
-        <v>2567.52</v>
+        <v>1859.66</v>
       </c>
       <c r="L24" t="n">
-        <v>2925.09</v>
+        <v>2450.19</v>
       </c>
       <c r="M24" t="n">
-        <v>3064.28</v>
+        <v>2676.27</v>
       </c>
       <c r="N24" t="n">
-        <v>3203.47</v>
+        <v>2902.34</v>
       </c>
       <c r="O24" t="n">
-        <v>3779.41</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>3857.32</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2536,7 +2536,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2546,50 +2546,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2267.56</v>
+        <v>2087.92</v>
       </c>
       <c r="C25" t="n">
-        <v>2393.06</v>
+        <v>2144.98</v>
       </c>
       <c r="D25" t="n">
-        <v>1748.63</v>
+        <v>1897.33</v>
       </c>
       <c r="E25" t="n">
-        <v>2088.76</v>
+        <v>1966.04</v>
       </c>
       <c r="F25" t="n">
-        <v>-179.2</v>
+        <v>-122.72</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.0588</v>
       </c>
       <c r="H25" t="n">
-        <v>644.4400000000001</v>
+        <v>247.64</v>
       </c>
       <c r="I25" t="n">
-        <v>1407.52</v>
+        <v>1104.19</v>
       </c>
       <c r="J25" t="n">
-        <v>1269.14</v>
+        <v>1453.29</v>
       </c>
       <c r="K25" t="n">
-        <v>1859.66</v>
+        <v>1766.55</v>
       </c>
       <c r="L25" t="n">
-        <v>2450.19</v>
+        <v>2079.8</v>
       </c>
       <c r="M25" t="n">
-        <v>2676.27</v>
+        <v>2410.98</v>
       </c>
       <c r="N25" t="n">
-        <v>2902.34</v>
+        <v>2742.16</v>
       </c>
       <c r="O25" t="n">
-        <v>3857.32</v>
+        <v>3037.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2597,14 +2597,12 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2616,60 +2614,64 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2087.92</v>
+        <v>1965.92</v>
       </c>
       <c r="C26" t="n">
-        <v>2144.98</v>
+        <v>2037.16</v>
       </c>
       <c r="D26" t="n">
-        <v>1897.33</v>
+        <v>1906.82</v>
       </c>
       <c r="E26" t="n">
-        <v>1966.04</v>
+        <v>1957.81</v>
       </c>
       <c r="F26" t="n">
-        <v>-122.72</v>
+        <v>-8.24</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0042</v>
       </c>
       <c r="H26" t="n">
-        <v>247.64</v>
+        <v>130.34</v>
       </c>
       <c r="I26" t="n">
-        <v>1104.19</v>
+        <v>1649.69</v>
       </c>
       <c r="J26" t="n">
-        <v>1453.29</v>
+        <v>1690.85</v>
       </c>
       <c r="K26" t="n">
-        <v>1766.55</v>
+        <v>1842.22</v>
       </c>
       <c r="L26" t="n">
-        <v>2079.8</v>
+        <v>1993.6</v>
       </c>
       <c r="M26" t="n">
-        <v>2410.98</v>
+        <v>2089.86</v>
       </c>
       <c r="N26" t="n">
-        <v>2742.16</v>
+        <v>2186.13</v>
       </c>
       <c r="O26" t="n">
-        <v>3037.5</v>
+        <v>2392.62</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,7 +2696,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2708,75 +2710,83 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1965.92</v>
+        <v>1958.14</v>
       </c>
       <c r="C27" t="n">
-        <v>2037.16</v>
+        <v>2145.51</v>
       </c>
       <c r="D27" t="n">
-        <v>1906.82</v>
+        <v>1804.11</v>
       </c>
       <c r="E27" t="n">
-        <v>1957.81</v>
+        <v>1939.07</v>
       </c>
       <c r="F27" t="n">
-        <v>-8.24</v>
+        <v>-18.74</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>130.34</v>
+        <v>341.39</v>
       </c>
       <c r="I27" t="n">
-        <v>1649.69</v>
+        <v>1776.49</v>
       </c>
       <c r="J27" t="n">
-        <v>1690.85</v>
+        <v>1820.38</v>
       </c>
       <c r="K27" t="n">
-        <v>1842.22</v>
+        <v>1892.64</v>
       </c>
       <c r="L27" t="n">
-        <v>1993.6</v>
+        <v>1964.9</v>
       </c>
       <c r="M27" t="n">
-        <v>2089.86</v>
+        <v>2022.97</v>
       </c>
       <c r="N27" t="n">
-        <v>2186.13</v>
+        <v>2081.05</v>
       </c>
       <c r="O27" t="n">
-        <v>2392.62</v>
+        <v>2167.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2790,140 +2800,134 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1958.14</v>
+        <v>1939.06</v>
       </c>
       <c r="C28" t="n">
-        <v>2145.51</v>
+        <v>2198.66</v>
       </c>
       <c r="D28" t="n">
-        <v>1804.11</v>
+        <v>1915.3</v>
       </c>
       <c r="E28" t="n">
-        <v>1939.07</v>
+        <v>1936.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-18.74</v>
+        <v>-2.46</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0013</v>
       </c>
       <c r="H28" t="n">
-        <v>341.39</v>
+        <v>283.36</v>
       </c>
       <c r="I28" t="n">
-        <v>1776.49</v>
+        <v>1462.72</v>
       </c>
       <c r="J28" t="n">
-        <v>1820.38</v>
+        <v>1579.8</v>
       </c>
       <c r="K28" t="n">
-        <v>1892.64</v>
+        <v>1768.37</v>
       </c>
       <c r="L28" t="n">
-        <v>1964.9</v>
+        <v>1956.94</v>
       </c>
       <c r="M28" t="n">
-        <v>2022.97</v>
+        <v>2109.76</v>
       </c>
       <c r="N28" t="n">
-        <v>2081.05</v>
+        <v>2262.59</v>
       </c>
       <c r="O28" t="n">
-        <v>2167.5</v>
+        <v>2486.9</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1939.06</v>
+        <v>1936.64</v>
       </c>
       <c r="C29" t="n">
-        <v>2198.66</v>
+        <v>2206.81</v>
       </c>
       <c r="D29" t="n">
-        <v>1915.3</v>
+        <v>1930.6</v>
       </c>
       <c r="E29" t="n">
-        <v>1936.6</v>
+        <v>2177.48</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.46</v>
+        <v>240.87</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.1244</v>
       </c>
       <c r="H29" t="n">
-        <v>283.36</v>
+        <v>276.21</v>
       </c>
       <c r="I29" t="n">
-        <v>1462.72</v>
+        <v>1631.95</v>
       </c>
       <c r="J29" t="n">
-        <v>1579.8</v>
+        <v>1593.06</v>
       </c>
       <c r="K29" t="n">
-        <v>1768.37</v>
+        <v>1794.93</v>
       </c>
       <c r="L29" t="n">
-        <v>1956.94</v>
+        <v>1996.79</v>
       </c>
       <c r="M29" t="n">
-        <v>2109.76</v>
+        <v>2078.28</v>
       </c>
       <c r="N29" t="n">
-        <v>2262.59</v>
+        <v>2159.77</v>
       </c>
       <c r="O29" t="n">
-        <v>2486.9</v>
+        <v>2482.01</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2934,9 +2938,9 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2944,70 +2948,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1936.64</v>
+        <v>2177.78</v>
       </c>
       <c r="C30" t="n">
-        <v>2206.81</v>
+        <v>2384.47</v>
       </c>
       <c r="D30" t="n">
-        <v>1930.6</v>
+        <v>2027.05</v>
       </c>
       <c r="E30" t="n">
-        <v>2177.48</v>
+        <v>2053.05</v>
       </c>
       <c r="F30" t="n">
-        <v>240.87</v>
+        <v>-124.43</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1244</v>
+        <v>-0.0571</v>
       </c>
       <c r="H30" t="n">
-        <v>276.21</v>
+        <v>357.42</v>
       </c>
       <c r="I30" t="n">
-        <v>1631.95</v>
+        <v>1654.39</v>
       </c>
       <c r="J30" t="n">
-        <v>1593.06</v>
+        <v>1955.65</v>
       </c>
       <c r="K30" t="n">
-        <v>1794.93</v>
+        <v>2039.37</v>
       </c>
       <c r="L30" t="n">
-        <v>1996.79</v>
+        <v>2123.09</v>
       </c>
       <c r="M30" t="n">
-        <v>2078.28</v>
+        <v>2315.58</v>
       </c>
       <c r="N30" t="n">
-        <v>2159.77</v>
+        <v>2508.08</v>
       </c>
       <c r="O30" t="n">
-        <v>2482.01</v>
+        <v>2483.03</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3015,12 +3017,14 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3028,68 +3032,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2177.78</v>
+        <v>2052.95</v>
       </c>
       <c r="C31" t="n">
-        <v>2384.47</v>
+        <v>2198.37</v>
       </c>
       <c r="D31" t="n">
-        <v>2027.05</v>
+        <v>1939.53</v>
       </c>
       <c r="E31" t="n">
-        <v>2053.05</v>
+        <v>1982.56</v>
       </c>
       <c r="F31" t="n">
-        <v>-124.43</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0571</v>
+        <v>-0.0343</v>
       </c>
       <c r="H31" t="n">
-        <v>357.42</v>
+        <v>258.84</v>
       </c>
       <c r="I31" t="n">
-        <v>1654.39</v>
+        <v>1669.63</v>
       </c>
       <c r="J31" t="n">
-        <v>1955.65</v>
+        <v>1619.28</v>
       </c>
       <c r="K31" t="n">
-        <v>2039.37</v>
+        <v>1874.34</v>
       </c>
       <c r="L31" t="n">
-        <v>2123.09</v>
+        <v>2129.4</v>
       </c>
       <c r="M31" t="n">
-        <v>2315.58</v>
+        <v>2231.76</v>
       </c>
       <c r="N31" t="n">
-        <v>2508.08</v>
+        <v>2334.11</v>
       </c>
       <c r="O31" t="n">
-        <v>2483.03</v>
+        <v>2741.89</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3107,10 +3113,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3118,64 +3122,64 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2052.95</v>
+        <v>1982.55</v>
       </c>
       <c r="C32" t="n">
-        <v>2198.37</v>
+        <v>2165.67</v>
       </c>
       <c r="D32" t="n">
-        <v>1939.53</v>
+        <v>1979.08</v>
       </c>
       <c r="E32" t="n">
-        <v>1982.56</v>
+        <v>2109</v>
       </c>
       <c r="F32" t="n">
-        <v>-70.48999999999999</v>
+        <v>126.44</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0343</v>
+        <v>0.0638</v>
       </c>
       <c r="H32" t="n">
-        <v>258.84</v>
+        <v>186.59</v>
       </c>
       <c r="I32" t="n">
-        <v>1669.63</v>
+        <v>1680.69</v>
       </c>
       <c r="J32" t="n">
-        <v>1619.28</v>
+        <v>1680.52</v>
       </c>
       <c r="K32" t="n">
-        <v>1874.34</v>
+        <v>1853.14</v>
       </c>
       <c r="L32" t="n">
-        <v>2129.4</v>
+        <v>2025.75</v>
       </c>
       <c r="M32" t="n">
-        <v>2231.76</v>
+        <v>2111.98</v>
       </c>
       <c r="N32" t="n">
-        <v>2334.11</v>
+        <v>2198.21</v>
       </c>
       <c r="O32" t="n">
-        <v>2741.89</v>
+        <v>2457.21</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3183,83 +3187,83 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1982.55</v>
+        <v>2108.94</v>
       </c>
       <c r="C33" t="n">
-        <v>2165.67</v>
+        <v>2327.46</v>
       </c>
       <c r="D33" t="n">
-        <v>1979.08</v>
+        <v>2061.47</v>
       </c>
       <c r="E33" t="n">
-        <v>2109</v>
+        <v>2192.2</v>
       </c>
       <c r="F33" t="n">
-        <v>126.44</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0638</v>
+        <v>0.0395</v>
       </c>
       <c r="H33" t="n">
-        <v>186.59</v>
+        <v>265.99</v>
       </c>
       <c r="I33" t="n">
-        <v>1680.69</v>
+        <v>1792.49</v>
       </c>
       <c r="J33" t="n">
-        <v>1680.52</v>
+        <v>1940.72</v>
       </c>
       <c r="K33" t="n">
-        <v>1853.14</v>
+        <v>2015.7</v>
       </c>
       <c r="L33" t="n">
-        <v>2025.75</v>
+        <v>2090.68</v>
       </c>
       <c r="M33" t="n">
-        <v>2111.98</v>
+        <v>2202.29</v>
       </c>
       <c r="N33" t="n">
-        <v>2198.21</v>
+        <v>2313.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2457.21</v>
+        <v>2352.26</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3280,70 +3284,68 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2108.94</v>
+        <v>2192.33</v>
       </c>
       <c r="C34" t="n">
-        <v>2327.46</v>
+        <v>2464.78</v>
       </c>
       <c r="D34" t="n">
-        <v>2061.47</v>
+        <v>2176.32</v>
       </c>
       <c r="E34" t="n">
-        <v>2192.2</v>
+        <v>2264.92</v>
       </c>
       <c r="F34" t="n">
-        <v>83.20999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0332</v>
       </c>
       <c r="H34" t="n">
-        <v>265.99</v>
+        <v>288.46</v>
       </c>
       <c r="I34" t="n">
-        <v>1792.49</v>
+        <v>1795.48</v>
       </c>
       <c r="J34" t="n">
-        <v>1940.72</v>
+        <v>1925.08</v>
       </c>
       <c r="K34" t="n">
-        <v>2015.7</v>
+        <v>2059.21</v>
       </c>
       <c r="L34" t="n">
-        <v>2090.68</v>
+        <v>2193.33</v>
       </c>
       <c r="M34" t="n">
-        <v>2202.29</v>
+        <v>2325.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2313.9</v>
+        <v>2457.06</v>
       </c>
       <c r="O34" t="n">
-        <v>2352.26</v>
+        <v>2593.45</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3372,7 +3374,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3382,50 +3384,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2192.33</v>
+        <v>2264.87</v>
       </c>
       <c r="C35" t="n">
-        <v>2464.78</v>
+        <v>2422.86</v>
       </c>
       <c r="D35" t="n">
-        <v>2176.32</v>
+        <v>2262.05</v>
       </c>
       <c r="E35" t="n">
-        <v>2264.92</v>
+        <v>2369.73</v>
       </c>
       <c r="F35" t="n">
-        <v>72.72</v>
+        <v>104.81</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0463</v>
       </c>
       <c r="H35" t="n">
-        <v>288.46</v>
+        <v>160.81</v>
       </c>
       <c r="I35" t="n">
-        <v>1795.48</v>
+        <v>1887.87</v>
       </c>
       <c r="J35" t="n">
-        <v>1925.08</v>
+        <v>1948.64</v>
       </c>
       <c r="K35" t="n">
-        <v>2059.21</v>
+        <v>2120.69</v>
       </c>
       <c r="L35" t="n">
-        <v>2193.33</v>
+        <v>2292.74</v>
       </c>
       <c r="M35" t="n">
-        <v>2325.2</v>
+        <v>2409.15</v>
       </c>
       <c r="N35" t="n">
-        <v>2457.06</v>
+        <v>2525.56</v>
       </c>
       <c r="O35" t="n">
-        <v>2593.45</v>
+        <v>2753.24</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3446,258 +3448,260 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2264.87</v>
+        <v>2369.84</v>
       </c>
       <c r="C36" t="n">
-        <v>2422.86</v>
+        <v>2403.73</v>
       </c>
       <c r="D36" t="n">
-        <v>2262.05</v>
+        <v>2221.22</v>
       </c>
       <c r="E36" t="n">
-        <v>2369.73</v>
+        <v>2321.64</v>
       </c>
       <c r="F36" t="n">
-        <v>104.81</v>
+        <v>-48.09</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0463</v>
+        <v>-0.0203</v>
       </c>
       <c r="H36" t="n">
-        <v>160.81</v>
+        <v>182.5</v>
       </c>
       <c r="I36" t="n">
-        <v>1887.87</v>
+        <v>2101.25</v>
       </c>
       <c r="J36" t="n">
-        <v>1948.64</v>
+        <v>2222.56</v>
       </c>
       <c r="K36" t="n">
-        <v>2120.69</v>
+        <v>2289.33</v>
       </c>
       <c r="L36" t="n">
-        <v>2292.74</v>
+        <v>2356.09</v>
       </c>
       <c r="M36" t="n">
-        <v>2409.15</v>
+        <v>2450.13</v>
       </c>
       <c r="N36" t="n">
-        <v>2525.56</v>
+        <v>2544.17</v>
       </c>
       <c r="O36" t="n">
-        <v>2753.24</v>
+        <v>2583.67</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2369.84</v>
+        <v>2321.82</v>
       </c>
       <c r="C37" t="n">
-        <v>2403.73</v>
+        <v>2423.04</v>
       </c>
       <c r="D37" t="n">
-        <v>2221.22</v>
+        <v>2265.83</v>
       </c>
       <c r="E37" t="n">
-        <v>2321.64</v>
+        <v>2369.04</v>
       </c>
       <c r="F37" t="n">
-        <v>-48.09</v>
+        <v>47.41</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="H37" t="n">
-        <v>182.5</v>
+        <v>157.21</v>
       </c>
       <c r="I37" t="n">
-        <v>2101.25</v>
+        <v>2038.72</v>
       </c>
       <c r="J37" t="n">
-        <v>2222.56</v>
+        <v>2143.71</v>
       </c>
       <c r="K37" t="n">
-        <v>2289.33</v>
+        <v>2230.38</v>
       </c>
       <c r="L37" t="n">
-        <v>2356.09</v>
+        <v>2317.06</v>
       </c>
       <c r="M37" t="n">
-        <v>2450.13</v>
+        <v>2412.89</v>
       </c>
       <c r="N37" t="n">
-        <v>2544.17</v>
+        <v>2508.72</v>
       </c>
       <c r="O37" t="n">
-        <v>2583.67</v>
+        <v>2586.23</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2321.82</v>
+        <v>2369.19</v>
       </c>
       <c r="C38" t="n">
-        <v>2423.04</v>
+        <v>2374.3</v>
       </c>
       <c r="D38" t="n">
-        <v>2265.83</v>
+        <v>2097.02</v>
       </c>
       <c r="E38" t="n">
-        <v>2369.04</v>
+        <v>2127.65</v>
       </c>
       <c r="F38" t="n">
-        <v>47.41</v>
+        <v>-241.4</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.1019</v>
       </c>
       <c r="H38" t="n">
-        <v>157.21</v>
+        <v>277.28</v>
       </c>
       <c r="I38" t="n">
-        <v>2038.72</v>
+        <v>2108.63</v>
       </c>
       <c r="J38" t="n">
-        <v>2143.71</v>
+        <v>2224.14</v>
       </c>
       <c r="K38" t="n">
-        <v>2230.38</v>
+        <v>2290.44</v>
       </c>
       <c r="L38" t="n">
-        <v>2317.06</v>
+        <v>2356.74</v>
       </c>
       <c r="M38" t="n">
-        <v>2412.89</v>
+        <v>2447.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2508.72</v>
+        <v>2538.55</v>
       </c>
       <c r="O38" t="n">
-        <v>2586.23</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+        <v>2580.25</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3706,7 +3710,7 @@
       </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3714,69 +3718,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2369.19</v>
+        <v>2127.68</v>
       </c>
       <c r="C39" t="n">
-        <v>2374.3</v>
+        <v>2155.96</v>
       </c>
       <c r="D39" t="n">
-        <v>2097.02</v>
+        <v>2010.55</v>
       </c>
       <c r="E39" t="n">
-        <v>2127.65</v>
+        <v>2097.99</v>
       </c>
       <c r="F39" t="n">
-        <v>-241.4</v>
+        <v>-29.65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.1019</v>
+        <v>-0.0139</v>
       </c>
       <c r="H39" t="n">
-        <v>277.28</v>
+        <v>145.41</v>
       </c>
       <c r="I39" t="n">
-        <v>2108.63</v>
+        <v>1819.74</v>
       </c>
       <c r="J39" t="n">
-        <v>2224.14</v>
+        <v>1796.35</v>
       </c>
       <c r="K39" t="n">
-        <v>2290.44</v>
+        <v>1989</v>
       </c>
       <c r="L39" t="n">
-        <v>2356.74</v>
+        <v>2181.65</v>
       </c>
       <c r="M39" t="n">
-        <v>2447.65</v>
+        <v>2266.29</v>
       </c>
       <c r="N39" t="n">
-        <v>2538.55</v>
+        <v>2350.92</v>
       </c>
       <c r="O39" t="n">
-        <v>2580.25</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>2651.59</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3788,7 +3786,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3798,50 +3796,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2127.68</v>
+        <v>2097.99</v>
       </c>
       <c r="C40" t="n">
-        <v>2155.96</v>
+        <v>2138.41</v>
       </c>
       <c r="D40" t="n">
-        <v>2010.55</v>
+        <v>1966.28</v>
       </c>
       <c r="E40" t="n">
-        <v>2097.99</v>
+        <v>2004.34</v>
       </c>
       <c r="F40" t="n">
-        <v>-29.65</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.0446</v>
       </c>
       <c r="H40" t="n">
-        <v>145.41</v>
+        <v>172.13</v>
       </c>
       <c r="I40" t="n">
-        <v>1819.74</v>
+        <v>1865.14</v>
       </c>
       <c r="J40" t="n">
-        <v>1796.35</v>
+        <v>1959.95</v>
       </c>
       <c r="K40" t="n">
-        <v>1989</v>
+        <v>2025.29</v>
       </c>
       <c r="L40" t="n">
-        <v>2181.65</v>
+        <v>2090.63</v>
       </c>
       <c r="M40" t="n">
-        <v>2266.29</v>
+        <v>2170.7</v>
       </c>
       <c r="N40" t="n">
-        <v>2350.92</v>
+        <v>2250.78</v>
       </c>
       <c r="O40" t="n">
-        <v>2651.59</v>
+        <v>2301.38</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3849,12 +3847,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3866,7 +3866,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3876,60 +3876,64 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2097.99</v>
+        <v>2004.24</v>
       </c>
       <c r="C41" t="n">
-        <v>2138.41</v>
+        <v>2017.61</v>
       </c>
       <c r="D41" t="n">
-        <v>1966.28</v>
+        <v>1506.51</v>
       </c>
       <c r="E41" t="n">
-        <v>2004.34</v>
+        <v>1686.4</v>
       </c>
       <c r="F41" t="n">
-        <v>-93.65000000000001</v>
+        <v>-317.95</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0446</v>
+        <v>-0.1586</v>
       </c>
       <c r="H41" t="n">
-        <v>172.13</v>
+        <v>511.1</v>
       </c>
       <c r="I41" t="n">
-        <v>1865.14</v>
+        <v>1794.15</v>
       </c>
       <c r="J41" t="n">
-        <v>1959.95</v>
+        <v>1808.21</v>
       </c>
       <c r="K41" t="n">
-        <v>2025.29</v>
+        <v>1918.28</v>
       </c>
       <c r="L41" t="n">
-        <v>2090.63</v>
+        <v>2028.34</v>
       </c>
       <c r="M41" t="n">
-        <v>2170.7</v>
+        <v>2090.41</v>
       </c>
       <c r="N41" t="n">
-        <v>2250.78</v>
+        <v>2152.47</v>
       </c>
       <c r="O41" t="n">
-        <v>2301.38</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>2310.54</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -3946,7 +3950,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3956,69 +3960,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2004.24</v>
+        <v>1686.25</v>
       </c>
       <c r="C42" t="n">
-        <v>2017.61</v>
+        <v>1729.35</v>
       </c>
       <c r="D42" t="n">
-        <v>1506.51</v>
+        <v>1603.83</v>
       </c>
       <c r="E42" t="n">
-        <v>1686.4</v>
+        <v>1724.61</v>
       </c>
       <c r="F42" t="n">
-        <v>-317.95</v>
+        <v>38.22</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.1586</v>
+        <v>0.0227</v>
       </c>
       <c r="H42" t="n">
-        <v>511.1</v>
+        <v>125.53</v>
       </c>
       <c r="I42" t="n">
-        <v>1794.15</v>
+        <v>995.4</v>
       </c>
       <c r="J42" t="n">
-        <v>1808.21</v>
+        <v>1137.46</v>
       </c>
       <c r="K42" t="n">
-        <v>1918.28</v>
+        <v>1430.85</v>
       </c>
       <c r="L42" t="n">
-        <v>2028.34</v>
+        <v>1724.23</v>
       </c>
       <c r="M42" t="n">
-        <v>2090.41</v>
+        <v>1941.95</v>
       </c>
       <c r="N42" t="n">
-        <v>2152.47</v>
+        <v>2159.67</v>
       </c>
       <c r="O42" t="n">
-        <v>2310.54</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>2528.71</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4030,60 +4028,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1686.25</v>
+        <v>1724.57</v>
       </c>
       <c r="C43" t="n">
-        <v>1729.35</v>
+        <v>1847.77</v>
       </c>
       <c r="D43" t="n">
-        <v>1603.83</v>
+        <v>1670.1</v>
       </c>
       <c r="E43" t="n">
-        <v>1724.61</v>
+        <v>1704.58</v>
       </c>
       <c r="F43" t="n">
-        <v>38.22</v>
+        <v>-20.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0227</v>
+        <v>-0.0116</v>
       </c>
       <c r="H43" t="n">
-        <v>125.53</v>
+        <v>177.67</v>
       </c>
       <c r="I43" t="n">
-        <v>995.4</v>
+        <v>1478.3</v>
       </c>
       <c r="J43" t="n">
-        <v>1137.46</v>
+        <v>1628.1</v>
       </c>
       <c r="K43" t="n">
-        <v>1430.85</v>
+        <v>1661.85</v>
       </c>
       <c r="L43" t="n">
-        <v>1724.23</v>
+        <v>1695.6</v>
       </c>
       <c r="M43" t="n">
-        <v>1941.95</v>
+        <v>1787.38</v>
       </c>
       <c r="N43" t="n">
-        <v>2159.67</v>
+        <v>1879.15</v>
       </c>
       <c r="O43" t="n">
-        <v>2528.71</v>
+        <v>1854.88</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4099,8 +4101,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4108,7 +4112,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4122,50 +4126,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1724.57</v>
+        <v>1704.63</v>
       </c>
       <c r="C44" t="n">
-        <v>1847.77</v>
+        <v>1776.83</v>
       </c>
       <c r="D44" t="n">
-        <v>1670.1</v>
+        <v>1510.51</v>
       </c>
       <c r="E44" t="n">
-        <v>1704.58</v>
+        <v>1570.36</v>
       </c>
       <c r="F44" t="n">
-        <v>-20.03</v>
+        <v>-134.22</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>177.67</v>
+        <v>266.33</v>
       </c>
       <c r="I44" t="n">
-        <v>1478.3</v>
+        <v>1492.44</v>
       </c>
       <c r="J44" t="n">
-        <v>1628.1</v>
+        <v>1499.74</v>
       </c>
       <c r="K44" t="n">
-        <v>1661.85</v>
+        <v>1615.75</v>
       </c>
       <c r="L44" t="n">
-        <v>1695.6</v>
+        <v>1731.76</v>
       </c>
       <c r="M44" t="n">
-        <v>1787.38</v>
+        <v>1793.41</v>
       </c>
       <c r="N44" t="n">
-        <v>1879.15</v>
+        <v>1855.07</v>
       </c>
       <c r="O44" t="n">
-        <v>1854.88</v>
+        <v>2025.44</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4173,18 +4177,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4192,64 +4196,60 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1704.63</v>
+        <v>1569.99</v>
       </c>
       <c r="C45" t="n">
-        <v>1776.83</v>
+        <v>1805.91</v>
       </c>
       <c r="D45" t="n">
-        <v>1510.51</v>
+        <v>1549.25</v>
       </c>
       <c r="E45" t="n">
-        <v>1570.36</v>
+        <v>1783.01</v>
       </c>
       <c r="F45" t="n">
-        <v>-134.22</v>
+        <v>212.64</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.1354</v>
       </c>
       <c r="H45" t="n">
-        <v>266.33</v>
+        <v>256.66</v>
       </c>
       <c r="I45" t="n">
-        <v>1492.44</v>
+        <v>1244.18</v>
       </c>
       <c r="J45" t="n">
-        <v>1499.74</v>
+        <v>1267.38</v>
       </c>
       <c r="K45" t="n">
-        <v>1615.75</v>
+        <v>1437.2</v>
       </c>
       <c r="L45" t="n">
-        <v>1731.76</v>
+        <v>1607.02</v>
       </c>
       <c r="M45" t="n">
-        <v>1793.41</v>
+        <v>1703.52</v>
       </c>
       <c r="N45" t="n">
-        <v>1855.07</v>
+        <v>1800.03</v>
       </c>
       <c r="O45" t="n">
-        <v>2025.44</v>
+        <v>2043.16</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4257,79 +4257,85 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1569.99</v>
+        <v>1783</v>
       </c>
       <c r="C46" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D46" t="n">
-        <v>1549.25</v>
+        <v>1711.9</v>
       </c>
       <c r="E46" t="n">
-        <v>1783.01</v>
+        <v>1805.79</v>
       </c>
       <c r="F46" t="n">
-        <v>212.64</v>
+        <v>22.78</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.1354</v>
+        <v>0.0128</v>
       </c>
       <c r="H46" t="n">
-        <v>256.66</v>
+        <v>117.61</v>
       </c>
       <c r="I46" t="n">
-        <v>1244.18</v>
+        <v>1292.59</v>
       </c>
       <c r="J46" t="n">
-        <v>1267.38</v>
+        <v>1579.06</v>
       </c>
       <c r="K46" t="n">
-        <v>1437.2</v>
+        <v>1654.67</v>
       </c>
       <c r="L46" t="n">
-        <v>1607.02</v>
+        <v>1730.29</v>
       </c>
       <c r="M46" t="n">
-        <v>1703.52</v>
+        <v>1911.34</v>
       </c>
       <c r="N46" t="n">
-        <v>1800.03</v>
+        <v>2092.38</v>
       </c>
       <c r="O46" t="n">
-        <v>2043.16</v>
+        <v>2062.58</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4342,23 +4348,19 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4372,50 +4374,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1783</v>
+        <v>1805.76</v>
       </c>
       <c r="C47" t="n">
-        <v>1829.51</v>
+        <v>1944.16</v>
       </c>
       <c r="D47" t="n">
-        <v>1711.9</v>
+        <v>1749.35</v>
       </c>
       <c r="E47" t="n">
-        <v>1805.79</v>
+        <v>1871.51</v>
       </c>
       <c r="F47" t="n">
-        <v>22.78</v>
+        <v>65.72</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0364</v>
       </c>
       <c r="H47" t="n">
-        <v>117.61</v>
+        <v>194.81</v>
       </c>
       <c r="I47" t="n">
-        <v>1292.59</v>
+        <v>1594.29</v>
       </c>
       <c r="J47" t="n">
-        <v>1579.06</v>
+        <v>1705.72</v>
       </c>
       <c r="K47" t="n">
-        <v>1654.67</v>
+        <v>1746.98</v>
       </c>
       <c r="L47" t="n">
-        <v>1730.29</v>
+        <v>1788.25</v>
       </c>
       <c r="M47" t="n">
-        <v>1911.34</v>
+        <v>1864.59</v>
       </c>
       <c r="N47" t="n">
-        <v>2092.38</v>
+        <v>1940.94</v>
       </c>
       <c r="O47" t="n">
-        <v>2062.58</v>
+        <v>1947.13</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4428,19 +4430,23 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4454,50 +4460,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1805.76</v>
+        <v>1871.28</v>
       </c>
       <c r="C48" t="n">
-        <v>1944.16</v>
+        <v>1963.25</v>
       </c>
       <c r="D48" t="n">
-        <v>1749.35</v>
+        <v>1842.82</v>
       </c>
       <c r="E48" t="n">
-        <v>1871.51</v>
+        <v>1953.41</v>
       </c>
       <c r="F48" t="n">
-        <v>65.72</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0364</v>
+        <v>0.0438</v>
       </c>
       <c r="H48" t="n">
-        <v>194.81</v>
+        <v>120.43</v>
       </c>
       <c r="I48" t="n">
-        <v>1594.29</v>
+        <v>1554.53</v>
       </c>
       <c r="J48" t="n">
-        <v>1705.72</v>
+        <v>1689.07</v>
       </c>
       <c r="K48" t="n">
-        <v>1746.98</v>
+        <v>1774.1</v>
       </c>
       <c r="L48" t="n">
-        <v>1788.25</v>
+        <v>1859.13</v>
       </c>
       <c r="M48" t="n">
-        <v>1864.59</v>
+        <v>1968.92</v>
       </c>
       <c r="N48" t="n">
-        <v>1940.94</v>
+        <v>2078.7</v>
       </c>
       <c r="O48" t="n">
-        <v>1947.13</v>
+        <v>2138.97</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4518,15 +4524,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4540,151 +4544,149 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1871.28</v>
+        <v>1953.41</v>
       </c>
       <c r="C49" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D49" t="n">
-        <v>1842.82</v>
+        <v>1821.49</v>
       </c>
       <c r="E49" t="n">
-        <v>1953.41</v>
+        <v>1882.52</v>
       </c>
       <c r="F49" t="n">
-        <v>81.90000000000001</v>
+        <v>-70.89</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0363</v>
       </c>
       <c r="H49" t="n">
-        <v>120.43</v>
+        <v>154.98</v>
       </c>
       <c r="I49" t="n">
-        <v>1554.53</v>
+        <v>1722.39</v>
       </c>
       <c r="J49" t="n">
-        <v>1689.07</v>
+        <v>1858.17</v>
       </c>
       <c r="K49" t="n">
-        <v>1774.1</v>
+        <v>1893.2</v>
       </c>
       <c r="L49" t="n">
-        <v>1859.13</v>
+        <v>1928.22</v>
       </c>
       <c r="M49" t="n">
-        <v>1968.92</v>
+        <v>2013.63</v>
       </c>
       <c r="N49" t="n">
-        <v>2078.7</v>
+        <v>2099.03</v>
       </c>
       <c r="O49" t="n">
-        <v>2138.97</v>
+        <v>2083.68</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1953.41</v>
+        <v>1882.78</v>
       </c>
       <c r="C50" t="n">
-        <v>1976.46</v>
+        <v>1937.17</v>
       </c>
       <c r="D50" t="n">
-        <v>1821.49</v>
+        <v>1827.7</v>
       </c>
       <c r="E50" t="n">
-        <v>1882.52</v>
+        <v>1908.68</v>
       </c>
       <c r="F50" t="n">
-        <v>-70.89</v>
+        <v>26.16</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0363</v>
+        <v>0.0139</v>
       </c>
       <c r="H50" t="n">
-        <v>154.98</v>
+        <v>109.47</v>
       </c>
       <c r="I50" t="n">
-        <v>1722.39</v>
+        <v>1666.51</v>
       </c>
       <c r="J50" t="n">
-        <v>1858.17</v>
+        <v>1719.32</v>
       </c>
       <c r="K50" t="n">
-        <v>1893.2</v>
+        <v>1805.03</v>
       </c>
       <c r="L50" t="n">
-        <v>1928.22</v>
+        <v>1890.75</v>
       </c>
       <c r="M50" t="n">
-        <v>2013.63</v>
+        <v>1960.01</v>
       </c>
       <c r="N50" t="n">
-        <v>2099.03</v>
+        <v>2029.27</v>
       </c>
       <c r="O50" t="n">
-        <v>2083.68</v>
+        <v>2131.44</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4696,64 +4698,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1882.78</v>
+        <v>1908.72</v>
       </c>
       <c r="C51" t="n">
-        <v>1937.17</v>
+        <v>1928.99</v>
       </c>
       <c r="D51" t="n">
-        <v>1827.7</v>
+        <v>1852.84</v>
       </c>
       <c r="E51" t="n">
-        <v>1908.68</v>
+        <v>1873.94</v>
       </c>
       <c r="F51" t="n">
-        <v>26.16</v>
+        <v>-34.74</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0182</v>
       </c>
       <c r="H51" t="n">
-        <v>109.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>1666.51</v>
+        <v>1718.23</v>
       </c>
       <c r="J51" t="n">
-        <v>1719.32</v>
+        <v>1812.34</v>
       </c>
       <c r="K51" t="n">
-        <v>1805.03</v>
+        <v>1853.95</v>
       </c>
       <c r="L51" t="n">
-        <v>1890.75</v>
+        <v>1895.56</v>
       </c>
       <c r="M51" t="n">
-        <v>1960.01</v>
+        <v>1963.42</v>
       </c>
       <c r="N51" t="n">
-        <v>2029.27</v>
+        <v>2031.28</v>
       </c>
       <c r="O51" t="n">
-        <v>2131.44</v>
+        <v>2046.64</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4761,12 +4763,14 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4778,64 +4782,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1908.72</v>
+        <v>1873.97</v>
       </c>
       <c r="C52" t="n">
-        <v>1928.99</v>
+        <v>2545.88</v>
       </c>
       <c r="D52" t="n">
-        <v>1852.84</v>
+        <v>1870.75</v>
       </c>
       <c r="E52" t="n">
-        <v>1873.94</v>
+        <v>2463.82</v>
       </c>
       <c r="F52" t="n">
-        <v>-34.74</v>
+        <v>589.87</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.3148</v>
       </c>
       <c r="H52" t="n">
-        <v>76.15000000000001</v>
+        <v>675.13</v>
       </c>
       <c r="I52" t="n">
-        <v>1718.23</v>
+        <v>1776.69</v>
       </c>
       <c r="J52" t="n">
-        <v>1812.34</v>
+        <v>1789.3</v>
       </c>
       <c r="K52" t="n">
-        <v>1853.95</v>
+        <v>1835.87</v>
       </c>
       <c r="L52" t="n">
-        <v>1895.56</v>
+        <v>1882.43</v>
       </c>
       <c r="M52" t="n">
-        <v>1963.42</v>
+        <v>1912.02</v>
       </c>
       <c r="N52" t="n">
-        <v>2031.28</v>
+        <v>1941.61</v>
       </c>
       <c r="O52" t="n">
-        <v>2046.64</v>
+        <v>2005.15</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4843,83 +4847,83 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1873.97</v>
+        <v>2463.64</v>
       </c>
       <c r="C53" t="n">
-        <v>2545.88</v>
+        <v>2564.27</v>
       </c>
       <c r="D53" t="n">
-        <v>1870.75</v>
+        <v>2389.47</v>
       </c>
       <c r="E53" t="n">
-        <v>2463.82</v>
+        <v>2417.94</v>
       </c>
       <c r="F53" t="n">
-        <v>589.87</v>
+        <v>-45.88</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.3148</v>
+        <v>-0.0186</v>
       </c>
       <c r="H53" t="n">
-        <v>675.13</v>
+        <v>174.81</v>
       </c>
       <c r="I53" t="n">
-        <v>1776.69</v>
+        <v>1195.61</v>
       </c>
       <c r="J53" t="n">
-        <v>1789.3</v>
+        <v>1916.43</v>
       </c>
       <c r="K53" t="n">
-        <v>1835.87</v>
+        <v>2126.25</v>
       </c>
       <c r="L53" t="n">
-        <v>1882.43</v>
+        <v>2336.07</v>
       </c>
       <c r="M53" t="n">
-        <v>1912.02</v>
+        <v>2801.38</v>
       </c>
       <c r="N53" t="n">
-        <v>1941.61</v>
+        <v>3266.7</v>
       </c>
       <c r="O53" t="n">
-        <v>2005.15</v>
+        <v>3221.01</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4932,78 +4936,76 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2463.64</v>
+        <v>2417.9</v>
       </c>
       <c r="C54" t="n">
-        <v>2564.27</v>
+        <v>2545.62</v>
       </c>
       <c r="D54" t="n">
-        <v>2389.47</v>
+        <v>2356.19</v>
       </c>
       <c r="E54" t="n">
-        <v>2417.94</v>
+        <v>2514.55</v>
       </c>
       <c r="F54" t="n">
-        <v>-45.88</v>
+        <v>96.61</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0186</v>
+        <v>0.04</v>
       </c>
       <c r="H54" t="n">
-        <v>174.81</v>
+        <v>189.44</v>
       </c>
       <c r="I54" t="n">
-        <v>1195.61</v>
+        <v>2214.66</v>
       </c>
       <c r="J54" t="n">
-        <v>1916.43</v>
+        <v>2213.67</v>
       </c>
       <c r="K54" t="n">
-        <v>2126.25</v>
+        <v>2330.54</v>
       </c>
       <c r="L54" t="n">
-        <v>2336.07</v>
+        <v>2447.41</v>
       </c>
       <c r="M54" t="n">
-        <v>2801.38</v>
+        <v>2505.34</v>
       </c>
       <c r="N54" t="n">
-        <v>3266.7</v>
+        <v>2563.28</v>
       </c>
       <c r="O54" t="n">
-        <v>3221.01</v>
+        <v>2739.08</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5016,11 +5018,13 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5028,64 +5032,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2417.9</v>
+        <v>2514.58</v>
       </c>
       <c r="C55" t="n">
-        <v>2545.62</v>
+        <v>2663.05</v>
       </c>
       <c r="D55" t="n">
-        <v>2356.19</v>
+        <v>2406.91</v>
       </c>
       <c r="E55" t="n">
-        <v>2514.55</v>
+        <v>2477.02</v>
       </c>
       <c r="F55" t="n">
-        <v>96.61</v>
+        <v>-37.53</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.0149</v>
       </c>
       <c r="H55" t="n">
-        <v>189.44</v>
+        <v>256.14</v>
       </c>
       <c r="I55" t="n">
-        <v>2214.66</v>
+        <v>2166.75</v>
       </c>
       <c r="J55" t="n">
-        <v>2213.67</v>
+        <v>2356.93</v>
       </c>
       <c r="K55" t="n">
-        <v>2330.54</v>
+        <v>2419.83</v>
       </c>
       <c r="L55" t="n">
-        <v>2447.41</v>
+        <v>2482.73</v>
       </c>
       <c r="M55" t="n">
-        <v>2505.34</v>
+        <v>2609.27</v>
       </c>
       <c r="N55" t="n">
-        <v>2563.28</v>
+        <v>2735.81</v>
       </c>
       <c r="O55" t="n">
-        <v>2739.08</v>
+        <v>2735.06</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5093,17 +5097,19 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U55" s="8" t="n">
@@ -5112,64 +5118,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2514.58</v>
+        <v>2476.6</v>
       </c>
       <c r="C56" t="n">
-        <v>2663.05</v>
+        <v>2659.72</v>
       </c>
       <c r="D56" t="n">
-        <v>2406.91</v>
+        <v>2357.96</v>
       </c>
       <c r="E56" t="n">
-        <v>2477.02</v>
+        <v>2643</v>
       </c>
       <c r="F56" t="n">
-        <v>-37.53</v>
+        <v>165.98</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.067</v>
       </c>
       <c r="H56" t="n">
-        <v>256.14</v>
+        <v>301.76</v>
       </c>
       <c r="I56" t="n">
-        <v>2166.75</v>
+        <v>2150.76</v>
       </c>
       <c r="J56" t="n">
-        <v>2356.93</v>
+        <v>2191.9</v>
       </c>
       <c r="K56" t="n">
-        <v>2419.83</v>
+        <v>2348.95</v>
       </c>
       <c r="L56" t="n">
-        <v>2482.73</v>
+        <v>2506</v>
       </c>
       <c r="M56" t="n">
-        <v>2609.27</v>
+        <v>2605.09</v>
       </c>
       <c r="N56" t="n">
-        <v>2735.81</v>
+        <v>2704.19</v>
       </c>
       <c r="O56" t="n">
-        <v>2735.06</v>
+        <v>2919.19</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5177,19 +5183,17 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5198,64 +5202,64 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2476.6</v>
+        <v>2642.78</v>
       </c>
       <c r="C57" t="n">
-        <v>2659.72</v>
+        <v>2805.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2357.96</v>
+        <v>2628.69</v>
       </c>
       <c r="E57" t="n">
-        <v>2643</v>
+        <v>2686.93</v>
       </c>
       <c r="F57" t="n">
-        <v>165.98</v>
+        <v>43.93</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.067</v>
+        <v>0.0166</v>
       </c>
       <c r="H57" t="n">
-        <v>301.76</v>
+        <v>176.81</v>
       </c>
       <c r="I57" t="n">
-        <v>2150.76</v>
+        <v>2056.2</v>
       </c>
       <c r="J57" t="n">
-        <v>2191.9</v>
+        <v>2408.32</v>
       </c>
       <c r="K57" t="n">
-        <v>2348.95</v>
+        <v>2492.12</v>
       </c>
       <c r="L57" t="n">
-        <v>2506</v>
+        <v>2575.92</v>
       </c>
       <c r="M57" t="n">
-        <v>2605.09</v>
+        <v>2793.88</v>
       </c>
       <c r="N57" t="n">
-        <v>2704.19</v>
+        <v>3011.84</v>
       </c>
       <c r="O57" t="n">
-        <v>2919.19</v>
+        <v>2961.48</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5282,64 +5286,60 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2642.78</v>
+        <v>2687.59</v>
       </c>
       <c r="C58" t="n">
-        <v>2805.5</v>
+        <v>2717.54</v>
       </c>
       <c r="D58" t="n">
-        <v>2628.69</v>
+        <v>2636.72</v>
       </c>
       <c r="E58" t="n">
-        <v>2673</v>
+        <v>2669.38</v>
       </c>
       <c r="F58" t="n">
-        <v>30</v>
+        <v>-17.55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0065</v>
       </c>
       <c r="H58" t="n">
-        <v>176.81</v>
+        <v>80.83</v>
       </c>
       <c r="I58" t="n">
-        <v>2056.2</v>
+        <v>2451.88</v>
       </c>
       <c r="J58" t="n">
-        <v>2408.32</v>
+        <v>2495.03</v>
       </c>
       <c r="K58" t="n">
-        <v>2492.12</v>
+        <v>2598.52</v>
       </c>
       <c r="L58" t="n">
-        <v>2575.92</v>
+        <v>2702.01</v>
       </c>
       <c r="M58" t="n">
-        <v>2793.88</v>
+        <v>2775.33</v>
       </c>
       <c r="N58" t="n">
-        <v>3011.84</v>
+        <v>2848.65</v>
       </c>
       <c r="O58" t="n">
-        <v>2961.48</v>
+        <v>2982.31</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5350,15 +5350,13 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5366,12 +5364,16 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>269.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3732.04</v>
+        <v>3868.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3787.74</v>
+        <v>3958.19</v>
       </c>
       <c r="K2" t="n">
-        <v>4123.94</v>
+        <v>4192.12</v>
       </c>
       <c r="L2" t="n">
-        <v>4460.15</v>
+        <v>4426.06</v>
       </c>
       <c r="M2" t="n">
-        <v>4656.1</v>
+        <v>4587.92</v>
       </c>
       <c r="N2" t="n">
-        <v>4852.05</v>
+        <v>4749.77</v>
       </c>
       <c r="O2" t="n">
-        <v>5328.5</v>
+        <v>5055.78</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,12 +685,14 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -5300,25 +5302,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2687.59</v>
+        <v>2687</v>
       </c>
       <c r="C58" t="n">
-        <v>2717.54</v>
+        <v>2742.02</v>
       </c>
       <c r="D58" t="n">
-        <v>2636.72</v>
+        <v>2635.48</v>
       </c>
       <c r="E58" t="n">
-        <v>2669.38</v>
+        <v>2680.09</v>
       </c>
       <c r="F58" t="n">
-        <v>-17.55</v>
+        <v>-6.84</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0025</v>
       </c>
       <c r="H58" t="n">
-        <v>80.83</v>
+        <v>106.54</v>
       </c>
       <c r="I58" t="n">
         <v>2451.88</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5305,22 +5305,22 @@
         <v>2687</v>
       </c>
       <c r="C58" t="n">
-        <v>2742.02</v>
+        <v>2746.01</v>
       </c>
       <c r="D58" t="n">
         <v>2635.48</v>
       </c>
       <c r="E58" t="n">
-        <v>2680.09</v>
+        <v>2681.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-6.84</v>
+        <v>-5.33</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.002</v>
       </c>
       <c r="H58" t="n">
-        <v>106.54</v>
+        <v>110.53</v>
       </c>
       <c r="I58" t="n">
         <v>2451.88</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>269.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3868.4</v>
+        <v>3899.36</v>
       </c>
       <c r="J2" t="n">
-        <v>3958.19</v>
+        <v>3996.89</v>
       </c>
       <c r="K2" t="n">
-        <v>4192.12</v>
+        <v>4207.6</v>
       </c>
       <c r="L2" t="n">
-        <v>4426.06</v>
+        <v>4418.32</v>
       </c>
       <c r="M2" t="n">
-        <v>4587.92</v>
+        <v>4572.44</v>
       </c>
       <c r="N2" t="n">
-        <v>4749.77</v>
+        <v>4726.56</v>
       </c>
       <c r="O2" t="n">
-        <v>5055.78</v>
+        <v>4993.87</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5311,13 +5311,13 @@
         <v>2635.48</v>
       </c>
       <c r="E58" t="n">
-        <v>2681.6</v>
+        <v>2699.08</v>
       </c>
       <c r="F58" t="n">
-        <v>-5.33</v>
+        <v>12.15</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0045</v>
       </c>
       <c r="H58" t="n">
         <v>110.53</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,31 +659,35 @@
         <v>269.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3899.36</v>
+        <v>4250.02</v>
       </c>
       <c r="J2" t="n">
-        <v>3996.89</v>
+        <v>4243.76</v>
       </c>
       <c r="K2" t="n">
-        <v>4207.6</v>
+        <v>4328.23</v>
       </c>
       <c r="L2" t="n">
-        <v>4418.32</v>
+        <v>4412.7</v>
       </c>
       <c r="M2" t="n">
-        <v>4572.44</v>
+        <v>4451.81</v>
       </c>
       <c r="N2" t="n">
-        <v>4726.56</v>
+        <v>4490.92</v>
       </c>
       <c r="O2" t="n">
-        <v>4993.87</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>4620.76</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -695,8 +699,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5305,22 +5311,22 @@
         <v>2687</v>
       </c>
       <c r="C58" t="n">
-        <v>2746.01</v>
+        <v>2773.52</v>
       </c>
       <c r="D58" t="n">
         <v>2635.48</v>
       </c>
       <c r="E58" t="n">
-        <v>2699.08</v>
+        <v>2719.14</v>
       </c>
       <c r="F58" t="n">
-        <v>12.15</v>
+        <v>32.21</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.012</v>
       </c>
       <c r="H58" t="n">
-        <v>110.53</v>
+        <v>138.04</v>
       </c>
       <c r="I58" t="n">
         <v>2451.88</v>
@@ -5352,9 +5358,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,140 +634,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4389.63</v>
+        <v>4305.38</v>
       </c>
       <c r="C2" t="n">
-        <v>4490.35</v>
+        <v>4763.36</v>
       </c>
       <c r="D2" t="n">
-        <v>4221.25</v>
+        <v>4277.85</v>
       </c>
       <c r="E2" t="n">
-        <v>4305.35</v>
+        <v>4609.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-84.67</v>
+        <v>304.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0193</v>
+        <v>0.0707</v>
       </c>
       <c r="H2" t="n">
-        <v>269.1</v>
+        <v>485.51</v>
       </c>
       <c r="I2" t="n">
-        <v>4250.02</v>
+        <v>3952.15</v>
       </c>
       <c r="J2" t="n">
-        <v>4243.76</v>
+        <v>4011.02</v>
       </c>
       <c r="K2" t="n">
-        <v>4328.23</v>
+        <v>4170.8</v>
       </c>
       <c r="L2" t="n">
-        <v>4412.7</v>
+        <v>4330.57</v>
       </c>
       <c r="M2" t="n">
-        <v>4451.81</v>
+        <v>4439.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4490.92</v>
+        <v>4549.22</v>
       </c>
       <c r="O2" t="n">
-        <v>4620.76</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>4759.45</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4305.38</v>
+        <v>4609.72</v>
       </c>
       <c r="C3" t="n">
-        <v>4763.36</v>
+        <v>4670.53</v>
       </c>
       <c r="D3" t="n">
-        <v>4277.85</v>
+        <v>4428.33</v>
       </c>
       <c r="E3" t="n">
-        <v>4609.6</v>
+        <v>4451.33</v>
       </c>
       <c r="F3" t="n">
-        <v>304.25</v>
+        <v>-158.27</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0707</v>
+        <v>-0.0343</v>
       </c>
       <c r="H3" t="n">
-        <v>485.51</v>
+        <v>242.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3952.15</v>
+        <v>3792.34</v>
       </c>
       <c r="J3" t="n">
-        <v>4011.02</v>
+        <v>4168.58</v>
       </c>
       <c r="K3" t="n">
-        <v>4170.8</v>
+        <v>4366.84</v>
       </c>
       <c r="L3" t="n">
-        <v>4330.57</v>
+        <v>4565.1</v>
       </c>
       <c r="M3" t="n">
-        <v>4439.9</v>
+        <v>4852.35</v>
       </c>
       <c r="N3" t="n">
-        <v>4549.22</v>
+        <v>5139.6</v>
       </c>
       <c r="O3" t="n">
-        <v>4759.45</v>
+        <v>5248.87</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -775,96 +769,100 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4609.72</v>
+        <v>4451.58</v>
       </c>
       <c r="C4" t="n">
-        <v>4670.53</v>
+        <v>4457.08</v>
       </c>
       <c r="D4" t="n">
-        <v>4428.33</v>
+        <v>3829.01</v>
       </c>
       <c r="E4" t="n">
-        <v>4451.33</v>
+        <v>4141.48</v>
       </c>
       <c r="F4" t="n">
-        <v>-158.27</v>
+        <v>-309.85</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0343</v>
+        <v>-0.0696</v>
       </c>
       <c r="H4" t="n">
-        <v>242.2</v>
+        <v>628.0700000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3792.34</v>
+        <v>4186.13</v>
       </c>
       <c r="J4" t="n">
-        <v>4168.58</v>
+        <v>4160.08</v>
       </c>
       <c r="K4" t="n">
-        <v>4366.84</v>
+        <v>4330.23</v>
       </c>
       <c r="L4" t="n">
-        <v>4565.1</v>
+        <v>4500.38</v>
       </c>
       <c r="M4" t="n">
-        <v>4852.35</v>
+        <v>4572.43</v>
       </c>
       <c r="N4" t="n">
-        <v>5139.6</v>
+        <v>4644.48</v>
       </c>
       <c r="O4" t="n">
-        <v>5248.87</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+        <v>4912.73</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -878,88 +876,80 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4451.58</v>
+        <v>4141.36</v>
       </c>
       <c r="C5" t="n">
-        <v>4457.08</v>
+        <v>4616.53</v>
       </c>
       <c r="D5" t="n">
-        <v>3829.01</v>
+        <v>4087.93</v>
       </c>
       <c r="E5" t="n">
-        <v>4141.48</v>
+        <v>4515.42</v>
       </c>
       <c r="F5" t="n">
-        <v>-309.85</v>
+        <v>373.95</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0696</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>628.0700000000001</v>
+        <v>528.61</v>
       </c>
       <c r="I5" t="n">
-        <v>4186.13</v>
+        <v>3200.94</v>
       </c>
       <c r="J5" t="n">
-        <v>4160.08</v>
+        <v>3512.62</v>
       </c>
       <c r="K5" t="n">
-        <v>4330.23</v>
+        <v>3827.44</v>
       </c>
       <c r="L5" t="n">
-        <v>4500.38</v>
+        <v>4142.26</v>
       </c>
       <c r="M5" t="n">
-        <v>4572.43</v>
+        <v>4455.51</v>
       </c>
       <c r="N5" t="n">
-        <v>4644.48</v>
+        <v>4768.76</v>
       </c>
       <c r="O5" t="n">
-        <v>4912.73</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
+        <v>5085.15</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -971,74 +961,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4141.36</v>
+        <v>4515.3</v>
       </c>
       <c r="C6" t="n">
-        <v>4616.53</v>
+        <v>4755.22</v>
       </c>
       <c r="D6" t="n">
-        <v>4087.93</v>
+        <v>3460.22</v>
       </c>
       <c r="E6" t="n">
-        <v>4515.42</v>
+        <v>4164.43</v>
       </c>
       <c r="F6" t="n">
-        <v>373.95</v>
+        <v>-351</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>528.61</v>
+        <v>1295</v>
       </c>
       <c r="I6" t="n">
-        <v>3200.94</v>
+        <v>3559.32</v>
       </c>
       <c r="J6" t="n">
-        <v>3512.62</v>
+        <v>4068.41</v>
       </c>
       <c r="K6" t="n">
-        <v>3827.44</v>
+        <v>4251.12</v>
       </c>
       <c r="L6" t="n">
-        <v>4142.26</v>
+        <v>4433.83</v>
       </c>
       <c r="M6" t="n">
-        <v>4455.51</v>
+        <v>4779.73</v>
       </c>
       <c r="N6" t="n">
-        <v>4768.76</v>
+        <v>5125.63</v>
       </c>
       <c r="O6" t="n">
-        <v>5085.15</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>5145.14</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1053,76 +1051,70 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4515.3</v>
+        <v>4164.05</v>
       </c>
       <c r="C7" t="n">
-        <v>4755.22</v>
+        <v>4292.85</v>
       </c>
       <c r="D7" t="n">
-        <v>3460.22</v>
+        <v>3678.62</v>
       </c>
       <c r="E7" t="n">
-        <v>4164.43</v>
+        <v>3984.65</v>
       </c>
       <c r="F7" t="n">
-        <v>-351</v>
+        <v>-179.78</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0432</v>
       </c>
       <c r="H7" t="n">
-        <v>1295</v>
+        <v>614.23</v>
       </c>
       <c r="I7" t="n">
-        <v>3559.32</v>
+        <v>2165.22</v>
       </c>
       <c r="J7" t="n">
-        <v>4068.41</v>
+        <v>2897.78</v>
       </c>
       <c r="K7" t="n">
-        <v>4251.12</v>
+        <v>3516.93</v>
       </c>
       <c r="L7" t="n">
-        <v>4433.83</v>
+        <v>4136.07</v>
       </c>
       <c r="M7" t="n">
-        <v>4779.73</v>
+        <v>4811.93</v>
       </c>
       <c r="N7" t="n">
-        <v>5125.63</v>
+        <v>5487.78</v>
       </c>
       <c r="O7" t="n">
-        <v>5145.14</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>6050.22</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1148,50 +1140,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4164.05</v>
+        <v>3984.7</v>
       </c>
       <c r="C8" t="n">
-        <v>4292.85</v>
+        <v>4177.31</v>
       </c>
       <c r="D8" t="n">
-        <v>3678.62</v>
+        <v>3718.08</v>
       </c>
       <c r="E8" t="n">
-        <v>3984.65</v>
+        <v>4157.99</v>
       </c>
       <c r="F8" t="n">
-        <v>-179.78</v>
+        <v>173.34</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0432</v>
+        <v>0.0435</v>
       </c>
       <c r="H8" t="n">
-        <v>614.23</v>
+        <v>459.23</v>
       </c>
       <c r="I8" t="n">
-        <v>2165.22</v>
+        <v>3064.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2897.78</v>
+        <v>3369.88</v>
       </c>
       <c r="K8" t="n">
-        <v>3516.93</v>
+        <v>3677.54</v>
       </c>
       <c r="L8" t="n">
-        <v>4136.07</v>
+        <v>3985.19</v>
       </c>
       <c r="M8" t="n">
-        <v>4811.93</v>
+        <v>4291.76</v>
       </c>
       <c r="N8" t="n">
-        <v>5487.78</v>
+        <v>4598.33</v>
       </c>
       <c r="O8" t="n">
-        <v>6050.22</v>
+        <v>4907.07</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1204,11 +1196,13 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1223,76 +1217,78 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3984.7</v>
+        <v>4158.01</v>
       </c>
       <c r="C9" t="n">
-        <v>4177.31</v>
+        <v>4250.67</v>
       </c>
       <c r="D9" t="n">
-        <v>3718.08</v>
+        <v>3681.91</v>
       </c>
       <c r="E9" t="n">
-        <v>4157.99</v>
+        <v>3911.06</v>
       </c>
       <c r="F9" t="n">
-        <v>173.34</v>
+        <v>-246.93</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0435</v>
+        <v>-0.0594</v>
       </c>
       <c r="H9" t="n">
-        <v>459.23</v>
+        <v>568.76</v>
       </c>
       <c r="I9" t="n">
-        <v>3064.4</v>
+        <v>3258.84</v>
       </c>
       <c r="J9" t="n">
-        <v>3369.88</v>
+        <v>3803.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3677.54</v>
+        <v>3928.37</v>
       </c>
       <c r="L9" t="n">
-        <v>3985.19</v>
+        <v>4052.84</v>
       </c>
       <c r="M9" t="n">
-        <v>4291.76</v>
+        <v>4387.61</v>
       </c>
       <c r="N9" t="n">
-        <v>4598.33</v>
+        <v>4722.37</v>
       </c>
       <c r="O9" t="n">
-        <v>4907.07</v>
+        <v>4636.54</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1307,60 +1303,62 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4158.01</v>
+        <v>3911.75</v>
       </c>
       <c r="C10" t="n">
-        <v>4250.67</v>
+        <v>3912.63</v>
       </c>
       <c r="D10" t="n">
-        <v>3681.91</v>
+        <v>3063.09</v>
       </c>
       <c r="E10" t="n">
-        <v>3911.06</v>
+        <v>3582.62</v>
       </c>
       <c r="F10" t="n">
-        <v>-246.93</v>
+        <v>-328.44</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>568.76</v>
+        <v>849.55</v>
       </c>
       <c r="I10" t="n">
-        <v>3258.84</v>
+        <v>3113.15</v>
       </c>
       <c r="J10" t="n">
-        <v>3803.9</v>
+        <v>3314.69</v>
       </c>
       <c r="K10" t="n">
-        <v>3928.37</v>
+        <v>3626.68</v>
       </c>
       <c r="L10" t="n">
-        <v>4052.84</v>
+        <v>3938.68</v>
       </c>
       <c r="M10" t="n">
-        <v>4387.61</v>
+        <v>4195.44</v>
       </c>
       <c r="N10" t="n">
-        <v>4722.37</v>
+        <v>4452.21</v>
       </c>
       <c r="O10" t="n">
-        <v>4636.54</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
+        <v>4819.43</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
@@ -1372,7 +1370,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1391,76 +1389,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3911.75</v>
+        <v>3583.44</v>
       </c>
       <c r="C11" t="n">
-        <v>3912.63</v>
+        <v>3656.15</v>
       </c>
       <c r="D11" t="n">
-        <v>3063.09</v>
+        <v>3007.07</v>
       </c>
       <c r="E11" t="n">
-        <v>3582.62</v>
+        <v>3092.85</v>
       </c>
       <c r="F11" t="n">
-        <v>-328.44</v>
+        <v>-489.77</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1367</v>
       </c>
       <c r="H11" t="n">
-        <v>849.55</v>
+        <v>649.08</v>
       </c>
       <c r="I11" t="n">
-        <v>3113.15</v>
+        <v>2213.54</v>
       </c>
       <c r="J11" t="n">
-        <v>3314.69</v>
+        <v>2780.46</v>
       </c>
       <c r="K11" t="n">
-        <v>3626.68</v>
+        <v>3157.85</v>
       </c>
       <c r="L11" t="n">
-        <v>3938.68</v>
+        <v>3535.24</v>
       </c>
       <c r="M11" t="n">
-        <v>4195.44</v>
+        <v>4007.39</v>
       </c>
       <c r="N11" t="n">
-        <v>4452.21</v>
+        <v>4479.55</v>
       </c>
       <c r="O11" t="n">
-        <v>4819.43</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4762.18</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1484,50 +1474,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3583.44</v>
+        <v>3092.94</v>
       </c>
       <c r="C12" t="n">
-        <v>3656.15</v>
+        <v>3218.13</v>
       </c>
       <c r="D12" t="n">
-        <v>3007.07</v>
+        <v>2626.87</v>
       </c>
       <c r="E12" t="n">
-        <v>3092.85</v>
+        <v>2801.68</v>
       </c>
       <c r="F12" t="n">
-        <v>-489.77</v>
+        <v>-291.17</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.1367</v>
+        <v>-0.0941</v>
       </c>
       <c r="H12" t="n">
-        <v>649.08</v>
+        <v>591.26</v>
       </c>
       <c r="I12" t="n">
-        <v>2213.54</v>
+        <v>2358</v>
       </c>
       <c r="J12" t="n">
-        <v>2780.46</v>
+        <v>2324.39</v>
       </c>
       <c r="K12" t="n">
-        <v>3157.85</v>
+        <v>2768.31</v>
       </c>
       <c r="L12" t="n">
-        <v>3535.24</v>
+        <v>3212.23</v>
       </c>
       <c r="M12" t="n">
-        <v>4007.39</v>
+        <v>3417.39</v>
       </c>
       <c r="N12" t="n">
-        <v>4479.55</v>
+        <v>3622.54</v>
       </c>
       <c r="O12" t="n">
-        <v>4762.18</v>
+        <v>4305.23</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1540,7 +1530,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1564,50 +1554,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3092.94</v>
+        <v>2801.2</v>
       </c>
       <c r="C13" t="n">
-        <v>3218.13</v>
+        <v>3095.03</v>
       </c>
       <c r="D13" t="n">
-        <v>2626.87</v>
+        <v>2763.38</v>
       </c>
       <c r="E13" t="n">
-        <v>2801.68</v>
+        <v>2992.11</v>
       </c>
       <c r="F13" t="n">
-        <v>-291.17</v>
+        <v>190.44</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0941</v>
+        <v>0.068</v>
       </c>
       <c r="H13" t="n">
-        <v>591.26</v>
+        <v>331.66</v>
       </c>
       <c r="I13" t="n">
-        <v>2358</v>
+        <v>2035.61</v>
       </c>
       <c r="J13" t="n">
-        <v>2324.39</v>
+        <v>2150</v>
       </c>
       <c r="K13" t="n">
-        <v>2768.31</v>
+        <v>2506.05</v>
       </c>
       <c r="L13" t="n">
-        <v>3212.23</v>
+        <v>2862.09</v>
       </c>
       <c r="M13" t="n">
-        <v>3417.39</v>
+        <v>3097.31</v>
       </c>
       <c r="N13" t="n">
-        <v>3622.54</v>
+        <v>3332.52</v>
       </c>
       <c r="O13" t="n">
-        <v>4305.23</v>
+        <v>3809.39</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1615,19 +1605,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1639,55 +1629,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2801.2</v>
+        <v>2991.92</v>
       </c>
       <c r="C14" t="n">
-        <v>3095.03</v>
+        <v>3238.56</v>
       </c>
       <c r="D14" t="n">
-        <v>2763.38</v>
+        <v>2720.44</v>
       </c>
       <c r="E14" t="n">
-        <v>2992.11</v>
+        <v>3061.3</v>
       </c>
       <c r="F14" t="n">
-        <v>190.44</v>
+        <v>69.19</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.068</v>
+        <v>0.0231</v>
       </c>
       <c r="H14" t="n">
-        <v>331.66</v>
+        <v>518.12</v>
       </c>
       <c r="I14" t="n">
-        <v>2035.61</v>
+        <v>2431.72</v>
       </c>
       <c r="J14" t="n">
-        <v>2150</v>
+        <v>2691.91</v>
       </c>
       <c r="K14" t="n">
-        <v>2506.05</v>
+        <v>2826.28</v>
       </c>
       <c r="L14" t="n">
-        <v>2862.09</v>
+        <v>2960.66</v>
       </c>
       <c r="M14" t="n">
-        <v>3097.31</v>
+        <v>3157.94</v>
       </c>
       <c r="N14" t="n">
-        <v>3332.52</v>
+        <v>3355.22</v>
       </c>
       <c r="O14" t="n">
-        <v>3809.39</v>
+        <v>3426.69</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1695,10 +1689,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1728,50 +1724,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2991.92</v>
+        <v>3061.01</v>
       </c>
       <c r="C15" t="n">
-        <v>3238.56</v>
+        <v>3446.62</v>
       </c>
       <c r="D15" t="n">
-        <v>2720.44</v>
+        <v>3034.69</v>
       </c>
       <c r="E15" t="n">
-        <v>3061.3</v>
+        <v>3060.59</v>
       </c>
       <c r="F15" t="n">
-        <v>69.19</v>
+        <v>-0.71</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0231</v>
+        <v>-0.0002</v>
       </c>
       <c r="H15" t="n">
-        <v>518.12</v>
+        <v>411.93</v>
       </c>
       <c r="I15" t="n">
-        <v>2431.72</v>
+        <v>2202.32</v>
       </c>
       <c r="J15" t="n">
-        <v>2691.91</v>
+        <v>2584.09</v>
       </c>
       <c r="K15" t="n">
-        <v>2826.28</v>
+        <v>2802.24</v>
       </c>
       <c r="L15" t="n">
-        <v>2960.66</v>
+        <v>3020.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3157.94</v>
+        <v>3320.36</v>
       </c>
       <c r="N15" t="n">
-        <v>3355.22</v>
+        <v>3620.32</v>
       </c>
       <c r="O15" t="n">
-        <v>3426.69</v>
+        <v>3756.67</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1779,19 +1775,17 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1814,50 +1808,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3061.01</v>
+        <v>3060.48</v>
       </c>
       <c r="C16" t="n">
-        <v>3446.62</v>
+        <v>3175.12</v>
       </c>
       <c r="D16" t="n">
-        <v>3034.69</v>
+        <v>2777.12</v>
       </c>
       <c r="E16" t="n">
-        <v>3060.59</v>
+        <v>3001.61</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.71</v>
+        <v>-58.98</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H16" t="n">
-        <v>411.93</v>
+        <v>398</v>
       </c>
       <c r="I16" t="n">
-        <v>2202.32</v>
+        <v>2622.76</v>
       </c>
       <c r="J16" t="n">
-        <v>2584.09</v>
+        <v>2558.63</v>
       </c>
       <c r="K16" t="n">
-        <v>2802.24</v>
+        <v>2854.63</v>
       </c>
       <c r="L16" t="n">
-        <v>3020.4</v>
+        <v>3150.63</v>
       </c>
       <c r="M16" t="n">
-        <v>3320.36</v>
+        <v>3266.56</v>
       </c>
       <c r="N16" t="n">
-        <v>3620.32</v>
+        <v>3382.49</v>
       </c>
       <c r="O16" t="n">
-        <v>3756.67</v>
+        <v>3858.55</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,18 +1859,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1889,59 +1883,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3060.48</v>
+        <v>3001.61</v>
       </c>
       <c r="C17" t="n">
-        <v>3175.12</v>
+        <v>3073.35</v>
       </c>
       <c r="D17" t="n">
-        <v>2777.12</v>
+        <v>2888.99</v>
       </c>
       <c r="E17" t="n">
-        <v>3001.61</v>
+        <v>2948.57</v>
       </c>
       <c r="F17" t="n">
-        <v>-58.98</v>
+        <v>-53.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0177</v>
       </c>
       <c r="H17" t="n">
-        <v>398</v>
+        <v>184.37</v>
       </c>
       <c r="I17" t="n">
-        <v>2622.76</v>
+        <v>2379.12</v>
       </c>
       <c r="J17" t="n">
-        <v>2558.63</v>
+        <v>2616.36</v>
       </c>
       <c r="K17" t="n">
-        <v>2854.63</v>
+        <v>2802.61</v>
       </c>
       <c r="L17" t="n">
-        <v>3150.63</v>
+        <v>2988.87</v>
       </c>
       <c r="M17" t="n">
-        <v>3266.56</v>
+        <v>3200.61</v>
       </c>
       <c r="N17" t="n">
-        <v>3382.49</v>
+        <v>3412.36</v>
       </c>
       <c r="O17" t="n">
-        <v>3858.55</v>
+        <v>3573.12</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,14 +1939,12 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1973,55 +1961,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3001.61</v>
+        <v>2948.56</v>
       </c>
       <c r="C18" t="n">
-        <v>3073.35</v>
+        <v>3160.55</v>
       </c>
       <c r="D18" t="n">
-        <v>2888.99</v>
+        <v>2908.75</v>
       </c>
       <c r="E18" t="n">
-        <v>2948.57</v>
+        <v>3140.71</v>
       </c>
       <c r="F18" t="n">
-        <v>-53.05</v>
+        <v>192.14</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0177</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>184.37</v>
+        <v>251.8</v>
       </c>
       <c r="I18" t="n">
-        <v>2379.12</v>
+        <v>2704.62</v>
       </c>
       <c r="J18" t="n">
-        <v>2616.36</v>
+        <v>2747.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2802.61</v>
+        <v>2856.39</v>
       </c>
       <c r="L18" t="n">
-        <v>2988.87</v>
+        <v>2964.87</v>
       </c>
       <c r="M18" t="n">
-        <v>3200.61</v>
+        <v>3040.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3412.36</v>
+        <v>3116.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3573.12</v>
+        <v>3257.72</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2034,76 +2026,76 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2948.56</v>
+        <v>3141.49</v>
       </c>
       <c r="C19" t="n">
-        <v>3160.55</v>
+        <v>3303.56</v>
       </c>
       <c r="D19" t="n">
-        <v>2908.75</v>
+        <v>3052.51</v>
       </c>
       <c r="E19" t="n">
-        <v>3140.71</v>
+        <v>3118.89</v>
       </c>
       <c r="F19" t="n">
-        <v>192.14</v>
+        <v>-21.83</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="H19" t="n">
-        <v>251.8</v>
+        <v>251.05</v>
       </c>
       <c r="I19" t="n">
-        <v>2704.62</v>
+        <v>2656.95</v>
       </c>
       <c r="J19" t="n">
-        <v>2747.9</v>
+        <v>2941.94</v>
       </c>
       <c r="K19" t="n">
-        <v>2856.39</v>
+        <v>3014.81</v>
       </c>
       <c r="L19" t="n">
-        <v>2964.87</v>
+        <v>3087.68</v>
       </c>
       <c r="M19" t="n">
-        <v>3040.75</v>
+        <v>3266.61</v>
       </c>
       <c r="N19" t="n">
-        <v>3116.63</v>
+        <v>3445.54</v>
       </c>
       <c r="O19" t="n">
-        <v>3257.72</v>
+        <v>3412.35</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,9 +2106,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2124,10 +2116,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2137,55 +2127,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3141.49</v>
+        <v>3118.83</v>
       </c>
       <c r="C20" t="n">
-        <v>3303.56</v>
+        <v>3397.9</v>
       </c>
       <c r="D20" t="n">
-        <v>3052.51</v>
+        <v>3068.07</v>
       </c>
       <c r="E20" t="n">
-        <v>3118.89</v>
+        <v>3281.16</v>
       </c>
       <c r="F20" t="n">
-        <v>-21.83</v>
+        <v>162.27</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.052</v>
       </c>
       <c r="H20" t="n">
-        <v>251.05</v>
+        <v>329.82</v>
       </c>
       <c r="I20" t="n">
-        <v>2656.95</v>
+        <v>2801.46</v>
       </c>
       <c r="J20" t="n">
-        <v>2941.94</v>
+        <v>2838.26</v>
       </c>
       <c r="K20" t="n">
-        <v>3014.81</v>
+        <v>2993.36</v>
       </c>
       <c r="L20" t="n">
-        <v>3087.68</v>
+        <v>3148.46</v>
       </c>
       <c r="M20" t="n">
-        <v>3266.61</v>
+        <v>3244.41</v>
       </c>
       <c r="N20" t="n">
-        <v>3445.54</v>
+        <v>3340.36</v>
       </c>
       <c r="O20" t="n">
-        <v>3412.35</v>
+        <v>3554.62</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2196,19 +2190,21 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2217,90 +2213,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3118.83</v>
+        <v>3282.2</v>
       </c>
       <c r="C21" t="n">
-        <v>3397.9</v>
+        <v>3282.65</v>
       </c>
       <c r="D21" t="n">
-        <v>3068.07</v>
+        <v>2785.9</v>
       </c>
       <c r="E21" t="n">
-        <v>3281.16</v>
+        <v>2815.9</v>
       </c>
       <c r="F21" t="n">
-        <v>162.27</v>
+        <v>-465.26</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.052</v>
+        <v>-0.1418</v>
       </c>
       <c r="H21" t="n">
-        <v>329.82</v>
+        <v>496.76</v>
       </c>
       <c r="I21" t="n">
-        <v>2801.46</v>
+        <v>2738.25</v>
       </c>
       <c r="J21" t="n">
-        <v>2838.26</v>
+        <v>2975.42</v>
       </c>
       <c r="K21" t="n">
-        <v>2993.36</v>
+        <v>3116.25</v>
       </c>
       <c r="L21" t="n">
-        <v>3148.46</v>
+        <v>3257.07</v>
       </c>
       <c r="M21" t="n">
-        <v>3244.41</v>
+        <v>3446.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3340.36</v>
+        <v>3635.07</v>
       </c>
       <c r="O21" t="n">
-        <v>3554.62</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>3727.72</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2308,67 +2302,65 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3282.2</v>
+        <v>2815.77</v>
       </c>
       <c r="C22" t="n">
-        <v>3282.65</v>
+        <v>3040.72</v>
       </c>
       <c r="D22" t="n">
-        <v>2785.9</v>
+        <v>2224.12</v>
       </c>
       <c r="E22" t="n">
-        <v>2815.9</v>
+        <v>2267.96</v>
       </c>
       <c r="F22" t="n">
-        <v>-465.26</v>
+        <v>-547.9400000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.1418</v>
+        <v>-0.1946</v>
       </c>
       <c r="H22" t="n">
-        <v>496.76</v>
+        <v>816.6</v>
       </c>
       <c r="I22" t="n">
-        <v>2738.25</v>
+        <v>2289.14</v>
       </c>
       <c r="J22" t="n">
-        <v>2975.42</v>
+        <v>2209.96</v>
       </c>
       <c r="K22" t="n">
-        <v>3116.25</v>
+        <v>2567.52</v>
       </c>
       <c r="L22" t="n">
-        <v>3257.07</v>
+        <v>2925.09</v>
       </c>
       <c r="M22" t="n">
-        <v>3446.07</v>
+        <v>3064.28</v>
       </c>
       <c r="N22" t="n">
-        <v>3635.07</v>
+        <v>3203.47</v>
       </c>
       <c r="O22" t="n">
-        <v>3727.72</v>
+        <v>3779.41</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2392,65 +2384,63 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2815.77</v>
+        <v>2267.56</v>
       </c>
       <c r="C23" t="n">
-        <v>3040.72</v>
+        <v>2393.06</v>
       </c>
       <c r="D23" t="n">
-        <v>2224.12</v>
+        <v>1748.63</v>
       </c>
       <c r="E23" t="n">
-        <v>2267.96</v>
+        <v>2088.76</v>
       </c>
       <c r="F23" t="n">
-        <v>-547.9400000000001</v>
+        <v>-179.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.1946</v>
+        <v>-0.079</v>
       </c>
       <c r="H23" t="n">
-        <v>816.6</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2289.14</v>
+        <v>1407.52</v>
       </c>
       <c r="J23" t="n">
-        <v>2209.96</v>
+        <v>1269.14</v>
       </c>
       <c r="K23" t="n">
-        <v>2567.52</v>
+        <v>1859.66</v>
       </c>
       <c r="L23" t="n">
-        <v>2925.09</v>
+        <v>2450.19</v>
       </c>
       <c r="M23" t="n">
-        <v>3064.28</v>
+        <v>2676.27</v>
       </c>
       <c r="N23" t="n">
-        <v>3203.47</v>
+        <v>2902.34</v>
       </c>
       <c r="O23" t="n">
-        <v>3779.41</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>3857.32</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2474,50 +2464,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2267.56</v>
+        <v>2087.92</v>
       </c>
       <c r="C24" t="n">
-        <v>2393.06</v>
+        <v>2144.98</v>
       </c>
       <c r="D24" t="n">
-        <v>1748.63</v>
+        <v>1897.33</v>
       </c>
       <c r="E24" t="n">
-        <v>2088.76</v>
+        <v>1966.04</v>
       </c>
       <c r="F24" t="n">
-        <v>-179.2</v>
+        <v>-122.72</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.0588</v>
       </c>
       <c r="H24" t="n">
-        <v>644.4400000000001</v>
+        <v>247.64</v>
       </c>
       <c r="I24" t="n">
-        <v>1407.52</v>
+        <v>1104.19</v>
       </c>
       <c r="J24" t="n">
-        <v>1269.14</v>
+        <v>1453.29</v>
       </c>
       <c r="K24" t="n">
-        <v>1859.66</v>
+        <v>1766.55</v>
       </c>
       <c r="L24" t="n">
-        <v>2450.19</v>
+        <v>2079.8</v>
       </c>
       <c r="M24" t="n">
-        <v>2676.27</v>
+        <v>2410.98</v>
       </c>
       <c r="N24" t="n">
-        <v>2902.34</v>
+        <v>2742.16</v>
       </c>
       <c r="O24" t="n">
-        <v>3857.32</v>
+        <v>3037.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,14 +2515,12 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2549,55 +2537,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2087.92</v>
+        <v>1965.92</v>
       </c>
       <c r="C25" t="n">
-        <v>2144.98</v>
+        <v>2037.16</v>
       </c>
       <c r="D25" t="n">
-        <v>1897.33</v>
+        <v>1906.82</v>
       </c>
       <c r="E25" t="n">
-        <v>1966.04</v>
+        <v>1957.81</v>
       </c>
       <c r="F25" t="n">
-        <v>-122.72</v>
+        <v>-8.24</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0042</v>
       </c>
       <c r="H25" t="n">
-        <v>247.64</v>
+        <v>130.34</v>
       </c>
       <c r="I25" t="n">
-        <v>1104.19</v>
+        <v>1649.69</v>
       </c>
       <c r="J25" t="n">
-        <v>1453.29</v>
+        <v>1690.85</v>
       </c>
       <c r="K25" t="n">
-        <v>1766.55</v>
+        <v>1842.22</v>
       </c>
       <c r="L25" t="n">
-        <v>2079.8</v>
+        <v>1993.6</v>
       </c>
       <c r="M25" t="n">
-        <v>2410.98</v>
+        <v>2089.86</v>
       </c>
       <c r="N25" t="n">
-        <v>2742.16</v>
+        <v>2186.13</v>
       </c>
       <c r="O25" t="n">
-        <v>3037.5</v>
+        <v>2392.62</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2608,7 +2600,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2636,70 +2628,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1965.92</v>
+        <v>1958.14</v>
       </c>
       <c r="C26" t="n">
-        <v>2037.16</v>
+        <v>2145.51</v>
       </c>
       <c r="D26" t="n">
-        <v>1906.82</v>
+        <v>1804.11</v>
       </c>
       <c r="E26" t="n">
-        <v>1957.81</v>
+        <v>1939.07</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.24</v>
+        <v>-18.74</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>130.34</v>
+        <v>341.39</v>
       </c>
       <c r="I26" t="n">
-        <v>1649.69</v>
+        <v>1776.49</v>
       </c>
       <c r="J26" t="n">
-        <v>1690.85</v>
+        <v>1820.38</v>
       </c>
       <c r="K26" t="n">
-        <v>1842.22</v>
+        <v>1892.64</v>
       </c>
       <c r="L26" t="n">
-        <v>1993.6</v>
+        <v>1964.9</v>
       </c>
       <c r="M26" t="n">
-        <v>2089.86</v>
+        <v>2022.97</v>
       </c>
       <c r="N26" t="n">
-        <v>2186.13</v>
+        <v>2081.05</v>
       </c>
       <c r="O26" t="n">
-        <v>2392.62</v>
+        <v>2167.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2718,78 +2718,72 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1958.14</v>
+        <v>1939.06</v>
       </c>
       <c r="C27" t="n">
-        <v>2145.51</v>
+        <v>2198.66</v>
       </c>
       <c r="D27" t="n">
-        <v>1804.11</v>
+        <v>1915.3</v>
       </c>
       <c r="E27" t="n">
-        <v>1939.07</v>
+        <v>1936.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-18.74</v>
+        <v>-2.46</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0013</v>
       </c>
       <c r="H27" t="n">
-        <v>341.39</v>
+        <v>283.36</v>
       </c>
       <c r="I27" t="n">
-        <v>1776.49</v>
+        <v>1462.72</v>
       </c>
       <c r="J27" t="n">
-        <v>1820.38</v>
+        <v>1579.8</v>
       </c>
       <c r="K27" t="n">
-        <v>1892.64</v>
+        <v>1768.37</v>
       </c>
       <c r="L27" t="n">
-        <v>1964.9</v>
+        <v>1956.94</v>
       </c>
       <c r="M27" t="n">
-        <v>2022.97</v>
+        <v>2109.76</v>
       </c>
       <c r="N27" t="n">
-        <v>2081.05</v>
+        <v>2262.59</v>
       </c>
       <c r="O27" t="n">
-        <v>2167.5</v>
+        <v>2486.9</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2801,57 +2795,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1939.06</v>
+        <v>1936.64</v>
       </c>
       <c r="C28" t="n">
-        <v>2198.66</v>
+        <v>2206.81</v>
       </c>
       <c r="D28" t="n">
-        <v>1915.3</v>
+        <v>1930.6</v>
       </c>
       <c r="E28" t="n">
-        <v>1936.6</v>
+        <v>2177.48</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.46</v>
+        <v>240.87</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.1244</v>
       </c>
       <c r="H28" t="n">
-        <v>283.36</v>
+        <v>276.21</v>
       </c>
       <c r="I28" t="n">
-        <v>1462.72</v>
+        <v>1631.95</v>
       </c>
       <c r="J28" t="n">
-        <v>1579.8</v>
+        <v>1593.06</v>
       </c>
       <c r="K28" t="n">
-        <v>1768.37</v>
+        <v>1794.93</v>
       </c>
       <c r="L28" t="n">
-        <v>1956.94</v>
+        <v>1996.79</v>
       </c>
       <c r="M28" t="n">
-        <v>2109.76</v>
+        <v>2078.28</v>
       </c>
       <c r="N28" t="n">
-        <v>2262.59</v>
+        <v>2159.77</v>
       </c>
       <c r="O28" t="n">
-        <v>2486.9</v>
+        <v>2482.01</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2864,7 +2858,7 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2872,70 +2866,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1936.64</v>
+        <v>2177.78</v>
       </c>
       <c r="C29" t="n">
-        <v>2206.81</v>
+        <v>2384.47</v>
       </c>
       <c r="D29" t="n">
-        <v>1930.6</v>
+        <v>2027.05</v>
       </c>
       <c r="E29" t="n">
-        <v>2177.48</v>
+        <v>2053.05</v>
       </c>
       <c r="F29" t="n">
-        <v>240.87</v>
+        <v>-124.43</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1244</v>
+        <v>-0.0571</v>
       </c>
       <c r="H29" t="n">
-        <v>276.21</v>
+        <v>357.42</v>
       </c>
       <c r="I29" t="n">
-        <v>1631.95</v>
+        <v>1654.39</v>
       </c>
       <c r="J29" t="n">
-        <v>1593.06</v>
+        <v>1955.65</v>
       </c>
       <c r="K29" t="n">
-        <v>1794.93</v>
+        <v>2039.37</v>
       </c>
       <c r="L29" t="n">
-        <v>1996.79</v>
+        <v>2123.09</v>
       </c>
       <c r="M29" t="n">
-        <v>2078.28</v>
+        <v>2315.58</v>
       </c>
       <c r="N29" t="n">
-        <v>2159.77</v>
+        <v>2508.08</v>
       </c>
       <c r="O29" t="n">
-        <v>2482.01</v>
+        <v>2483.03</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2943,12 +2935,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2956,10 +2950,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2969,55 +2961,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2177.78</v>
+        <v>2052.95</v>
       </c>
       <c r="C30" t="n">
-        <v>2384.47</v>
+        <v>2198.37</v>
       </c>
       <c r="D30" t="n">
-        <v>2027.05</v>
+        <v>1939.53</v>
       </c>
       <c r="E30" t="n">
-        <v>2053.05</v>
+        <v>1982.56</v>
       </c>
       <c r="F30" t="n">
-        <v>-124.43</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0571</v>
+        <v>-0.0343</v>
       </c>
       <c r="H30" t="n">
-        <v>357.42</v>
+        <v>258.84</v>
       </c>
       <c r="I30" t="n">
-        <v>1654.39</v>
+        <v>1669.63</v>
       </c>
       <c r="J30" t="n">
-        <v>1955.65</v>
+        <v>1619.28</v>
       </c>
       <c r="K30" t="n">
-        <v>2039.37</v>
+        <v>1874.34</v>
       </c>
       <c r="L30" t="n">
-        <v>2123.09</v>
+        <v>2129.4</v>
       </c>
       <c r="M30" t="n">
-        <v>2315.58</v>
+        <v>2231.76</v>
       </c>
       <c r="N30" t="n">
-        <v>2508.08</v>
+        <v>2334.11</v>
       </c>
       <c r="O30" t="n">
-        <v>2483.03</v>
+        <v>2741.89</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3030,15 +3026,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3053,57 +3047,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2052.95</v>
+        <v>1982.55</v>
       </c>
       <c r="C31" t="n">
-        <v>2198.37</v>
+        <v>2165.67</v>
       </c>
       <c r="D31" t="n">
-        <v>1939.53</v>
+        <v>1979.08</v>
       </c>
       <c r="E31" t="n">
-        <v>1982.56</v>
+        <v>2109</v>
       </c>
       <c r="F31" t="n">
-        <v>-70.48999999999999</v>
+        <v>126.44</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0343</v>
+        <v>0.0638</v>
       </c>
       <c r="H31" t="n">
-        <v>258.84</v>
+        <v>186.59</v>
       </c>
       <c r="I31" t="n">
-        <v>1669.63</v>
+        <v>1680.69</v>
       </c>
       <c r="J31" t="n">
-        <v>1619.28</v>
+        <v>1680.52</v>
       </c>
       <c r="K31" t="n">
-        <v>1874.34</v>
+        <v>1853.14</v>
       </c>
       <c r="L31" t="n">
-        <v>2129.4</v>
+        <v>2025.75</v>
       </c>
       <c r="M31" t="n">
-        <v>2231.76</v>
+        <v>2111.98</v>
       </c>
       <c r="N31" t="n">
-        <v>2334.11</v>
+        <v>2198.21</v>
       </c>
       <c r="O31" t="n">
-        <v>2741.89</v>
+        <v>2457.21</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3111,19 +3105,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3137,57 +3131,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1982.55</v>
+        <v>2108.94</v>
       </c>
       <c r="C32" t="n">
-        <v>2165.67</v>
+        <v>2327.46</v>
       </c>
       <c r="D32" t="n">
-        <v>1979.08</v>
+        <v>2061.47</v>
       </c>
       <c r="E32" t="n">
-        <v>2109</v>
+        <v>2192.2</v>
       </c>
       <c r="F32" t="n">
-        <v>126.44</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0638</v>
+        <v>0.0395</v>
       </c>
       <c r="H32" t="n">
-        <v>186.59</v>
+        <v>265.99</v>
       </c>
       <c r="I32" t="n">
-        <v>1680.69</v>
+        <v>1792.49</v>
       </c>
       <c r="J32" t="n">
-        <v>1680.52</v>
+        <v>1940.72</v>
       </c>
       <c r="K32" t="n">
-        <v>1853.14</v>
+        <v>2015.7</v>
       </c>
       <c r="L32" t="n">
-        <v>2025.75</v>
+        <v>2090.68</v>
       </c>
       <c r="M32" t="n">
-        <v>2111.98</v>
+        <v>2202.29</v>
       </c>
       <c r="N32" t="n">
-        <v>2198.21</v>
+        <v>2313.9</v>
       </c>
       <c r="O32" t="n">
-        <v>2457.21</v>
+        <v>2352.26</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3198,7 +3192,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3208,8 +3202,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3219,59 +3215,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2108.94</v>
+        <v>2192.33</v>
       </c>
       <c r="C33" t="n">
-        <v>2327.46</v>
+        <v>2464.78</v>
       </c>
       <c r="D33" t="n">
-        <v>2061.47</v>
+        <v>2176.32</v>
       </c>
       <c r="E33" t="n">
-        <v>2192.2</v>
+        <v>2264.92</v>
       </c>
       <c r="F33" t="n">
-        <v>83.20999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0332</v>
       </c>
       <c r="H33" t="n">
-        <v>265.99</v>
+        <v>288.46</v>
       </c>
       <c r="I33" t="n">
-        <v>1792.49</v>
+        <v>1795.48</v>
       </c>
       <c r="J33" t="n">
-        <v>1940.72</v>
+        <v>1925.08</v>
       </c>
       <c r="K33" t="n">
-        <v>2015.7</v>
+        <v>2059.21</v>
       </c>
       <c r="L33" t="n">
-        <v>2090.68</v>
+        <v>2193.33</v>
       </c>
       <c r="M33" t="n">
-        <v>2202.29</v>
+        <v>2325.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2313.9</v>
+        <v>2457.06</v>
       </c>
       <c r="O33" t="n">
-        <v>2352.26</v>
+        <v>2593.45</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3282,7 +3274,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3310,50 +3302,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2192.33</v>
+        <v>2264.87</v>
       </c>
       <c r="C34" t="n">
-        <v>2464.78</v>
+        <v>2422.86</v>
       </c>
       <c r="D34" t="n">
-        <v>2176.32</v>
+        <v>2262.05</v>
       </c>
       <c r="E34" t="n">
-        <v>2264.92</v>
+        <v>2369.73</v>
       </c>
       <c r="F34" t="n">
-        <v>72.72</v>
+        <v>104.81</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0463</v>
       </c>
       <c r="H34" t="n">
-        <v>288.46</v>
+        <v>160.81</v>
       </c>
       <c r="I34" t="n">
-        <v>1795.48</v>
+        <v>1887.87</v>
       </c>
       <c r="J34" t="n">
-        <v>1925.08</v>
+        <v>1948.64</v>
       </c>
       <c r="K34" t="n">
-        <v>2059.21</v>
+        <v>2120.69</v>
       </c>
       <c r="L34" t="n">
-        <v>2193.33</v>
+        <v>2292.74</v>
       </c>
       <c r="M34" t="n">
-        <v>2325.2</v>
+        <v>2409.15</v>
       </c>
       <c r="N34" t="n">
-        <v>2457.06</v>
+        <v>2525.56</v>
       </c>
       <c r="O34" t="n">
-        <v>2593.45</v>
+        <v>2753.24</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3364,7 +3356,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3374,10 +3366,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3387,74 +3377,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2264.87</v>
+        <v>2369.84</v>
       </c>
       <c r="C35" t="n">
-        <v>2422.86</v>
+        <v>2403.73</v>
       </c>
       <c r="D35" t="n">
-        <v>2262.05</v>
+        <v>2221.22</v>
       </c>
       <c r="E35" t="n">
-        <v>2369.73</v>
+        <v>2321.64</v>
       </c>
       <c r="F35" t="n">
-        <v>104.81</v>
+        <v>-48.09</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0463</v>
+        <v>-0.0203</v>
       </c>
       <c r="H35" t="n">
-        <v>160.81</v>
+        <v>182.5</v>
       </c>
       <c r="I35" t="n">
-        <v>1887.87</v>
+        <v>2101.25</v>
       </c>
       <c r="J35" t="n">
-        <v>1948.64</v>
+        <v>2222.56</v>
       </c>
       <c r="K35" t="n">
-        <v>2120.69</v>
+        <v>2289.33</v>
       </c>
       <c r="L35" t="n">
-        <v>2292.74</v>
+        <v>2356.09</v>
       </c>
       <c r="M35" t="n">
-        <v>2409.15</v>
+        <v>2450.13</v>
       </c>
       <c r="N35" t="n">
-        <v>2525.56</v>
+        <v>2544.17</v>
       </c>
       <c r="O35" t="n">
-        <v>2753.24</v>
+        <v>2583.67</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3469,79 +3465,77 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2369.84</v>
+        <v>2321.82</v>
       </c>
       <c r="C36" t="n">
-        <v>2403.73</v>
+        <v>2423.04</v>
       </c>
       <c r="D36" t="n">
-        <v>2221.22</v>
+        <v>2265.83</v>
       </c>
       <c r="E36" t="n">
-        <v>2321.64</v>
+        <v>2369.04</v>
       </c>
       <c r="F36" t="n">
-        <v>-48.09</v>
+        <v>47.41</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="H36" t="n">
-        <v>182.5</v>
+        <v>157.21</v>
       </c>
       <c r="I36" t="n">
-        <v>2101.25</v>
+        <v>2038.72</v>
       </c>
       <c r="J36" t="n">
-        <v>2222.56</v>
+        <v>2143.71</v>
       </c>
       <c r="K36" t="n">
-        <v>2289.33</v>
+        <v>2230.38</v>
       </c>
       <c r="L36" t="n">
-        <v>2356.09</v>
+        <v>2317.06</v>
       </c>
       <c r="M36" t="n">
-        <v>2450.13</v>
+        <v>2412.89</v>
       </c>
       <c r="N36" t="n">
-        <v>2544.17</v>
+        <v>2508.72</v>
       </c>
       <c r="O36" t="n">
-        <v>2583.67</v>
+        <v>2586.23</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3553,78 +3547,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2321.82</v>
+        <v>2369.19</v>
       </c>
       <c r="C37" t="n">
-        <v>2423.04</v>
+        <v>2374.3</v>
       </c>
       <c r="D37" t="n">
-        <v>2265.83</v>
+        <v>2097.02</v>
       </c>
       <c r="E37" t="n">
-        <v>2369.04</v>
+        <v>2127.65</v>
       </c>
       <c r="F37" t="n">
-        <v>47.41</v>
+        <v>-241.4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.1019</v>
       </c>
       <c r="H37" t="n">
-        <v>157.21</v>
+        <v>277.28</v>
       </c>
       <c r="I37" t="n">
-        <v>2038.72</v>
+        <v>2108.63</v>
       </c>
       <c r="J37" t="n">
-        <v>2143.71</v>
+        <v>2224.14</v>
       </c>
       <c r="K37" t="n">
-        <v>2230.38</v>
+        <v>2290.44</v>
       </c>
       <c r="L37" t="n">
-        <v>2317.06</v>
+        <v>2356.74</v>
       </c>
       <c r="M37" t="n">
-        <v>2412.89</v>
+        <v>2447.65</v>
       </c>
       <c r="N37" t="n">
-        <v>2508.72</v>
+        <v>2538.55</v>
       </c>
       <c r="O37" t="n">
-        <v>2586.23</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+        <v>2580.25</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3632,9 +3626,9 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3642,69 +3636,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2369.19</v>
+        <v>2127.68</v>
       </c>
       <c r="C38" t="n">
-        <v>2374.3</v>
+        <v>2155.96</v>
       </c>
       <c r="D38" t="n">
-        <v>2097.02</v>
+        <v>2010.55</v>
       </c>
       <c r="E38" t="n">
-        <v>2127.65</v>
+        <v>2097.99</v>
       </c>
       <c r="F38" t="n">
-        <v>-241.4</v>
+        <v>-29.65</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.1019</v>
+        <v>-0.0139</v>
       </c>
       <c r="H38" t="n">
-        <v>277.28</v>
+        <v>145.41</v>
       </c>
       <c r="I38" t="n">
-        <v>2108.63</v>
+        <v>1819.74</v>
       </c>
       <c r="J38" t="n">
-        <v>2224.14</v>
+        <v>1796.35</v>
       </c>
       <c r="K38" t="n">
-        <v>2290.44</v>
+        <v>1989</v>
       </c>
       <c r="L38" t="n">
-        <v>2356.74</v>
+        <v>2181.65</v>
       </c>
       <c r="M38" t="n">
-        <v>2447.65</v>
+        <v>2266.29</v>
       </c>
       <c r="N38" t="n">
-        <v>2538.55</v>
+        <v>2350.92</v>
       </c>
       <c r="O38" t="n">
-        <v>2580.25</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>2651.59</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3726,50 +3714,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2127.68</v>
+        <v>2097.99</v>
       </c>
       <c r="C39" t="n">
-        <v>2155.96</v>
+        <v>2138.41</v>
       </c>
       <c r="D39" t="n">
-        <v>2010.55</v>
+        <v>1966.28</v>
       </c>
       <c r="E39" t="n">
-        <v>2097.99</v>
+        <v>2004.34</v>
       </c>
       <c r="F39" t="n">
-        <v>-29.65</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.0446</v>
       </c>
       <c r="H39" t="n">
-        <v>145.41</v>
+        <v>172.13</v>
       </c>
       <c r="I39" t="n">
-        <v>1819.74</v>
+        <v>1865.14</v>
       </c>
       <c r="J39" t="n">
-        <v>1796.35</v>
+        <v>1959.95</v>
       </c>
       <c r="K39" t="n">
-        <v>1989</v>
+        <v>2025.29</v>
       </c>
       <c r="L39" t="n">
-        <v>2181.65</v>
+        <v>2090.63</v>
       </c>
       <c r="M39" t="n">
-        <v>2266.29</v>
+        <v>2170.7</v>
       </c>
       <c r="N39" t="n">
-        <v>2350.92</v>
+        <v>2250.78</v>
       </c>
       <c r="O39" t="n">
-        <v>2651.59</v>
+        <v>2301.38</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3777,12 +3765,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3804,63 +3794,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2097.99</v>
+        <v>2004.24</v>
       </c>
       <c r="C40" t="n">
-        <v>2138.41</v>
+        <v>2017.61</v>
       </c>
       <c r="D40" t="n">
-        <v>1966.28</v>
+        <v>1506.51</v>
       </c>
       <c r="E40" t="n">
-        <v>2004.34</v>
+        <v>1686.4</v>
       </c>
       <c r="F40" t="n">
-        <v>-93.65000000000001</v>
+        <v>-317.95</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0446</v>
+        <v>-0.1586</v>
       </c>
       <c r="H40" t="n">
-        <v>172.13</v>
+        <v>511.1</v>
       </c>
       <c r="I40" t="n">
-        <v>1865.14</v>
+        <v>1794.15</v>
       </c>
       <c r="J40" t="n">
-        <v>1959.95</v>
+        <v>1808.21</v>
       </c>
       <c r="K40" t="n">
-        <v>2025.29</v>
+        <v>1918.28</v>
       </c>
       <c r="L40" t="n">
-        <v>2090.63</v>
+        <v>2028.34</v>
       </c>
       <c r="M40" t="n">
-        <v>2170.7</v>
+        <v>2090.41</v>
       </c>
       <c r="N40" t="n">
-        <v>2250.78</v>
+        <v>2152.47</v>
       </c>
       <c r="O40" t="n">
-        <v>2301.38</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>2310.54</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3884,69 +3878,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2004.24</v>
+        <v>1686.25</v>
       </c>
       <c r="C41" t="n">
-        <v>2017.61</v>
+        <v>1729.35</v>
       </c>
       <c r="D41" t="n">
-        <v>1506.51</v>
+        <v>1603.83</v>
       </c>
       <c r="E41" t="n">
-        <v>1686.4</v>
+        <v>1724.61</v>
       </c>
       <c r="F41" t="n">
-        <v>-317.95</v>
+        <v>38.22</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.1586</v>
+        <v>0.0227</v>
       </c>
       <c r="H41" t="n">
-        <v>511.1</v>
+        <v>125.53</v>
       </c>
       <c r="I41" t="n">
-        <v>1794.15</v>
+        <v>995.4</v>
       </c>
       <c r="J41" t="n">
-        <v>1808.21</v>
+        <v>1137.46</v>
       </c>
       <c r="K41" t="n">
-        <v>1918.28</v>
+        <v>1430.85</v>
       </c>
       <c r="L41" t="n">
-        <v>2028.34</v>
+        <v>1724.23</v>
       </c>
       <c r="M41" t="n">
-        <v>2090.41</v>
+        <v>1941.95</v>
       </c>
       <c r="N41" t="n">
-        <v>2152.47</v>
+        <v>2159.67</v>
       </c>
       <c r="O41" t="n">
-        <v>2310.54</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>2528.71</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3963,55 +3951,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1686.25</v>
+        <v>1724.57</v>
       </c>
       <c r="C42" t="n">
-        <v>1729.35</v>
+        <v>1847.77</v>
       </c>
       <c r="D42" t="n">
-        <v>1603.83</v>
+        <v>1670.1</v>
       </c>
       <c r="E42" t="n">
-        <v>1724.61</v>
+        <v>1704.58</v>
       </c>
       <c r="F42" t="n">
-        <v>38.22</v>
+        <v>-20.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0227</v>
+        <v>-0.0116</v>
       </c>
       <c r="H42" t="n">
-        <v>125.53</v>
+        <v>177.67</v>
       </c>
       <c r="I42" t="n">
-        <v>995.4</v>
+        <v>1478.3</v>
       </c>
       <c r="J42" t="n">
-        <v>1137.46</v>
+        <v>1628.1</v>
       </c>
       <c r="K42" t="n">
-        <v>1430.85</v>
+        <v>1661.85</v>
       </c>
       <c r="L42" t="n">
-        <v>1724.23</v>
+        <v>1695.6</v>
       </c>
       <c r="M42" t="n">
-        <v>1941.95</v>
+        <v>1787.38</v>
       </c>
       <c r="N42" t="n">
-        <v>2159.67</v>
+        <v>1879.15</v>
       </c>
       <c r="O42" t="n">
-        <v>2528.71</v>
+        <v>1854.88</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4022,13 +4014,15 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4050,50 +4044,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1724.57</v>
+        <v>1704.63</v>
       </c>
       <c r="C43" t="n">
-        <v>1847.77</v>
+        <v>1776.83</v>
       </c>
       <c r="D43" t="n">
-        <v>1670.1</v>
+        <v>1510.51</v>
       </c>
       <c r="E43" t="n">
-        <v>1704.58</v>
+        <v>1570.36</v>
       </c>
       <c r="F43" t="n">
-        <v>-20.03</v>
+        <v>-134.22</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>177.67</v>
+        <v>266.33</v>
       </c>
       <c r="I43" t="n">
-        <v>1478.3</v>
+        <v>1492.44</v>
       </c>
       <c r="J43" t="n">
-        <v>1628.1</v>
+        <v>1499.74</v>
       </c>
       <c r="K43" t="n">
-        <v>1661.85</v>
+        <v>1615.75</v>
       </c>
       <c r="L43" t="n">
-        <v>1695.6</v>
+        <v>1731.76</v>
       </c>
       <c r="M43" t="n">
-        <v>1787.38</v>
+        <v>1793.41</v>
       </c>
       <c r="N43" t="n">
-        <v>1879.15</v>
+        <v>1855.07</v>
       </c>
       <c r="O43" t="n">
-        <v>1854.88</v>
+        <v>2025.44</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4101,18 +4095,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4125,59 +4119,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1704.63</v>
+        <v>1569.99</v>
       </c>
       <c r="C44" t="n">
-        <v>1776.83</v>
+        <v>1805.91</v>
       </c>
       <c r="D44" t="n">
-        <v>1510.51</v>
+        <v>1549.25</v>
       </c>
       <c r="E44" t="n">
-        <v>1570.36</v>
+        <v>1783.01</v>
       </c>
       <c r="F44" t="n">
-        <v>-134.22</v>
+        <v>212.64</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.1354</v>
       </c>
       <c r="H44" t="n">
-        <v>266.33</v>
+        <v>256.66</v>
       </c>
       <c r="I44" t="n">
-        <v>1492.44</v>
+        <v>1244.18</v>
       </c>
       <c r="J44" t="n">
-        <v>1499.74</v>
+        <v>1267.38</v>
       </c>
       <c r="K44" t="n">
-        <v>1615.75</v>
+        <v>1437.2</v>
       </c>
       <c r="L44" t="n">
-        <v>1731.76</v>
+        <v>1607.02</v>
       </c>
       <c r="M44" t="n">
-        <v>1793.41</v>
+        <v>1703.52</v>
       </c>
       <c r="N44" t="n">
-        <v>1855.07</v>
+        <v>1800.03</v>
       </c>
       <c r="O44" t="n">
-        <v>2025.44</v>
+        <v>2043.16</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4185,22 +4175,24 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4209,55 +4201,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1569.99</v>
+        <v>1783</v>
       </c>
       <c r="C45" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D45" t="n">
-        <v>1549.25</v>
+        <v>1711.9</v>
       </c>
       <c r="E45" t="n">
-        <v>1783.01</v>
+        <v>1805.79</v>
       </c>
       <c r="F45" t="n">
-        <v>212.64</v>
+        <v>22.78</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.1354</v>
+        <v>0.0128</v>
       </c>
       <c r="H45" t="n">
-        <v>256.66</v>
+        <v>117.61</v>
       </c>
       <c r="I45" t="n">
-        <v>1244.18</v>
+        <v>1292.59</v>
       </c>
       <c r="J45" t="n">
-        <v>1267.38</v>
+        <v>1579.06</v>
       </c>
       <c r="K45" t="n">
-        <v>1437.2</v>
+        <v>1654.67</v>
       </c>
       <c r="L45" t="n">
-        <v>1607.02</v>
+        <v>1730.29</v>
       </c>
       <c r="M45" t="n">
-        <v>1703.52</v>
+        <v>1911.34</v>
       </c>
       <c r="N45" t="n">
-        <v>1800.03</v>
+        <v>2092.38</v>
       </c>
       <c r="O45" t="n">
-        <v>2043.16</v>
+        <v>2062.58</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4268,20 +4264,16 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4300,50 +4292,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1783</v>
+        <v>1805.76</v>
       </c>
       <c r="C46" t="n">
-        <v>1829.51</v>
+        <v>1944.16</v>
       </c>
       <c r="D46" t="n">
-        <v>1711.9</v>
+        <v>1749.35</v>
       </c>
       <c r="E46" t="n">
-        <v>1805.79</v>
+        <v>1871.51</v>
       </c>
       <c r="F46" t="n">
-        <v>22.78</v>
+        <v>65.72</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0364</v>
       </c>
       <c r="H46" t="n">
-        <v>117.61</v>
+        <v>194.81</v>
       </c>
       <c r="I46" t="n">
-        <v>1292.59</v>
+        <v>1594.29</v>
       </c>
       <c r="J46" t="n">
-        <v>1579.06</v>
+        <v>1705.72</v>
       </c>
       <c r="K46" t="n">
-        <v>1654.67</v>
+        <v>1746.98</v>
       </c>
       <c r="L46" t="n">
-        <v>1730.29</v>
+        <v>1788.25</v>
       </c>
       <c r="M46" t="n">
-        <v>1911.34</v>
+        <v>1864.59</v>
       </c>
       <c r="N46" t="n">
-        <v>2092.38</v>
+        <v>1940.94</v>
       </c>
       <c r="O46" t="n">
-        <v>2062.58</v>
+        <v>1947.13</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4354,16 +4346,20 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4382,50 +4378,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1805.76</v>
+        <v>1871.28</v>
       </c>
       <c r="C47" t="n">
-        <v>1944.16</v>
+        <v>1963.25</v>
       </c>
       <c r="D47" t="n">
-        <v>1749.35</v>
+        <v>1842.82</v>
       </c>
       <c r="E47" t="n">
-        <v>1871.51</v>
+        <v>1953.41</v>
       </c>
       <c r="F47" t="n">
-        <v>65.72</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0364</v>
+        <v>0.0438</v>
       </c>
       <c r="H47" t="n">
-        <v>194.81</v>
+        <v>120.43</v>
       </c>
       <c r="I47" t="n">
-        <v>1594.29</v>
+        <v>1554.53</v>
       </c>
       <c r="J47" t="n">
-        <v>1705.72</v>
+        <v>1689.07</v>
       </c>
       <c r="K47" t="n">
-        <v>1746.98</v>
+        <v>1774.1</v>
       </c>
       <c r="L47" t="n">
-        <v>1788.25</v>
+        <v>1859.13</v>
       </c>
       <c r="M47" t="n">
-        <v>1864.59</v>
+        <v>1968.92</v>
       </c>
       <c r="N47" t="n">
-        <v>1940.94</v>
+        <v>2078.7</v>
       </c>
       <c r="O47" t="n">
-        <v>1947.13</v>
+        <v>2138.97</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4436,7 +4432,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4446,10 +4442,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4468,69 +4462,71 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1871.28</v>
+        <v>1953.41</v>
       </c>
       <c r="C48" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D48" t="n">
-        <v>1842.82</v>
+        <v>1821.49</v>
       </c>
       <c r="E48" t="n">
-        <v>1953.41</v>
+        <v>1882.52</v>
       </c>
       <c r="F48" t="n">
-        <v>81.90000000000001</v>
+        <v>-70.89</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0363</v>
       </c>
       <c r="H48" t="n">
-        <v>120.43</v>
+        <v>154.98</v>
       </c>
       <c r="I48" t="n">
-        <v>1554.53</v>
+        <v>1722.39</v>
       </c>
       <c r="J48" t="n">
-        <v>1689.07</v>
+        <v>1858.17</v>
       </c>
       <c r="K48" t="n">
-        <v>1774.1</v>
+        <v>1893.2</v>
       </c>
       <c r="L48" t="n">
-        <v>1859.13</v>
+        <v>1928.22</v>
       </c>
       <c r="M48" t="n">
-        <v>1968.92</v>
+        <v>2013.63</v>
       </c>
       <c r="N48" t="n">
-        <v>2078.7</v>
+        <v>2099.03</v>
       </c>
       <c r="O48" t="n">
-        <v>2138.97</v>
+        <v>2083.68</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4545,74 +4541,70 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1953.41</v>
+        <v>1882.78</v>
       </c>
       <c r="C49" t="n">
-        <v>1976.46</v>
+        <v>1937.17</v>
       </c>
       <c r="D49" t="n">
-        <v>1821.49</v>
+        <v>1827.7</v>
       </c>
       <c r="E49" t="n">
-        <v>1882.52</v>
+        <v>1908.68</v>
       </c>
       <c r="F49" t="n">
-        <v>-70.89</v>
+        <v>26.16</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0363</v>
+        <v>0.0139</v>
       </c>
       <c r="H49" t="n">
-        <v>154.98</v>
+        <v>109.47</v>
       </c>
       <c r="I49" t="n">
-        <v>1722.39</v>
+        <v>1666.51</v>
       </c>
       <c r="J49" t="n">
-        <v>1858.17</v>
+        <v>1719.32</v>
       </c>
       <c r="K49" t="n">
-        <v>1893.2</v>
+        <v>1805.03</v>
       </c>
       <c r="L49" t="n">
-        <v>1928.22</v>
+        <v>1890.75</v>
       </c>
       <c r="M49" t="n">
-        <v>2013.63</v>
+        <v>1960.01</v>
       </c>
       <c r="N49" t="n">
-        <v>2099.03</v>
+        <v>2029.27</v>
       </c>
       <c r="O49" t="n">
-        <v>2083.68</v>
+        <v>2131.44</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4631,57 +4623,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1882.78</v>
+        <v>1908.72</v>
       </c>
       <c r="C50" t="n">
-        <v>1937.17</v>
+        <v>1928.99</v>
       </c>
       <c r="D50" t="n">
-        <v>1827.7</v>
+        <v>1852.84</v>
       </c>
       <c r="E50" t="n">
-        <v>1908.68</v>
+        <v>1873.94</v>
       </c>
       <c r="F50" t="n">
-        <v>26.16</v>
+        <v>-34.74</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0182</v>
       </c>
       <c r="H50" t="n">
-        <v>109.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>1666.51</v>
+        <v>1718.23</v>
       </c>
       <c r="J50" t="n">
-        <v>1719.32</v>
+        <v>1812.34</v>
       </c>
       <c r="K50" t="n">
-        <v>1805.03</v>
+        <v>1853.95</v>
       </c>
       <c r="L50" t="n">
-        <v>1890.75</v>
+        <v>1895.56</v>
       </c>
       <c r="M50" t="n">
-        <v>1960.01</v>
+        <v>1963.42</v>
       </c>
       <c r="N50" t="n">
-        <v>2029.27</v>
+        <v>2031.28</v>
       </c>
       <c r="O50" t="n">
-        <v>2131.44</v>
+        <v>2046.64</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4689,12 +4681,14 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4713,57 +4707,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1908.72</v>
+        <v>1873.97</v>
       </c>
       <c r="C51" t="n">
-        <v>1928.99</v>
+        <v>2545.88</v>
       </c>
       <c r="D51" t="n">
-        <v>1852.84</v>
+        <v>1870.75</v>
       </c>
       <c r="E51" t="n">
-        <v>1873.94</v>
+        <v>2463.82</v>
       </c>
       <c r="F51" t="n">
-        <v>-34.74</v>
+        <v>589.87</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.3148</v>
       </c>
       <c r="H51" t="n">
-        <v>76.15000000000001</v>
+        <v>675.13</v>
       </c>
       <c r="I51" t="n">
-        <v>1718.23</v>
+        <v>1776.69</v>
       </c>
       <c r="J51" t="n">
-        <v>1812.34</v>
+        <v>1789.3</v>
       </c>
       <c r="K51" t="n">
-        <v>1853.95</v>
+        <v>1835.87</v>
       </c>
       <c r="L51" t="n">
-        <v>1895.56</v>
+        <v>1882.43</v>
       </c>
       <c r="M51" t="n">
-        <v>1963.42</v>
+        <v>1912.02</v>
       </c>
       <c r="N51" t="n">
-        <v>2031.28</v>
+        <v>1941.61</v>
       </c>
       <c r="O51" t="n">
-        <v>2046.64</v>
+        <v>2005.15</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4771,83 +4765,83 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1873.97</v>
+        <v>2463.64</v>
       </c>
       <c r="C52" t="n">
-        <v>2545.88</v>
+        <v>2564.27</v>
       </c>
       <c r="D52" t="n">
-        <v>1870.75</v>
+        <v>2389.47</v>
       </c>
       <c r="E52" t="n">
-        <v>2463.82</v>
+        <v>2417.94</v>
       </c>
       <c r="F52" t="n">
-        <v>589.87</v>
+        <v>-45.88</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.3148</v>
+        <v>-0.0186</v>
       </c>
       <c r="H52" t="n">
-        <v>675.13</v>
+        <v>174.81</v>
       </c>
       <c r="I52" t="n">
-        <v>1776.69</v>
+        <v>1195.61</v>
       </c>
       <c r="J52" t="n">
-        <v>1789.3</v>
+        <v>1916.43</v>
       </c>
       <c r="K52" t="n">
-        <v>1835.87</v>
+        <v>2126.25</v>
       </c>
       <c r="L52" t="n">
-        <v>1882.43</v>
+        <v>2336.07</v>
       </c>
       <c r="M52" t="n">
-        <v>1912.02</v>
+        <v>2801.38</v>
       </c>
       <c r="N52" t="n">
-        <v>1941.61</v>
+        <v>3266.7</v>
       </c>
       <c r="O52" t="n">
-        <v>2005.15</v>
+        <v>3221.01</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4858,80 +4852,78 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2463.64</v>
+        <v>2417.9</v>
       </c>
       <c r="C53" t="n">
-        <v>2564.27</v>
+        <v>2545.62</v>
       </c>
       <c r="D53" t="n">
-        <v>2389.47</v>
+        <v>2356.19</v>
       </c>
       <c r="E53" t="n">
-        <v>2417.94</v>
+        <v>2514.55</v>
       </c>
       <c r="F53" t="n">
-        <v>-45.88</v>
+        <v>96.61</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0186</v>
+        <v>0.04</v>
       </c>
       <c r="H53" t="n">
-        <v>174.81</v>
+        <v>189.44</v>
       </c>
       <c r="I53" t="n">
-        <v>1195.61</v>
+        <v>2214.66</v>
       </c>
       <c r="J53" t="n">
-        <v>1916.43</v>
+        <v>2213.67</v>
       </c>
       <c r="K53" t="n">
-        <v>2126.25</v>
+        <v>2330.54</v>
       </c>
       <c r="L53" t="n">
-        <v>2336.07</v>
+        <v>2447.41</v>
       </c>
       <c r="M53" t="n">
-        <v>2801.38</v>
+        <v>2505.34</v>
       </c>
       <c r="N53" t="n">
-        <v>3266.7</v>
+        <v>2563.28</v>
       </c>
       <c r="O53" t="n">
-        <v>3221.01</v>
+        <v>2739.08</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4942,13 +4934,15 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4963,57 +4957,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2417.9</v>
+        <v>2514.58</v>
       </c>
       <c r="C54" t="n">
-        <v>2545.62</v>
+        <v>2663.05</v>
       </c>
       <c r="D54" t="n">
-        <v>2356.19</v>
+        <v>2406.91</v>
       </c>
       <c r="E54" t="n">
-        <v>2514.55</v>
+        <v>2477.02</v>
       </c>
       <c r="F54" t="n">
-        <v>96.61</v>
+        <v>-37.53</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.0149</v>
       </c>
       <c r="H54" t="n">
-        <v>189.44</v>
+        <v>256.14</v>
       </c>
       <c r="I54" t="n">
-        <v>2214.66</v>
+        <v>2166.75</v>
       </c>
       <c r="J54" t="n">
-        <v>2213.67</v>
+        <v>2356.93</v>
       </c>
       <c r="K54" t="n">
-        <v>2330.54</v>
+        <v>2419.83</v>
       </c>
       <c r="L54" t="n">
-        <v>2447.41</v>
+        <v>2482.73</v>
       </c>
       <c r="M54" t="n">
-        <v>2505.34</v>
+        <v>2609.27</v>
       </c>
       <c r="N54" t="n">
-        <v>2563.28</v>
+        <v>2735.81</v>
       </c>
       <c r="O54" t="n">
-        <v>2739.08</v>
+        <v>2735.06</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5021,17 +5015,19 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5047,57 +5043,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2514.58</v>
+        <v>2476.6</v>
       </c>
       <c r="C55" t="n">
-        <v>2663.05</v>
+        <v>2659.72</v>
       </c>
       <c r="D55" t="n">
-        <v>2406.91</v>
+        <v>2357.96</v>
       </c>
       <c r="E55" t="n">
-        <v>2477.02</v>
+        <v>2643</v>
       </c>
       <c r="F55" t="n">
-        <v>-37.53</v>
+        <v>165.98</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.067</v>
       </c>
       <c r="H55" t="n">
-        <v>256.14</v>
+        <v>301.76</v>
       </c>
       <c r="I55" t="n">
-        <v>2166.75</v>
+        <v>2150.76</v>
       </c>
       <c r="J55" t="n">
-        <v>2356.93</v>
+        <v>2191.9</v>
       </c>
       <c r="K55" t="n">
-        <v>2419.83</v>
+        <v>2348.95</v>
       </c>
       <c r="L55" t="n">
-        <v>2482.73</v>
+        <v>2506</v>
       </c>
       <c r="M55" t="n">
-        <v>2609.27</v>
+        <v>2605.09</v>
       </c>
       <c r="N55" t="n">
-        <v>2735.81</v>
+        <v>2704.19</v>
       </c>
       <c r="O55" t="n">
-        <v>2735.06</v>
+        <v>2919.19</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5105,19 +5101,17 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U55" s="8" t="n">
@@ -5133,57 +5127,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2476.6</v>
+        <v>2642.78</v>
       </c>
       <c r="C56" t="n">
-        <v>2659.72</v>
+        <v>2805.5</v>
       </c>
       <c r="D56" t="n">
-        <v>2357.96</v>
+        <v>2628.69</v>
       </c>
       <c r="E56" t="n">
-        <v>2643</v>
+        <v>2686.93</v>
       </c>
       <c r="F56" t="n">
-        <v>165.98</v>
+        <v>43.93</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.067</v>
+        <v>0.0166</v>
       </c>
       <c r="H56" t="n">
-        <v>301.76</v>
+        <v>176.81</v>
       </c>
       <c r="I56" t="n">
-        <v>2150.76</v>
+        <v>2056.2</v>
       </c>
       <c r="J56" t="n">
-        <v>2191.9</v>
+        <v>2408.32</v>
       </c>
       <c r="K56" t="n">
-        <v>2348.95</v>
+        <v>2492.12</v>
       </c>
       <c r="L56" t="n">
-        <v>2506</v>
+        <v>2575.92</v>
       </c>
       <c r="M56" t="n">
-        <v>2605.09</v>
+        <v>2793.88</v>
       </c>
       <c r="N56" t="n">
-        <v>2704.19</v>
+        <v>3011.84</v>
       </c>
       <c r="O56" t="n">
-        <v>2919.19</v>
+        <v>2961.48</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5194,7 +5188,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5215,59 +5209,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2642.78</v>
+        <v>2687</v>
       </c>
       <c r="C57" t="n">
-        <v>2805.5</v>
+        <v>2773.52</v>
       </c>
       <c r="D57" t="n">
-        <v>2628.69</v>
+        <v>2635.48</v>
       </c>
       <c r="E57" t="n">
-        <v>2686.93</v>
+        <v>2726.51</v>
       </c>
       <c r="F57" t="n">
-        <v>43.93</v>
+        <v>39.58</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0147</v>
       </c>
       <c r="H57" t="n">
-        <v>176.81</v>
+        <v>138.04</v>
       </c>
       <c r="I57" t="n">
-        <v>2056.2</v>
+        <v>2451.88</v>
       </c>
       <c r="J57" t="n">
-        <v>2408.32</v>
+        <v>2495.03</v>
       </c>
       <c r="K57" t="n">
-        <v>2492.12</v>
+        <v>2598.52</v>
       </c>
       <c r="L57" t="n">
-        <v>2575.92</v>
+        <v>2702.01</v>
       </c>
       <c r="M57" t="n">
-        <v>2793.88</v>
+        <v>2775.33</v>
       </c>
       <c r="N57" t="n">
-        <v>3011.84</v>
+        <v>2848.65</v>
       </c>
       <c r="O57" t="n">
-        <v>2961.48</v>
+        <v>2982.31</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5278,15 +5268,13 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5299,55 +5287,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2687</v>
+        <v>2726.72</v>
       </c>
       <c r="C58" t="n">
-        <v>2773.52</v>
+        <v>2735.62</v>
       </c>
       <c r="D58" t="n">
-        <v>2635.48</v>
+        <v>2683.87</v>
       </c>
       <c r="E58" t="n">
-        <v>2719.14</v>
+        <v>2718.72</v>
       </c>
       <c r="F58" t="n">
-        <v>32.21</v>
+        <v>-7.79</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.0029</v>
       </c>
       <c r="H58" t="n">
-        <v>138.04</v>
+        <v>51.75</v>
       </c>
       <c r="I58" t="n">
-        <v>2451.88</v>
+        <v>2497.44</v>
       </c>
       <c r="J58" t="n">
-        <v>2495.03</v>
+        <v>2599.47</v>
       </c>
       <c r="K58" t="n">
-        <v>2598.52</v>
+        <v>2657.49</v>
       </c>
       <c r="L58" t="n">
-        <v>2702.01</v>
+        <v>2715.51</v>
       </c>
       <c r="M58" t="n">
-        <v>2775.33</v>
+        <v>2795.53</v>
       </c>
       <c r="N58" t="n">
-        <v>2848.65</v>
+        <v>2875.55</v>
       </c>
       <c r="O58" t="n">
-        <v>2982.31</v>
+        <v>2911.57</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5358,7 +5350,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5379,7 +5371,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>485.51</v>
       </c>
       <c r="I2" t="n">
-        <v>3952.15</v>
+        <v>4000.31</v>
       </c>
       <c r="J2" t="n">
-        <v>4011.02</v>
+        <v>4030.09</v>
       </c>
       <c r="K2" t="n">
-        <v>4170.8</v>
+        <v>4183.13</v>
       </c>
       <c r="L2" t="n">
-        <v>4330.57</v>
+        <v>4336.16</v>
       </c>
       <c r="M2" t="n">
-        <v>4439.9</v>
+        <v>4427.57</v>
       </c>
       <c r="N2" t="n">
-        <v>4549.22</v>
+        <v>4518.98</v>
       </c>
       <c r="O2" t="n">
-        <v>4759.45</v>
+        <v>4733.64</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5300,25 +5300,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2726.72</v>
+        <v>2726.65</v>
       </c>
       <c r="C58" t="n">
-        <v>2735.62</v>
+        <v>2736.79</v>
       </c>
       <c r="D58" t="n">
-        <v>2683.87</v>
+        <v>2679.35</v>
       </c>
       <c r="E58" t="n">
-        <v>2718.72</v>
+        <v>2689.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-7.79</v>
+        <v>-37.01</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0136</v>
       </c>
       <c r="H58" t="n">
-        <v>51.75</v>
+        <v>57.43</v>
       </c>
       <c r="I58" t="n">
         <v>2497.44</v>
@@ -5350,9 +5350,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>485.51</v>
       </c>
       <c r="I2" t="n">
-        <v>4000.31</v>
+        <v>4005.15</v>
       </c>
       <c r="J2" t="n">
-        <v>4030.09</v>
+        <v>4036.14</v>
       </c>
       <c r="K2" t="n">
-        <v>4183.13</v>
+        <v>4185.54</v>
       </c>
       <c r="L2" t="n">
-        <v>4336.16</v>
+        <v>4334.95</v>
       </c>
       <c r="M2" t="n">
-        <v>4427.57</v>
+        <v>4425.15</v>
       </c>
       <c r="N2" t="n">
-        <v>4518.98</v>
+        <v>4515.35</v>
       </c>
       <c r="O2" t="n">
-        <v>4733.64</v>
+        <v>4723.97</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5306,19 +5306,19 @@
         <v>2736.79</v>
       </c>
       <c r="D58" t="n">
-        <v>2679.35</v>
+        <v>2570.39</v>
       </c>
       <c r="E58" t="n">
-        <v>2689.5</v>
+        <v>2572.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-37.01</v>
+        <v>-154.31</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0136</v>
+        <v>-0.0566</v>
       </c>
       <c r="H58" t="n">
-        <v>57.43</v>
+        <v>166.39</v>
       </c>
       <c r="I58" t="n">
         <v>2497.44</v>
@@ -5344,15 +5344,19 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5364,16 +5368,12 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5306,19 +5306,19 @@
         <v>2736.79</v>
       </c>
       <c r="D58" t="n">
-        <v>2570.39</v>
+        <v>2570.35</v>
       </c>
       <c r="E58" t="n">
-        <v>2572.2</v>
+        <v>2581.16</v>
       </c>
       <c r="F58" t="n">
-        <v>-154.31</v>
+        <v>-145.35</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0566</v>
+        <v>-0.0533</v>
       </c>
       <c r="H58" t="n">
-        <v>166.39</v>
+        <v>166.44</v>
       </c>
       <c r="I58" t="n">
         <v>2497.44</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5306,19 +5306,19 @@
         <v>2736.79</v>
       </c>
       <c r="D58" t="n">
-        <v>2570.35</v>
+        <v>2469.69</v>
       </c>
       <c r="E58" t="n">
-        <v>2581.16</v>
+        <v>2480.99</v>
       </c>
       <c r="F58" t="n">
-        <v>-145.35</v>
+        <v>-245.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0533</v>
+        <v>-0.09</v>
       </c>
       <c r="H58" t="n">
-        <v>166.44</v>
+        <v>267.1</v>
       </c>
       <c r="I58" t="n">
         <v>2497.44</v>
@@ -5341,12 +5341,14 @@
       <c r="O58" t="n">
         <v>2911.57</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>485.51</v>
       </c>
       <c r="I2" t="n">
-        <v>4005.15</v>
+        <v>4155.24</v>
       </c>
       <c r="J2" t="n">
-        <v>4036.14</v>
+        <v>4223.74</v>
       </c>
       <c r="K2" t="n">
-        <v>4185.54</v>
+        <v>4260.59</v>
       </c>
       <c r="L2" t="n">
-        <v>4334.95</v>
+        <v>4297.43</v>
       </c>
       <c r="M2" t="n">
-        <v>4425.15</v>
+        <v>4350.11</v>
       </c>
       <c r="N2" t="n">
-        <v>4515.35</v>
+        <v>4402.78</v>
       </c>
       <c r="O2" t="n">
-        <v>4723.97</v>
+        <v>4423.79</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5306,19 +5306,19 @@
         <v>2736.79</v>
       </c>
       <c r="D58" t="n">
-        <v>2469.69</v>
+        <v>2406.15</v>
       </c>
       <c r="E58" t="n">
-        <v>2480.99</v>
+        <v>2494.58</v>
       </c>
       <c r="F58" t="n">
-        <v>-245.52</v>
+        <v>-231.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.09</v>
+        <v>-0.0851</v>
       </c>
       <c r="H58" t="n">
-        <v>267.1</v>
+        <v>330.63</v>
       </c>
       <c r="I58" t="n">
         <v>2497.44</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5309,13 +5309,13 @@
         <v>2406.15</v>
       </c>
       <c r="E58" t="n">
-        <v>2494.58</v>
+        <v>2501.88</v>
       </c>
       <c r="F58" t="n">
-        <v>-231.93</v>
+        <v>-224.63</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0851</v>
+        <v>-0.0824</v>
       </c>
       <c r="H58" t="n">
         <v>330.63</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4305.38</v>
+        <v>4609.72</v>
       </c>
       <c r="C2" t="n">
-        <v>4763.36</v>
+        <v>4670.53</v>
       </c>
       <c r="D2" t="n">
-        <v>4277.85</v>
+        <v>4428.33</v>
       </c>
       <c r="E2" t="n">
-        <v>4609.6</v>
+        <v>4451.33</v>
       </c>
       <c r="F2" t="n">
-        <v>304.25</v>
+        <v>-158.27</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0707</v>
+        <v>-0.0343</v>
       </c>
       <c r="H2" t="n">
-        <v>485.51</v>
+        <v>242.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4155.24</v>
+        <v>3792.34</v>
       </c>
       <c r="J2" t="n">
-        <v>4223.74</v>
+        <v>4168.58</v>
       </c>
       <c r="K2" t="n">
-        <v>4260.59</v>
+        <v>4366.84</v>
       </c>
       <c r="L2" t="n">
-        <v>4297.43</v>
+        <v>4565.1</v>
       </c>
       <c r="M2" t="n">
-        <v>4350.11</v>
+        <v>4852.35</v>
       </c>
       <c r="N2" t="n">
-        <v>4402.78</v>
+        <v>5139.6</v>
       </c>
       <c r="O2" t="n">
-        <v>4423.79</v>
+        <v>5248.87</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,96 +685,100 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4609.72</v>
+        <v>4451.58</v>
       </c>
       <c r="C3" t="n">
-        <v>4670.53</v>
+        <v>4457.08</v>
       </c>
       <c r="D3" t="n">
-        <v>4428.33</v>
+        <v>3829.01</v>
       </c>
       <c r="E3" t="n">
-        <v>4451.33</v>
+        <v>4141.48</v>
       </c>
       <c r="F3" t="n">
-        <v>-158.27</v>
+        <v>-309.85</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0343</v>
+        <v>-0.0696</v>
       </c>
       <c r="H3" t="n">
-        <v>242.2</v>
+        <v>628.0700000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3792.34</v>
+        <v>4186.13</v>
       </c>
       <c r="J3" t="n">
-        <v>4168.58</v>
+        <v>4160.08</v>
       </c>
       <c r="K3" t="n">
-        <v>4366.84</v>
+        <v>4330.23</v>
       </c>
       <c r="L3" t="n">
-        <v>4565.1</v>
+        <v>4500.38</v>
       </c>
       <c r="M3" t="n">
-        <v>4852.35</v>
+        <v>4572.43</v>
       </c>
       <c r="N3" t="n">
-        <v>5139.6</v>
+        <v>4644.48</v>
       </c>
       <c r="O3" t="n">
-        <v>5248.87</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+        <v>4912.73</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -788,167 +792,167 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4451.58</v>
+        <v>4141.36</v>
       </c>
       <c r="C4" t="n">
-        <v>4457.08</v>
+        <v>4616.53</v>
       </c>
       <c r="D4" t="n">
-        <v>3829.01</v>
+        <v>4087.93</v>
       </c>
       <c r="E4" t="n">
-        <v>4141.48</v>
+        <v>4515.42</v>
       </c>
       <c r="F4" t="n">
-        <v>-309.85</v>
+        <v>373.95</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0696</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>628.0700000000001</v>
+        <v>528.61</v>
       </c>
       <c r="I4" t="n">
-        <v>4186.13</v>
+        <v>3200.94</v>
       </c>
       <c r="J4" t="n">
-        <v>4160.08</v>
+        <v>3512.62</v>
       </c>
       <c r="K4" t="n">
-        <v>4330.23</v>
+        <v>3827.44</v>
       </c>
       <c r="L4" t="n">
-        <v>4500.38</v>
+        <v>4142.26</v>
       </c>
       <c r="M4" t="n">
-        <v>4572.43</v>
+        <v>4455.51</v>
       </c>
       <c r="N4" t="n">
-        <v>4644.48</v>
+        <v>4768.76</v>
       </c>
       <c r="O4" t="n">
-        <v>4912.73</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
+        <v>5085.15</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4141.36</v>
+        <v>4515.3</v>
       </c>
       <c r="C5" t="n">
-        <v>4616.53</v>
+        <v>4755.22</v>
       </c>
       <c r="D5" t="n">
-        <v>4087.93</v>
+        <v>3460.22</v>
       </c>
       <c r="E5" t="n">
-        <v>4515.42</v>
+        <v>4164.43</v>
       </c>
       <c r="F5" t="n">
-        <v>373.95</v>
+        <v>-351</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>528.61</v>
+        <v>1295</v>
       </c>
       <c r="I5" t="n">
-        <v>3200.94</v>
+        <v>3559.32</v>
       </c>
       <c r="J5" t="n">
-        <v>3512.62</v>
+        <v>4068.41</v>
       </c>
       <c r="K5" t="n">
-        <v>3827.44</v>
+        <v>4251.12</v>
       </c>
       <c r="L5" t="n">
-        <v>4142.26</v>
+        <v>4433.83</v>
       </c>
       <c r="M5" t="n">
-        <v>4455.51</v>
+        <v>4779.73</v>
       </c>
       <c r="N5" t="n">
-        <v>4768.76</v>
+        <v>5125.63</v>
       </c>
       <c r="O5" t="n">
-        <v>5085.15</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+        <v>5145.14</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -956,83 +960,77 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4515.3</v>
+        <v>4164.05</v>
       </c>
       <c r="C6" t="n">
-        <v>4755.22</v>
+        <v>4292.85</v>
       </c>
       <c r="D6" t="n">
-        <v>3460.22</v>
+        <v>3678.62</v>
       </c>
       <c r="E6" t="n">
-        <v>4164.43</v>
+        <v>3984.65</v>
       </c>
       <c r="F6" t="n">
-        <v>-351</v>
+        <v>-179.78</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0432</v>
       </c>
       <c r="H6" t="n">
-        <v>1295</v>
+        <v>614.23</v>
       </c>
       <c r="I6" t="n">
-        <v>3559.32</v>
+        <v>2165.22</v>
       </c>
       <c r="J6" t="n">
-        <v>4068.41</v>
+        <v>2897.78</v>
       </c>
       <c r="K6" t="n">
-        <v>4251.12</v>
+        <v>3516.93</v>
       </c>
       <c r="L6" t="n">
-        <v>4433.83</v>
+        <v>4136.07</v>
       </c>
       <c r="M6" t="n">
-        <v>4779.73</v>
+        <v>4811.93</v>
       </c>
       <c r="N6" t="n">
-        <v>5125.63</v>
+        <v>5487.78</v>
       </c>
       <c r="O6" t="n">
-        <v>5145.14</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>6050.22</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1044,7 +1042,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1058,50 +1056,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4164.05</v>
+        <v>3984.7</v>
       </c>
       <c r="C7" t="n">
-        <v>4292.85</v>
+        <v>4177.31</v>
       </c>
       <c r="D7" t="n">
-        <v>3678.62</v>
+        <v>3718.08</v>
       </c>
       <c r="E7" t="n">
-        <v>3984.65</v>
+        <v>4157.99</v>
       </c>
       <c r="F7" t="n">
-        <v>-179.78</v>
+        <v>173.34</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0432</v>
+        <v>0.0435</v>
       </c>
       <c r="H7" t="n">
-        <v>614.23</v>
+        <v>459.23</v>
       </c>
       <c r="I7" t="n">
-        <v>2165.22</v>
+        <v>3064.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2897.78</v>
+        <v>3369.88</v>
       </c>
       <c r="K7" t="n">
-        <v>3516.93</v>
+        <v>3677.54</v>
       </c>
       <c r="L7" t="n">
-        <v>4136.07</v>
+        <v>3985.19</v>
       </c>
       <c r="M7" t="n">
-        <v>4811.93</v>
+        <v>4291.76</v>
       </c>
       <c r="N7" t="n">
-        <v>5487.78</v>
+        <v>4598.33</v>
       </c>
       <c r="O7" t="n">
-        <v>6050.22</v>
+        <v>4907.07</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,13 +1110,15 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1126,83 +1126,85 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3984.7</v>
+        <v>4158.01</v>
       </c>
       <c r="C8" t="n">
-        <v>4177.31</v>
+        <v>4250.67</v>
       </c>
       <c r="D8" t="n">
-        <v>3718.08</v>
+        <v>3681.91</v>
       </c>
       <c r="E8" t="n">
-        <v>4157.99</v>
+        <v>3911.06</v>
       </c>
       <c r="F8" t="n">
-        <v>173.34</v>
+        <v>-246.93</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0435</v>
+        <v>-0.0594</v>
       </c>
       <c r="H8" t="n">
-        <v>459.23</v>
+        <v>568.76</v>
       </c>
       <c r="I8" t="n">
-        <v>3064.4</v>
+        <v>3258.84</v>
       </c>
       <c r="J8" t="n">
-        <v>3369.88</v>
+        <v>3803.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3677.54</v>
+        <v>3928.37</v>
       </c>
       <c r="L8" t="n">
-        <v>3985.19</v>
+        <v>4052.84</v>
       </c>
       <c r="M8" t="n">
-        <v>4291.76</v>
+        <v>4387.61</v>
       </c>
       <c r="N8" t="n">
-        <v>4598.33</v>
+        <v>4722.37</v>
       </c>
       <c r="O8" t="n">
-        <v>4907.07</v>
+        <v>4636.54</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1210,67 +1212,69 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4158.01</v>
+        <v>3911.75</v>
       </c>
       <c r="C9" t="n">
-        <v>4250.67</v>
+        <v>3912.63</v>
       </c>
       <c r="D9" t="n">
-        <v>3681.91</v>
+        <v>3063.09</v>
       </c>
       <c r="E9" t="n">
-        <v>3911.06</v>
+        <v>3582.62</v>
       </c>
       <c r="F9" t="n">
-        <v>-246.93</v>
+        <v>-328.44</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>568.76</v>
+        <v>849.55</v>
       </c>
       <c r="I9" t="n">
-        <v>3258.84</v>
+        <v>3113.15</v>
       </c>
       <c r="J9" t="n">
-        <v>3803.9</v>
+        <v>3314.69</v>
       </c>
       <c r="K9" t="n">
-        <v>3928.37</v>
+        <v>3626.68</v>
       </c>
       <c r="L9" t="n">
-        <v>4052.84</v>
+        <v>3938.68</v>
       </c>
       <c r="M9" t="n">
-        <v>4387.61</v>
+        <v>4195.44</v>
       </c>
       <c r="N9" t="n">
-        <v>4722.37</v>
+        <v>4452.21</v>
       </c>
       <c r="O9" t="n">
-        <v>4636.54</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
+        <v>4819.43</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
@@ -1282,7 +1286,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1296,81 +1300,73 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3911.75</v>
+        <v>3583.44</v>
       </c>
       <c r="C10" t="n">
-        <v>3912.63</v>
+        <v>3656.15</v>
       </c>
       <c r="D10" t="n">
-        <v>3063.09</v>
+        <v>3007.07</v>
       </c>
       <c r="E10" t="n">
-        <v>3582.62</v>
+        <v>3092.85</v>
       </c>
       <c r="F10" t="n">
-        <v>-328.44</v>
+        <v>-489.77</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1367</v>
       </c>
       <c r="H10" t="n">
-        <v>849.55</v>
+        <v>649.08</v>
       </c>
       <c r="I10" t="n">
-        <v>3113.15</v>
+        <v>2213.54</v>
       </c>
       <c r="J10" t="n">
-        <v>3314.69</v>
+        <v>2780.46</v>
       </c>
       <c r="K10" t="n">
-        <v>3626.68</v>
+        <v>3157.85</v>
       </c>
       <c r="L10" t="n">
-        <v>3938.68</v>
+        <v>3535.24</v>
       </c>
       <c r="M10" t="n">
-        <v>4195.44</v>
+        <v>4007.39</v>
       </c>
       <c r="N10" t="n">
-        <v>4452.21</v>
+        <v>4479.55</v>
       </c>
       <c r="O10" t="n">
-        <v>4819.43</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4762.18</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1384,7 +1380,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1394,50 +1390,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3583.44</v>
+        <v>3092.94</v>
       </c>
       <c r="C11" t="n">
-        <v>3656.15</v>
+        <v>3218.13</v>
       </c>
       <c r="D11" t="n">
-        <v>3007.07</v>
+        <v>2626.87</v>
       </c>
       <c r="E11" t="n">
-        <v>3092.85</v>
+        <v>2801.68</v>
       </c>
       <c r="F11" t="n">
-        <v>-489.77</v>
+        <v>-291.17</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.1367</v>
+        <v>-0.0941</v>
       </c>
       <c r="H11" t="n">
-        <v>649.08</v>
+        <v>591.26</v>
       </c>
       <c r="I11" t="n">
-        <v>2213.54</v>
+        <v>2358</v>
       </c>
       <c r="J11" t="n">
-        <v>2780.46</v>
+        <v>2324.39</v>
       </c>
       <c r="K11" t="n">
-        <v>3157.85</v>
+        <v>2768.31</v>
       </c>
       <c r="L11" t="n">
-        <v>3535.24</v>
+        <v>3212.23</v>
       </c>
       <c r="M11" t="n">
-        <v>4007.39</v>
+        <v>3417.39</v>
       </c>
       <c r="N11" t="n">
-        <v>4479.55</v>
+        <v>3622.54</v>
       </c>
       <c r="O11" t="n">
-        <v>4762.18</v>
+        <v>4305.23</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1450,7 +1446,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1464,7 +1460,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1474,50 +1470,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3092.94</v>
+        <v>2801.2</v>
       </c>
       <c r="C12" t="n">
-        <v>3218.13</v>
+        <v>3095.03</v>
       </c>
       <c r="D12" t="n">
-        <v>2626.87</v>
+        <v>2763.38</v>
       </c>
       <c r="E12" t="n">
-        <v>2801.68</v>
+        <v>2992.11</v>
       </c>
       <c r="F12" t="n">
-        <v>-291.17</v>
+        <v>190.44</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0941</v>
+        <v>0.068</v>
       </c>
       <c r="H12" t="n">
-        <v>591.26</v>
+        <v>331.66</v>
       </c>
       <c r="I12" t="n">
-        <v>2358</v>
+        <v>2035.61</v>
       </c>
       <c r="J12" t="n">
-        <v>2324.39</v>
+        <v>2150</v>
       </c>
       <c r="K12" t="n">
-        <v>2768.31</v>
+        <v>2506.05</v>
       </c>
       <c r="L12" t="n">
-        <v>3212.23</v>
+        <v>2862.09</v>
       </c>
       <c r="M12" t="n">
-        <v>3417.39</v>
+        <v>3097.31</v>
       </c>
       <c r="N12" t="n">
-        <v>3622.54</v>
+        <v>3332.52</v>
       </c>
       <c r="O12" t="n">
-        <v>4305.23</v>
+        <v>3809.39</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,79 +1521,83 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2801.2</v>
+        <v>2991.92</v>
       </c>
       <c r="C13" t="n">
-        <v>3095.03</v>
+        <v>3238.56</v>
       </c>
       <c r="D13" t="n">
-        <v>2763.38</v>
+        <v>2720.44</v>
       </c>
       <c r="E13" t="n">
-        <v>2992.11</v>
+        <v>3061.3</v>
       </c>
       <c r="F13" t="n">
-        <v>190.44</v>
+        <v>69.19</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.068</v>
+        <v>0.0231</v>
       </c>
       <c r="H13" t="n">
-        <v>331.66</v>
+        <v>518.12</v>
       </c>
       <c r="I13" t="n">
-        <v>2035.61</v>
+        <v>2431.72</v>
       </c>
       <c r="J13" t="n">
-        <v>2150</v>
+        <v>2691.91</v>
       </c>
       <c r="K13" t="n">
-        <v>2506.05</v>
+        <v>2826.28</v>
       </c>
       <c r="L13" t="n">
-        <v>2862.09</v>
+        <v>2960.66</v>
       </c>
       <c r="M13" t="n">
-        <v>3097.31</v>
+        <v>3157.94</v>
       </c>
       <c r="N13" t="n">
-        <v>3332.52</v>
+        <v>3355.22</v>
       </c>
       <c r="O13" t="n">
-        <v>3809.39</v>
+        <v>3426.69</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,10 +1605,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1624,7 +1626,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1638,50 +1640,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2991.92</v>
+        <v>3061.01</v>
       </c>
       <c r="C14" t="n">
-        <v>3238.56</v>
+        <v>3446.62</v>
       </c>
       <c r="D14" t="n">
-        <v>2720.44</v>
+        <v>3034.69</v>
       </c>
       <c r="E14" t="n">
-        <v>3061.3</v>
+        <v>3060.59</v>
       </c>
       <c r="F14" t="n">
-        <v>69.19</v>
+        <v>-0.71</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0231</v>
+        <v>-0.0002</v>
       </c>
       <c r="H14" t="n">
-        <v>518.12</v>
+        <v>411.93</v>
       </c>
       <c r="I14" t="n">
-        <v>2431.72</v>
+        <v>2202.32</v>
       </c>
       <c r="J14" t="n">
-        <v>2691.91</v>
+        <v>2584.09</v>
       </c>
       <c r="K14" t="n">
-        <v>2826.28</v>
+        <v>2802.24</v>
       </c>
       <c r="L14" t="n">
-        <v>2960.66</v>
+        <v>3020.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3157.94</v>
+        <v>3320.36</v>
       </c>
       <c r="N14" t="n">
-        <v>3355.22</v>
+        <v>3620.32</v>
       </c>
       <c r="O14" t="n">
-        <v>3426.69</v>
+        <v>3756.67</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,28 +1691,26 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1724,50 +1724,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3061.01</v>
+        <v>3060.48</v>
       </c>
       <c r="C15" t="n">
-        <v>3446.62</v>
+        <v>3175.12</v>
       </c>
       <c r="D15" t="n">
-        <v>3034.69</v>
+        <v>2777.12</v>
       </c>
       <c r="E15" t="n">
-        <v>3060.59</v>
+        <v>3001.61</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.71</v>
+        <v>-58.98</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H15" t="n">
-        <v>411.93</v>
+        <v>398</v>
       </c>
       <c r="I15" t="n">
-        <v>2202.32</v>
+        <v>2622.76</v>
       </c>
       <c r="J15" t="n">
-        <v>2584.09</v>
+        <v>2558.63</v>
       </c>
       <c r="K15" t="n">
-        <v>2802.24</v>
+        <v>2854.63</v>
       </c>
       <c r="L15" t="n">
-        <v>3020.4</v>
+        <v>3150.63</v>
       </c>
       <c r="M15" t="n">
-        <v>3320.36</v>
+        <v>3266.56</v>
       </c>
       <c r="N15" t="n">
-        <v>3620.32</v>
+        <v>3382.49</v>
       </c>
       <c r="O15" t="n">
-        <v>3756.67</v>
+        <v>3858.55</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1775,18 +1775,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1794,64 +1794,60 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3060.48</v>
+        <v>3001.61</v>
       </c>
       <c r="C16" t="n">
-        <v>3175.12</v>
+        <v>3073.35</v>
       </c>
       <c r="D16" t="n">
-        <v>2777.12</v>
+        <v>2888.99</v>
       </c>
       <c r="E16" t="n">
-        <v>3001.61</v>
+        <v>2948.57</v>
       </c>
       <c r="F16" t="n">
-        <v>-58.98</v>
+        <v>-53.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0177</v>
       </c>
       <c r="H16" t="n">
-        <v>398</v>
+        <v>184.37</v>
       </c>
       <c r="I16" t="n">
-        <v>2622.76</v>
+        <v>2379.12</v>
       </c>
       <c r="J16" t="n">
-        <v>2558.63</v>
+        <v>2616.36</v>
       </c>
       <c r="K16" t="n">
-        <v>2854.63</v>
+        <v>2802.61</v>
       </c>
       <c r="L16" t="n">
-        <v>3150.63</v>
+        <v>2988.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3266.56</v>
+        <v>3200.61</v>
       </c>
       <c r="N16" t="n">
-        <v>3382.49</v>
+        <v>3412.36</v>
       </c>
       <c r="O16" t="n">
-        <v>3858.55</v>
+        <v>3573.12</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1859,14 +1855,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1878,60 +1872,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3001.61</v>
+        <v>2948.56</v>
       </c>
       <c r="C17" t="n">
-        <v>3073.35</v>
+        <v>3160.55</v>
       </c>
       <c r="D17" t="n">
-        <v>2888.99</v>
+        <v>2908.75</v>
       </c>
       <c r="E17" t="n">
-        <v>2948.57</v>
+        <v>3140.71</v>
       </c>
       <c r="F17" t="n">
-        <v>-53.05</v>
+        <v>192.14</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0177</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>184.37</v>
+        <v>251.8</v>
       </c>
       <c r="I17" t="n">
-        <v>2379.12</v>
+        <v>2704.62</v>
       </c>
       <c r="J17" t="n">
-        <v>2616.36</v>
+        <v>2747.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2802.61</v>
+        <v>2856.39</v>
       </c>
       <c r="L17" t="n">
-        <v>2988.87</v>
+        <v>2964.87</v>
       </c>
       <c r="M17" t="n">
-        <v>3200.61</v>
+        <v>3040.75</v>
       </c>
       <c r="N17" t="n">
-        <v>3412.36</v>
+        <v>3116.63</v>
       </c>
       <c r="O17" t="n">
-        <v>3573.12</v>
+        <v>3257.72</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,78 +1940,78 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2948.56</v>
+        <v>3141.49</v>
       </c>
       <c r="C18" t="n">
-        <v>3160.55</v>
+        <v>3303.56</v>
       </c>
       <c r="D18" t="n">
-        <v>2908.75</v>
+        <v>3052.51</v>
       </c>
       <c r="E18" t="n">
-        <v>3140.71</v>
+        <v>3118.89</v>
       </c>
       <c r="F18" t="n">
-        <v>192.14</v>
+        <v>-21.83</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="H18" t="n">
-        <v>251.8</v>
+        <v>251.05</v>
       </c>
       <c r="I18" t="n">
-        <v>2704.62</v>
+        <v>2656.95</v>
       </c>
       <c r="J18" t="n">
-        <v>2747.9</v>
+        <v>2941.94</v>
       </c>
       <c r="K18" t="n">
-        <v>2856.39</v>
+        <v>3014.81</v>
       </c>
       <c r="L18" t="n">
-        <v>2964.87</v>
+        <v>3087.68</v>
       </c>
       <c r="M18" t="n">
-        <v>3040.75</v>
+        <v>3266.61</v>
       </c>
       <c r="N18" t="n">
-        <v>3116.63</v>
+        <v>3445.54</v>
       </c>
       <c r="O18" t="n">
-        <v>3257.72</v>
+        <v>3412.35</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,9 +2022,9 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2034,10 +2032,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2047,55 +2043,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3141.49</v>
+        <v>3118.83</v>
       </c>
       <c r="C19" t="n">
-        <v>3303.56</v>
+        <v>3397.9</v>
       </c>
       <c r="D19" t="n">
-        <v>3052.51</v>
+        <v>3068.07</v>
       </c>
       <c r="E19" t="n">
-        <v>3118.89</v>
+        <v>3281.16</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.83</v>
+        <v>162.27</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.052</v>
       </c>
       <c r="H19" t="n">
-        <v>251.05</v>
+        <v>329.82</v>
       </c>
       <c r="I19" t="n">
-        <v>2656.95</v>
+        <v>2801.46</v>
       </c>
       <c r="J19" t="n">
-        <v>2941.94</v>
+        <v>2838.26</v>
       </c>
       <c r="K19" t="n">
-        <v>3014.81</v>
+        <v>2993.36</v>
       </c>
       <c r="L19" t="n">
-        <v>3087.68</v>
+        <v>3148.46</v>
       </c>
       <c r="M19" t="n">
-        <v>3266.61</v>
+        <v>3244.41</v>
       </c>
       <c r="N19" t="n">
-        <v>3445.54</v>
+        <v>3340.36</v>
       </c>
       <c r="O19" t="n">
-        <v>3412.35</v>
+        <v>3554.62</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,19 +2106,21 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2127,90 +2129,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3118.83</v>
+        <v>3282.2</v>
       </c>
       <c r="C20" t="n">
-        <v>3397.9</v>
+        <v>3282.65</v>
       </c>
       <c r="D20" t="n">
-        <v>3068.07</v>
+        <v>2785.9</v>
       </c>
       <c r="E20" t="n">
-        <v>3281.16</v>
+        <v>2815.9</v>
       </c>
       <c r="F20" t="n">
-        <v>162.27</v>
+        <v>-465.26</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.052</v>
+        <v>-0.1418</v>
       </c>
       <c r="H20" t="n">
-        <v>329.82</v>
+        <v>496.76</v>
       </c>
       <c r="I20" t="n">
-        <v>2801.46</v>
+        <v>2738.25</v>
       </c>
       <c r="J20" t="n">
-        <v>2838.26</v>
+        <v>2975.42</v>
       </c>
       <c r="K20" t="n">
-        <v>2993.36</v>
+        <v>3116.25</v>
       </c>
       <c r="L20" t="n">
-        <v>3148.46</v>
+        <v>3257.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3244.41</v>
+        <v>3446.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3340.36</v>
+        <v>3635.07</v>
       </c>
       <c r="O20" t="n">
-        <v>3554.62</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>3727.72</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2218,67 +2218,65 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3282.2</v>
+        <v>2815.77</v>
       </c>
       <c r="C21" t="n">
-        <v>3282.65</v>
+        <v>3040.72</v>
       </c>
       <c r="D21" t="n">
-        <v>2785.9</v>
+        <v>2224.12</v>
       </c>
       <c r="E21" t="n">
-        <v>2815.9</v>
+        <v>2267.96</v>
       </c>
       <c r="F21" t="n">
-        <v>-465.26</v>
+        <v>-547.9400000000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.1418</v>
+        <v>-0.1946</v>
       </c>
       <c r="H21" t="n">
-        <v>496.76</v>
+        <v>816.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2738.25</v>
+        <v>2289.14</v>
       </c>
       <c r="J21" t="n">
-        <v>2975.42</v>
+        <v>2209.96</v>
       </c>
       <c r="K21" t="n">
-        <v>3116.25</v>
+        <v>2567.52</v>
       </c>
       <c r="L21" t="n">
-        <v>3257.07</v>
+        <v>2925.09</v>
       </c>
       <c r="M21" t="n">
-        <v>3446.07</v>
+        <v>3064.28</v>
       </c>
       <c r="N21" t="n">
-        <v>3635.07</v>
+        <v>3203.47</v>
       </c>
       <c r="O21" t="n">
-        <v>3727.72</v>
+        <v>3779.41</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2292,7 +2290,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2302,65 +2300,63 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2815.77</v>
+        <v>2267.56</v>
       </c>
       <c r="C22" t="n">
-        <v>3040.72</v>
+        <v>2393.06</v>
       </c>
       <c r="D22" t="n">
-        <v>2224.12</v>
+        <v>1748.63</v>
       </c>
       <c r="E22" t="n">
-        <v>2267.96</v>
+        <v>2088.76</v>
       </c>
       <c r="F22" t="n">
-        <v>-547.9400000000001</v>
+        <v>-179.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.1946</v>
+        <v>-0.079</v>
       </c>
       <c r="H22" t="n">
-        <v>816.6</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>2289.14</v>
+        <v>1407.52</v>
       </c>
       <c r="J22" t="n">
-        <v>2209.96</v>
+        <v>1269.14</v>
       </c>
       <c r="K22" t="n">
-        <v>2567.52</v>
+        <v>1859.66</v>
       </c>
       <c r="L22" t="n">
-        <v>2925.09</v>
+        <v>2450.19</v>
       </c>
       <c r="M22" t="n">
-        <v>3064.28</v>
+        <v>2676.27</v>
       </c>
       <c r="N22" t="n">
-        <v>3203.47</v>
+        <v>2902.34</v>
       </c>
       <c r="O22" t="n">
-        <v>3779.41</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>3857.32</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2374,7 +2370,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2384,50 +2380,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2267.56</v>
+        <v>2087.92</v>
       </c>
       <c r="C23" t="n">
-        <v>2393.06</v>
+        <v>2144.98</v>
       </c>
       <c r="D23" t="n">
-        <v>1748.63</v>
+        <v>1897.33</v>
       </c>
       <c r="E23" t="n">
-        <v>2088.76</v>
+        <v>1966.04</v>
       </c>
       <c r="F23" t="n">
-        <v>-179.2</v>
+        <v>-122.72</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.0588</v>
       </c>
       <c r="H23" t="n">
-        <v>644.4400000000001</v>
+        <v>247.64</v>
       </c>
       <c r="I23" t="n">
-        <v>1407.52</v>
+        <v>1104.19</v>
       </c>
       <c r="J23" t="n">
-        <v>1269.14</v>
+        <v>1453.29</v>
       </c>
       <c r="K23" t="n">
-        <v>1859.66</v>
+        <v>1766.55</v>
       </c>
       <c r="L23" t="n">
-        <v>2450.19</v>
+        <v>2079.8</v>
       </c>
       <c r="M23" t="n">
-        <v>2676.27</v>
+        <v>2410.98</v>
       </c>
       <c r="N23" t="n">
-        <v>2902.34</v>
+        <v>2742.16</v>
       </c>
       <c r="O23" t="n">
-        <v>3857.32</v>
+        <v>3037.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2435,14 +2431,12 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2454,60 +2448,64 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2087.92</v>
+        <v>1965.92</v>
       </c>
       <c r="C24" t="n">
-        <v>2144.98</v>
+        <v>2037.16</v>
       </c>
       <c r="D24" t="n">
-        <v>1897.33</v>
+        <v>1906.82</v>
       </c>
       <c r="E24" t="n">
-        <v>1966.04</v>
+        <v>1957.81</v>
       </c>
       <c r="F24" t="n">
-        <v>-122.72</v>
+        <v>-8.24</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0042</v>
       </c>
       <c r="H24" t="n">
-        <v>247.64</v>
+        <v>130.34</v>
       </c>
       <c r="I24" t="n">
-        <v>1104.19</v>
+        <v>1649.69</v>
       </c>
       <c r="J24" t="n">
-        <v>1453.29</v>
+        <v>1690.85</v>
       </c>
       <c r="K24" t="n">
-        <v>1766.55</v>
+        <v>1842.22</v>
       </c>
       <c r="L24" t="n">
-        <v>2079.8</v>
+        <v>1993.6</v>
       </c>
       <c r="M24" t="n">
-        <v>2410.98</v>
+        <v>2089.86</v>
       </c>
       <c r="N24" t="n">
-        <v>2742.16</v>
+        <v>2186.13</v>
       </c>
       <c r="O24" t="n">
-        <v>3037.5</v>
+        <v>2392.62</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2518,7 +2516,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2532,7 +2530,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2546,75 +2544,83 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1965.92</v>
+        <v>1958.14</v>
       </c>
       <c r="C25" t="n">
-        <v>2037.16</v>
+        <v>2145.51</v>
       </c>
       <c r="D25" t="n">
-        <v>1906.82</v>
+        <v>1804.11</v>
       </c>
       <c r="E25" t="n">
-        <v>1957.81</v>
+        <v>1939.07</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.24</v>
+        <v>-18.74</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>130.34</v>
+        <v>341.39</v>
       </c>
       <c r="I25" t="n">
-        <v>1649.69</v>
+        <v>1776.49</v>
       </c>
       <c r="J25" t="n">
-        <v>1690.85</v>
+        <v>1820.38</v>
       </c>
       <c r="K25" t="n">
-        <v>1842.22</v>
+        <v>1892.64</v>
       </c>
       <c r="L25" t="n">
-        <v>1993.6</v>
+        <v>1964.9</v>
       </c>
       <c r="M25" t="n">
-        <v>2089.86</v>
+        <v>2022.97</v>
       </c>
       <c r="N25" t="n">
-        <v>2186.13</v>
+        <v>2081.05</v>
       </c>
       <c r="O25" t="n">
-        <v>2392.62</v>
+        <v>2167.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2628,140 +2634,134 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1958.14</v>
+        <v>1939.06</v>
       </c>
       <c r="C26" t="n">
-        <v>2145.51</v>
+        <v>2198.66</v>
       </c>
       <c r="D26" t="n">
-        <v>1804.11</v>
+        <v>1915.3</v>
       </c>
       <c r="E26" t="n">
-        <v>1939.07</v>
+        <v>1936.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.74</v>
+        <v>-2.46</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0013</v>
       </c>
       <c r="H26" t="n">
-        <v>341.39</v>
+        <v>283.36</v>
       </c>
       <c r="I26" t="n">
-        <v>1776.49</v>
+        <v>1462.72</v>
       </c>
       <c r="J26" t="n">
-        <v>1820.38</v>
+        <v>1579.8</v>
       </c>
       <c r="K26" t="n">
-        <v>1892.64</v>
+        <v>1768.37</v>
       </c>
       <c r="L26" t="n">
-        <v>1964.9</v>
+        <v>1956.94</v>
       </c>
       <c r="M26" t="n">
-        <v>2022.97</v>
+        <v>2109.76</v>
       </c>
       <c r="N26" t="n">
-        <v>2081.05</v>
+        <v>2262.59</v>
       </c>
       <c r="O26" t="n">
-        <v>2167.5</v>
+        <v>2486.9</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1939.06</v>
+        <v>1936.64</v>
       </c>
       <c r="C27" t="n">
-        <v>2198.66</v>
+        <v>2206.81</v>
       </c>
       <c r="D27" t="n">
-        <v>1915.3</v>
+        <v>1930.6</v>
       </c>
       <c r="E27" t="n">
-        <v>1936.6</v>
+        <v>2177.48</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.46</v>
+        <v>240.87</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.1244</v>
       </c>
       <c r="H27" t="n">
-        <v>283.36</v>
+        <v>276.21</v>
       </c>
       <c r="I27" t="n">
-        <v>1462.72</v>
+        <v>1631.95</v>
       </c>
       <c r="J27" t="n">
-        <v>1579.8</v>
+        <v>1593.06</v>
       </c>
       <c r="K27" t="n">
-        <v>1768.37</v>
+        <v>1794.93</v>
       </c>
       <c r="L27" t="n">
-        <v>1956.94</v>
+        <v>1996.79</v>
       </c>
       <c r="M27" t="n">
-        <v>2109.76</v>
+        <v>2078.28</v>
       </c>
       <c r="N27" t="n">
-        <v>2262.59</v>
+        <v>2159.77</v>
       </c>
       <c r="O27" t="n">
-        <v>2486.9</v>
+        <v>2482.01</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2772,9 +2772,9 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2782,70 +2782,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1936.64</v>
+        <v>2177.78</v>
       </c>
       <c r="C28" t="n">
-        <v>2206.81</v>
+        <v>2384.47</v>
       </c>
       <c r="D28" t="n">
-        <v>1930.6</v>
+        <v>2027.05</v>
       </c>
       <c r="E28" t="n">
-        <v>2177.48</v>
+        <v>2053.05</v>
       </c>
       <c r="F28" t="n">
-        <v>240.87</v>
+        <v>-124.43</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.1244</v>
+        <v>-0.0571</v>
       </c>
       <c r="H28" t="n">
-        <v>276.21</v>
+        <v>357.42</v>
       </c>
       <c r="I28" t="n">
-        <v>1631.95</v>
+        <v>1654.39</v>
       </c>
       <c r="J28" t="n">
-        <v>1593.06</v>
+        <v>1955.65</v>
       </c>
       <c r="K28" t="n">
-        <v>1794.93</v>
+        <v>2039.37</v>
       </c>
       <c r="L28" t="n">
-        <v>1996.79</v>
+        <v>2123.09</v>
       </c>
       <c r="M28" t="n">
-        <v>2078.28</v>
+        <v>2315.58</v>
       </c>
       <c r="N28" t="n">
-        <v>2159.77</v>
+        <v>2508.08</v>
       </c>
       <c r="O28" t="n">
-        <v>2482.01</v>
+        <v>2483.03</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2853,12 +2851,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2866,10 +2866,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2879,55 +2877,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2177.78</v>
+        <v>2052.95</v>
       </c>
       <c r="C29" t="n">
-        <v>2384.47</v>
+        <v>2198.37</v>
       </c>
       <c r="D29" t="n">
-        <v>2027.05</v>
+        <v>1939.53</v>
       </c>
       <c r="E29" t="n">
-        <v>2053.05</v>
+        <v>1982.56</v>
       </c>
       <c r="F29" t="n">
-        <v>-124.43</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0571</v>
+        <v>-0.0343</v>
       </c>
       <c r="H29" t="n">
-        <v>357.42</v>
+        <v>258.84</v>
       </c>
       <c r="I29" t="n">
-        <v>1654.39</v>
+        <v>1669.63</v>
       </c>
       <c r="J29" t="n">
-        <v>1955.65</v>
+        <v>1619.28</v>
       </c>
       <c r="K29" t="n">
-        <v>2039.37</v>
+        <v>1874.34</v>
       </c>
       <c r="L29" t="n">
-        <v>2123.09</v>
+        <v>2129.4</v>
       </c>
       <c r="M29" t="n">
-        <v>2315.58</v>
+        <v>2231.76</v>
       </c>
       <c r="N29" t="n">
-        <v>2508.08</v>
+        <v>2334.11</v>
       </c>
       <c r="O29" t="n">
-        <v>2483.03</v>
+        <v>2741.89</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,15 +2942,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2963,57 +2963,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2052.95</v>
+        <v>1982.55</v>
       </c>
       <c r="C30" t="n">
-        <v>2198.37</v>
+        <v>2165.67</v>
       </c>
       <c r="D30" t="n">
-        <v>1939.53</v>
+        <v>1979.08</v>
       </c>
       <c r="E30" t="n">
-        <v>1982.56</v>
+        <v>2109</v>
       </c>
       <c r="F30" t="n">
-        <v>-70.48999999999999</v>
+        <v>126.44</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0343</v>
+        <v>0.0638</v>
       </c>
       <c r="H30" t="n">
-        <v>258.84</v>
+        <v>186.59</v>
       </c>
       <c r="I30" t="n">
-        <v>1669.63</v>
+        <v>1680.69</v>
       </c>
       <c r="J30" t="n">
-        <v>1619.28</v>
+        <v>1680.52</v>
       </c>
       <c r="K30" t="n">
-        <v>1874.34</v>
+        <v>1853.14</v>
       </c>
       <c r="L30" t="n">
-        <v>2129.4</v>
+        <v>2025.75</v>
       </c>
       <c r="M30" t="n">
-        <v>2231.76</v>
+        <v>2111.98</v>
       </c>
       <c r="N30" t="n">
-        <v>2334.11</v>
+        <v>2198.21</v>
       </c>
       <c r="O30" t="n">
-        <v>2741.89</v>
+        <v>2457.21</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3021,19 +3021,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3047,57 +3047,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1982.55</v>
+        <v>2108.94</v>
       </c>
       <c r="C31" t="n">
-        <v>2165.67</v>
+        <v>2327.46</v>
       </c>
       <c r="D31" t="n">
-        <v>1979.08</v>
+        <v>2061.47</v>
       </c>
       <c r="E31" t="n">
-        <v>2109</v>
+        <v>2192.2</v>
       </c>
       <c r="F31" t="n">
-        <v>126.44</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0638</v>
+        <v>0.0395</v>
       </c>
       <c r="H31" t="n">
-        <v>186.59</v>
+        <v>265.99</v>
       </c>
       <c r="I31" t="n">
-        <v>1680.69</v>
+        <v>1792.49</v>
       </c>
       <c r="J31" t="n">
-        <v>1680.52</v>
+        <v>1940.72</v>
       </c>
       <c r="K31" t="n">
-        <v>1853.14</v>
+        <v>2015.7</v>
       </c>
       <c r="L31" t="n">
-        <v>2025.75</v>
+        <v>2090.68</v>
       </c>
       <c r="M31" t="n">
-        <v>2111.98</v>
+        <v>2202.29</v>
       </c>
       <c r="N31" t="n">
-        <v>2198.21</v>
+        <v>2313.9</v>
       </c>
       <c r="O31" t="n">
-        <v>2457.21</v>
+        <v>2352.26</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3108,7 +3108,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3118,8 +3118,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3129,59 +3131,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2108.94</v>
+        <v>2192.33</v>
       </c>
       <c r="C32" t="n">
-        <v>2327.46</v>
+        <v>2464.78</v>
       </c>
       <c r="D32" t="n">
-        <v>2061.47</v>
+        <v>2176.32</v>
       </c>
       <c r="E32" t="n">
-        <v>2192.2</v>
+        <v>2264.92</v>
       </c>
       <c r="F32" t="n">
-        <v>83.20999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0332</v>
       </c>
       <c r="H32" t="n">
-        <v>265.99</v>
+        <v>288.46</v>
       </c>
       <c r="I32" t="n">
-        <v>1792.49</v>
+        <v>1795.48</v>
       </c>
       <c r="J32" t="n">
-        <v>1940.72</v>
+        <v>1925.08</v>
       </c>
       <c r="K32" t="n">
-        <v>2015.7</v>
+        <v>2059.21</v>
       </c>
       <c r="L32" t="n">
-        <v>2090.68</v>
+        <v>2193.33</v>
       </c>
       <c r="M32" t="n">
-        <v>2202.29</v>
+        <v>2325.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2313.9</v>
+        <v>2457.06</v>
       </c>
       <c r="O32" t="n">
-        <v>2352.26</v>
+        <v>2593.45</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3192,7 +3190,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3220,50 +3218,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2192.33</v>
+        <v>2264.87</v>
       </c>
       <c r="C33" t="n">
-        <v>2464.78</v>
+        <v>2422.86</v>
       </c>
       <c r="D33" t="n">
-        <v>2176.32</v>
+        <v>2262.05</v>
       </c>
       <c r="E33" t="n">
-        <v>2264.92</v>
+        <v>2369.73</v>
       </c>
       <c r="F33" t="n">
-        <v>72.72</v>
+        <v>104.81</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0463</v>
       </c>
       <c r="H33" t="n">
-        <v>288.46</v>
+        <v>160.81</v>
       </c>
       <c r="I33" t="n">
-        <v>1795.48</v>
+        <v>1887.87</v>
       </c>
       <c r="J33" t="n">
-        <v>1925.08</v>
+        <v>1948.64</v>
       </c>
       <c r="K33" t="n">
-        <v>2059.21</v>
+        <v>2120.69</v>
       </c>
       <c r="L33" t="n">
-        <v>2193.33</v>
+        <v>2292.74</v>
       </c>
       <c r="M33" t="n">
-        <v>2325.2</v>
+        <v>2409.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2457.06</v>
+        <v>2525.56</v>
       </c>
       <c r="O33" t="n">
-        <v>2593.45</v>
+        <v>2753.24</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3274,7 +3272,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3284,10 +3282,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3297,74 +3293,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2264.87</v>
+        <v>2369.84</v>
       </c>
       <c r="C34" t="n">
-        <v>2422.86</v>
+        <v>2403.73</v>
       </c>
       <c r="D34" t="n">
-        <v>2262.05</v>
+        <v>2221.22</v>
       </c>
       <c r="E34" t="n">
-        <v>2369.73</v>
+        <v>2321.64</v>
       </c>
       <c r="F34" t="n">
-        <v>104.81</v>
+        <v>-48.09</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0463</v>
+        <v>-0.0203</v>
       </c>
       <c r="H34" t="n">
-        <v>160.81</v>
+        <v>182.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1887.87</v>
+        <v>2101.25</v>
       </c>
       <c r="J34" t="n">
-        <v>1948.64</v>
+        <v>2222.56</v>
       </c>
       <c r="K34" t="n">
-        <v>2120.69</v>
+        <v>2289.33</v>
       </c>
       <c r="L34" t="n">
-        <v>2292.74</v>
+        <v>2356.09</v>
       </c>
       <c r="M34" t="n">
-        <v>2409.15</v>
+        <v>2450.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2525.56</v>
+        <v>2544.17</v>
       </c>
       <c r="O34" t="n">
-        <v>2753.24</v>
+        <v>2583.67</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3379,79 +3381,77 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2369.84</v>
+        <v>2321.82</v>
       </c>
       <c r="C35" t="n">
-        <v>2403.73</v>
+        <v>2423.04</v>
       </c>
       <c r="D35" t="n">
-        <v>2221.22</v>
+        <v>2265.83</v>
       </c>
       <c r="E35" t="n">
-        <v>2321.64</v>
+        <v>2369.04</v>
       </c>
       <c r="F35" t="n">
-        <v>-48.09</v>
+        <v>47.41</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="H35" t="n">
-        <v>182.5</v>
+        <v>157.21</v>
       </c>
       <c r="I35" t="n">
-        <v>2101.25</v>
+        <v>2038.72</v>
       </c>
       <c r="J35" t="n">
-        <v>2222.56</v>
+        <v>2143.71</v>
       </c>
       <c r="K35" t="n">
-        <v>2289.33</v>
+        <v>2230.38</v>
       </c>
       <c r="L35" t="n">
-        <v>2356.09</v>
+        <v>2317.06</v>
       </c>
       <c r="M35" t="n">
-        <v>2450.13</v>
+        <v>2412.89</v>
       </c>
       <c r="N35" t="n">
-        <v>2544.17</v>
+        <v>2508.72</v>
       </c>
       <c r="O35" t="n">
-        <v>2583.67</v>
+        <v>2586.23</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3463,78 +3463,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2321.82</v>
+        <v>2369.19</v>
       </c>
       <c r="C36" t="n">
-        <v>2423.04</v>
+        <v>2374.3</v>
       </c>
       <c r="D36" t="n">
-        <v>2265.83</v>
+        <v>2097.02</v>
       </c>
       <c r="E36" t="n">
-        <v>2369.04</v>
+        <v>2127.65</v>
       </c>
       <c r="F36" t="n">
-        <v>47.41</v>
+        <v>-241.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.1019</v>
       </c>
       <c r="H36" t="n">
-        <v>157.21</v>
+        <v>277.28</v>
       </c>
       <c r="I36" t="n">
-        <v>2038.72</v>
+        <v>2108.63</v>
       </c>
       <c r="J36" t="n">
-        <v>2143.71</v>
+        <v>2224.14</v>
       </c>
       <c r="K36" t="n">
-        <v>2230.38</v>
+        <v>2290.44</v>
       </c>
       <c r="L36" t="n">
-        <v>2317.06</v>
+        <v>2356.74</v>
       </c>
       <c r="M36" t="n">
-        <v>2412.89</v>
+        <v>2447.65</v>
       </c>
       <c r="N36" t="n">
-        <v>2508.72</v>
+        <v>2538.55</v>
       </c>
       <c r="O36" t="n">
-        <v>2586.23</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>2580.25</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3542,9 +3542,9 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W36" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3552,69 +3552,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2369.19</v>
+        <v>2127.68</v>
       </c>
       <c r="C37" t="n">
-        <v>2374.3</v>
+        <v>2155.96</v>
       </c>
       <c r="D37" t="n">
-        <v>2097.02</v>
+        <v>2010.55</v>
       </c>
       <c r="E37" t="n">
-        <v>2127.65</v>
+        <v>2097.99</v>
       </c>
       <c r="F37" t="n">
-        <v>-241.4</v>
+        <v>-29.65</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.1019</v>
+        <v>-0.0139</v>
       </c>
       <c r="H37" t="n">
-        <v>277.28</v>
+        <v>145.41</v>
       </c>
       <c r="I37" t="n">
-        <v>2108.63</v>
+        <v>1819.74</v>
       </c>
       <c r="J37" t="n">
-        <v>2224.14</v>
+        <v>1796.35</v>
       </c>
       <c r="K37" t="n">
-        <v>2290.44</v>
+        <v>1989</v>
       </c>
       <c r="L37" t="n">
-        <v>2356.74</v>
+        <v>2181.65</v>
       </c>
       <c r="M37" t="n">
-        <v>2447.65</v>
+        <v>2266.29</v>
       </c>
       <c r="N37" t="n">
-        <v>2538.55</v>
+        <v>2350.92</v>
       </c>
       <c r="O37" t="n">
-        <v>2580.25</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>2651.59</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3626,7 +3620,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3636,50 +3630,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2127.68</v>
+        <v>2097.99</v>
       </c>
       <c r="C38" t="n">
-        <v>2155.96</v>
+        <v>2138.41</v>
       </c>
       <c r="D38" t="n">
-        <v>2010.55</v>
+        <v>1966.28</v>
       </c>
       <c r="E38" t="n">
-        <v>2097.99</v>
+        <v>2004.34</v>
       </c>
       <c r="F38" t="n">
-        <v>-29.65</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.0446</v>
       </c>
       <c r="H38" t="n">
-        <v>145.41</v>
+        <v>172.13</v>
       </c>
       <c r="I38" t="n">
-        <v>1819.74</v>
+        <v>1865.14</v>
       </c>
       <c r="J38" t="n">
-        <v>1796.35</v>
+        <v>1959.95</v>
       </c>
       <c r="K38" t="n">
-        <v>1989</v>
+        <v>2025.29</v>
       </c>
       <c r="L38" t="n">
-        <v>2181.65</v>
+        <v>2090.63</v>
       </c>
       <c r="M38" t="n">
-        <v>2266.29</v>
+        <v>2170.7</v>
       </c>
       <c r="N38" t="n">
-        <v>2350.92</v>
+        <v>2250.78</v>
       </c>
       <c r="O38" t="n">
-        <v>2651.59</v>
+        <v>2301.38</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3687,12 +3681,14 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3704,7 +3700,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3714,63 +3710,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2097.99</v>
+        <v>2004.24</v>
       </c>
       <c r="C39" t="n">
-        <v>2138.41</v>
+        <v>2017.61</v>
       </c>
       <c r="D39" t="n">
-        <v>1966.28</v>
+        <v>1506.51</v>
       </c>
       <c r="E39" t="n">
-        <v>2004.34</v>
+        <v>1686.4</v>
       </c>
       <c r="F39" t="n">
-        <v>-93.65000000000001</v>
+        <v>-317.95</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0446</v>
+        <v>-0.1586</v>
       </c>
       <c r="H39" t="n">
-        <v>172.13</v>
+        <v>511.1</v>
       </c>
       <c r="I39" t="n">
-        <v>1865.14</v>
+        <v>1794.15</v>
       </c>
       <c r="J39" t="n">
-        <v>1959.95</v>
+        <v>1808.21</v>
       </c>
       <c r="K39" t="n">
-        <v>2025.29</v>
+        <v>1918.28</v>
       </c>
       <c r="L39" t="n">
-        <v>2090.63</v>
+        <v>2028.34</v>
       </c>
       <c r="M39" t="n">
-        <v>2170.7</v>
+        <v>2090.41</v>
       </c>
       <c r="N39" t="n">
-        <v>2250.78</v>
+        <v>2152.47</v>
       </c>
       <c r="O39" t="n">
-        <v>2301.38</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+        <v>2310.54</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3784,7 +3784,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3794,69 +3794,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2004.24</v>
+        <v>1686.25</v>
       </c>
       <c r="C40" t="n">
-        <v>2017.61</v>
+        <v>1729.35</v>
       </c>
       <c r="D40" t="n">
-        <v>1506.51</v>
+        <v>1603.83</v>
       </c>
       <c r="E40" t="n">
-        <v>1686.4</v>
+        <v>1724.61</v>
       </c>
       <c r="F40" t="n">
-        <v>-317.95</v>
+        <v>38.22</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.1586</v>
+        <v>0.0227</v>
       </c>
       <c r="H40" t="n">
-        <v>511.1</v>
+        <v>125.53</v>
       </c>
       <c r="I40" t="n">
-        <v>1794.15</v>
+        <v>995.4</v>
       </c>
       <c r="J40" t="n">
-        <v>1808.21</v>
+        <v>1137.46</v>
       </c>
       <c r="K40" t="n">
-        <v>1918.28</v>
+        <v>1430.85</v>
       </c>
       <c r="L40" t="n">
-        <v>2028.34</v>
+        <v>1724.23</v>
       </c>
       <c r="M40" t="n">
-        <v>2090.41</v>
+        <v>1941.95</v>
       </c>
       <c r="N40" t="n">
-        <v>2152.47</v>
+        <v>2159.67</v>
       </c>
       <c r="O40" t="n">
-        <v>2310.54</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>2528.71</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3868,60 +3862,64 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1686.25</v>
+        <v>1724.57</v>
       </c>
       <c r="C41" t="n">
-        <v>1729.35</v>
+        <v>1847.77</v>
       </c>
       <c r="D41" t="n">
-        <v>1603.83</v>
+        <v>1670.1</v>
       </c>
       <c r="E41" t="n">
-        <v>1724.61</v>
+        <v>1704.58</v>
       </c>
       <c r="F41" t="n">
-        <v>38.22</v>
+        <v>-20.03</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0227</v>
+        <v>-0.0116</v>
       </c>
       <c r="H41" t="n">
-        <v>125.53</v>
+        <v>177.67</v>
       </c>
       <c r="I41" t="n">
-        <v>995.4</v>
+        <v>1478.3</v>
       </c>
       <c r="J41" t="n">
-        <v>1137.46</v>
+        <v>1628.1</v>
       </c>
       <c r="K41" t="n">
-        <v>1430.85</v>
+        <v>1661.85</v>
       </c>
       <c r="L41" t="n">
-        <v>1724.23</v>
+        <v>1695.6</v>
       </c>
       <c r="M41" t="n">
-        <v>1941.95</v>
+        <v>1787.38</v>
       </c>
       <c r="N41" t="n">
-        <v>2159.67</v>
+        <v>1879.15</v>
       </c>
       <c r="O41" t="n">
-        <v>2528.71</v>
+        <v>1854.88</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3932,13 +3930,15 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3946,7 +3946,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3960,50 +3960,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1724.57</v>
+        <v>1704.63</v>
       </c>
       <c r="C42" t="n">
-        <v>1847.77</v>
+        <v>1776.83</v>
       </c>
       <c r="D42" t="n">
-        <v>1670.1</v>
+        <v>1510.51</v>
       </c>
       <c r="E42" t="n">
-        <v>1704.58</v>
+        <v>1570.36</v>
       </c>
       <c r="F42" t="n">
-        <v>-20.03</v>
+        <v>-134.22</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>177.67</v>
+        <v>266.33</v>
       </c>
       <c r="I42" t="n">
-        <v>1478.3</v>
+        <v>1492.44</v>
       </c>
       <c r="J42" t="n">
-        <v>1628.1</v>
+        <v>1499.74</v>
       </c>
       <c r="K42" t="n">
-        <v>1661.85</v>
+        <v>1615.75</v>
       </c>
       <c r="L42" t="n">
-        <v>1695.6</v>
+        <v>1731.76</v>
       </c>
       <c r="M42" t="n">
-        <v>1787.38</v>
+        <v>1793.41</v>
       </c>
       <c r="N42" t="n">
-        <v>1879.15</v>
+        <v>1855.07</v>
       </c>
       <c r="O42" t="n">
-        <v>1854.88</v>
+        <v>2025.44</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4011,18 +4011,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4030,64 +4030,60 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1704.63</v>
+        <v>1569.99</v>
       </c>
       <c r="C43" t="n">
-        <v>1776.83</v>
+        <v>1805.91</v>
       </c>
       <c r="D43" t="n">
-        <v>1510.51</v>
+        <v>1549.25</v>
       </c>
       <c r="E43" t="n">
-        <v>1570.36</v>
+        <v>1783.01</v>
       </c>
       <c r="F43" t="n">
-        <v>-134.22</v>
+        <v>212.64</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.1354</v>
       </c>
       <c r="H43" t="n">
-        <v>266.33</v>
+        <v>256.66</v>
       </c>
       <c r="I43" t="n">
-        <v>1492.44</v>
+        <v>1244.18</v>
       </c>
       <c r="J43" t="n">
-        <v>1499.74</v>
+        <v>1267.38</v>
       </c>
       <c r="K43" t="n">
-        <v>1615.75</v>
+        <v>1437.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1731.76</v>
+        <v>1607.02</v>
       </c>
       <c r="M43" t="n">
-        <v>1793.41</v>
+        <v>1703.52</v>
       </c>
       <c r="N43" t="n">
-        <v>1855.07</v>
+        <v>1800.03</v>
       </c>
       <c r="O43" t="n">
-        <v>2025.44</v>
+        <v>2043.16</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4095,79 +4091,85 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1569.99</v>
+        <v>1783</v>
       </c>
       <c r="C44" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D44" t="n">
-        <v>1549.25</v>
+        <v>1711.9</v>
       </c>
       <c r="E44" t="n">
-        <v>1783.01</v>
+        <v>1805.79</v>
       </c>
       <c r="F44" t="n">
-        <v>212.64</v>
+        <v>22.78</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.1354</v>
+        <v>0.0128</v>
       </c>
       <c r="H44" t="n">
-        <v>256.66</v>
+        <v>117.61</v>
       </c>
       <c r="I44" t="n">
-        <v>1244.18</v>
+        <v>1292.59</v>
       </c>
       <c r="J44" t="n">
-        <v>1267.38</v>
+        <v>1579.06</v>
       </c>
       <c r="K44" t="n">
-        <v>1437.2</v>
+        <v>1654.67</v>
       </c>
       <c r="L44" t="n">
-        <v>1607.02</v>
+        <v>1730.29</v>
       </c>
       <c r="M44" t="n">
-        <v>1703.52</v>
+        <v>1911.34</v>
       </c>
       <c r="N44" t="n">
-        <v>1800.03</v>
+        <v>2092.38</v>
       </c>
       <c r="O44" t="n">
-        <v>2043.16</v>
+        <v>2062.58</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4178,25 +4180,21 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4210,50 +4208,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1783</v>
+        <v>1805.76</v>
       </c>
       <c r="C45" t="n">
-        <v>1829.51</v>
+        <v>1944.16</v>
       </c>
       <c r="D45" t="n">
-        <v>1711.9</v>
+        <v>1749.35</v>
       </c>
       <c r="E45" t="n">
-        <v>1805.79</v>
+        <v>1871.51</v>
       </c>
       <c r="F45" t="n">
-        <v>22.78</v>
+        <v>65.72</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0364</v>
       </c>
       <c r="H45" t="n">
-        <v>117.61</v>
+        <v>194.81</v>
       </c>
       <c r="I45" t="n">
-        <v>1292.59</v>
+        <v>1594.29</v>
       </c>
       <c r="J45" t="n">
-        <v>1579.06</v>
+        <v>1705.72</v>
       </c>
       <c r="K45" t="n">
-        <v>1654.67</v>
+        <v>1746.98</v>
       </c>
       <c r="L45" t="n">
-        <v>1730.29</v>
+        <v>1788.25</v>
       </c>
       <c r="M45" t="n">
-        <v>1911.34</v>
+        <v>1864.59</v>
       </c>
       <c r="N45" t="n">
-        <v>2092.38</v>
+        <v>1940.94</v>
       </c>
       <c r="O45" t="n">
-        <v>2062.58</v>
+        <v>1947.13</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4264,21 +4262,25 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="S45" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4292,50 +4294,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1805.76</v>
+        <v>1871.28</v>
       </c>
       <c r="C46" t="n">
-        <v>1944.16</v>
+        <v>1963.25</v>
       </c>
       <c r="D46" t="n">
-        <v>1749.35</v>
+        <v>1842.82</v>
       </c>
       <c r="E46" t="n">
-        <v>1871.51</v>
+        <v>1953.41</v>
       </c>
       <c r="F46" t="n">
-        <v>65.72</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0364</v>
+        <v>0.0438</v>
       </c>
       <c r="H46" t="n">
-        <v>194.81</v>
+        <v>120.43</v>
       </c>
       <c r="I46" t="n">
-        <v>1594.29</v>
+        <v>1554.53</v>
       </c>
       <c r="J46" t="n">
-        <v>1705.72</v>
+        <v>1689.07</v>
       </c>
       <c r="K46" t="n">
-        <v>1746.98</v>
+        <v>1774.1</v>
       </c>
       <c r="L46" t="n">
-        <v>1788.25</v>
+        <v>1859.13</v>
       </c>
       <c r="M46" t="n">
-        <v>1864.59</v>
+        <v>1968.92</v>
       </c>
       <c r="N46" t="n">
-        <v>1940.94</v>
+        <v>2078.7</v>
       </c>
       <c r="O46" t="n">
-        <v>1947.13</v>
+        <v>2138.97</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4346,7 +4348,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4356,15 +4358,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4378,69 +4378,71 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1871.28</v>
+        <v>1953.41</v>
       </c>
       <c r="C47" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D47" t="n">
-        <v>1842.82</v>
+        <v>1821.49</v>
       </c>
       <c r="E47" t="n">
-        <v>1953.41</v>
+        <v>1882.52</v>
       </c>
       <c r="F47" t="n">
-        <v>81.90000000000001</v>
+        <v>-70.89</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0363</v>
       </c>
       <c r="H47" t="n">
-        <v>120.43</v>
+        <v>154.98</v>
       </c>
       <c r="I47" t="n">
-        <v>1554.53</v>
+        <v>1722.39</v>
       </c>
       <c r="J47" t="n">
-        <v>1689.07</v>
+        <v>1858.17</v>
       </c>
       <c r="K47" t="n">
-        <v>1774.1</v>
+        <v>1893.2</v>
       </c>
       <c r="L47" t="n">
-        <v>1859.13</v>
+        <v>1928.22</v>
       </c>
       <c r="M47" t="n">
-        <v>1968.92</v>
+        <v>2013.63</v>
       </c>
       <c r="N47" t="n">
-        <v>2078.7</v>
+        <v>2099.03</v>
       </c>
       <c r="O47" t="n">
-        <v>2138.97</v>
+        <v>2083.68</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4448,81 +4450,77 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1953.41</v>
+        <v>1882.78</v>
       </c>
       <c r="C48" t="n">
-        <v>1976.46</v>
+        <v>1937.17</v>
       </c>
       <c r="D48" t="n">
-        <v>1821.49</v>
+        <v>1827.7</v>
       </c>
       <c r="E48" t="n">
-        <v>1882.52</v>
+        <v>1908.68</v>
       </c>
       <c r="F48" t="n">
-        <v>-70.89</v>
+        <v>26.16</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0363</v>
+        <v>0.0139</v>
       </c>
       <c r="H48" t="n">
-        <v>154.98</v>
+        <v>109.47</v>
       </c>
       <c r="I48" t="n">
-        <v>1722.39</v>
+        <v>1666.51</v>
       </c>
       <c r="J48" t="n">
-        <v>1858.17</v>
+        <v>1719.32</v>
       </c>
       <c r="K48" t="n">
-        <v>1893.2</v>
+        <v>1805.03</v>
       </c>
       <c r="L48" t="n">
-        <v>1928.22</v>
+        <v>1890.75</v>
       </c>
       <c r="M48" t="n">
-        <v>2013.63</v>
+        <v>1960.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2099.03</v>
+        <v>2029.27</v>
       </c>
       <c r="O48" t="n">
-        <v>2083.68</v>
+        <v>2131.44</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4534,64 +4532,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1882.78</v>
+        <v>1908.72</v>
       </c>
       <c r="C49" t="n">
-        <v>1937.17</v>
+        <v>1928.99</v>
       </c>
       <c r="D49" t="n">
-        <v>1827.7</v>
+        <v>1852.84</v>
       </c>
       <c r="E49" t="n">
-        <v>1908.68</v>
+        <v>1873.94</v>
       </c>
       <c r="F49" t="n">
-        <v>26.16</v>
+        <v>-34.74</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0182</v>
       </c>
       <c r="H49" t="n">
-        <v>109.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>1666.51</v>
+        <v>1718.23</v>
       </c>
       <c r="J49" t="n">
-        <v>1719.32</v>
+        <v>1812.34</v>
       </c>
       <c r="K49" t="n">
-        <v>1805.03</v>
+        <v>1853.95</v>
       </c>
       <c r="L49" t="n">
-        <v>1890.75</v>
+        <v>1895.56</v>
       </c>
       <c r="M49" t="n">
-        <v>1960.01</v>
+        <v>1963.42</v>
       </c>
       <c r="N49" t="n">
-        <v>2029.27</v>
+        <v>2031.28</v>
       </c>
       <c r="O49" t="n">
-        <v>2131.44</v>
+        <v>2046.64</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4599,12 +4597,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4616,64 +4616,64 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1908.72</v>
+        <v>1873.97</v>
       </c>
       <c r="C50" t="n">
-        <v>1928.99</v>
+        <v>2545.88</v>
       </c>
       <c r="D50" t="n">
-        <v>1852.84</v>
+        <v>1870.75</v>
       </c>
       <c r="E50" t="n">
-        <v>1873.94</v>
+        <v>2463.82</v>
       </c>
       <c r="F50" t="n">
-        <v>-34.74</v>
+        <v>589.87</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.3148</v>
       </c>
       <c r="H50" t="n">
-        <v>76.15000000000001</v>
+        <v>675.13</v>
       </c>
       <c r="I50" t="n">
-        <v>1718.23</v>
+        <v>1776.69</v>
       </c>
       <c r="J50" t="n">
-        <v>1812.34</v>
+        <v>1789.3</v>
       </c>
       <c r="K50" t="n">
-        <v>1853.95</v>
+        <v>1835.87</v>
       </c>
       <c r="L50" t="n">
-        <v>1895.56</v>
+        <v>1882.43</v>
       </c>
       <c r="M50" t="n">
-        <v>1963.42</v>
+        <v>1912.02</v>
       </c>
       <c r="N50" t="n">
-        <v>2031.28</v>
+        <v>1941.61</v>
       </c>
       <c r="O50" t="n">
-        <v>2046.64</v>
+        <v>2005.15</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4681,83 +4681,83 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1873.97</v>
+        <v>2463.64</v>
       </c>
       <c r="C51" t="n">
-        <v>2545.88</v>
+        <v>2564.27</v>
       </c>
       <c r="D51" t="n">
-        <v>1870.75</v>
+        <v>2389.47</v>
       </c>
       <c r="E51" t="n">
-        <v>2463.82</v>
+        <v>2417.94</v>
       </c>
       <c r="F51" t="n">
-        <v>589.87</v>
+        <v>-45.88</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.3148</v>
+        <v>-0.0186</v>
       </c>
       <c r="H51" t="n">
-        <v>675.13</v>
+        <v>174.81</v>
       </c>
       <c r="I51" t="n">
-        <v>1776.69</v>
+        <v>1195.61</v>
       </c>
       <c r="J51" t="n">
-        <v>1789.3</v>
+        <v>1916.43</v>
       </c>
       <c r="K51" t="n">
-        <v>1835.87</v>
+        <v>2126.25</v>
       </c>
       <c r="L51" t="n">
-        <v>1882.43</v>
+        <v>2336.07</v>
       </c>
       <c r="M51" t="n">
-        <v>1912.02</v>
+        <v>2801.38</v>
       </c>
       <c r="N51" t="n">
-        <v>1941.61</v>
+        <v>3266.7</v>
       </c>
       <c r="O51" t="n">
-        <v>2005.15</v>
+        <v>3221.01</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4768,80 +4768,78 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S51" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2463.64</v>
+        <v>2417.9</v>
       </c>
       <c r="C52" t="n">
-        <v>2564.27</v>
+        <v>2545.62</v>
       </c>
       <c r="D52" t="n">
-        <v>2389.47</v>
+        <v>2356.19</v>
       </c>
       <c r="E52" t="n">
-        <v>2417.94</v>
+        <v>2514.55</v>
       </c>
       <c r="F52" t="n">
-        <v>-45.88</v>
+        <v>96.61</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0186</v>
+        <v>0.04</v>
       </c>
       <c r="H52" t="n">
-        <v>174.81</v>
+        <v>189.44</v>
       </c>
       <c r="I52" t="n">
-        <v>1195.61</v>
+        <v>2214.66</v>
       </c>
       <c r="J52" t="n">
-        <v>1916.43</v>
+        <v>2213.67</v>
       </c>
       <c r="K52" t="n">
-        <v>2126.25</v>
+        <v>2330.54</v>
       </c>
       <c r="L52" t="n">
-        <v>2336.07</v>
+        <v>2447.41</v>
       </c>
       <c r="M52" t="n">
-        <v>2801.38</v>
+        <v>2505.34</v>
       </c>
       <c r="N52" t="n">
-        <v>3266.7</v>
+        <v>2563.28</v>
       </c>
       <c r="O52" t="n">
-        <v>3221.01</v>
+        <v>2739.08</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4852,13 +4850,15 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="S52" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4873,57 +4873,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2417.9</v>
+        <v>2514.58</v>
       </c>
       <c r="C53" t="n">
-        <v>2545.62</v>
+        <v>2663.05</v>
       </c>
       <c r="D53" t="n">
-        <v>2356.19</v>
+        <v>2406.91</v>
       </c>
       <c r="E53" t="n">
-        <v>2514.55</v>
+        <v>2477.02</v>
       </c>
       <c r="F53" t="n">
-        <v>96.61</v>
+        <v>-37.53</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.0149</v>
       </c>
       <c r="H53" t="n">
-        <v>189.44</v>
+        <v>256.14</v>
       </c>
       <c r="I53" t="n">
-        <v>2214.66</v>
+        <v>2166.75</v>
       </c>
       <c r="J53" t="n">
-        <v>2213.67</v>
+        <v>2356.93</v>
       </c>
       <c r="K53" t="n">
-        <v>2330.54</v>
+        <v>2419.83</v>
       </c>
       <c r="L53" t="n">
-        <v>2447.41</v>
+        <v>2482.73</v>
       </c>
       <c r="M53" t="n">
-        <v>2505.34</v>
+        <v>2609.27</v>
       </c>
       <c r="N53" t="n">
-        <v>2563.28</v>
+        <v>2735.81</v>
       </c>
       <c r="O53" t="n">
-        <v>2739.08</v>
+        <v>2735.06</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4931,17 +4931,19 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4957,57 +4959,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2514.58</v>
+        <v>2476.6</v>
       </c>
       <c r="C54" t="n">
-        <v>2663.05</v>
+        <v>2659.72</v>
       </c>
       <c r="D54" t="n">
-        <v>2406.91</v>
+        <v>2357.96</v>
       </c>
       <c r="E54" t="n">
-        <v>2477.02</v>
+        <v>2643</v>
       </c>
       <c r="F54" t="n">
-        <v>-37.53</v>
+        <v>165.98</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.067</v>
       </c>
       <c r="H54" t="n">
-        <v>256.14</v>
+        <v>301.76</v>
       </c>
       <c r="I54" t="n">
-        <v>2166.75</v>
+        <v>2150.76</v>
       </c>
       <c r="J54" t="n">
-        <v>2356.93</v>
+        <v>2191.9</v>
       </c>
       <c r="K54" t="n">
-        <v>2419.83</v>
+        <v>2348.95</v>
       </c>
       <c r="L54" t="n">
-        <v>2482.73</v>
+        <v>2506</v>
       </c>
       <c r="M54" t="n">
-        <v>2609.27</v>
+        <v>2605.09</v>
       </c>
       <c r="N54" t="n">
-        <v>2735.81</v>
+        <v>2704.19</v>
       </c>
       <c r="O54" t="n">
-        <v>2735.06</v>
+        <v>2919.19</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5015,19 +5017,17 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5043,57 +5043,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2476.6</v>
+        <v>2642.78</v>
       </c>
       <c r="C55" t="n">
-        <v>2659.72</v>
+        <v>2805.5</v>
       </c>
       <c r="D55" t="n">
-        <v>2357.96</v>
+        <v>2628.69</v>
       </c>
       <c r="E55" t="n">
-        <v>2643</v>
+        <v>2686.93</v>
       </c>
       <c r="F55" t="n">
-        <v>165.98</v>
+        <v>43.93</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.067</v>
+        <v>0.0166</v>
       </c>
       <c r="H55" t="n">
-        <v>301.76</v>
+        <v>176.81</v>
       </c>
       <c r="I55" t="n">
-        <v>2150.76</v>
+        <v>2056.2</v>
       </c>
       <c r="J55" t="n">
-        <v>2191.9</v>
+        <v>2408.32</v>
       </c>
       <c r="K55" t="n">
-        <v>2348.95</v>
+        <v>2492.12</v>
       </c>
       <c r="L55" t="n">
-        <v>2506</v>
+        <v>2575.92</v>
       </c>
       <c r="M55" t="n">
-        <v>2605.09</v>
+        <v>2793.88</v>
       </c>
       <c r="N55" t="n">
-        <v>2704.19</v>
+        <v>3011.84</v>
       </c>
       <c r="O55" t="n">
-        <v>2919.19</v>
+        <v>2961.48</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5104,7 +5104,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5125,59 +5125,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2642.78</v>
+        <v>2687</v>
       </c>
       <c r="C56" t="n">
-        <v>2805.5</v>
+        <v>2773.52</v>
       </c>
       <c r="D56" t="n">
-        <v>2628.69</v>
+        <v>2635.48</v>
       </c>
       <c r="E56" t="n">
-        <v>2686.93</v>
+        <v>2726.51</v>
       </c>
       <c r="F56" t="n">
-        <v>43.93</v>
+        <v>39.58</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0147</v>
       </c>
       <c r="H56" t="n">
-        <v>176.81</v>
+        <v>138.04</v>
       </c>
       <c r="I56" t="n">
-        <v>2056.2</v>
+        <v>2451.88</v>
       </c>
       <c r="J56" t="n">
-        <v>2408.32</v>
+        <v>2495.03</v>
       </c>
       <c r="K56" t="n">
-        <v>2492.12</v>
+        <v>2598.52</v>
       </c>
       <c r="L56" t="n">
-        <v>2575.92</v>
+        <v>2702.01</v>
       </c>
       <c r="M56" t="n">
-        <v>2793.88</v>
+        <v>2775.33</v>
       </c>
       <c r="N56" t="n">
-        <v>3011.84</v>
+        <v>2848.65</v>
       </c>
       <c r="O56" t="n">
-        <v>2961.48</v>
+        <v>2982.31</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5188,15 +5184,13 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S56" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5209,68 +5203,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2687</v>
+        <v>2726.65</v>
       </c>
       <c r="C57" t="n">
-        <v>2773.52</v>
+        <v>2736.79</v>
       </c>
       <c r="D57" t="n">
-        <v>2635.48</v>
+        <v>2406.15</v>
       </c>
       <c r="E57" t="n">
-        <v>2726.51</v>
+        <v>2504.03</v>
       </c>
       <c r="F57" t="n">
-        <v>39.58</v>
+        <v>-222.48</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>138.04</v>
+        <v>330.63</v>
       </c>
       <c r="I57" t="n">
-        <v>2451.88</v>
+        <v>2497.44</v>
       </c>
       <c r="J57" t="n">
-        <v>2495.03</v>
+        <v>2599.47</v>
       </c>
       <c r="K57" t="n">
-        <v>2598.52</v>
+        <v>2657.49</v>
       </c>
       <c r="L57" t="n">
-        <v>2702.01</v>
+        <v>2715.51</v>
       </c>
       <c r="M57" t="n">
-        <v>2775.33</v>
+        <v>2795.53</v>
       </c>
       <c r="N57" t="n">
-        <v>2848.65</v>
+        <v>2875.55</v>
       </c>
       <c r="O57" t="n">
-        <v>2982.31</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+        <v>2911.57</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5282,83 +5286,73 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2726.65</v>
+        <v>2534.3</v>
       </c>
       <c r="C58" t="n">
-        <v>2736.79</v>
+        <v>2547.11</v>
       </c>
       <c r="D58" t="n">
-        <v>2406.15</v>
+        <v>2534.3</v>
       </c>
       <c r="E58" t="n">
-        <v>2501.88</v>
+        <v>2542.59</v>
       </c>
       <c r="F58" t="n">
-        <v>-224.63</v>
+        <v>38.56</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0824</v>
+        <v>0.0154</v>
       </c>
       <c r="H58" t="n">
-        <v>330.63</v>
+        <v>12.81</v>
       </c>
       <c r="I58" t="n">
-        <v>2497.44</v>
+        <v>2075.52</v>
       </c>
       <c r="J58" t="n">
-        <v>2599.47</v>
+        <v>2139.67</v>
       </c>
       <c r="K58" t="n">
-        <v>2657.49</v>
+        <v>2338.71</v>
       </c>
       <c r="L58" t="n">
-        <v>2715.51</v>
+        <v>2537.75</v>
       </c>
       <c r="M58" t="n">
-        <v>2795.53</v>
+        <v>2669.34</v>
       </c>
       <c r="N58" t="n">
-        <v>2875.55</v>
+        <v>2800.94</v>
       </c>
       <c r="O58" t="n">
-        <v>2911.57</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>3067.42</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5370,12 +5364,16 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5303,22 +5303,22 @@
         <v>2534.3</v>
       </c>
       <c r="C58" t="n">
-        <v>2547.11</v>
+        <v>2545.2</v>
       </c>
       <c r="D58" t="n">
         <v>2534.3</v>
       </c>
       <c r="E58" t="n">
-        <v>2542.59</v>
+        <v>2537.22</v>
       </c>
       <c r="F58" t="n">
-        <v>38.56</v>
+        <v>33.19</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0133</v>
       </c>
       <c r="H58" t="n">
-        <v>12.81</v>
+        <v>10.89</v>
       </c>
       <c r="I58" t="n">
         <v>2075.52</v>
@@ -5350,9 +5350,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5225,13 +5225,13 @@
         <v>2406.15</v>
       </c>
       <c r="E57" t="n">
-        <v>2504.03</v>
+        <v>2534.7</v>
       </c>
       <c r="F57" t="n">
-        <v>-222.48</v>
+        <v>-191.81</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0703</v>
       </c>
       <c r="H57" t="n">
         <v>330.63</v>
@@ -5300,43 +5300,43 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2534.3</v>
+        <v>2444.14</v>
       </c>
       <c r="C58" t="n">
-        <v>2545.2</v>
+        <v>2491.49</v>
       </c>
       <c r="D58" t="n">
-        <v>2534.3</v>
+        <v>2419.05</v>
       </c>
       <c r="E58" t="n">
-        <v>2537.22</v>
+        <v>2487.94</v>
       </c>
       <c r="F58" t="n">
-        <v>33.19</v>
+        <v>-46.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0184</v>
       </c>
       <c r="H58" t="n">
-        <v>10.89</v>
+        <v>72.45</v>
       </c>
       <c r="I58" t="n">
         <v>2075.52</v>
       </c>
       <c r="J58" t="n">
-        <v>2139.67</v>
+        <v>2185.68</v>
       </c>
       <c r="K58" t="n">
-        <v>2338.71</v>
+        <v>2369.38</v>
       </c>
       <c r="L58" t="n">
-        <v>2537.75</v>
+        <v>2553.08</v>
       </c>
       <c r="M58" t="n">
-        <v>2669.34</v>
+        <v>2700.02</v>
       </c>
       <c r="N58" t="n">
-        <v>2800.94</v>
+        <v>2846.95</v>
       </c>
       <c r="O58" t="n">
         <v>3067.42</v>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>242.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3792.34</v>
+        <v>3808.76</v>
       </c>
       <c r="J2" t="n">
-        <v>4168.58</v>
+        <v>4174.74</v>
       </c>
       <c r="K2" t="n">
-        <v>4366.84</v>
+        <v>4370.95</v>
       </c>
       <c r="L2" t="n">
-        <v>4565.1</v>
+        <v>4567.15</v>
       </c>
       <c r="M2" t="n">
-        <v>4852.35</v>
+        <v>4848.25</v>
       </c>
       <c r="N2" t="n">
-        <v>5139.6</v>
+        <v>5129.34</v>
       </c>
       <c r="O2" t="n">
-        <v>5248.87</v>
+        <v>5240.66</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5300,25 +5300,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2444.14</v>
+        <v>2534.7</v>
       </c>
       <c r="C58" t="n">
-        <v>2491.49</v>
+        <v>2576.58</v>
       </c>
       <c r="D58" t="n">
-        <v>2419.05</v>
+        <v>2441.68</v>
       </c>
       <c r="E58" t="n">
-        <v>2487.94</v>
+        <v>2499.08</v>
       </c>
       <c r="F58" t="n">
-        <v>-46.76</v>
+        <v>-35.62</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0184</v>
+        <v>-0.0141</v>
       </c>
       <c r="H58" t="n">
-        <v>72.45</v>
+        <v>134.9</v>
       </c>
       <c r="I58" t="n">
         <v>2075.52</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>242.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3808.76</v>
+        <v>3916.07</v>
       </c>
       <c r="J2" t="n">
-        <v>4174.74</v>
+        <v>4214.98</v>
       </c>
       <c r="K2" t="n">
-        <v>4370.95</v>
+        <v>4397.78</v>
       </c>
       <c r="L2" t="n">
-        <v>4567.15</v>
+        <v>4580.57</v>
       </c>
       <c r="M2" t="n">
-        <v>4848.25</v>
+        <v>4821.42</v>
       </c>
       <c r="N2" t="n">
-        <v>5129.34</v>
+        <v>5062.27</v>
       </c>
       <c r="O2" t="n">
-        <v>5240.66</v>
+        <v>5187.01</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5306,19 +5306,19 @@
         <v>2576.58</v>
       </c>
       <c r="D58" t="n">
-        <v>2441.68</v>
+        <v>2407.63</v>
       </c>
       <c r="E58" t="n">
-        <v>2499.08</v>
+        <v>2413.34</v>
       </c>
       <c r="F58" t="n">
-        <v>-35.62</v>
+        <v>-121.36</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0479</v>
       </c>
       <c r="H58" t="n">
-        <v>134.9</v>
+        <v>168.95</v>
       </c>
       <c r="I58" t="n">
         <v>2075.52</v>
@@ -5347,12 +5347,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5309,13 +5309,13 @@
         <v>2407.63</v>
       </c>
       <c r="E58" t="n">
-        <v>2413.34</v>
+        <v>2412.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-121.36</v>
+        <v>-122.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0479</v>
+        <v>-0.0482</v>
       </c>
       <c r="H58" t="n">
         <v>168.95</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5309,13 +5309,13 @@
         <v>2407.63</v>
       </c>
       <c r="E58" t="n">
-        <v>2412.5</v>
+        <v>2416.18</v>
       </c>
       <c r="F58" t="n">
-        <v>-122.2</v>
+        <v>-118.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0482</v>
+        <v>-0.0468</v>
       </c>
       <c r="H58" t="n">
         <v>168.95</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>242.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3916.07</v>
+        <v>4143.21</v>
       </c>
       <c r="J2" t="n">
-        <v>4214.98</v>
+        <v>4300.16</v>
       </c>
       <c r="K2" t="n">
-        <v>4397.78</v>
+        <v>4454.56</v>
       </c>
       <c r="L2" t="n">
-        <v>4580.57</v>
+        <v>4608.96</v>
       </c>
       <c r="M2" t="n">
-        <v>4821.42</v>
+        <v>4764.64</v>
       </c>
       <c r="N2" t="n">
-        <v>5062.27</v>
+        <v>4920.31</v>
       </c>
       <c r="O2" t="n">
-        <v>5187.01</v>
+        <v>5073.44</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -711,7 +711,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5306,19 +5306,19 @@
         <v>2576.58</v>
       </c>
       <c r="D58" t="n">
-        <v>2407.63</v>
+        <v>2403.21</v>
       </c>
       <c r="E58" t="n">
-        <v>2416.18</v>
+        <v>2439.35</v>
       </c>
       <c r="F58" t="n">
-        <v>-118.52</v>
+        <v>-95.34999999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0468</v>
+        <v>-0.0376</v>
       </c>
       <c r="H58" t="n">
-        <v>168.95</v>
+        <v>173.37</v>
       </c>
       <c r="I58" t="n">
         <v>2075.52</v>
@@ -5371,11 +5371,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,35 +659,37 @@
         <v>242.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4143.21</v>
+        <v>4400.33</v>
       </c>
       <c r="J2" t="n">
-        <v>4300.16</v>
+        <v>4396.58</v>
       </c>
       <c r="K2" t="n">
-        <v>4454.56</v>
+        <v>4518.84</v>
       </c>
       <c r="L2" t="n">
-        <v>4608.96</v>
+        <v>4641.1</v>
       </c>
       <c r="M2" t="n">
-        <v>4764.64</v>
+        <v>4700.35</v>
       </c>
       <c r="N2" t="n">
-        <v>4920.31</v>
+        <v>4759.61</v>
       </c>
       <c r="O2" t="n">
-        <v>5073.44</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>4944.88</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -5306,19 +5308,19 @@
         <v>2576.58</v>
       </c>
       <c r="D58" t="n">
-        <v>2403.21</v>
+        <v>2320.55</v>
       </c>
       <c r="E58" t="n">
-        <v>2439.35</v>
+        <v>2417.89</v>
       </c>
       <c r="F58" t="n">
-        <v>-95.34999999999999</v>
+        <v>-116.81</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0376</v>
+        <v>-0.0461</v>
       </c>
       <c r="H58" t="n">
-        <v>173.37</v>
+        <v>256.03</v>
       </c>
       <c r="I58" t="n">
         <v>2075.52</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5311,13 +5311,13 @@
         <v>2320.55</v>
       </c>
       <c r="E58" t="n">
-        <v>2417.89</v>
+        <v>2421.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-116.81</v>
+        <v>-113</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0461</v>
+        <v>-0.0446</v>
       </c>
       <c r="H58" t="n">
         <v>256.03</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,33 +659,35 @@
         <v>242.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4400.33</v>
+        <v>4473.05</v>
       </c>
       <c r="J2" t="n">
-        <v>4396.58</v>
+        <v>4487.48</v>
       </c>
       <c r="K2" t="n">
-        <v>4518.84</v>
+        <v>4555.2</v>
       </c>
       <c r="L2" t="n">
-        <v>4641.1</v>
+        <v>4622.92</v>
       </c>
       <c r="M2" t="n">
-        <v>4700.35</v>
+        <v>4664</v>
       </c>
       <c r="N2" t="n">
-        <v>4759.61</v>
+        <v>4705.07</v>
       </c>
       <c r="O2" t="n">
-        <v>4944.88</v>
+        <v>4799.44</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -697,8 +699,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -708,14 +712,10 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -794,7 +794,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -858,7 +858,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -874,7 +874,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -962,7 +962,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1044,7 +1044,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1112,7 +1112,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="11" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1128,7 +1128,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1214,7 +1214,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1302,7 +1302,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1382,7 +1382,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1462,7 +1462,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1526,7 +1526,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1542,7 +1542,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1612,7 +1612,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="11" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1628,7 +1628,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1696,7 +1696,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1712,7 +1712,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="10" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1796,7 +1796,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1874,7 +1874,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1942,7 +1942,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1960,7 +1960,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2024,7 +2024,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2040,7 +2040,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2108,7 +2108,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2126,7 +2126,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2210,7 +2210,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="10" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2292,7 +2292,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="10" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2372,7 +2372,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="10" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2450,7 +2450,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="10" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2532,7 +2532,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="10" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2622,7 +2622,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="10" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2706,7 +2706,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="10" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2774,7 +2774,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="11" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2792,7 +2792,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2874,7 +2874,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2958,7 +2958,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3026,7 +3026,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="11" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3042,7 +3042,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3110,7 +3110,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="11" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3128,7 +3128,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3192,7 +3192,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="11" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3210,7 +3210,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3274,7 +3274,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="11" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3290,7 +3290,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3376,7 +3376,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3444,7 +3444,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="11" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3460,7 +3460,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3544,7 +3544,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="10" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3622,7 +3622,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="10" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3702,7 +3702,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="10" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3786,7 +3786,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="10" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3850,7 +3850,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="11" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3864,7 +3864,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="10" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3932,7 +3932,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="11" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3948,7 +3948,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="10" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4032,7 +4032,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="10" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4096,7 +4096,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="11" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4114,7 +4114,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="10" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4182,7 +4182,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="11" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4196,7 +4196,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="10" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4264,7 +4264,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="11" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4282,7 +4282,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="10" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4350,7 +4350,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="11" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4366,7 +4366,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="10" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4452,7 +4452,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="10" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4520,7 +4520,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="11" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4534,7 +4534,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="10" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4618,7 +4618,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="10" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4686,7 +4686,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="11" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4706,7 +4706,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4770,7 +4770,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="11" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4784,7 +4784,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4852,7 +4852,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="11" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4868,7 +4868,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4954,7 +4954,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5022,7 +5022,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="11" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5038,7 +5038,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5106,7 +5106,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="11" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5122,7 +5122,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5186,7 +5186,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="11" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5200,7 +5200,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5288,7 +5288,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="10" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5311,13 +5311,13 @@
         <v>2320.55</v>
       </c>
       <c r="E58" t="n">
-        <v>2421.7</v>
+        <v>2409.69</v>
       </c>
       <c r="F58" t="n">
-        <v>-113</v>
+        <v>-125.01</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0446</v>
+        <v>-0.0493</v>
       </c>
       <c r="H58" t="n">
         <v>256.03</v>
@@ -5368,7 +5368,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="10" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5311,13 +5311,13 @@
         <v>2320.55</v>
       </c>
       <c r="E58" t="n">
-        <v>2409.69</v>
+        <v>2403.48</v>
       </c>
       <c r="F58" t="n">
-        <v>-125.01</v>
+        <v>-131.22</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0493</v>
+        <v>-0.0518</v>
       </c>
       <c r="H58" t="n">
         <v>256.03</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -634,75 +634,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4609.72</v>
+        <v>4451.58</v>
       </c>
       <c r="C2" t="n">
-        <v>4670.53</v>
+        <v>4457.08</v>
       </c>
       <c r="D2" t="n">
-        <v>4428.33</v>
+        <v>3829.01</v>
       </c>
       <c r="E2" t="n">
-        <v>4451.33</v>
+        <v>4141.48</v>
       </c>
       <c r="F2" t="n">
-        <v>-158.27</v>
+        <v>-309.85</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0343</v>
+        <v>-0.0696</v>
       </c>
       <c r="H2" t="n">
-        <v>242.2</v>
+        <v>628.0700000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4473.05</v>
+        <v>4186.13</v>
       </c>
       <c r="J2" t="n">
-        <v>4487.48</v>
+        <v>4160.08</v>
       </c>
       <c r="K2" t="n">
-        <v>4555.2</v>
+        <v>4330.23</v>
       </c>
       <c r="L2" t="n">
-        <v>4622.92</v>
+        <v>4500.38</v>
       </c>
       <c r="M2" t="n">
-        <v>4664</v>
+        <v>4572.43</v>
       </c>
       <c r="N2" t="n">
-        <v>4705.07</v>
+        <v>4644.48</v>
       </c>
       <c r="O2" t="n">
-        <v>4799.44</v>
+        <v>4912.73</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -720,74 +718,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4451.58</v>
+        <v>4141.36</v>
       </c>
       <c r="C3" t="n">
-        <v>4457.08</v>
+        <v>4616.53</v>
       </c>
       <c r="D3" t="n">
-        <v>3829.01</v>
+        <v>4087.93</v>
       </c>
       <c r="E3" t="n">
-        <v>4141.48</v>
+        <v>4515.42</v>
       </c>
       <c r="F3" t="n">
-        <v>-309.85</v>
+        <v>373.95</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0696</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>628.0700000000001</v>
+        <v>528.61</v>
       </c>
       <c r="I3" t="n">
-        <v>4186.13</v>
+        <v>3200.94</v>
       </c>
       <c r="J3" t="n">
-        <v>4160.08</v>
+        <v>3512.62</v>
       </c>
       <c r="K3" t="n">
-        <v>4330.23</v>
+        <v>3827.44</v>
       </c>
       <c r="L3" t="n">
-        <v>4500.38</v>
+        <v>4142.26</v>
       </c>
       <c r="M3" t="n">
-        <v>4572.43</v>
+        <v>4455.51</v>
       </c>
       <c r="N3" t="n">
-        <v>4644.48</v>
+        <v>4768.76</v>
       </c>
       <c r="O3" t="n">
-        <v>4912.73</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
+        <v>5085.15</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -799,75 +793,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4141.36</v>
+        <v>4515.3</v>
       </c>
       <c r="C4" t="n">
-        <v>4616.53</v>
+        <v>4755.22</v>
       </c>
       <c r="D4" t="n">
-        <v>4087.93</v>
+        <v>3460.22</v>
       </c>
       <c r="E4" t="n">
-        <v>4515.42</v>
+        <v>4164.43</v>
       </c>
       <c r="F4" t="n">
-        <v>373.95</v>
+        <v>-351</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>528.61</v>
+        <v>1295</v>
       </c>
       <c r="I4" t="n">
-        <v>3200.94</v>
+        <v>3559.32</v>
       </c>
       <c r="J4" t="n">
-        <v>3512.62</v>
+        <v>4068.41</v>
       </c>
       <c r="K4" t="n">
-        <v>3827.44</v>
+        <v>4251.12</v>
       </c>
       <c r="L4" t="n">
-        <v>4142.26</v>
+        <v>4433.83</v>
       </c>
       <c r="M4" t="n">
-        <v>4455.51</v>
+        <v>4779.73</v>
       </c>
       <c r="N4" t="n">
-        <v>4768.76</v>
+        <v>5125.63</v>
       </c>
       <c r="O4" t="n">
-        <v>5085.15</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+        <v>5145.14</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -881,76 +883,70 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4515.3</v>
+        <v>4164.05</v>
       </c>
       <c r="C5" t="n">
-        <v>4755.22</v>
+        <v>4292.85</v>
       </c>
       <c r="D5" t="n">
-        <v>3460.22</v>
+        <v>3678.62</v>
       </c>
       <c r="E5" t="n">
-        <v>4164.43</v>
+        <v>3984.65</v>
       </c>
       <c r="F5" t="n">
-        <v>-351</v>
+        <v>-179.78</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0432</v>
       </c>
       <c r="H5" t="n">
-        <v>1295</v>
+        <v>614.23</v>
       </c>
       <c r="I5" t="n">
-        <v>3559.32</v>
+        <v>2165.22</v>
       </c>
       <c r="J5" t="n">
-        <v>4068.41</v>
+        <v>2897.78</v>
       </c>
       <c r="K5" t="n">
-        <v>4251.12</v>
+        <v>3516.93</v>
       </c>
       <c r="L5" t="n">
-        <v>4433.83</v>
+        <v>4136.07</v>
       </c>
       <c r="M5" t="n">
-        <v>4779.73</v>
+        <v>4811.93</v>
       </c>
       <c r="N5" t="n">
-        <v>5125.63</v>
+        <v>5487.78</v>
       </c>
       <c r="O5" t="n">
-        <v>5145.14</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>6050.22</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -976,50 +972,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4164.05</v>
+        <v>3984.7</v>
       </c>
       <c r="C6" t="n">
-        <v>4292.85</v>
+        <v>4177.31</v>
       </c>
       <c r="D6" t="n">
-        <v>3678.62</v>
+        <v>3718.08</v>
       </c>
       <c r="E6" t="n">
-        <v>3984.65</v>
+        <v>4157.99</v>
       </c>
       <c r="F6" t="n">
-        <v>-179.78</v>
+        <v>173.34</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0432</v>
+        <v>0.0435</v>
       </c>
       <c r="H6" t="n">
-        <v>614.23</v>
+        <v>459.23</v>
       </c>
       <c r="I6" t="n">
-        <v>2165.22</v>
+        <v>3064.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2897.78</v>
+        <v>3369.88</v>
       </c>
       <c r="K6" t="n">
-        <v>3516.93</v>
+        <v>3677.54</v>
       </c>
       <c r="L6" t="n">
-        <v>4136.07</v>
+        <v>3985.19</v>
       </c>
       <c r="M6" t="n">
-        <v>4811.93</v>
+        <v>4291.76</v>
       </c>
       <c r="N6" t="n">
-        <v>5487.78</v>
+        <v>4598.33</v>
       </c>
       <c r="O6" t="n">
-        <v>6050.22</v>
+        <v>4907.07</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1030,13 +1026,15 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1051,77 +1049,79 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3984.7</v>
+        <v>4158.01</v>
       </c>
       <c r="C7" t="n">
-        <v>4177.31</v>
+        <v>4250.67</v>
       </c>
       <c r="D7" t="n">
-        <v>3718.08</v>
+        <v>3681.91</v>
       </c>
       <c r="E7" t="n">
-        <v>4157.99</v>
+        <v>3911.06</v>
       </c>
       <c r="F7" t="n">
-        <v>173.34</v>
+        <v>-246.93</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0435</v>
+        <v>-0.0594</v>
       </c>
       <c r="H7" t="n">
-        <v>459.23</v>
+        <v>568.76</v>
       </c>
       <c r="I7" t="n">
-        <v>3064.4</v>
+        <v>3258.84</v>
       </c>
       <c r="J7" t="n">
-        <v>3369.88</v>
+        <v>3803.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3677.54</v>
+        <v>3928.37</v>
       </c>
       <c r="L7" t="n">
-        <v>3985.19</v>
+        <v>4052.84</v>
       </c>
       <c r="M7" t="n">
-        <v>4291.76</v>
+        <v>4387.61</v>
       </c>
       <c r="N7" t="n">
-        <v>4598.33</v>
+        <v>4722.37</v>
       </c>
       <c r="O7" t="n">
-        <v>4907.07</v>
+        <v>4636.54</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1135,60 +1135,62 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4158.01</v>
+        <v>3911.75</v>
       </c>
       <c r="C8" t="n">
-        <v>4250.67</v>
+        <v>3912.63</v>
       </c>
       <c r="D8" t="n">
-        <v>3681.91</v>
+        <v>3063.09</v>
       </c>
       <c r="E8" t="n">
-        <v>3911.06</v>
+        <v>3582.62</v>
       </c>
       <c r="F8" t="n">
-        <v>-246.93</v>
+        <v>-328.44</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>568.76</v>
+        <v>849.55</v>
       </c>
       <c r="I8" t="n">
-        <v>3258.84</v>
+        <v>3113.15</v>
       </c>
       <c r="J8" t="n">
-        <v>3803.9</v>
+        <v>3314.69</v>
       </c>
       <c r="K8" t="n">
-        <v>3928.37</v>
+        <v>3626.68</v>
       </c>
       <c r="L8" t="n">
-        <v>4052.84</v>
+        <v>3938.68</v>
       </c>
       <c r="M8" t="n">
-        <v>4387.61</v>
+        <v>4195.44</v>
       </c>
       <c r="N8" t="n">
-        <v>4722.37</v>
+        <v>4452.21</v>
       </c>
       <c r="O8" t="n">
-        <v>4636.54</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
+        <v>4819.43</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
@@ -1219,69 +1221,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3911.75</v>
+        <v>3583.44</v>
       </c>
       <c r="C9" t="n">
-        <v>3912.63</v>
+        <v>3656.15</v>
       </c>
       <c r="D9" t="n">
-        <v>3063.09</v>
+        <v>3007.07</v>
       </c>
       <c r="E9" t="n">
-        <v>3582.62</v>
+        <v>3092.85</v>
       </c>
       <c r="F9" t="n">
-        <v>-328.44</v>
+        <v>-489.77</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1367</v>
       </c>
       <c r="H9" t="n">
-        <v>849.55</v>
+        <v>649.08</v>
       </c>
       <c r="I9" t="n">
-        <v>3113.15</v>
+        <v>2213.54</v>
       </c>
       <c r="J9" t="n">
-        <v>3314.69</v>
+        <v>2780.46</v>
       </c>
       <c r="K9" t="n">
-        <v>3626.68</v>
+        <v>3157.85</v>
       </c>
       <c r="L9" t="n">
-        <v>3938.68</v>
+        <v>3535.24</v>
       </c>
       <c r="M9" t="n">
-        <v>4195.44</v>
+        <v>4007.39</v>
       </c>
       <c r="N9" t="n">
-        <v>4452.21</v>
+        <v>4479.55</v>
       </c>
       <c r="O9" t="n">
-        <v>4819.43</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4762.18</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
@@ -1312,50 +1306,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3583.44</v>
+        <v>3092.94</v>
       </c>
       <c r="C10" t="n">
-        <v>3656.15</v>
+        <v>3218.13</v>
       </c>
       <c r="D10" t="n">
-        <v>3007.07</v>
+        <v>2626.87</v>
       </c>
       <c r="E10" t="n">
-        <v>3092.85</v>
+        <v>2801.68</v>
       </c>
       <c r="F10" t="n">
-        <v>-489.77</v>
+        <v>-291.17</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.1367</v>
+        <v>-0.0941</v>
       </c>
       <c r="H10" t="n">
-        <v>649.08</v>
+        <v>591.26</v>
       </c>
       <c r="I10" t="n">
-        <v>2213.54</v>
+        <v>2358</v>
       </c>
       <c r="J10" t="n">
-        <v>2780.46</v>
+        <v>2324.39</v>
       </c>
       <c r="K10" t="n">
-        <v>3157.85</v>
+        <v>2768.31</v>
       </c>
       <c r="L10" t="n">
-        <v>3535.24</v>
+        <v>3212.23</v>
       </c>
       <c r="M10" t="n">
-        <v>4007.39</v>
+        <v>3417.39</v>
       </c>
       <c r="N10" t="n">
-        <v>4479.55</v>
+        <v>3622.54</v>
       </c>
       <c r="O10" t="n">
-        <v>4762.18</v>
+        <v>4305.23</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1392,50 +1386,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3092.94</v>
+        <v>2801.2</v>
       </c>
       <c r="C11" t="n">
-        <v>3218.13</v>
+        <v>3095.03</v>
       </c>
       <c r="D11" t="n">
-        <v>2626.87</v>
+        <v>2763.38</v>
       </c>
       <c r="E11" t="n">
-        <v>2801.68</v>
+        <v>2992.11</v>
       </c>
       <c r="F11" t="n">
-        <v>-291.17</v>
+        <v>190.44</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0941</v>
+        <v>0.068</v>
       </c>
       <c r="H11" t="n">
-        <v>591.26</v>
+        <v>331.66</v>
       </c>
       <c r="I11" t="n">
-        <v>2358</v>
+        <v>2035.61</v>
       </c>
       <c r="J11" t="n">
-        <v>2324.39</v>
+        <v>2150</v>
       </c>
       <c r="K11" t="n">
-        <v>2768.31</v>
+        <v>2506.05</v>
       </c>
       <c r="L11" t="n">
-        <v>3212.23</v>
+        <v>2862.09</v>
       </c>
       <c r="M11" t="n">
-        <v>3417.39</v>
+        <v>3097.31</v>
       </c>
       <c r="N11" t="n">
-        <v>3622.54</v>
+        <v>3332.52</v>
       </c>
       <c r="O11" t="n">
-        <v>4305.23</v>
+        <v>3809.39</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1443,19 +1437,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1467,55 +1461,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2801.2</v>
+        <v>2991.92</v>
       </c>
       <c r="C12" t="n">
-        <v>3095.03</v>
+        <v>3238.56</v>
       </c>
       <c r="D12" t="n">
-        <v>2763.38</v>
+        <v>2720.44</v>
       </c>
       <c r="E12" t="n">
-        <v>2992.11</v>
+        <v>3061.3</v>
       </c>
       <c r="F12" t="n">
-        <v>190.44</v>
+        <v>69.19</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.068</v>
+        <v>0.0231</v>
       </c>
       <c r="H12" t="n">
-        <v>331.66</v>
+        <v>518.12</v>
       </c>
       <c r="I12" t="n">
-        <v>2035.61</v>
+        <v>2431.72</v>
       </c>
       <c r="J12" t="n">
-        <v>2150</v>
+        <v>2691.91</v>
       </c>
       <c r="K12" t="n">
-        <v>2506.05</v>
+        <v>2826.28</v>
       </c>
       <c r="L12" t="n">
-        <v>2862.09</v>
+        <v>2960.66</v>
       </c>
       <c r="M12" t="n">
-        <v>3097.31</v>
+        <v>3157.94</v>
       </c>
       <c r="N12" t="n">
-        <v>3332.52</v>
+        <v>3355.22</v>
       </c>
       <c r="O12" t="n">
-        <v>3809.39</v>
+        <v>3426.69</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1523,8 +1521,10 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
@@ -1556,50 +1556,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2991.92</v>
+        <v>3061.01</v>
       </c>
       <c r="C13" t="n">
-        <v>3238.56</v>
+        <v>3446.62</v>
       </c>
       <c r="D13" t="n">
-        <v>2720.44</v>
+        <v>3034.69</v>
       </c>
       <c r="E13" t="n">
-        <v>3061.3</v>
+        <v>3060.59</v>
       </c>
       <c r="F13" t="n">
-        <v>69.19</v>
+        <v>-0.71</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0231</v>
+        <v>-0.0002</v>
       </c>
       <c r="H13" t="n">
-        <v>518.12</v>
+        <v>411.93</v>
       </c>
       <c r="I13" t="n">
-        <v>2431.72</v>
+        <v>2202.32</v>
       </c>
       <c r="J13" t="n">
-        <v>2691.91</v>
+        <v>2584.09</v>
       </c>
       <c r="K13" t="n">
-        <v>2826.28</v>
+        <v>2802.24</v>
       </c>
       <c r="L13" t="n">
-        <v>2960.66</v>
+        <v>3020.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3157.94</v>
+        <v>3320.36</v>
       </c>
       <c r="N13" t="n">
-        <v>3355.22</v>
+        <v>3620.32</v>
       </c>
       <c r="O13" t="n">
-        <v>3426.69</v>
+        <v>3756.67</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1607,19 +1607,17 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1642,50 +1640,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3061.01</v>
+        <v>3060.48</v>
       </c>
       <c r="C14" t="n">
-        <v>3446.62</v>
+        <v>3175.12</v>
       </c>
       <c r="D14" t="n">
-        <v>3034.69</v>
+        <v>2777.12</v>
       </c>
       <c r="E14" t="n">
-        <v>3060.59</v>
+        <v>3001.61</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.71</v>
+        <v>-58.98</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H14" t="n">
-        <v>411.93</v>
+        <v>398</v>
       </c>
       <c r="I14" t="n">
-        <v>2202.32</v>
+        <v>2622.76</v>
       </c>
       <c r="J14" t="n">
-        <v>2584.09</v>
+        <v>2558.63</v>
       </c>
       <c r="K14" t="n">
-        <v>2802.24</v>
+        <v>2854.63</v>
       </c>
       <c r="L14" t="n">
-        <v>3020.4</v>
+        <v>3150.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3320.36</v>
+        <v>3266.56</v>
       </c>
       <c r="N14" t="n">
-        <v>3620.32</v>
+        <v>3382.49</v>
       </c>
       <c r="O14" t="n">
-        <v>3756.67</v>
+        <v>3858.55</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,18 +1691,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1717,59 +1715,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3060.48</v>
+        <v>3001.61</v>
       </c>
       <c r="C15" t="n">
-        <v>3175.12</v>
+        <v>3073.35</v>
       </c>
       <c r="D15" t="n">
-        <v>2777.12</v>
+        <v>2888.99</v>
       </c>
       <c r="E15" t="n">
-        <v>3001.61</v>
+        <v>2948.57</v>
       </c>
       <c r="F15" t="n">
-        <v>-58.98</v>
+        <v>-53.05</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0177</v>
       </c>
       <c r="H15" t="n">
-        <v>398</v>
+        <v>184.37</v>
       </c>
       <c r="I15" t="n">
-        <v>2622.76</v>
+        <v>2379.12</v>
       </c>
       <c r="J15" t="n">
-        <v>2558.63</v>
+        <v>2616.36</v>
       </c>
       <c r="K15" t="n">
-        <v>2854.63</v>
+        <v>2802.61</v>
       </c>
       <c r="L15" t="n">
-        <v>3150.63</v>
+        <v>2988.87</v>
       </c>
       <c r="M15" t="n">
-        <v>3266.56</v>
+        <v>3200.61</v>
       </c>
       <c r="N15" t="n">
-        <v>3382.49</v>
+        <v>3412.36</v>
       </c>
       <c r="O15" t="n">
-        <v>3858.55</v>
+        <v>3573.12</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1777,14 +1771,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1801,55 +1793,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3001.61</v>
+        <v>2948.56</v>
       </c>
       <c r="C16" t="n">
-        <v>3073.35</v>
+        <v>3160.55</v>
       </c>
       <c r="D16" t="n">
-        <v>2888.99</v>
+        <v>2908.75</v>
       </c>
       <c r="E16" t="n">
-        <v>2948.57</v>
+        <v>3140.71</v>
       </c>
       <c r="F16" t="n">
-        <v>-53.05</v>
+        <v>192.14</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0177</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>184.37</v>
+        <v>251.8</v>
       </c>
       <c r="I16" t="n">
-        <v>2379.12</v>
+        <v>2704.62</v>
       </c>
       <c r="J16" t="n">
-        <v>2616.36</v>
+        <v>2747.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2802.61</v>
+        <v>2856.39</v>
       </c>
       <c r="L16" t="n">
-        <v>2988.87</v>
+        <v>2964.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3200.61</v>
+        <v>3040.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3412.36</v>
+        <v>3116.63</v>
       </c>
       <c r="O16" t="n">
-        <v>3573.12</v>
+        <v>3257.72</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,78 +1856,78 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2948.56</v>
+        <v>3141.49</v>
       </c>
       <c r="C17" t="n">
-        <v>3160.55</v>
+        <v>3303.56</v>
       </c>
       <c r="D17" t="n">
-        <v>2908.75</v>
+        <v>3052.51</v>
       </c>
       <c r="E17" t="n">
-        <v>3140.71</v>
+        <v>3118.89</v>
       </c>
       <c r="F17" t="n">
-        <v>192.14</v>
+        <v>-21.83</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="H17" t="n">
-        <v>251.8</v>
+        <v>251.05</v>
       </c>
       <c r="I17" t="n">
-        <v>2704.62</v>
+        <v>2656.95</v>
       </c>
       <c r="J17" t="n">
-        <v>2747.9</v>
+        <v>2941.94</v>
       </c>
       <c r="K17" t="n">
-        <v>2856.39</v>
+        <v>3014.81</v>
       </c>
       <c r="L17" t="n">
-        <v>2964.87</v>
+        <v>3087.68</v>
       </c>
       <c r="M17" t="n">
-        <v>3040.75</v>
+        <v>3266.61</v>
       </c>
       <c r="N17" t="n">
-        <v>3116.63</v>
+        <v>3445.54</v>
       </c>
       <c r="O17" t="n">
-        <v>3257.72</v>
+        <v>3412.35</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1944,7 +1940,7 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1952,10 +1948,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1965,55 +1959,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3141.49</v>
+        <v>3118.83</v>
       </c>
       <c r="C18" t="n">
-        <v>3303.56</v>
+        <v>3397.9</v>
       </c>
       <c r="D18" t="n">
-        <v>3052.51</v>
+        <v>3068.07</v>
       </c>
       <c r="E18" t="n">
-        <v>3118.89</v>
+        <v>3281.16</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.83</v>
+        <v>162.27</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.052</v>
       </c>
       <c r="H18" t="n">
-        <v>251.05</v>
+        <v>329.82</v>
       </c>
       <c r="I18" t="n">
-        <v>2656.95</v>
+        <v>2801.46</v>
       </c>
       <c r="J18" t="n">
-        <v>2941.94</v>
+        <v>2838.26</v>
       </c>
       <c r="K18" t="n">
-        <v>3014.81</v>
+        <v>2993.36</v>
       </c>
       <c r="L18" t="n">
-        <v>3087.68</v>
+        <v>3148.46</v>
       </c>
       <c r="M18" t="n">
-        <v>3266.61</v>
+        <v>3244.41</v>
       </c>
       <c r="N18" t="n">
-        <v>3445.54</v>
+        <v>3340.36</v>
       </c>
       <c r="O18" t="n">
-        <v>3412.35</v>
+        <v>3554.62</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,17 +2024,19 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2045,90 +2045,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3118.83</v>
+        <v>3282.2</v>
       </c>
       <c r="C19" t="n">
-        <v>3397.9</v>
+        <v>3282.65</v>
       </c>
       <c r="D19" t="n">
-        <v>3068.07</v>
+        <v>2785.9</v>
       </c>
       <c r="E19" t="n">
-        <v>3281.16</v>
+        <v>2815.9</v>
       </c>
       <c r="F19" t="n">
-        <v>162.27</v>
+        <v>-465.26</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.052</v>
+        <v>-0.1418</v>
       </c>
       <c r="H19" t="n">
-        <v>329.82</v>
+        <v>496.76</v>
       </c>
       <c r="I19" t="n">
-        <v>2801.46</v>
+        <v>2738.25</v>
       </c>
       <c r="J19" t="n">
-        <v>2838.26</v>
+        <v>2975.42</v>
       </c>
       <c r="K19" t="n">
-        <v>2993.36</v>
+        <v>3116.25</v>
       </c>
       <c r="L19" t="n">
-        <v>3148.46</v>
+        <v>3257.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3244.41</v>
+        <v>3446.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3340.36</v>
+        <v>3635.07</v>
       </c>
       <c r="O19" t="n">
-        <v>3554.62</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+        <v>3727.72</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2136,60 +2134,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3282.2</v>
+        <v>2815.77</v>
       </c>
       <c r="C20" t="n">
-        <v>3282.65</v>
+        <v>3040.72</v>
       </c>
       <c r="D20" t="n">
-        <v>2785.9</v>
+        <v>2224.12</v>
       </c>
       <c r="E20" t="n">
-        <v>2815.9</v>
+        <v>2267.96</v>
       </c>
       <c r="F20" t="n">
-        <v>-465.26</v>
+        <v>-547.9400000000001</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.1418</v>
+        <v>-0.1946</v>
       </c>
       <c r="H20" t="n">
-        <v>496.76</v>
+        <v>816.6</v>
       </c>
       <c r="I20" t="n">
-        <v>2738.25</v>
+        <v>2289.14</v>
       </c>
       <c r="J20" t="n">
-        <v>2975.42</v>
+        <v>2209.96</v>
       </c>
       <c r="K20" t="n">
-        <v>3116.25</v>
+        <v>2567.52</v>
       </c>
       <c r="L20" t="n">
-        <v>3257.07</v>
+        <v>2925.09</v>
       </c>
       <c r="M20" t="n">
-        <v>3446.07</v>
+        <v>3064.28</v>
       </c>
       <c r="N20" t="n">
-        <v>3635.07</v>
+        <v>3203.47</v>
       </c>
       <c r="O20" t="n">
-        <v>3727.72</v>
+        <v>3779.41</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q20" s="6" t="n">
+        <v/>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
@@ -2220,62 +2216,60 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2815.77</v>
+        <v>2267.56</v>
       </c>
       <c r="C21" t="n">
-        <v>3040.72</v>
+        <v>2393.06</v>
       </c>
       <c r="D21" t="n">
-        <v>2224.12</v>
+        <v>1748.63</v>
       </c>
       <c r="E21" t="n">
-        <v>2267.96</v>
+        <v>2088.76</v>
       </c>
       <c r="F21" t="n">
-        <v>-547.9400000000001</v>
+        <v>-179.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.1946</v>
+        <v>-0.079</v>
       </c>
       <c r="H21" t="n">
-        <v>816.6</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2289.14</v>
+        <v>1407.52</v>
       </c>
       <c r="J21" t="n">
-        <v>2209.96</v>
+        <v>1269.14</v>
       </c>
       <c r="K21" t="n">
-        <v>2567.52</v>
+        <v>1859.66</v>
       </c>
       <c r="L21" t="n">
-        <v>2925.09</v>
+        <v>2450.19</v>
       </c>
       <c r="M21" t="n">
-        <v>3064.28</v>
+        <v>2676.27</v>
       </c>
       <c r="N21" t="n">
-        <v>3203.47</v>
+        <v>2902.34</v>
       </c>
       <c r="O21" t="n">
-        <v>3779.41</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>3857.32</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
@@ -2302,50 +2296,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2267.56</v>
+        <v>2087.92</v>
       </c>
       <c r="C22" t="n">
-        <v>2393.06</v>
+        <v>2144.98</v>
       </c>
       <c r="D22" t="n">
-        <v>1748.63</v>
+        <v>1897.33</v>
       </c>
       <c r="E22" t="n">
-        <v>2088.76</v>
+        <v>1966.04</v>
       </c>
       <c r="F22" t="n">
-        <v>-179.2</v>
+        <v>-122.72</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.0588</v>
       </c>
       <c r="H22" t="n">
-        <v>644.4400000000001</v>
+        <v>247.64</v>
       </c>
       <c r="I22" t="n">
-        <v>1407.52</v>
+        <v>1104.19</v>
       </c>
       <c r="J22" t="n">
-        <v>1269.14</v>
+        <v>1453.29</v>
       </c>
       <c r="K22" t="n">
-        <v>1859.66</v>
+        <v>1766.55</v>
       </c>
       <c r="L22" t="n">
-        <v>2450.19</v>
+        <v>2079.8</v>
       </c>
       <c r="M22" t="n">
-        <v>2676.27</v>
+        <v>2410.98</v>
       </c>
       <c r="N22" t="n">
-        <v>2902.34</v>
+        <v>2742.16</v>
       </c>
       <c r="O22" t="n">
-        <v>3857.32</v>
+        <v>3037.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,14 +2347,12 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2377,55 +2369,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2087.92</v>
+        <v>1965.92</v>
       </c>
       <c r="C23" t="n">
-        <v>2144.98</v>
+        <v>2037.16</v>
       </c>
       <c r="D23" t="n">
-        <v>1897.33</v>
+        <v>1906.82</v>
       </c>
       <c r="E23" t="n">
-        <v>1966.04</v>
+        <v>1957.81</v>
       </c>
       <c r="F23" t="n">
-        <v>-122.72</v>
+        <v>-8.24</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0042</v>
       </c>
       <c r="H23" t="n">
-        <v>247.64</v>
+        <v>130.34</v>
       </c>
       <c r="I23" t="n">
-        <v>1104.19</v>
+        <v>1649.69</v>
       </c>
       <c r="J23" t="n">
-        <v>1453.29</v>
+        <v>1690.85</v>
       </c>
       <c r="K23" t="n">
-        <v>1766.55</v>
+        <v>1842.22</v>
       </c>
       <c r="L23" t="n">
-        <v>2079.8</v>
+        <v>1993.6</v>
       </c>
       <c r="M23" t="n">
-        <v>2410.98</v>
+        <v>2089.86</v>
       </c>
       <c r="N23" t="n">
-        <v>2742.16</v>
+        <v>2186.13</v>
       </c>
       <c r="O23" t="n">
-        <v>3037.5</v>
+        <v>2392.62</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2464,70 +2460,78 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1965.92</v>
+        <v>1958.14</v>
       </c>
       <c r="C24" t="n">
-        <v>2037.16</v>
+        <v>2145.51</v>
       </c>
       <c r="D24" t="n">
-        <v>1906.82</v>
+        <v>1804.11</v>
       </c>
       <c r="E24" t="n">
-        <v>1957.81</v>
+        <v>1939.07</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.24</v>
+        <v>-18.74</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>130.34</v>
+        <v>341.39</v>
       </c>
       <c r="I24" t="n">
-        <v>1649.69</v>
+        <v>1776.49</v>
       </c>
       <c r="J24" t="n">
-        <v>1690.85</v>
+        <v>1820.38</v>
       </c>
       <c r="K24" t="n">
-        <v>1842.22</v>
+        <v>1892.64</v>
       </c>
       <c r="L24" t="n">
-        <v>1993.6</v>
+        <v>1964.9</v>
       </c>
       <c r="M24" t="n">
-        <v>2089.86</v>
+        <v>2022.97</v>
       </c>
       <c r="N24" t="n">
-        <v>2186.13</v>
+        <v>2081.05</v>
       </c>
       <c r="O24" t="n">
-        <v>2392.62</v>
+        <v>2167.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2546,78 +2550,72 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1958.14</v>
+        <v>1939.06</v>
       </c>
       <c r="C25" t="n">
-        <v>2145.51</v>
+        <v>2198.66</v>
       </c>
       <c r="D25" t="n">
-        <v>1804.11</v>
+        <v>1915.3</v>
       </c>
       <c r="E25" t="n">
-        <v>1939.07</v>
+        <v>1936.6</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.74</v>
+        <v>-2.46</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0013</v>
       </c>
       <c r="H25" t="n">
-        <v>341.39</v>
+        <v>283.36</v>
       </c>
       <c r="I25" t="n">
-        <v>1776.49</v>
+        <v>1462.72</v>
       </c>
       <c r="J25" t="n">
-        <v>1820.38</v>
+        <v>1579.8</v>
       </c>
       <c r="K25" t="n">
-        <v>1892.64</v>
+        <v>1768.37</v>
       </c>
       <c r="L25" t="n">
-        <v>1964.9</v>
+        <v>1956.94</v>
       </c>
       <c r="M25" t="n">
-        <v>2022.97</v>
+        <v>2109.76</v>
       </c>
       <c r="N25" t="n">
-        <v>2081.05</v>
+        <v>2262.59</v>
       </c>
       <c r="O25" t="n">
-        <v>2167.5</v>
+        <v>2486.9</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2629,57 +2627,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1939.06</v>
+        <v>1936.64</v>
       </c>
       <c r="C26" t="n">
-        <v>2198.66</v>
+        <v>2206.81</v>
       </c>
       <c r="D26" t="n">
-        <v>1915.3</v>
+        <v>1930.6</v>
       </c>
       <c r="E26" t="n">
-        <v>1936.6</v>
+        <v>2177.48</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.46</v>
+        <v>240.87</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.1244</v>
       </c>
       <c r="H26" t="n">
-        <v>283.36</v>
+        <v>276.21</v>
       </c>
       <c r="I26" t="n">
-        <v>1462.72</v>
+        <v>1631.95</v>
       </c>
       <c r="J26" t="n">
-        <v>1579.8</v>
+        <v>1593.06</v>
       </c>
       <c r="K26" t="n">
-        <v>1768.37</v>
+        <v>1794.93</v>
       </c>
       <c r="L26" t="n">
-        <v>1956.94</v>
+        <v>1996.79</v>
       </c>
       <c r="M26" t="n">
-        <v>2109.76</v>
+        <v>2078.28</v>
       </c>
       <c r="N26" t="n">
-        <v>2262.59</v>
+        <v>2159.77</v>
       </c>
       <c r="O26" t="n">
-        <v>2486.9</v>
+        <v>2482.01</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2690,9 +2688,9 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2700,70 +2698,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1936.64</v>
+        <v>2177.78</v>
       </c>
       <c r="C27" t="n">
-        <v>2206.81</v>
+        <v>2384.47</v>
       </c>
       <c r="D27" t="n">
-        <v>1930.6</v>
+        <v>2027.05</v>
       </c>
       <c r="E27" t="n">
-        <v>2177.48</v>
+        <v>2053.05</v>
       </c>
       <c r="F27" t="n">
-        <v>240.87</v>
+        <v>-124.43</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.1244</v>
+        <v>-0.0571</v>
       </c>
       <c r="H27" t="n">
-        <v>276.21</v>
+        <v>357.42</v>
       </c>
       <c r="I27" t="n">
-        <v>1631.95</v>
+        <v>1654.39</v>
       </c>
       <c r="J27" t="n">
-        <v>1593.06</v>
+        <v>1955.65</v>
       </c>
       <c r="K27" t="n">
-        <v>1794.93</v>
+        <v>2039.37</v>
       </c>
       <c r="L27" t="n">
-        <v>1996.79</v>
+        <v>2123.09</v>
       </c>
       <c r="M27" t="n">
-        <v>2078.28</v>
+        <v>2315.58</v>
       </c>
       <c r="N27" t="n">
-        <v>2159.77</v>
+        <v>2508.08</v>
       </c>
       <c r="O27" t="n">
-        <v>2482.01</v>
+        <v>2483.03</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2771,12 +2767,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2784,10 +2782,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2797,55 +2793,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2177.78</v>
+        <v>2052.95</v>
       </c>
       <c r="C28" t="n">
-        <v>2384.47</v>
+        <v>2198.37</v>
       </c>
       <c r="D28" t="n">
-        <v>2027.05</v>
+        <v>1939.53</v>
       </c>
       <c r="E28" t="n">
-        <v>2053.05</v>
+        <v>1982.56</v>
       </c>
       <c r="F28" t="n">
-        <v>-124.43</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0571</v>
+        <v>-0.0343</v>
       </c>
       <c r="H28" t="n">
-        <v>357.42</v>
+        <v>258.84</v>
       </c>
       <c r="I28" t="n">
-        <v>1654.39</v>
+        <v>1669.63</v>
       </c>
       <c r="J28" t="n">
-        <v>1955.65</v>
+        <v>1619.28</v>
       </c>
       <c r="K28" t="n">
-        <v>2039.37</v>
+        <v>1874.34</v>
       </c>
       <c r="L28" t="n">
-        <v>2123.09</v>
+        <v>2129.4</v>
       </c>
       <c r="M28" t="n">
-        <v>2315.58</v>
+        <v>2231.76</v>
       </c>
       <c r="N28" t="n">
-        <v>2508.08</v>
+        <v>2334.11</v>
       </c>
       <c r="O28" t="n">
-        <v>2483.03</v>
+        <v>2741.89</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2863,10 +2863,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2881,57 +2879,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2052.95</v>
+        <v>1982.55</v>
       </c>
       <c r="C29" t="n">
-        <v>2198.37</v>
+        <v>2165.67</v>
       </c>
       <c r="D29" t="n">
-        <v>1939.53</v>
+        <v>1979.08</v>
       </c>
       <c r="E29" t="n">
-        <v>1982.56</v>
+        <v>2109</v>
       </c>
       <c r="F29" t="n">
-        <v>-70.48999999999999</v>
+        <v>126.44</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0343</v>
+        <v>0.0638</v>
       </c>
       <c r="H29" t="n">
-        <v>258.84</v>
+        <v>186.59</v>
       </c>
       <c r="I29" t="n">
-        <v>1669.63</v>
+        <v>1680.69</v>
       </c>
       <c r="J29" t="n">
-        <v>1619.28</v>
+        <v>1680.52</v>
       </c>
       <c r="K29" t="n">
-        <v>1874.34</v>
+        <v>1853.14</v>
       </c>
       <c r="L29" t="n">
-        <v>2129.4</v>
+        <v>2025.75</v>
       </c>
       <c r="M29" t="n">
-        <v>2231.76</v>
+        <v>2111.98</v>
       </c>
       <c r="N29" t="n">
-        <v>2334.11</v>
+        <v>2198.21</v>
       </c>
       <c r="O29" t="n">
-        <v>2741.89</v>
+        <v>2457.21</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,19 +2937,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2965,57 +2963,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1982.55</v>
+        <v>2108.94</v>
       </c>
       <c r="C30" t="n">
-        <v>2165.67</v>
+        <v>2327.46</v>
       </c>
       <c r="D30" t="n">
-        <v>1979.08</v>
+        <v>2061.47</v>
       </c>
       <c r="E30" t="n">
-        <v>2109</v>
+        <v>2192.2</v>
       </c>
       <c r="F30" t="n">
-        <v>126.44</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0638</v>
+        <v>0.0395</v>
       </c>
       <c r="H30" t="n">
-        <v>186.59</v>
+        <v>265.99</v>
       </c>
       <c r="I30" t="n">
-        <v>1680.69</v>
+        <v>1792.49</v>
       </c>
       <c r="J30" t="n">
-        <v>1680.52</v>
+        <v>1940.72</v>
       </c>
       <c r="K30" t="n">
-        <v>1853.14</v>
+        <v>2015.7</v>
       </c>
       <c r="L30" t="n">
-        <v>2025.75</v>
+        <v>2090.68</v>
       </c>
       <c r="M30" t="n">
-        <v>2111.98</v>
+        <v>2202.29</v>
       </c>
       <c r="N30" t="n">
-        <v>2198.21</v>
+        <v>2313.9</v>
       </c>
       <c r="O30" t="n">
-        <v>2457.21</v>
+        <v>2352.26</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3036,8 +3034,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3047,59 +3047,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2108.94</v>
+        <v>2192.33</v>
       </c>
       <c r="C31" t="n">
-        <v>2327.46</v>
+        <v>2464.78</v>
       </c>
       <c r="D31" t="n">
-        <v>2061.47</v>
+        <v>2176.32</v>
       </c>
       <c r="E31" t="n">
-        <v>2192.2</v>
+        <v>2264.92</v>
       </c>
       <c r="F31" t="n">
-        <v>83.20999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0332</v>
       </c>
       <c r="H31" t="n">
-        <v>265.99</v>
+        <v>288.46</v>
       </c>
       <c r="I31" t="n">
-        <v>1792.49</v>
+        <v>1795.48</v>
       </c>
       <c r="J31" t="n">
-        <v>1940.72</v>
+        <v>1925.08</v>
       </c>
       <c r="K31" t="n">
-        <v>2015.7</v>
+        <v>2059.21</v>
       </c>
       <c r="L31" t="n">
-        <v>2090.68</v>
+        <v>2193.33</v>
       </c>
       <c r="M31" t="n">
-        <v>2202.29</v>
+        <v>2325.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2313.9</v>
+        <v>2457.06</v>
       </c>
       <c r="O31" t="n">
-        <v>2352.26</v>
+        <v>2593.45</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3138,50 +3134,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2192.33</v>
+        <v>2264.87</v>
       </c>
       <c r="C32" t="n">
-        <v>2464.78</v>
+        <v>2422.86</v>
       </c>
       <c r="D32" t="n">
-        <v>2176.32</v>
+        <v>2262.05</v>
       </c>
       <c r="E32" t="n">
-        <v>2264.92</v>
+        <v>2369.73</v>
       </c>
       <c r="F32" t="n">
-        <v>72.72</v>
+        <v>104.81</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0463</v>
       </c>
       <c r="H32" t="n">
-        <v>288.46</v>
+        <v>160.81</v>
       </c>
       <c r="I32" t="n">
-        <v>1795.48</v>
+        <v>1887.87</v>
       </c>
       <c r="J32" t="n">
-        <v>1925.08</v>
+        <v>1948.64</v>
       </c>
       <c r="K32" t="n">
-        <v>2059.21</v>
+        <v>2120.69</v>
       </c>
       <c r="L32" t="n">
-        <v>2193.33</v>
+        <v>2292.74</v>
       </c>
       <c r="M32" t="n">
-        <v>2325.2</v>
+        <v>2409.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2457.06</v>
+        <v>2525.56</v>
       </c>
       <c r="O32" t="n">
-        <v>2593.45</v>
+        <v>2753.24</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3202,10 +3198,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3215,75 +3209,81 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2264.87</v>
+        <v>2369.84</v>
       </c>
       <c r="C33" t="n">
-        <v>2422.86</v>
+        <v>2403.73</v>
       </c>
       <c r="D33" t="n">
-        <v>2262.05</v>
+        <v>2221.22</v>
       </c>
       <c r="E33" t="n">
-        <v>2369.73</v>
+        <v>2321.64</v>
       </c>
       <c r="F33" t="n">
-        <v>104.81</v>
+        <v>-48.09</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0463</v>
+        <v>-0.0203</v>
       </c>
       <c r="H33" t="n">
-        <v>160.81</v>
+        <v>182.5</v>
       </c>
       <c r="I33" t="n">
-        <v>1887.87</v>
+        <v>2101.25</v>
       </c>
       <c r="J33" t="n">
-        <v>1948.64</v>
+        <v>2222.56</v>
       </c>
       <c r="K33" t="n">
-        <v>2120.69</v>
+        <v>2289.33</v>
       </c>
       <c r="L33" t="n">
-        <v>2292.74</v>
+        <v>2356.09</v>
       </c>
       <c r="M33" t="n">
-        <v>2409.15</v>
+        <v>2450.13</v>
       </c>
       <c r="N33" t="n">
-        <v>2525.56</v>
+        <v>2544.17</v>
       </c>
       <c r="O33" t="n">
-        <v>2753.24</v>
+        <v>2583.67</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3297,79 +3297,77 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2369.84</v>
+        <v>2321.82</v>
       </c>
       <c r="C34" t="n">
-        <v>2403.73</v>
+        <v>2423.04</v>
       </c>
       <c r="D34" t="n">
-        <v>2221.22</v>
+        <v>2265.83</v>
       </c>
       <c r="E34" t="n">
-        <v>2321.64</v>
+        <v>2369.04</v>
       </c>
       <c r="F34" t="n">
-        <v>-48.09</v>
+        <v>47.41</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="H34" t="n">
-        <v>182.5</v>
+        <v>157.21</v>
       </c>
       <c r="I34" t="n">
-        <v>2101.25</v>
+        <v>2038.72</v>
       </c>
       <c r="J34" t="n">
-        <v>2222.56</v>
+        <v>2143.71</v>
       </c>
       <c r="K34" t="n">
-        <v>2289.33</v>
+        <v>2230.38</v>
       </c>
       <c r="L34" t="n">
-        <v>2356.09</v>
+        <v>2317.06</v>
       </c>
       <c r="M34" t="n">
-        <v>2450.13</v>
+        <v>2412.89</v>
       </c>
       <c r="N34" t="n">
-        <v>2544.17</v>
+        <v>2508.72</v>
       </c>
       <c r="O34" t="n">
-        <v>2583.67</v>
+        <v>2586.23</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3381,88 +3379,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2321.82</v>
+        <v>2369.19</v>
       </c>
       <c r="C35" t="n">
-        <v>2423.04</v>
+        <v>2374.3</v>
       </c>
       <c r="D35" t="n">
-        <v>2265.83</v>
+        <v>2097.02</v>
       </c>
       <c r="E35" t="n">
-        <v>2369.04</v>
+        <v>2127.65</v>
       </c>
       <c r="F35" t="n">
-        <v>47.41</v>
+        <v>-241.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.1019</v>
       </c>
       <c r="H35" t="n">
-        <v>157.21</v>
+        <v>277.28</v>
       </c>
       <c r="I35" t="n">
-        <v>2038.72</v>
+        <v>2108.63</v>
       </c>
       <c r="J35" t="n">
-        <v>2143.71</v>
+        <v>2224.14</v>
       </c>
       <c r="K35" t="n">
-        <v>2230.38</v>
+        <v>2290.44</v>
       </c>
       <c r="L35" t="n">
-        <v>2317.06</v>
+        <v>2356.74</v>
       </c>
       <c r="M35" t="n">
-        <v>2412.89</v>
+        <v>2447.65</v>
       </c>
       <c r="N35" t="n">
-        <v>2508.72</v>
+        <v>2538.55</v>
       </c>
       <c r="O35" t="n">
-        <v>2586.23</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+        <v>2580.25</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3470,69 +3468,63 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2369.19</v>
+        <v>2127.68</v>
       </c>
       <c r="C36" t="n">
-        <v>2374.3</v>
+        <v>2155.96</v>
       </c>
       <c r="D36" t="n">
-        <v>2097.02</v>
+        <v>2010.55</v>
       </c>
       <c r="E36" t="n">
-        <v>2127.65</v>
+        <v>2097.99</v>
       </c>
       <c r="F36" t="n">
-        <v>-241.4</v>
+        <v>-29.65</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.1019</v>
+        <v>-0.0139</v>
       </c>
       <c r="H36" t="n">
-        <v>277.28</v>
+        <v>145.41</v>
       </c>
       <c r="I36" t="n">
-        <v>2108.63</v>
+        <v>1819.74</v>
       </c>
       <c r="J36" t="n">
-        <v>2224.14</v>
+        <v>1796.35</v>
       </c>
       <c r="K36" t="n">
-        <v>2290.44</v>
+        <v>1989</v>
       </c>
       <c r="L36" t="n">
-        <v>2356.74</v>
+        <v>2181.65</v>
       </c>
       <c r="M36" t="n">
-        <v>2447.65</v>
+        <v>2266.29</v>
       </c>
       <c r="N36" t="n">
-        <v>2538.55</v>
+        <v>2350.92</v>
       </c>
       <c r="O36" t="n">
-        <v>2580.25</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>2651.59</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3554,50 +3546,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2127.68</v>
+        <v>2097.99</v>
       </c>
       <c r="C37" t="n">
-        <v>2155.96</v>
+        <v>2138.41</v>
       </c>
       <c r="D37" t="n">
-        <v>2010.55</v>
+        <v>1966.28</v>
       </c>
       <c r="E37" t="n">
-        <v>2097.99</v>
+        <v>2004.34</v>
       </c>
       <c r="F37" t="n">
-        <v>-29.65</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.0446</v>
       </c>
       <c r="H37" t="n">
-        <v>145.41</v>
+        <v>172.13</v>
       </c>
       <c r="I37" t="n">
-        <v>1819.74</v>
+        <v>1865.14</v>
       </c>
       <c r="J37" t="n">
-        <v>1796.35</v>
+        <v>1959.95</v>
       </c>
       <c r="K37" t="n">
-        <v>1989</v>
+        <v>2025.29</v>
       </c>
       <c r="L37" t="n">
-        <v>2181.65</v>
+        <v>2090.63</v>
       </c>
       <c r="M37" t="n">
-        <v>2266.29</v>
+        <v>2170.7</v>
       </c>
       <c r="N37" t="n">
-        <v>2350.92</v>
+        <v>2250.78</v>
       </c>
       <c r="O37" t="n">
-        <v>2651.59</v>
+        <v>2301.38</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3605,12 +3597,14 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3632,60 +3626,64 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2097.99</v>
+        <v>2004.24</v>
       </c>
       <c r="C38" t="n">
-        <v>2138.41</v>
+        <v>2017.61</v>
       </c>
       <c r="D38" t="n">
-        <v>1966.28</v>
+        <v>1506.51</v>
       </c>
       <c r="E38" t="n">
-        <v>2004.34</v>
+        <v>1686.4</v>
       </c>
       <c r="F38" t="n">
-        <v>-93.65000000000001</v>
+        <v>-317.95</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0446</v>
+        <v>-0.1586</v>
       </c>
       <c r="H38" t="n">
-        <v>172.13</v>
+        <v>511.1</v>
       </c>
       <c r="I38" t="n">
-        <v>1865.14</v>
+        <v>1794.15</v>
       </c>
       <c r="J38" t="n">
-        <v>1959.95</v>
+        <v>1808.21</v>
       </c>
       <c r="K38" t="n">
-        <v>2025.29</v>
+        <v>1918.28</v>
       </c>
       <c r="L38" t="n">
-        <v>2090.63</v>
+        <v>2028.34</v>
       </c>
       <c r="M38" t="n">
-        <v>2170.7</v>
+        <v>2090.41</v>
       </c>
       <c r="N38" t="n">
-        <v>2250.78</v>
+        <v>2152.47</v>
       </c>
       <c r="O38" t="n">
-        <v>2301.38</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+        <v>2310.54</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -3712,69 +3710,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2004.24</v>
+        <v>1686.25</v>
       </c>
       <c r="C39" t="n">
-        <v>2017.61</v>
+        <v>1729.35</v>
       </c>
       <c r="D39" t="n">
-        <v>1506.51</v>
+        <v>1603.83</v>
       </c>
       <c r="E39" t="n">
-        <v>1686.4</v>
+        <v>1724.61</v>
       </c>
       <c r="F39" t="n">
-        <v>-317.95</v>
+        <v>38.22</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.1586</v>
+        <v>0.0227</v>
       </c>
       <c r="H39" t="n">
-        <v>511.1</v>
+        <v>125.53</v>
       </c>
       <c r="I39" t="n">
-        <v>1794.15</v>
+        <v>995.4</v>
       </c>
       <c r="J39" t="n">
-        <v>1808.21</v>
+        <v>1137.46</v>
       </c>
       <c r="K39" t="n">
-        <v>1918.28</v>
+        <v>1430.85</v>
       </c>
       <c r="L39" t="n">
-        <v>2028.34</v>
+        <v>1724.23</v>
       </c>
       <c r="M39" t="n">
-        <v>2090.41</v>
+        <v>1941.95</v>
       </c>
       <c r="N39" t="n">
-        <v>2152.47</v>
+        <v>2159.67</v>
       </c>
       <c r="O39" t="n">
-        <v>2310.54</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>2528.71</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3791,55 +3783,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1686.25</v>
+        <v>1724.57</v>
       </c>
       <c r="C40" t="n">
-        <v>1729.35</v>
+        <v>1847.77</v>
       </c>
       <c r="D40" t="n">
-        <v>1603.83</v>
+        <v>1670.1</v>
       </c>
       <c r="E40" t="n">
-        <v>1724.61</v>
+        <v>1704.58</v>
       </c>
       <c r="F40" t="n">
-        <v>38.22</v>
+        <v>-20.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0227</v>
+        <v>-0.0116</v>
       </c>
       <c r="H40" t="n">
-        <v>125.53</v>
+        <v>177.67</v>
       </c>
       <c r="I40" t="n">
-        <v>995.4</v>
+        <v>1478.3</v>
       </c>
       <c r="J40" t="n">
-        <v>1137.46</v>
+        <v>1628.1</v>
       </c>
       <c r="K40" t="n">
-        <v>1430.85</v>
+        <v>1661.85</v>
       </c>
       <c r="L40" t="n">
-        <v>1724.23</v>
+        <v>1695.6</v>
       </c>
       <c r="M40" t="n">
-        <v>1941.95</v>
+        <v>1787.38</v>
       </c>
       <c r="N40" t="n">
-        <v>2159.67</v>
+        <v>1879.15</v>
       </c>
       <c r="O40" t="n">
-        <v>2528.71</v>
+        <v>1854.88</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,8 +3851,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3878,50 +3876,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1724.57</v>
+        <v>1704.63</v>
       </c>
       <c r="C41" t="n">
-        <v>1847.77</v>
+        <v>1776.83</v>
       </c>
       <c r="D41" t="n">
-        <v>1670.1</v>
+        <v>1510.51</v>
       </c>
       <c r="E41" t="n">
-        <v>1704.58</v>
+        <v>1570.36</v>
       </c>
       <c r="F41" t="n">
-        <v>-20.03</v>
+        <v>-134.22</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>177.67</v>
+        <v>266.33</v>
       </c>
       <c r="I41" t="n">
-        <v>1478.3</v>
+        <v>1492.44</v>
       </c>
       <c r="J41" t="n">
-        <v>1628.1</v>
+        <v>1499.74</v>
       </c>
       <c r="K41" t="n">
-        <v>1661.85</v>
+        <v>1615.75</v>
       </c>
       <c r="L41" t="n">
-        <v>1695.6</v>
+        <v>1731.76</v>
       </c>
       <c r="M41" t="n">
-        <v>1787.38</v>
+        <v>1793.41</v>
       </c>
       <c r="N41" t="n">
-        <v>1879.15</v>
+        <v>1855.07</v>
       </c>
       <c r="O41" t="n">
-        <v>1854.88</v>
+        <v>2025.44</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3929,18 +3927,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3953,59 +3951,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1704.63</v>
+        <v>1569.99</v>
       </c>
       <c r="C42" t="n">
-        <v>1776.83</v>
+        <v>1805.91</v>
       </c>
       <c r="D42" t="n">
-        <v>1510.51</v>
+        <v>1549.25</v>
       </c>
       <c r="E42" t="n">
-        <v>1570.36</v>
+        <v>1783.01</v>
       </c>
       <c r="F42" t="n">
-        <v>-134.22</v>
+        <v>212.64</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.1354</v>
       </c>
       <c r="H42" t="n">
-        <v>266.33</v>
+        <v>256.66</v>
       </c>
       <c r="I42" t="n">
-        <v>1492.44</v>
+        <v>1244.18</v>
       </c>
       <c r="J42" t="n">
-        <v>1499.74</v>
+        <v>1267.38</v>
       </c>
       <c r="K42" t="n">
-        <v>1615.75</v>
+        <v>1437.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1731.76</v>
+        <v>1607.02</v>
       </c>
       <c r="M42" t="n">
-        <v>1793.41</v>
+        <v>1703.52</v>
       </c>
       <c r="N42" t="n">
-        <v>1855.07</v>
+        <v>1800.03</v>
       </c>
       <c r="O42" t="n">
-        <v>2025.44</v>
+        <v>2043.16</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4013,22 +4007,24 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4037,55 +4033,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1569.99</v>
+        <v>1783</v>
       </c>
       <c r="C43" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D43" t="n">
-        <v>1549.25</v>
+        <v>1711.9</v>
       </c>
       <c r="E43" t="n">
-        <v>1783.01</v>
+        <v>1805.79</v>
       </c>
       <c r="F43" t="n">
-        <v>212.64</v>
+        <v>22.78</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.1354</v>
+        <v>0.0128</v>
       </c>
       <c r="H43" t="n">
-        <v>256.66</v>
+        <v>117.61</v>
       </c>
       <c r="I43" t="n">
-        <v>1244.18</v>
+        <v>1292.59</v>
       </c>
       <c r="J43" t="n">
-        <v>1267.38</v>
+        <v>1579.06</v>
       </c>
       <c r="K43" t="n">
-        <v>1437.2</v>
+        <v>1654.67</v>
       </c>
       <c r="L43" t="n">
-        <v>1607.02</v>
+        <v>1730.29</v>
       </c>
       <c r="M43" t="n">
-        <v>1703.52</v>
+        <v>1911.34</v>
       </c>
       <c r="N43" t="n">
-        <v>1800.03</v>
+        <v>2092.38</v>
       </c>
       <c r="O43" t="n">
-        <v>2043.16</v>
+        <v>2062.58</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4098,18 +4098,14 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4128,50 +4124,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1783</v>
+        <v>1805.76</v>
       </c>
       <c r="C44" t="n">
-        <v>1829.51</v>
+        <v>1944.16</v>
       </c>
       <c r="D44" t="n">
-        <v>1711.9</v>
+        <v>1749.35</v>
       </c>
       <c r="E44" t="n">
-        <v>1805.79</v>
+        <v>1871.51</v>
       </c>
       <c r="F44" t="n">
-        <v>22.78</v>
+        <v>65.72</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0364</v>
       </c>
       <c r="H44" t="n">
-        <v>117.61</v>
+        <v>194.81</v>
       </c>
       <c r="I44" t="n">
-        <v>1292.59</v>
+        <v>1594.29</v>
       </c>
       <c r="J44" t="n">
-        <v>1579.06</v>
+        <v>1705.72</v>
       </c>
       <c r="K44" t="n">
-        <v>1654.67</v>
+        <v>1746.98</v>
       </c>
       <c r="L44" t="n">
-        <v>1730.29</v>
+        <v>1788.25</v>
       </c>
       <c r="M44" t="n">
-        <v>1911.34</v>
+        <v>1864.59</v>
       </c>
       <c r="N44" t="n">
-        <v>2092.38</v>
+        <v>1940.94</v>
       </c>
       <c r="O44" t="n">
-        <v>2062.58</v>
+        <v>1947.13</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4184,14 +4180,18 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4210,50 +4210,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1805.76</v>
+        <v>1871.28</v>
       </c>
       <c r="C45" t="n">
-        <v>1944.16</v>
+        <v>1963.25</v>
       </c>
       <c r="D45" t="n">
-        <v>1749.35</v>
+        <v>1842.82</v>
       </c>
       <c r="E45" t="n">
-        <v>1871.51</v>
+        <v>1953.41</v>
       </c>
       <c r="F45" t="n">
-        <v>65.72</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0364</v>
+        <v>0.0438</v>
       </c>
       <c r="H45" t="n">
-        <v>194.81</v>
+        <v>120.43</v>
       </c>
       <c r="I45" t="n">
-        <v>1594.29</v>
+        <v>1554.53</v>
       </c>
       <c r="J45" t="n">
-        <v>1705.72</v>
+        <v>1689.07</v>
       </c>
       <c r="K45" t="n">
-        <v>1746.98</v>
+        <v>1774.1</v>
       </c>
       <c r="L45" t="n">
-        <v>1788.25</v>
+        <v>1859.13</v>
       </c>
       <c r="M45" t="n">
-        <v>1864.59</v>
+        <v>1968.92</v>
       </c>
       <c r="N45" t="n">
-        <v>1940.94</v>
+        <v>2078.7</v>
       </c>
       <c r="O45" t="n">
-        <v>1947.13</v>
+        <v>2138.97</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4274,10 +4274,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4296,70 +4294,72 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1871.28</v>
+        <v>1953.41</v>
       </c>
       <c r="C46" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D46" t="n">
-        <v>1842.82</v>
+        <v>1821.49</v>
       </c>
       <c r="E46" t="n">
-        <v>1953.41</v>
+        <v>1882.52</v>
       </c>
       <c r="F46" t="n">
-        <v>81.90000000000001</v>
+        <v>-70.89</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0363</v>
       </c>
       <c r="H46" t="n">
-        <v>120.43</v>
+        <v>154.98</v>
       </c>
       <c r="I46" t="n">
-        <v>1554.53</v>
+        <v>1722.39</v>
       </c>
       <c r="J46" t="n">
-        <v>1689.07</v>
+        <v>1858.17</v>
       </c>
       <c r="K46" t="n">
-        <v>1774.1</v>
+        <v>1893.2</v>
       </c>
       <c r="L46" t="n">
-        <v>1859.13</v>
+        <v>1928.22</v>
       </c>
       <c r="M46" t="n">
-        <v>1968.92</v>
+        <v>2013.63</v>
       </c>
       <c r="N46" t="n">
-        <v>2078.7</v>
+        <v>2099.03</v>
       </c>
       <c r="O46" t="n">
-        <v>2138.97</v>
+        <v>2083.68</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4373,74 +4373,70 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1953.41</v>
+        <v>1882.78</v>
       </c>
       <c r="C47" t="n">
-        <v>1976.46</v>
+        <v>1937.17</v>
       </c>
       <c r="D47" t="n">
-        <v>1821.49</v>
+        <v>1827.7</v>
       </c>
       <c r="E47" t="n">
-        <v>1882.52</v>
+        <v>1908.68</v>
       </c>
       <c r="F47" t="n">
-        <v>-70.89</v>
+        <v>26.16</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0363</v>
+        <v>0.0139</v>
       </c>
       <c r="H47" t="n">
-        <v>154.98</v>
+        <v>109.47</v>
       </c>
       <c r="I47" t="n">
-        <v>1722.39</v>
+        <v>1666.51</v>
       </c>
       <c r="J47" t="n">
-        <v>1858.17</v>
+        <v>1719.32</v>
       </c>
       <c r="K47" t="n">
-        <v>1893.2</v>
+        <v>1805.03</v>
       </c>
       <c r="L47" t="n">
-        <v>1928.22</v>
+        <v>1890.75</v>
       </c>
       <c r="M47" t="n">
-        <v>2013.63</v>
+        <v>1960.01</v>
       </c>
       <c r="N47" t="n">
-        <v>2099.03</v>
+        <v>2029.27</v>
       </c>
       <c r="O47" t="n">
-        <v>2083.68</v>
+        <v>2131.44</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4459,57 +4455,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1882.78</v>
+        <v>1908.72</v>
       </c>
       <c r="C48" t="n">
-        <v>1937.17</v>
+        <v>1928.99</v>
       </c>
       <c r="D48" t="n">
-        <v>1827.7</v>
+        <v>1852.84</v>
       </c>
       <c r="E48" t="n">
-        <v>1908.68</v>
+        <v>1873.94</v>
       </c>
       <c r="F48" t="n">
-        <v>26.16</v>
+        <v>-34.74</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0182</v>
       </c>
       <c r="H48" t="n">
-        <v>109.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>1666.51</v>
+        <v>1718.23</v>
       </c>
       <c r="J48" t="n">
-        <v>1719.32</v>
+        <v>1812.34</v>
       </c>
       <c r="K48" t="n">
-        <v>1805.03</v>
+        <v>1853.95</v>
       </c>
       <c r="L48" t="n">
-        <v>1890.75</v>
+        <v>1895.56</v>
       </c>
       <c r="M48" t="n">
-        <v>1960.01</v>
+        <v>1963.42</v>
       </c>
       <c r="N48" t="n">
-        <v>2029.27</v>
+        <v>2031.28</v>
       </c>
       <c r="O48" t="n">
-        <v>2131.44</v>
+        <v>2046.64</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4517,12 +4513,14 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4541,57 +4539,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1908.72</v>
+        <v>1873.97</v>
       </c>
       <c r="C49" t="n">
-        <v>1928.99</v>
+        <v>2545.88</v>
       </c>
       <c r="D49" t="n">
-        <v>1852.84</v>
+        <v>1870.75</v>
       </c>
       <c r="E49" t="n">
-        <v>1873.94</v>
+        <v>2463.82</v>
       </c>
       <c r="F49" t="n">
-        <v>-34.74</v>
+        <v>589.87</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.3148</v>
       </c>
       <c r="H49" t="n">
-        <v>76.15000000000001</v>
+        <v>675.13</v>
       </c>
       <c r="I49" t="n">
-        <v>1718.23</v>
+        <v>1776.69</v>
       </c>
       <c r="J49" t="n">
-        <v>1812.34</v>
+        <v>1789.3</v>
       </c>
       <c r="K49" t="n">
-        <v>1853.95</v>
+        <v>1835.87</v>
       </c>
       <c r="L49" t="n">
-        <v>1895.56</v>
+        <v>1882.43</v>
       </c>
       <c r="M49" t="n">
-        <v>1963.42</v>
+        <v>1912.02</v>
       </c>
       <c r="N49" t="n">
-        <v>2031.28</v>
+        <v>1941.61</v>
       </c>
       <c r="O49" t="n">
-        <v>2046.64</v>
+        <v>2005.15</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4599,83 +4597,83 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1873.97</v>
+        <v>2463.64</v>
       </c>
       <c r="C50" t="n">
-        <v>2545.88</v>
+        <v>2564.27</v>
       </c>
       <c r="D50" t="n">
-        <v>1870.75</v>
+        <v>2389.47</v>
       </c>
       <c r="E50" t="n">
-        <v>2463.82</v>
+        <v>2417.94</v>
       </c>
       <c r="F50" t="n">
-        <v>589.87</v>
+        <v>-45.88</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.3148</v>
+        <v>-0.0186</v>
       </c>
       <c r="H50" t="n">
-        <v>675.13</v>
+        <v>174.81</v>
       </c>
       <c r="I50" t="n">
-        <v>1776.69</v>
+        <v>1195.61</v>
       </c>
       <c r="J50" t="n">
-        <v>1789.3</v>
+        <v>1916.43</v>
       </c>
       <c r="K50" t="n">
-        <v>1835.87</v>
+        <v>2126.25</v>
       </c>
       <c r="L50" t="n">
-        <v>1882.43</v>
+        <v>2336.07</v>
       </c>
       <c r="M50" t="n">
-        <v>1912.02</v>
+        <v>2801.38</v>
       </c>
       <c r="N50" t="n">
-        <v>1941.61</v>
+        <v>3266.7</v>
       </c>
       <c r="O50" t="n">
-        <v>2005.15</v>
+        <v>3221.01</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4688,78 +4686,76 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2463.64</v>
+        <v>2417.9</v>
       </c>
       <c r="C51" t="n">
-        <v>2564.27</v>
+        <v>2545.62</v>
       </c>
       <c r="D51" t="n">
-        <v>2389.47</v>
+        <v>2356.19</v>
       </c>
       <c r="E51" t="n">
-        <v>2417.94</v>
+        <v>2514.55</v>
       </c>
       <c r="F51" t="n">
-        <v>-45.88</v>
+        <v>96.61</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0186</v>
+        <v>0.04</v>
       </c>
       <c r="H51" t="n">
-        <v>174.81</v>
+        <v>189.44</v>
       </c>
       <c r="I51" t="n">
-        <v>1195.61</v>
+        <v>2214.66</v>
       </c>
       <c r="J51" t="n">
-        <v>1916.43</v>
+        <v>2213.67</v>
       </c>
       <c r="K51" t="n">
-        <v>2126.25</v>
+        <v>2330.54</v>
       </c>
       <c r="L51" t="n">
-        <v>2336.07</v>
+        <v>2447.41</v>
       </c>
       <c r="M51" t="n">
-        <v>2801.38</v>
+        <v>2505.34</v>
       </c>
       <c r="N51" t="n">
-        <v>3266.7</v>
+        <v>2563.28</v>
       </c>
       <c r="O51" t="n">
-        <v>3221.01</v>
+        <v>2739.08</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4772,11 +4768,13 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4791,57 +4789,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2417.9</v>
+        <v>2514.58</v>
       </c>
       <c r="C52" t="n">
-        <v>2545.62</v>
+        <v>2663.05</v>
       </c>
       <c r="D52" t="n">
-        <v>2356.19</v>
+        <v>2406.91</v>
       </c>
       <c r="E52" t="n">
-        <v>2514.55</v>
+        <v>2477.02</v>
       </c>
       <c r="F52" t="n">
-        <v>96.61</v>
+        <v>-37.53</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.0149</v>
       </c>
       <c r="H52" t="n">
-        <v>189.44</v>
+        <v>256.14</v>
       </c>
       <c r="I52" t="n">
-        <v>2214.66</v>
+        <v>2166.75</v>
       </c>
       <c r="J52" t="n">
-        <v>2213.67</v>
+        <v>2356.93</v>
       </c>
       <c r="K52" t="n">
-        <v>2330.54</v>
+        <v>2419.83</v>
       </c>
       <c r="L52" t="n">
-        <v>2447.41</v>
+        <v>2482.73</v>
       </c>
       <c r="M52" t="n">
-        <v>2505.34</v>
+        <v>2609.27</v>
       </c>
       <c r="N52" t="n">
-        <v>2563.28</v>
+        <v>2735.81</v>
       </c>
       <c r="O52" t="n">
-        <v>2739.08</v>
+        <v>2735.06</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4849,17 +4847,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4875,57 +4875,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2514.58</v>
+        <v>2476.6</v>
       </c>
       <c r="C53" t="n">
-        <v>2663.05</v>
+        <v>2659.72</v>
       </c>
       <c r="D53" t="n">
-        <v>2406.91</v>
+        <v>2357.96</v>
       </c>
       <c r="E53" t="n">
-        <v>2477.02</v>
+        <v>2643</v>
       </c>
       <c r="F53" t="n">
-        <v>-37.53</v>
+        <v>165.98</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.067</v>
       </c>
       <c r="H53" t="n">
-        <v>256.14</v>
+        <v>301.76</v>
       </c>
       <c r="I53" t="n">
-        <v>2166.75</v>
+        <v>2150.76</v>
       </c>
       <c r="J53" t="n">
-        <v>2356.93</v>
+        <v>2191.9</v>
       </c>
       <c r="K53" t="n">
-        <v>2419.83</v>
+        <v>2348.95</v>
       </c>
       <c r="L53" t="n">
-        <v>2482.73</v>
+        <v>2506</v>
       </c>
       <c r="M53" t="n">
-        <v>2609.27</v>
+        <v>2605.09</v>
       </c>
       <c r="N53" t="n">
-        <v>2735.81</v>
+        <v>2704.19</v>
       </c>
       <c r="O53" t="n">
-        <v>2735.06</v>
+        <v>2919.19</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4933,19 +4933,17 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4961,57 +4959,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2476.6</v>
+        <v>2642.78</v>
       </c>
       <c r="C54" t="n">
-        <v>2659.72</v>
+        <v>2805.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2357.96</v>
+        <v>2628.69</v>
       </c>
       <c r="E54" t="n">
-        <v>2643</v>
+        <v>2686.93</v>
       </c>
       <c r="F54" t="n">
-        <v>165.98</v>
+        <v>43.93</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.067</v>
+        <v>0.0166</v>
       </c>
       <c r="H54" t="n">
-        <v>301.76</v>
+        <v>176.81</v>
       </c>
       <c r="I54" t="n">
-        <v>2150.76</v>
+        <v>2056.2</v>
       </c>
       <c r="J54" t="n">
-        <v>2191.9</v>
+        <v>2408.32</v>
       </c>
       <c r="K54" t="n">
-        <v>2348.95</v>
+        <v>2492.12</v>
       </c>
       <c r="L54" t="n">
-        <v>2506</v>
+        <v>2575.92</v>
       </c>
       <c r="M54" t="n">
-        <v>2605.09</v>
+        <v>2793.88</v>
       </c>
       <c r="N54" t="n">
-        <v>2704.19</v>
+        <v>3011.84</v>
       </c>
       <c r="O54" t="n">
-        <v>2919.19</v>
+        <v>2961.48</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5043,59 +5041,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2642.78</v>
+        <v>2687</v>
       </c>
       <c r="C55" t="n">
-        <v>2805.5</v>
+        <v>2773.52</v>
       </c>
       <c r="D55" t="n">
-        <v>2628.69</v>
+        <v>2635.48</v>
       </c>
       <c r="E55" t="n">
-        <v>2686.93</v>
+        <v>2726.51</v>
       </c>
       <c r="F55" t="n">
-        <v>43.93</v>
+        <v>39.58</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0147</v>
       </c>
       <c r="H55" t="n">
-        <v>176.81</v>
+        <v>138.04</v>
       </c>
       <c r="I55" t="n">
-        <v>2056.2</v>
+        <v>2451.88</v>
       </c>
       <c r="J55" t="n">
-        <v>2408.32</v>
+        <v>2495.03</v>
       </c>
       <c r="K55" t="n">
-        <v>2492.12</v>
+        <v>2598.52</v>
       </c>
       <c r="L55" t="n">
-        <v>2575.92</v>
+        <v>2702.01</v>
       </c>
       <c r="M55" t="n">
-        <v>2793.88</v>
+        <v>2775.33</v>
       </c>
       <c r="N55" t="n">
-        <v>3011.84</v>
+        <v>2848.65</v>
       </c>
       <c r="O55" t="n">
-        <v>2961.48</v>
+        <v>2982.31</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5108,13 +5102,11 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5127,68 +5119,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2687</v>
+        <v>2726.65</v>
       </c>
       <c r="C56" t="n">
-        <v>2773.52</v>
+        <v>2736.79</v>
       </c>
       <c r="D56" t="n">
-        <v>2635.48</v>
+        <v>2406.15</v>
       </c>
       <c r="E56" t="n">
-        <v>2726.51</v>
+        <v>2534.7</v>
       </c>
       <c r="F56" t="n">
-        <v>39.58</v>
+        <v>-191.81</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0703</v>
       </c>
       <c r="H56" t="n">
-        <v>138.04</v>
+        <v>330.63</v>
       </c>
       <c r="I56" t="n">
-        <v>2451.88</v>
+        <v>2497.44</v>
       </c>
       <c r="J56" t="n">
-        <v>2495.03</v>
+        <v>2599.47</v>
       </c>
       <c r="K56" t="n">
-        <v>2598.52</v>
+        <v>2657.49</v>
       </c>
       <c r="L56" t="n">
-        <v>2702.01</v>
+        <v>2715.51</v>
       </c>
       <c r="M56" t="n">
-        <v>2775.33</v>
+        <v>2795.53</v>
       </c>
       <c r="N56" t="n">
-        <v>2848.65</v>
+        <v>2875.55</v>
       </c>
       <c r="O56" t="n">
-        <v>2982.31</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>2911.57</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5200,78 +5202,70 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2726.65</v>
+        <v>2534.7</v>
       </c>
       <c r="C57" t="n">
-        <v>2736.79</v>
+        <v>2576.58</v>
       </c>
       <c r="D57" t="n">
-        <v>2406.15</v>
+        <v>2320.55</v>
       </c>
       <c r="E57" t="n">
-        <v>2534.7</v>
+        <v>2399.8</v>
       </c>
       <c r="F57" t="n">
-        <v>-191.81</v>
+        <v>-134.9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0703</v>
+        <v>-0.0532</v>
       </c>
       <c r="H57" t="n">
-        <v>330.63</v>
+        <v>256.03</v>
       </c>
       <c r="I57" t="n">
-        <v>2497.44</v>
+        <v>2075.52</v>
       </c>
       <c r="J57" t="n">
-        <v>2599.47</v>
+        <v>2185.68</v>
       </c>
       <c r="K57" t="n">
-        <v>2657.49</v>
+        <v>2369.38</v>
       </c>
       <c r="L57" t="n">
-        <v>2715.51</v>
+        <v>2553.08</v>
       </c>
       <c r="M57" t="n">
-        <v>2795.53</v>
+        <v>2700.02</v>
       </c>
       <c r="N57" t="n">
-        <v>2875.55</v>
+        <v>2846.95</v>
       </c>
       <c r="O57" t="n">
-        <v>2911.57</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>3067.42</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
@@ -5298,50 +5292,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2534.7</v>
+        <v>2408.26</v>
       </c>
       <c r="C58" t="n">
-        <v>2576.58</v>
+        <v>2414.05</v>
       </c>
       <c r="D58" t="n">
-        <v>2320.55</v>
+        <v>2402.11</v>
       </c>
       <c r="E58" t="n">
-        <v>2403.48</v>
+        <v>2412.72</v>
       </c>
       <c r="F58" t="n">
-        <v>-131.22</v>
+        <v>12.92</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0518</v>
+        <v>0.0054</v>
       </c>
       <c r="H58" t="n">
-        <v>256.03</v>
+        <v>11.94</v>
       </c>
       <c r="I58" t="n">
-        <v>2075.52</v>
+        <v>2064.52</v>
       </c>
       <c r="J58" t="n">
-        <v>2185.68</v>
+        <v>2119.39</v>
       </c>
       <c r="K58" t="n">
-        <v>2369.38</v>
+        <v>2271.78</v>
       </c>
       <c r="L58" t="n">
-        <v>2553.08</v>
+        <v>2424.18</v>
       </c>
       <c r="M58" t="n">
-        <v>2700.02</v>
+        <v>2527.81</v>
       </c>
       <c r="N58" t="n">
-        <v>2846.95</v>
+        <v>2631.45</v>
       </c>
       <c r="O58" t="n">
-        <v>3067.42</v>
+        <v>2832.61</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5349,14 +5343,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5373,7 +5365,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>628.0700000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4186.13</v>
+        <v>4212.69</v>
       </c>
       <c r="J2" t="n">
-        <v>4160.08</v>
+        <v>4193.28</v>
       </c>
       <c r="K2" t="n">
-        <v>4330.23</v>
+        <v>4343.51</v>
       </c>
       <c r="L2" t="n">
-        <v>4500.38</v>
+        <v>4493.74</v>
       </c>
       <c r="M2" t="n">
-        <v>4572.43</v>
+        <v>4559.15</v>
       </c>
       <c r="N2" t="n">
-        <v>4644.48</v>
+        <v>4624.56</v>
       </c>
       <c r="O2" t="n">
-        <v>4912.73</v>
+        <v>4859.62</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5225,13 +5225,13 @@
         <v>2320.55</v>
       </c>
       <c r="E57" t="n">
-        <v>2399.8</v>
+        <v>2408.74</v>
       </c>
       <c r="F57" t="n">
-        <v>-134.9</v>
+        <v>-125.96</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0532</v>
+        <v>-0.0497</v>
       </c>
       <c r="H57" t="n">
         <v>256.03</v>
@@ -5296,43 +5296,43 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2408.26</v>
+        <v>2405.06</v>
       </c>
       <c r="C58" t="n">
-        <v>2414.05</v>
+        <v>2405.06</v>
       </c>
       <c r="D58" t="n">
-        <v>2402.11</v>
+        <v>2392.69</v>
       </c>
       <c r="E58" t="n">
-        <v>2412.72</v>
+        <v>2394.67</v>
       </c>
       <c r="F58" t="n">
-        <v>12.92</v>
+        <v>-14.07</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0058</v>
       </c>
       <c r="H58" t="n">
-        <v>11.94</v>
+        <v>12.37</v>
       </c>
       <c r="I58" t="n">
         <v>2064.52</v>
       </c>
       <c r="J58" t="n">
-        <v>2119.39</v>
+        <v>2132.8</v>
       </c>
       <c r="K58" t="n">
-        <v>2271.78</v>
+        <v>2280.73</v>
       </c>
       <c r="L58" t="n">
-        <v>2424.18</v>
+        <v>2428.65</v>
       </c>
       <c r="M58" t="n">
-        <v>2527.81</v>
+        <v>2536.76</v>
       </c>
       <c r="N58" t="n">
-        <v>2631.45</v>
+        <v>2644.86</v>
       </c>
       <c r="O58" t="n">
         <v>2832.61</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5302,19 +5302,19 @@
         <v>2405.06</v>
       </c>
       <c r="D58" t="n">
-        <v>2392.69</v>
+        <v>2374.15</v>
       </c>
       <c r="E58" t="n">
-        <v>2394.67</v>
+        <v>2392.62</v>
       </c>
       <c r="F58" t="n">
-        <v>-14.07</v>
+        <v>-16.12</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0067</v>
       </c>
       <c r="H58" t="n">
-        <v>12.37</v>
+        <v>30.91</v>
       </c>
       <c r="I58" t="n">
         <v>2064.52</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>628.0700000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4212.69</v>
+        <v>4215.32</v>
       </c>
       <c r="J2" t="n">
-        <v>4193.28</v>
+        <v>4194.26</v>
       </c>
       <c r="K2" t="n">
-        <v>4343.51</v>
+        <v>4344.17</v>
       </c>
       <c r="L2" t="n">
-        <v>4493.74</v>
+        <v>4494.07</v>
       </c>
       <c r="M2" t="n">
-        <v>4559.15</v>
+        <v>4558.49</v>
       </c>
       <c r="N2" t="n">
-        <v>4624.56</v>
+        <v>4622.92</v>
       </c>
       <c r="O2" t="n">
-        <v>4859.62</v>
+        <v>4858.3</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5296,25 +5296,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2405.06</v>
+        <v>2408.74</v>
       </c>
       <c r="C58" t="n">
-        <v>2405.06</v>
+        <v>2454.92</v>
       </c>
       <c r="D58" t="n">
-        <v>2374.15</v>
+        <v>2383.53</v>
       </c>
       <c r="E58" t="n">
-        <v>2392.62</v>
+        <v>2443.58</v>
       </c>
       <c r="F58" t="n">
-        <v>-16.12</v>
+        <v>34.84</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0067</v>
+        <v>0.0145</v>
       </c>
       <c r="H58" t="n">
-        <v>30.91</v>
+        <v>71.39</v>
       </c>
       <c r="I58" t="n">
         <v>2064.52</v>
@@ -5346,9 +5346,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>628.0700000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4215.32</v>
+        <v>4242.56</v>
       </c>
       <c r="J2" t="n">
-        <v>4194.26</v>
+        <v>4204.48</v>
       </c>
       <c r="K2" t="n">
-        <v>4344.17</v>
+        <v>4350.98</v>
       </c>
       <c r="L2" t="n">
-        <v>4494.07</v>
+        <v>4497.47</v>
       </c>
       <c r="M2" t="n">
-        <v>4558.49</v>
+        <v>4551.68</v>
       </c>
       <c r="N2" t="n">
-        <v>4622.92</v>
+        <v>4605.89</v>
       </c>
       <c r="O2" t="n">
-        <v>4858.3</v>
+        <v>4844.68</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5299,22 +5299,22 @@
         <v>2408.74</v>
       </c>
       <c r="C58" t="n">
-        <v>2454.92</v>
+        <v>2479.28</v>
       </c>
       <c r="D58" t="n">
-        <v>2383.53</v>
+        <v>2372.89</v>
       </c>
       <c r="E58" t="n">
-        <v>2443.58</v>
+        <v>2475.49</v>
       </c>
       <c r="F58" t="n">
-        <v>34.84</v>
+        <v>66.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0277</v>
       </c>
       <c r="H58" t="n">
-        <v>71.39</v>
+        <v>106.39</v>
       </c>
       <c r="I58" t="n">
         <v>2064.52</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>2372.89</v>
       </c>
       <c r="E58" t="n">
-        <v>2475.49</v>
+        <v>2434.13</v>
       </c>
       <c r="F58" t="n">
-        <v>66.75</v>
+        <v>25.39</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0277</v>
+        <v>0.0105</v>
       </c>
       <c r="H58" t="n">
         <v>106.39</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>628.0700000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4242.56</v>
+        <v>4265.74</v>
       </c>
       <c r="J2" t="n">
-        <v>4204.48</v>
+        <v>4233.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4350.98</v>
+        <v>4362.56</v>
       </c>
       <c r="L2" t="n">
-        <v>4497.47</v>
+        <v>4491.68</v>
       </c>
       <c r="M2" t="n">
-        <v>4551.68</v>
+        <v>4540.09</v>
       </c>
       <c r="N2" t="n">
-        <v>4605.89</v>
+        <v>4588.51</v>
       </c>
       <c r="O2" t="n">
-        <v>4844.68</v>
+        <v>4798.32</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5299,22 +5299,22 @@
         <v>2408.74</v>
       </c>
       <c r="C58" t="n">
-        <v>2479.28</v>
+        <v>2522.84</v>
       </c>
       <c r="D58" t="n">
         <v>2372.89</v>
       </c>
       <c r="E58" t="n">
-        <v>2434.13</v>
+        <v>2380.88</v>
       </c>
       <c r="F58" t="n">
-        <v>25.39</v>
+        <v>-27.86</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.0116</v>
       </c>
       <c r="H58" t="n">
-        <v>106.39</v>
+        <v>149.95</v>
       </c>
       <c r="I58" t="n">
         <v>2064.52</v>
@@ -5346,9 +5346,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>628.0700000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4265.74</v>
+        <v>4384.43</v>
       </c>
       <c r="J2" t="n">
-        <v>4233.45</v>
+        <v>4375.07</v>
       </c>
       <c r="K2" t="n">
-        <v>4362.56</v>
+        <v>4419.98</v>
       </c>
       <c r="L2" t="n">
-        <v>4491.68</v>
+        <v>4464.9</v>
       </c>
       <c r="M2" t="n">
-        <v>4540.09</v>
+        <v>4482.68</v>
       </c>
       <c r="N2" t="n">
-        <v>4588.51</v>
+        <v>4500.45</v>
       </c>
       <c r="O2" t="n">
-        <v>4798.32</v>
+        <v>4572.5</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5302,19 +5302,19 @@
         <v>2522.84</v>
       </c>
       <c r="D58" t="n">
-        <v>2372.89</v>
+        <v>2358.75</v>
       </c>
       <c r="E58" t="n">
-        <v>2380.88</v>
+        <v>2376.32</v>
       </c>
       <c r="F58" t="n">
-        <v>-27.86</v>
+        <v>-32.42</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0135</v>
       </c>
       <c r="H58" t="n">
-        <v>149.95</v>
+        <v>164.09</v>
       </c>
       <c r="I58" t="n">
         <v>2064.52</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,74 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4451.58</v>
+        <v>4141.36</v>
       </c>
       <c r="C2" t="n">
-        <v>4457.08</v>
+        <v>4616.53</v>
       </c>
       <c r="D2" t="n">
-        <v>3829.01</v>
+        <v>4087.93</v>
       </c>
       <c r="E2" t="n">
-        <v>4141.48</v>
+        <v>4515.42</v>
       </c>
       <c r="F2" t="n">
-        <v>-309.85</v>
+        <v>373.95</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0696</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>628.0700000000001</v>
+        <v>528.61</v>
       </c>
       <c r="I2" t="n">
-        <v>4384.43</v>
+        <v>3200.94</v>
       </c>
       <c r="J2" t="n">
-        <v>4375.07</v>
+        <v>3512.62</v>
       </c>
       <c r="K2" t="n">
-        <v>4419.98</v>
+        <v>3827.44</v>
       </c>
       <c r="L2" t="n">
-        <v>4464.9</v>
+        <v>4142.26</v>
       </c>
       <c r="M2" t="n">
-        <v>4482.68</v>
+        <v>4455.51</v>
       </c>
       <c r="N2" t="n">
-        <v>4500.45</v>
+        <v>4768.76</v>
       </c>
       <c r="O2" t="n">
-        <v>4572.5</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>5085.15</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -710,7 +706,7 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -718,69 +714,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4141.36</v>
+        <v>4515.3</v>
       </c>
       <c r="C3" t="n">
-        <v>4616.53</v>
+        <v>4755.22</v>
       </c>
       <c r="D3" t="n">
-        <v>4087.93</v>
+        <v>3460.22</v>
       </c>
       <c r="E3" t="n">
-        <v>4515.42</v>
+        <v>4164.43</v>
       </c>
       <c r="F3" t="n">
-        <v>373.95</v>
+        <v>-351</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>528.61</v>
+        <v>1295</v>
       </c>
       <c r="I3" t="n">
-        <v>3200.94</v>
+        <v>3559.32</v>
       </c>
       <c r="J3" t="n">
-        <v>3512.62</v>
+        <v>4068.41</v>
       </c>
       <c r="K3" t="n">
-        <v>3827.44</v>
+        <v>4251.12</v>
       </c>
       <c r="L3" t="n">
-        <v>4142.26</v>
+        <v>4433.83</v>
       </c>
       <c r="M3" t="n">
-        <v>4455.51</v>
+        <v>4779.73</v>
       </c>
       <c r="N3" t="n">
-        <v>4768.76</v>
+        <v>5125.63</v>
       </c>
       <c r="O3" t="n">
-        <v>5085.15</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+        <v>5145.14</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -790,81 +790,75 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4515.3</v>
+        <v>4164.05</v>
       </c>
       <c r="C4" t="n">
-        <v>4755.22</v>
+        <v>4292.85</v>
       </c>
       <c r="D4" t="n">
-        <v>3460.22</v>
+        <v>3678.62</v>
       </c>
       <c r="E4" t="n">
-        <v>4164.43</v>
+        <v>3984.65</v>
       </c>
       <c r="F4" t="n">
-        <v>-351</v>
+        <v>-179.78</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0432</v>
       </c>
       <c r="H4" t="n">
-        <v>1295</v>
+        <v>614.23</v>
       </c>
       <c r="I4" t="n">
-        <v>3559.32</v>
+        <v>2165.22</v>
       </c>
       <c r="J4" t="n">
-        <v>4068.41</v>
+        <v>2897.78</v>
       </c>
       <c r="K4" t="n">
-        <v>4251.12</v>
+        <v>3516.93</v>
       </c>
       <c r="L4" t="n">
-        <v>4433.83</v>
+        <v>4136.07</v>
       </c>
       <c r="M4" t="n">
-        <v>4779.73</v>
+        <v>4811.93</v>
       </c>
       <c r="N4" t="n">
-        <v>5125.63</v>
+        <v>5487.78</v>
       </c>
       <c r="O4" t="n">
-        <v>5145.14</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>6050.22</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -878,62 +872,62 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4164.05</v>
+        <v>3984.7</v>
       </c>
       <c r="C5" t="n">
-        <v>4292.85</v>
+        <v>4177.31</v>
       </c>
       <c r="D5" t="n">
-        <v>3678.62</v>
+        <v>3718.08</v>
       </c>
       <c r="E5" t="n">
-        <v>3984.65</v>
+        <v>4157.99</v>
       </c>
       <c r="F5" t="n">
-        <v>-179.78</v>
+        <v>173.34</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0432</v>
+        <v>0.0435</v>
       </c>
       <c r="H5" t="n">
-        <v>614.23</v>
+        <v>459.23</v>
       </c>
       <c r="I5" t="n">
-        <v>2165.22</v>
+        <v>3064.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2897.78</v>
+        <v>3369.88</v>
       </c>
       <c r="K5" t="n">
-        <v>3516.93</v>
+        <v>3677.54</v>
       </c>
       <c r="L5" t="n">
-        <v>4136.07</v>
+        <v>3985.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4811.93</v>
+        <v>4291.76</v>
       </c>
       <c r="N5" t="n">
-        <v>5487.78</v>
+        <v>4598.33</v>
       </c>
       <c r="O5" t="n">
-        <v>6050.22</v>
+        <v>4907.07</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,11 +940,13 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -960,7 +956,7 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -972,69 +968,71 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3984.7</v>
+        <v>4158.01</v>
       </c>
       <c r="C6" t="n">
-        <v>4177.31</v>
+        <v>4250.67</v>
       </c>
       <c r="D6" t="n">
-        <v>3718.08</v>
+        <v>3681.91</v>
       </c>
       <c r="E6" t="n">
-        <v>4157.99</v>
+        <v>3911.06</v>
       </c>
       <c r="F6" t="n">
-        <v>173.34</v>
+        <v>-246.93</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0435</v>
+        <v>-0.0594</v>
       </c>
       <c r="H6" t="n">
-        <v>459.23</v>
+        <v>568.76</v>
       </c>
       <c r="I6" t="n">
-        <v>3064.4</v>
+        <v>3258.84</v>
       </c>
       <c r="J6" t="n">
-        <v>3369.88</v>
+        <v>3803.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3677.54</v>
+        <v>3928.37</v>
       </c>
       <c r="L6" t="n">
-        <v>3985.19</v>
+        <v>4052.84</v>
       </c>
       <c r="M6" t="n">
-        <v>4291.76</v>
+        <v>4387.61</v>
       </c>
       <c r="N6" t="n">
-        <v>4598.33</v>
+        <v>4722.37</v>
       </c>
       <c r="O6" t="n">
-        <v>4907.07</v>
+        <v>4636.54</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1044,7 +1042,7 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1056,53 +1054,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4158.01</v>
+        <v>3911.75</v>
       </c>
       <c r="C7" t="n">
-        <v>4250.67</v>
+        <v>3912.63</v>
       </c>
       <c r="D7" t="n">
-        <v>3681.91</v>
+        <v>3063.09</v>
       </c>
       <c r="E7" t="n">
-        <v>3911.06</v>
+        <v>3582.62</v>
       </c>
       <c r="F7" t="n">
-        <v>-246.93</v>
+        <v>-328.44</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>568.76</v>
+        <v>849.55</v>
       </c>
       <c r="I7" t="n">
-        <v>3258.84</v>
+        <v>3113.15</v>
       </c>
       <c r="J7" t="n">
-        <v>3803.9</v>
+        <v>3314.69</v>
       </c>
       <c r="K7" t="n">
-        <v>3928.37</v>
+        <v>3626.68</v>
       </c>
       <c r="L7" t="n">
-        <v>4052.84</v>
+        <v>3938.68</v>
       </c>
       <c r="M7" t="n">
-        <v>4387.61</v>
+        <v>4195.44</v>
       </c>
       <c r="N7" t="n">
-        <v>4722.37</v>
+        <v>4452.21</v>
       </c>
       <c r="O7" t="n">
-        <v>4636.54</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
+        <v>4819.43</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1130,79 +1130,75 @@
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3911.75</v>
+        <v>3583.44</v>
       </c>
       <c r="C8" t="n">
-        <v>3912.63</v>
+        <v>3656.15</v>
       </c>
       <c r="D8" t="n">
-        <v>3063.09</v>
+        <v>3007.07</v>
       </c>
       <c r="E8" t="n">
-        <v>3582.62</v>
+        <v>3092.85</v>
       </c>
       <c r="F8" t="n">
-        <v>-328.44</v>
+        <v>-489.77</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1367</v>
       </c>
       <c r="H8" t="n">
-        <v>849.55</v>
+        <v>649.08</v>
       </c>
       <c r="I8" t="n">
-        <v>3113.15</v>
+        <v>2213.54</v>
       </c>
       <c r="J8" t="n">
-        <v>3314.69</v>
+        <v>2780.46</v>
       </c>
       <c r="K8" t="n">
-        <v>3626.68</v>
+        <v>3157.85</v>
       </c>
       <c r="L8" t="n">
-        <v>3938.68</v>
+        <v>3535.24</v>
       </c>
       <c r="M8" t="n">
-        <v>4195.44</v>
+        <v>4007.39</v>
       </c>
       <c r="N8" t="n">
-        <v>4452.21</v>
+        <v>4479.55</v>
       </c>
       <c r="O8" t="n">
-        <v>4819.43</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4762.18</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1218,58 +1214,62 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3583.44</v>
+        <v>3092.94</v>
       </c>
       <c r="C9" t="n">
-        <v>3656.15</v>
+        <v>3218.13</v>
       </c>
       <c r="D9" t="n">
-        <v>3007.07</v>
+        <v>2626.87</v>
       </c>
       <c r="E9" t="n">
-        <v>3092.85</v>
+        <v>2801.68</v>
       </c>
       <c r="F9" t="n">
-        <v>-489.77</v>
+        <v>-291.17</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.1367</v>
+        <v>-0.0941</v>
       </c>
       <c r="H9" t="n">
-        <v>649.08</v>
+        <v>591.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2213.54</v>
+        <v>2358</v>
       </c>
       <c r="J9" t="n">
-        <v>2780.46</v>
+        <v>2324.39</v>
       </c>
       <c r="K9" t="n">
-        <v>3157.85</v>
+        <v>2768.31</v>
       </c>
       <c r="L9" t="n">
-        <v>3535.24</v>
+        <v>3212.23</v>
       </c>
       <c r="M9" t="n">
-        <v>4007.39</v>
+        <v>3417.39</v>
       </c>
       <c r="N9" t="n">
-        <v>4479.55</v>
+        <v>3622.54</v>
       </c>
       <c r="O9" t="n">
-        <v>4762.18</v>
+        <v>4305.23</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1282,7 +1282,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1298,58 +1298,62 @@
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3092.94</v>
+        <v>2801.2</v>
       </c>
       <c r="C10" t="n">
-        <v>3218.13</v>
+        <v>3095.03</v>
       </c>
       <c r="D10" t="n">
-        <v>2626.87</v>
+        <v>2763.38</v>
       </c>
       <c r="E10" t="n">
-        <v>2801.68</v>
+        <v>2992.11</v>
       </c>
       <c r="F10" t="n">
-        <v>-291.17</v>
+        <v>190.44</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0941</v>
+        <v>0.068</v>
       </c>
       <c r="H10" t="n">
-        <v>591.26</v>
+        <v>331.66</v>
       </c>
       <c r="I10" t="n">
-        <v>2358</v>
+        <v>2035.61</v>
       </c>
       <c r="J10" t="n">
-        <v>2324.39</v>
+        <v>2150</v>
       </c>
       <c r="K10" t="n">
-        <v>2768.31</v>
+        <v>2506.05</v>
       </c>
       <c r="L10" t="n">
-        <v>3212.23</v>
+        <v>2862.09</v>
       </c>
       <c r="M10" t="n">
-        <v>3417.39</v>
+        <v>3097.31</v>
       </c>
       <c r="N10" t="n">
-        <v>3622.54</v>
+        <v>3332.52</v>
       </c>
       <c r="O10" t="n">
-        <v>4305.23</v>
+        <v>3809.39</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,19 +1361,19 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1378,58 +1382,62 @@
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2801.2</v>
+        <v>2991.92</v>
       </c>
       <c r="C11" t="n">
-        <v>3095.03</v>
+        <v>3238.56</v>
       </c>
       <c r="D11" t="n">
-        <v>2763.38</v>
+        <v>2720.44</v>
       </c>
       <c r="E11" t="n">
-        <v>2992.11</v>
+        <v>3061.3</v>
       </c>
       <c r="F11" t="n">
-        <v>190.44</v>
+        <v>69.19</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.068</v>
+        <v>0.0231</v>
       </c>
       <c r="H11" t="n">
-        <v>331.66</v>
+        <v>518.12</v>
       </c>
       <c r="I11" t="n">
-        <v>2035.61</v>
+        <v>2431.72</v>
       </c>
       <c r="J11" t="n">
-        <v>2150</v>
+        <v>2691.91</v>
       </c>
       <c r="K11" t="n">
-        <v>2506.05</v>
+        <v>2826.28</v>
       </c>
       <c r="L11" t="n">
-        <v>2862.09</v>
+        <v>2960.66</v>
       </c>
       <c r="M11" t="n">
-        <v>3097.31</v>
+        <v>3157.94</v>
       </c>
       <c r="N11" t="n">
-        <v>3332.52</v>
+        <v>3355.22</v>
       </c>
       <c r="O11" t="n">
-        <v>3809.39</v>
+        <v>3426.69</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,10 +1445,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1458,62 +1468,62 @@
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2991.92</v>
+        <v>3061.01</v>
       </c>
       <c r="C12" t="n">
-        <v>3238.56</v>
+        <v>3446.62</v>
       </c>
       <c r="D12" t="n">
-        <v>2720.44</v>
+        <v>3034.69</v>
       </c>
       <c r="E12" t="n">
-        <v>3061.3</v>
+        <v>3060.59</v>
       </c>
       <c r="F12" t="n">
-        <v>69.19</v>
+        <v>-0.71</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0231</v>
+        <v>-0.0002</v>
       </c>
       <c r="H12" t="n">
-        <v>518.12</v>
+        <v>411.93</v>
       </c>
       <c r="I12" t="n">
-        <v>2431.72</v>
+        <v>2202.32</v>
       </c>
       <c r="J12" t="n">
-        <v>2691.91</v>
+        <v>2584.09</v>
       </c>
       <c r="K12" t="n">
-        <v>2826.28</v>
+        <v>2802.24</v>
       </c>
       <c r="L12" t="n">
-        <v>2960.66</v>
+        <v>3020.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3157.94</v>
+        <v>3320.36</v>
       </c>
       <c r="N12" t="n">
-        <v>3355.22</v>
+        <v>3620.32</v>
       </c>
       <c r="O12" t="n">
-        <v>3426.69</v>
+        <v>3756.67</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,21 +1531,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1544,62 +1552,62 @@
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3061.01</v>
+        <v>3060.48</v>
       </c>
       <c r="C13" t="n">
-        <v>3446.62</v>
+        <v>3175.12</v>
       </c>
       <c r="D13" t="n">
-        <v>3034.69</v>
+        <v>2777.12</v>
       </c>
       <c r="E13" t="n">
-        <v>3060.59</v>
+        <v>3001.61</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.71</v>
+        <v>-58.98</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0002</v>
+        <v>-0.0193</v>
       </c>
       <c r="H13" t="n">
-        <v>411.93</v>
+        <v>398</v>
       </c>
       <c r="I13" t="n">
-        <v>2202.32</v>
+        <v>2622.76</v>
       </c>
       <c r="J13" t="n">
-        <v>2584.09</v>
+        <v>2558.63</v>
       </c>
       <c r="K13" t="n">
-        <v>2802.24</v>
+        <v>2854.63</v>
       </c>
       <c r="L13" t="n">
-        <v>3020.4</v>
+        <v>3150.63</v>
       </c>
       <c r="M13" t="n">
-        <v>3320.36</v>
+        <v>3266.56</v>
       </c>
       <c r="N13" t="n">
-        <v>3620.32</v>
+        <v>3382.49</v>
       </c>
       <c r="O13" t="n">
-        <v>3756.67</v>
+        <v>3858.55</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1607,18 +1615,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1628,62 +1636,62 @@
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3060.48</v>
+        <v>3001.61</v>
       </c>
       <c r="C14" t="n">
-        <v>3175.12</v>
+        <v>3073.35</v>
       </c>
       <c r="D14" t="n">
-        <v>2777.12</v>
+        <v>2888.99</v>
       </c>
       <c r="E14" t="n">
-        <v>3001.61</v>
+        <v>2948.57</v>
       </c>
       <c r="F14" t="n">
-        <v>-58.98</v>
+        <v>-53.05</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0177</v>
       </c>
       <c r="H14" t="n">
-        <v>398</v>
+        <v>184.37</v>
       </c>
       <c r="I14" t="n">
-        <v>2622.76</v>
+        <v>2379.12</v>
       </c>
       <c r="J14" t="n">
-        <v>2558.63</v>
+        <v>2616.36</v>
       </c>
       <c r="K14" t="n">
-        <v>2854.63</v>
+        <v>2802.61</v>
       </c>
       <c r="L14" t="n">
-        <v>3150.63</v>
+        <v>2988.87</v>
       </c>
       <c r="M14" t="n">
-        <v>3266.56</v>
+        <v>3200.61</v>
       </c>
       <c r="N14" t="n">
-        <v>3382.49</v>
+        <v>3412.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3858.55</v>
+        <v>3573.12</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,14 +1699,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1712,58 +1718,62 @@
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3001.61</v>
+        <v>2948.56</v>
       </c>
       <c r="C15" t="n">
-        <v>3073.35</v>
+        <v>3160.55</v>
       </c>
       <c r="D15" t="n">
-        <v>2888.99</v>
+        <v>2908.75</v>
       </c>
       <c r="E15" t="n">
-        <v>2948.57</v>
+        <v>3140.71</v>
       </c>
       <c r="F15" t="n">
-        <v>-53.05</v>
+        <v>192.14</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0177</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>184.37</v>
+        <v>251.8</v>
       </c>
       <c r="I15" t="n">
-        <v>2379.12</v>
+        <v>2704.62</v>
       </c>
       <c r="J15" t="n">
-        <v>2616.36</v>
+        <v>2747.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2802.61</v>
+        <v>2856.39</v>
       </c>
       <c r="L15" t="n">
-        <v>2988.87</v>
+        <v>2964.87</v>
       </c>
       <c r="M15" t="n">
-        <v>3200.61</v>
+        <v>3040.75</v>
       </c>
       <c r="N15" t="n">
-        <v>3412.36</v>
+        <v>3116.63</v>
       </c>
       <c r="O15" t="n">
-        <v>3573.12</v>
+        <v>3257.72</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,76 +1786,76 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2948.56</v>
+        <v>3141.49</v>
       </c>
       <c r="C16" t="n">
-        <v>3160.55</v>
+        <v>3303.56</v>
       </c>
       <c r="D16" t="n">
-        <v>2908.75</v>
+        <v>3052.51</v>
       </c>
       <c r="E16" t="n">
-        <v>3140.71</v>
+        <v>3118.89</v>
       </c>
       <c r="F16" t="n">
-        <v>192.14</v>
+        <v>-21.83</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="H16" t="n">
-        <v>251.8</v>
+        <v>251.05</v>
       </c>
       <c r="I16" t="n">
-        <v>2704.62</v>
+        <v>2656.95</v>
       </c>
       <c r="J16" t="n">
-        <v>2747.9</v>
+        <v>2941.94</v>
       </c>
       <c r="K16" t="n">
-        <v>2856.39</v>
+        <v>3014.81</v>
       </c>
       <c r="L16" t="n">
-        <v>2964.87</v>
+        <v>3087.68</v>
       </c>
       <c r="M16" t="n">
-        <v>3040.75</v>
+        <v>3266.61</v>
       </c>
       <c r="N16" t="n">
-        <v>3116.63</v>
+        <v>3445.54</v>
       </c>
       <c r="O16" t="n">
-        <v>3257.72</v>
+        <v>3412.35</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1856,9 +1866,9 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1866,68 +1876,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3141.49</v>
+        <v>3118.83</v>
       </c>
       <c r="C17" t="n">
-        <v>3303.56</v>
+        <v>3397.9</v>
       </c>
       <c r="D17" t="n">
-        <v>3052.51</v>
+        <v>3068.07</v>
       </c>
       <c r="E17" t="n">
-        <v>3118.89</v>
+        <v>3281.16</v>
       </c>
       <c r="F17" t="n">
-        <v>-21.83</v>
+        <v>162.27</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.052</v>
       </c>
       <c r="H17" t="n">
-        <v>251.05</v>
+        <v>329.82</v>
       </c>
       <c r="I17" t="n">
-        <v>2656.95</v>
+        <v>2801.46</v>
       </c>
       <c r="J17" t="n">
-        <v>2941.94</v>
+        <v>2838.26</v>
       </c>
       <c r="K17" t="n">
-        <v>3014.81</v>
+        <v>2993.36</v>
       </c>
       <c r="L17" t="n">
-        <v>3087.68</v>
+        <v>3148.46</v>
       </c>
       <c r="M17" t="n">
-        <v>3266.61</v>
+        <v>3244.41</v>
       </c>
       <c r="N17" t="n">
-        <v>3445.54</v>
+        <v>3340.36</v>
       </c>
       <c r="O17" t="n">
-        <v>3412.35</v>
+        <v>3554.62</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1938,111 +1950,111 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3118.83</v>
+        <v>3282.2</v>
       </c>
       <c r="C18" t="n">
-        <v>3397.9</v>
+        <v>3282.65</v>
       </c>
       <c r="D18" t="n">
-        <v>3068.07</v>
+        <v>2785.9</v>
       </c>
       <c r="E18" t="n">
-        <v>3281.16</v>
+        <v>2815.9</v>
       </c>
       <c r="F18" t="n">
-        <v>162.27</v>
+        <v>-465.26</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.052</v>
+        <v>-0.1418</v>
       </c>
       <c r="H18" t="n">
-        <v>329.82</v>
+        <v>496.76</v>
       </c>
       <c r="I18" t="n">
-        <v>2801.46</v>
+        <v>2738.25</v>
       </c>
       <c r="J18" t="n">
-        <v>2838.26</v>
+        <v>2975.42</v>
       </c>
       <c r="K18" t="n">
-        <v>2993.36</v>
+        <v>3116.25</v>
       </c>
       <c r="L18" t="n">
-        <v>3148.46</v>
+        <v>3257.07</v>
       </c>
       <c r="M18" t="n">
-        <v>3244.41</v>
+        <v>3446.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3340.36</v>
+        <v>3635.07</v>
       </c>
       <c r="O18" t="n">
-        <v>3554.62</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>3727.72</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2050,67 +2062,65 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3282.2</v>
+        <v>2815.77</v>
       </c>
       <c r="C19" t="n">
-        <v>3282.65</v>
+        <v>3040.72</v>
       </c>
       <c r="D19" t="n">
-        <v>2785.9</v>
+        <v>2224.12</v>
       </c>
       <c r="E19" t="n">
-        <v>2815.9</v>
+        <v>2267.96</v>
       </c>
       <c r="F19" t="n">
-        <v>-465.26</v>
+        <v>-547.9400000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.1418</v>
+        <v>-0.1946</v>
       </c>
       <c r="H19" t="n">
-        <v>496.76</v>
+        <v>816.6</v>
       </c>
       <c r="I19" t="n">
-        <v>2738.25</v>
+        <v>2289.14</v>
       </c>
       <c r="J19" t="n">
-        <v>2975.42</v>
+        <v>2209.96</v>
       </c>
       <c r="K19" t="n">
-        <v>3116.25</v>
+        <v>2567.52</v>
       </c>
       <c r="L19" t="n">
-        <v>3257.07</v>
+        <v>2925.09</v>
       </c>
       <c r="M19" t="n">
-        <v>3446.07</v>
+        <v>3064.28</v>
       </c>
       <c r="N19" t="n">
-        <v>3635.07</v>
+        <v>3203.47</v>
       </c>
       <c r="O19" t="n">
-        <v>3727.72</v>
+        <v>3779.41</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2124,7 +2134,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2134,65 +2144,63 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2815.77</v>
+        <v>2267.56</v>
       </c>
       <c r="C20" t="n">
-        <v>3040.72</v>
+        <v>2393.06</v>
       </c>
       <c r="D20" t="n">
-        <v>2224.12</v>
+        <v>1748.63</v>
       </c>
       <c r="E20" t="n">
-        <v>2267.96</v>
+        <v>2088.76</v>
       </c>
       <c r="F20" t="n">
-        <v>-547.9400000000001</v>
+        <v>-179.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.1946</v>
+        <v>-0.079</v>
       </c>
       <c r="H20" t="n">
-        <v>816.6</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>2289.14</v>
+        <v>1407.52</v>
       </c>
       <c r="J20" t="n">
-        <v>2209.96</v>
+        <v>1269.14</v>
       </c>
       <c r="K20" t="n">
-        <v>2567.52</v>
+        <v>1859.66</v>
       </c>
       <c r="L20" t="n">
-        <v>2925.09</v>
+        <v>2450.19</v>
       </c>
       <c r="M20" t="n">
-        <v>3064.28</v>
+        <v>2676.27</v>
       </c>
       <c r="N20" t="n">
-        <v>3203.47</v>
+        <v>2902.34</v>
       </c>
       <c r="O20" t="n">
-        <v>3779.41</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>3857.32</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2206,7 +2214,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2216,50 +2224,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2267.56</v>
+        <v>2087.92</v>
       </c>
       <c r="C21" t="n">
-        <v>2393.06</v>
+        <v>2144.98</v>
       </c>
       <c r="D21" t="n">
-        <v>1748.63</v>
+        <v>1897.33</v>
       </c>
       <c r="E21" t="n">
-        <v>2088.76</v>
+        <v>1966.04</v>
       </c>
       <c r="F21" t="n">
-        <v>-179.2</v>
+        <v>-122.72</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.079</v>
+        <v>-0.0588</v>
       </c>
       <c r="H21" t="n">
-        <v>644.4400000000001</v>
+        <v>247.64</v>
       </c>
       <c r="I21" t="n">
-        <v>1407.52</v>
+        <v>1104.19</v>
       </c>
       <c r="J21" t="n">
-        <v>1269.14</v>
+        <v>1453.29</v>
       </c>
       <c r="K21" t="n">
-        <v>1859.66</v>
+        <v>1766.55</v>
       </c>
       <c r="L21" t="n">
-        <v>2450.19</v>
+        <v>2079.8</v>
       </c>
       <c r="M21" t="n">
-        <v>2676.27</v>
+        <v>2410.98</v>
       </c>
       <c r="N21" t="n">
-        <v>2902.34</v>
+        <v>2742.16</v>
       </c>
       <c r="O21" t="n">
-        <v>3857.32</v>
+        <v>3037.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2267,14 +2275,12 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2286,60 +2292,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2087.92</v>
+        <v>1965.92</v>
       </c>
       <c r="C22" t="n">
-        <v>2144.98</v>
+        <v>2037.16</v>
       </c>
       <c r="D22" t="n">
-        <v>1897.33</v>
+        <v>1906.82</v>
       </c>
       <c r="E22" t="n">
-        <v>1966.04</v>
+        <v>1957.81</v>
       </c>
       <c r="F22" t="n">
-        <v>-122.72</v>
+        <v>-8.24</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0588</v>
+        <v>-0.0042</v>
       </c>
       <c r="H22" t="n">
-        <v>247.64</v>
+        <v>130.34</v>
       </c>
       <c r="I22" t="n">
-        <v>1104.19</v>
+        <v>1649.69</v>
       </c>
       <c r="J22" t="n">
-        <v>1453.29</v>
+        <v>1690.85</v>
       </c>
       <c r="K22" t="n">
-        <v>1766.55</v>
+        <v>1842.22</v>
       </c>
       <c r="L22" t="n">
-        <v>2079.8</v>
+        <v>1993.6</v>
       </c>
       <c r="M22" t="n">
-        <v>2410.98</v>
+        <v>2089.86</v>
       </c>
       <c r="N22" t="n">
-        <v>2742.16</v>
+        <v>2186.13</v>
       </c>
       <c r="O22" t="n">
-        <v>3037.5</v>
+        <v>2392.62</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,7 +2360,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2364,7 +2374,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2378,75 +2388,83 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1965.92</v>
+        <v>1958.14</v>
       </c>
       <c r="C23" t="n">
-        <v>2037.16</v>
+        <v>2145.51</v>
       </c>
       <c r="D23" t="n">
-        <v>1906.82</v>
+        <v>1804.11</v>
       </c>
       <c r="E23" t="n">
-        <v>1957.81</v>
+        <v>1939.07</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.24</v>
+        <v>-18.74</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>130.34</v>
+        <v>341.39</v>
       </c>
       <c r="I23" t="n">
-        <v>1649.69</v>
+        <v>1776.49</v>
       </c>
       <c r="J23" t="n">
-        <v>1690.85</v>
+        <v>1820.38</v>
       </c>
       <c r="K23" t="n">
-        <v>1842.22</v>
+        <v>1892.64</v>
       </c>
       <c r="L23" t="n">
-        <v>1993.6</v>
+        <v>1964.9</v>
       </c>
       <c r="M23" t="n">
-        <v>2089.86</v>
+        <v>2022.97</v>
       </c>
       <c r="N23" t="n">
-        <v>2186.13</v>
+        <v>2081.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2392.62</v>
+        <v>2167.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2460,140 +2478,134 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1958.14</v>
+        <v>1939.06</v>
       </c>
       <c r="C24" t="n">
-        <v>2145.51</v>
+        <v>2198.66</v>
       </c>
       <c r="D24" t="n">
-        <v>1804.11</v>
+        <v>1915.3</v>
       </c>
       <c r="E24" t="n">
-        <v>1939.07</v>
+        <v>1936.6</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.74</v>
+        <v>-2.46</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0013</v>
       </c>
       <c r="H24" t="n">
-        <v>341.39</v>
+        <v>283.36</v>
       </c>
       <c r="I24" t="n">
-        <v>1776.49</v>
+        <v>1462.72</v>
       </c>
       <c r="J24" t="n">
-        <v>1820.38</v>
+        <v>1579.8</v>
       </c>
       <c r="K24" t="n">
-        <v>1892.64</v>
+        <v>1768.37</v>
       </c>
       <c r="L24" t="n">
-        <v>1964.9</v>
+        <v>1956.94</v>
       </c>
       <c r="M24" t="n">
-        <v>2022.97</v>
+        <v>2109.76</v>
       </c>
       <c r="N24" t="n">
-        <v>2081.05</v>
+        <v>2262.59</v>
       </c>
       <c r="O24" t="n">
-        <v>2167.5</v>
+        <v>2486.9</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1939.06</v>
+        <v>1936.64</v>
       </c>
       <c r="C25" t="n">
-        <v>2198.66</v>
+        <v>2206.81</v>
       </c>
       <c r="D25" t="n">
-        <v>1915.3</v>
+        <v>1930.6</v>
       </c>
       <c r="E25" t="n">
-        <v>1936.6</v>
+        <v>2177.48</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.46</v>
+        <v>240.87</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.1244</v>
       </c>
       <c r="H25" t="n">
-        <v>283.36</v>
+        <v>276.21</v>
       </c>
       <c r="I25" t="n">
-        <v>1462.72</v>
+        <v>1631.95</v>
       </c>
       <c r="J25" t="n">
-        <v>1579.8</v>
+        <v>1593.06</v>
       </c>
       <c r="K25" t="n">
-        <v>1768.37</v>
+        <v>1794.93</v>
       </c>
       <c r="L25" t="n">
-        <v>1956.94</v>
+        <v>1996.79</v>
       </c>
       <c r="M25" t="n">
-        <v>2109.76</v>
+        <v>2078.28</v>
       </c>
       <c r="N25" t="n">
-        <v>2262.59</v>
+        <v>2159.77</v>
       </c>
       <c r="O25" t="n">
-        <v>2486.9</v>
+        <v>2482.01</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2606,7 +2618,7 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2614,70 +2626,68 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1936.64</v>
+        <v>2177.78</v>
       </c>
       <c r="C26" t="n">
-        <v>2206.81</v>
+        <v>2384.47</v>
       </c>
       <c r="D26" t="n">
-        <v>1930.6</v>
+        <v>2027.05</v>
       </c>
       <c r="E26" t="n">
-        <v>2177.48</v>
+        <v>2053.05</v>
       </c>
       <c r="F26" t="n">
-        <v>240.87</v>
+        <v>-124.43</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.1244</v>
+        <v>-0.0571</v>
       </c>
       <c r="H26" t="n">
-        <v>276.21</v>
+        <v>357.42</v>
       </c>
       <c r="I26" t="n">
-        <v>1631.95</v>
+        <v>1654.39</v>
       </c>
       <c r="J26" t="n">
-        <v>1593.06</v>
+        <v>1955.65</v>
       </c>
       <c r="K26" t="n">
-        <v>1794.93</v>
+        <v>2039.37</v>
       </c>
       <c r="L26" t="n">
-        <v>1996.79</v>
+        <v>2123.09</v>
       </c>
       <c r="M26" t="n">
-        <v>2078.28</v>
+        <v>2315.58</v>
       </c>
       <c r="N26" t="n">
-        <v>2159.77</v>
+        <v>2508.08</v>
       </c>
       <c r="O26" t="n">
-        <v>2482.01</v>
+        <v>2483.03</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2685,12 +2695,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2698,68 +2710,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2177.78</v>
+        <v>2052.95</v>
       </c>
       <c r="C27" t="n">
-        <v>2384.47</v>
+        <v>2198.37</v>
       </c>
       <c r="D27" t="n">
-        <v>2027.05</v>
+        <v>1939.53</v>
       </c>
       <c r="E27" t="n">
-        <v>2053.05</v>
+        <v>1982.56</v>
       </c>
       <c r="F27" t="n">
-        <v>-124.43</v>
+        <v>-70.48999999999999</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0571</v>
+        <v>-0.0343</v>
       </c>
       <c r="H27" t="n">
-        <v>357.42</v>
+        <v>258.84</v>
       </c>
       <c r="I27" t="n">
-        <v>1654.39</v>
+        <v>1669.63</v>
       </c>
       <c r="J27" t="n">
-        <v>1955.65</v>
+        <v>1619.28</v>
       </c>
       <c r="K27" t="n">
-        <v>2039.37</v>
+        <v>1874.34</v>
       </c>
       <c r="L27" t="n">
-        <v>2123.09</v>
+        <v>2129.4</v>
       </c>
       <c r="M27" t="n">
-        <v>2315.58</v>
+        <v>2231.76</v>
       </c>
       <c r="N27" t="n">
-        <v>2508.08</v>
+        <v>2334.11</v>
       </c>
       <c r="O27" t="n">
-        <v>2483.03</v>
+        <v>2741.89</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2772,15 +2786,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2788,64 +2800,64 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2052.95</v>
+        <v>1982.55</v>
       </c>
       <c r="C28" t="n">
-        <v>2198.37</v>
+        <v>2165.67</v>
       </c>
       <c r="D28" t="n">
-        <v>1939.53</v>
+        <v>1979.08</v>
       </c>
       <c r="E28" t="n">
-        <v>1982.56</v>
+        <v>2109</v>
       </c>
       <c r="F28" t="n">
-        <v>-70.48999999999999</v>
+        <v>126.44</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0343</v>
+        <v>0.0638</v>
       </c>
       <c r="H28" t="n">
-        <v>258.84</v>
+        <v>186.59</v>
       </c>
       <c r="I28" t="n">
-        <v>1669.63</v>
+        <v>1680.69</v>
       </c>
       <c r="J28" t="n">
-        <v>1619.28</v>
+        <v>1680.52</v>
       </c>
       <c r="K28" t="n">
-        <v>1874.34</v>
+        <v>1853.14</v>
       </c>
       <c r="L28" t="n">
-        <v>2129.4</v>
+        <v>2025.75</v>
       </c>
       <c r="M28" t="n">
-        <v>2231.76</v>
+        <v>2111.98</v>
       </c>
       <c r="N28" t="n">
-        <v>2334.11</v>
+        <v>2198.21</v>
       </c>
       <c r="O28" t="n">
-        <v>2741.89</v>
+        <v>2457.21</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2853,83 +2865,83 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1982.55</v>
+        <v>2108.94</v>
       </c>
       <c r="C29" t="n">
-        <v>2165.67</v>
+        <v>2327.46</v>
       </c>
       <c r="D29" t="n">
-        <v>1979.08</v>
+        <v>2061.47</v>
       </c>
       <c r="E29" t="n">
-        <v>2109</v>
+        <v>2192.2</v>
       </c>
       <c r="F29" t="n">
-        <v>126.44</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0638</v>
+        <v>0.0395</v>
       </c>
       <c r="H29" t="n">
-        <v>186.59</v>
+        <v>265.99</v>
       </c>
       <c r="I29" t="n">
-        <v>1680.69</v>
+        <v>1792.49</v>
       </c>
       <c r="J29" t="n">
-        <v>1680.52</v>
+        <v>1940.72</v>
       </c>
       <c r="K29" t="n">
-        <v>1853.14</v>
+        <v>2015.7</v>
       </c>
       <c r="L29" t="n">
-        <v>2025.75</v>
+        <v>2090.68</v>
       </c>
       <c r="M29" t="n">
-        <v>2111.98</v>
+        <v>2202.29</v>
       </c>
       <c r="N29" t="n">
-        <v>2198.21</v>
+        <v>2313.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2457.21</v>
+        <v>2352.26</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,7 +2952,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2950,70 +2962,68 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2108.94</v>
+        <v>2192.33</v>
       </c>
       <c r="C30" t="n">
-        <v>2327.46</v>
+        <v>2464.78</v>
       </c>
       <c r="D30" t="n">
-        <v>2061.47</v>
+        <v>2176.32</v>
       </c>
       <c r="E30" t="n">
-        <v>2192.2</v>
+        <v>2264.92</v>
       </c>
       <c r="F30" t="n">
-        <v>83.20999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0332</v>
       </c>
       <c r="H30" t="n">
-        <v>265.99</v>
+        <v>288.46</v>
       </c>
       <c r="I30" t="n">
-        <v>1792.49</v>
+        <v>1795.48</v>
       </c>
       <c r="J30" t="n">
-        <v>1940.72</v>
+        <v>1925.08</v>
       </c>
       <c r="K30" t="n">
-        <v>2015.7</v>
+        <v>2059.21</v>
       </c>
       <c r="L30" t="n">
-        <v>2090.68</v>
+        <v>2193.33</v>
       </c>
       <c r="M30" t="n">
-        <v>2202.29</v>
+        <v>2325.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2313.9</v>
+        <v>2457.06</v>
       </c>
       <c r="O30" t="n">
-        <v>2352.26</v>
+        <v>2593.45</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3024,7 +3034,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3042,7 +3052,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3052,50 +3062,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2192.33</v>
+        <v>2264.87</v>
       </c>
       <c r="C31" t="n">
-        <v>2464.78</v>
+        <v>2422.86</v>
       </c>
       <c r="D31" t="n">
-        <v>2176.32</v>
+        <v>2262.05</v>
       </c>
       <c r="E31" t="n">
-        <v>2264.92</v>
+        <v>2369.73</v>
       </c>
       <c r="F31" t="n">
-        <v>72.72</v>
+        <v>104.81</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0463</v>
       </c>
       <c r="H31" t="n">
-        <v>288.46</v>
+        <v>160.81</v>
       </c>
       <c r="I31" t="n">
-        <v>1795.48</v>
+        <v>1887.87</v>
       </c>
       <c r="J31" t="n">
-        <v>1925.08</v>
+        <v>1948.64</v>
       </c>
       <c r="K31" t="n">
-        <v>2059.21</v>
+        <v>2120.69</v>
       </c>
       <c r="L31" t="n">
-        <v>2193.33</v>
+        <v>2292.74</v>
       </c>
       <c r="M31" t="n">
-        <v>2325.2</v>
+        <v>2409.15</v>
       </c>
       <c r="N31" t="n">
-        <v>2457.06</v>
+        <v>2525.56</v>
       </c>
       <c r="O31" t="n">
-        <v>2593.45</v>
+        <v>2753.24</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3106,7 +3116,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3116,87 +3126,91 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2264.87</v>
+        <v>2369.84</v>
       </c>
       <c r="C32" t="n">
-        <v>2422.86</v>
+        <v>2403.73</v>
       </c>
       <c r="D32" t="n">
-        <v>2262.05</v>
+        <v>2221.22</v>
       </c>
       <c r="E32" t="n">
-        <v>2369.73</v>
+        <v>2321.64</v>
       </c>
       <c r="F32" t="n">
-        <v>104.81</v>
+        <v>-48.09</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0463</v>
+        <v>-0.0203</v>
       </c>
       <c r="H32" t="n">
-        <v>160.81</v>
+        <v>182.5</v>
       </c>
       <c r="I32" t="n">
-        <v>1887.87</v>
+        <v>2101.25</v>
       </c>
       <c r="J32" t="n">
-        <v>1948.64</v>
+        <v>2222.56</v>
       </c>
       <c r="K32" t="n">
-        <v>2120.69</v>
+        <v>2289.33</v>
       </c>
       <c r="L32" t="n">
-        <v>2292.74</v>
+        <v>2356.09</v>
       </c>
       <c r="M32" t="n">
-        <v>2409.15</v>
+        <v>2450.13</v>
       </c>
       <c r="N32" t="n">
-        <v>2525.56</v>
+        <v>2544.17</v>
       </c>
       <c r="O32" t="n">
-        <v>2753.24</v>
+        <v>2583.67</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3204,169 +3218,167 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2369.84</v>
+        <v>2321.82</v>
       </c>
       <c r="C33" t="n">
-        <v>2403.73</v>
+        <v>2423.04</v>
       </c>
       <c r="D33" t="n">
-        <v>2221.22</v>
+        <v>2265.83</v>
       </c>
       <c r="E33" t="n">
-        <v>2321.64</v>
+        <v>2369.04</v>
       </c>
       <c r="F33" t="n">
-        <v>-48.09</v>
+        <v>47.41</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0204</v>
       </c>
       <c r="H33" t="n">
-        <v>182.5</v>
+        <v>157.21</v>
       </c>
       <c r="I33" t="n">
-        <v>2101.25</v>
+        <v>2038.72</v>
       </c>
       <c r="J33" t="n">
-        <v>2222.56</v>
+        <v>2143.71</v>
       </c>
       <c r="K33" t="n">
-        <v>2289.33</v>
+        <v>2230.38</v>
       </c>
       <c r="L33" t="n">
-        <v>2356.09</v>
+        <v>2317.06</v>
       </c>
       <c r="M33" t="n">
-        <v>2450.13</v>
+        <v>2412.89</v>
       </c>
       <c r="N33" t="n">
-        <v>2544.17</v>
+        <v>2508.72</v>
       </c>
       <c r="O33" t="n">
-        <v>2583.67</v>
+        <v>2586.23</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2321.82</v>
+        <v>2369.19</v>
       </c>
       <c r="C34" t="n">
-        <v>2423.04</v>
+        <v>2374.3</v>
       </c>
       <c r="D34" t="n">
-        <v>2265.83</v>
+        <v>2097.02</v>
       </c>
       <c r="E34" t="n">
-        <v>2369.04</v>
+        <v>2127.65</v>
       </c>
       <c r="F34" t="n">
-        <v>47.41</v>
+        <v>-241.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.1019</v>
       </c>
       <c r="H34" t="n">
-        <v>157.21</v>
+        <v>277.28</v>
       </c>
       <c r="I34" t="n">
-        <v>2038.72</v>
+        <v>2108.63</v>
       </c>
       <c r="J34" t="n">
-        <v>2143.71</v>
+        <v>2224.14</v>
       </c>
       <c r="K34" t="n">
-        <v>2230.38</v>
+        <v>2290.44</v>
       </c>
       <c r="L34" t="n">
-        <v>2317.06</v>
+        <v>2356.74</v>
       </c>
       <c r="M34" t="n">
-        <v>2412.89</v>
+        <v>2447.65</v>
       </c>
       <c r="N34" t="n">
-        <v>2508.72</v>
+        <v>2538.55</v>
       </c>
       <c r="O34" t="n">
-        <v>2586.23</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+        <v>2580.25</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3376,7 +3388,7 @@
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3384,69 +3396,63 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2369.19</v>
+        <v>2127.68</v>
       </c>
       <c r="C35" t="n">
-        <v>2374.3</v>
+        <v>2155.96</v>
       </c>
       <c r="D35" t="n">
-        <v>2097.02</v>
+        <v>2010.55</v>
       </c>
       <c r="E35" t="n">
-        <v>2127.65</v>
+        <v>2097.99</v>
       </c>
       <c r="F35" t="n">
-        <v>-241.4</v>
+        <v>-29.65</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.1019</v>
+        <v>-0.0139</v>
       </c>
       <c r="H35" t="n">
-        <v>277.28</v>
+        <v>145.41</v>
       </c>
       <c r="I35" t="n">
-        <v>2108.63</v>
+        <v>1819.74</v>
       </c>
       <c r="J35" t="n">
-        <v>2224.14</v>
+        <v>1796.35</v>
       </c>
       <c r="K35" t="n">
-        <v>2290.44</v>
+        <v>1989</v>
       </c>
       <c r="L35" t="n">
-        <v>2356.74</v>
+        <v>2181.65</v>
       </c>
       <c r="M35" t="n">
-        <v>2447.65</v>
+        <v>2266.29</v>
       </c>
       <c r="N35" t="n">
-        <v>2538.55</v>
+        <v>2350.92</v>
       </c>
       <c r="O35" t="n">
-        <v>2580.25</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>2651.59</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3458,7 +3464,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3468,50 +3474,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2127.68</v>
+        <v>2097.99</v>
       </c>
       <c r="C36" t="n">
-        <v>2155.96</v>
+        <v>2138.41</v>
       </c>
       <c r="D36" t="n">
-        <v>2010.55</v>
+        <v>1966.28</v>
       </c>
       <c r="E36" t="n">
-        <v>2097.99</v>
+        <v>2004.34</v>
       </c>
       <c r="F36" t="n">
-        <v>-29.65</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.0446</v>
       </c>
       <c r="H36" t="n">
-        <v>145.41</v>
+        <v>172.13</v>
       </c>
       <c r="I36" t="n">
-        <v>1819.74</v>
+        <v>1865.14</v>
       </c>
       <c r="J36" t="n">
-        <v>1796.35</v>
+        <v>1959.95</v>
       </c>
       <c r="K36" t="n">
-        <v>1989</v>
+        <v>2025.29</v>
       </c>
       <c r="L36" t="n">
-        <v>2181.65</v>
+        <v>2090.63</v>
       </c>
       <c r="M36" t="n">
-        <v>2266.29</v>
+        <v>2170.7</v>
       </c>
       <c r="N36" t="n">
-        <v>2350.92</v>
+        <v>2250.78</v>
       </c>
       <c r="O36" t="n">
-        <v>2651.59</v>
+        <v>2301.38</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3519,12 +3525,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3536,7 +3544,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3546,63 +3554,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2097.99</v>
+        <v>2004.24</v>
       </c>
       <c r="C37" t="n">
-        <v>2138.41</v>
+        <v>2017.61</v>
       </c>
       <c r="D37" t="n">
-        <v>1966.28</v>
+        <v>1506.51</v>
       </c>
       <c r="E37" t="n">
-        <v>2004.34</v>
+        <v>1686.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-93.65000000000001</v>
+        <v>-317.95</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0446</v>
+        <v>-0.1586</v>
       </c>
       <c r="H37" t="n">
-        <v>172.13</v>
+        <v>511.1</v>
       </c>
       <c r="I37" t="n">
-        <v>1865.14</v>
+        <v>1794.15</v>
       </c>
       <c r="J37" t="n">
-        <v>1959.95</v>
+        <v>1808.21</v>
       </c>
       <c r="K37" t="n">
-        <v>2025.29</v>
+        <v>1918.28</v>
       </c>
       <c r="L37" t="n">
-        <v>2090.63</v>
+        <v>2028.34</v>
       </c>
       <c r="M37" t="n">
-        <v>2170.7</v>
+        <v>2090.41</v>
       </c>
       <c r="N37" t="n">
-        <v>2250.78</v>
+        <v>2152.47</v>
       </c>
       <c r="O37" t="n">
-        <v>2301.38</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>2310.54</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3616,7 +3628,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3626,69 +3638,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2004.24</v>
+        <v>1686.25</v>
       </c>
       <c r="C38" t="n">
-        <v>2017.61</v>
+        <v>1729.35</v>
       </c>
       <c r="D38" t="n">
-        <v>1506.51</v>
+        <v>1603.83</v>
       </c>
       <c r="E38" t="n">
-        <v>1686.4</v>
+        <v>1724.61</v>
       </c>
       <c r="F38" t="n">
-        <v>-317.95</v>
+        <v>38.22</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.1586</v>
+        <v>0.0227</v>
       </c>
       <c r="H38" t="n">
-        <v>511.1</v>
+        <v>125.53</v>
       </c>
       <c r="I38" t="n">
-        <v>1794.15</v>
+        <v>995.4</v>
       </c>
       <c r="J38" t="n">
-        <v>1808.21</v>
+        <v>1137.46</v>
       </c>
       <c r="K38" t="n">
-        <v>1918.28</v>
+        <v>1430.85</v>
       </c>
       <c r="L38" t="n">
-        <v>2028.34</v>
+        <v>1724.23</v>
       </c>
       <c r="M38" t="n">
-        <v>2090.41</v>
+        <v>1941.95</v>
       </c>
       <c r="N38" t="n">
-        <v>2152.47</v>
+        <v>2159.67</v>
       </c>
       <c r="O38" t="n">
-        <v>2310.54</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>2528.71</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3700,60 +3706,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1686.25</v>
+        <v>1724.57</v>
       </c>
       <c r="C39" t="n">
-        <v>1729.35</v>
+        <v>1847.77</v>
       </c>
       <c r="D39" t="n">
-        <v>1603.83</v>
+        <v>1670.1</v>
       </c>
       <c r="E39" t="n">
-        <v>1724.61</v>
+        <v>1704.58</v>
       </c>
       <c r="F39" t="n">
-        <v>38.22</v>
+        <v>-20.03</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0227</v>
+        <v>-0.0116</v>
       </c>
       <c r="H39" t="n">
-        <v>125.53</v>
+        <v>177.67</v>
       </c>
       <c r="I39" t="n">
-        <v>995.4</v>
+        <v>1478.3</v>
       </c>
       <c r="J39" t="n">
-        <v>1137.46</v>
+        <v>1628.1</v>
       </c>
       <c r="K39" t="n">
-        <v>1430.85</v>
+        <v>1661.85</v>
       </c>
       <c r="L39" t="n">
-        <v>1724.23</v>
+        <v>1695.6</v>
       </c>
       <c r="M39" t="n">
-        <v>1941.95</v>
+        <v>1787.38</v>
       </c>
       <c r="N39" t="n">
-        <v>2159.67</v>
+        <v>1879.15</v>
       </c>
       <c r="O39" t="n">
-        <v>2528.71</v>
+        <v>1854.88</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3764,13 +3774,15 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3778,7 +3790,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3792,50 +3804,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1724.57</v>
+        <v>1704.63</v>
       </c>
       <c r="C40" t="n">
-        <v>1847.77</v>
+        <v>1776.83</v>
       </c>
       <c r="D40" t="n">
-        <v>1670.1</v>
+        <v>1510.51</v>
       </c>
       <c r="E40" t="n">
-        <v>1704.58</v>
+        <v>1570.36</v>
       </c>
       <c r="F40" t="n">
-        <v>-20.03</v>
+        <v>-134.22</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>177.67</v>
+        <v>266.33</v>
       </c>
       <c r="I40" t="n">
-        <v>1478.3</v>
+        <v>1492.44</v>
       </c>
       <c r="J40" t="n">
-        <v>1628.1</v>
+        <v>1499.74</v>
       </c>
       <c r="K40" t="n">
-        <v>1661.85</v>
+        <v>1615.75</v>
       </c>
       <c r="L40" t="n">
-        <v>1695.6</v>
+        <v>1731.76</v>
       </c>
       <c r="M40" t="n">
-        <v>1787.38</v>
+        <v>1793.41</v>
       </c>
       <c r="N40" t="n">
-        <v>1879.15</v>
+        <v>1855.07</v>
       </c>
       <c r="O40" t="n">
-        <v>1854.88</v>
+        <v>2025.44</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3843,18 +3855,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3862,64 +3874,60 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1704.63</v>
+        <v>1569.99</v>
       </c>
       <c r="C41" t="n">
-        <v>1776.83</v>
+        <v>1805.91</v>
       </c>
       <c r="D41" t="n">
-        <v>1510.51</v>
+        <v>1549.25</v>
       </c>
       <c r="E41" t="n">
-        <v>1570.36</v>
+        <v>1783.01</v>
       </c>
       <c r="F41" t="n">
-        <v>-134.22</v>
+        <v>212.64</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.1354</v>
       </c>
       <c r="H41" t="n">
-        <v>266.33</v>
+        <v>256.66</v>
       </c>
       <c r="I41" t="n">
-        <v>1492.44</v>
+        <v>1244.18</v>
       </c>
       <c r="J41" t="n">
-        <v>1499.74</v>
+        <v>1267.38</v>
       </c>
       <c r="K41" t="n">
-        <v>1615.75</v>
+        <v>1437.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1731.76</v>
+        <v>1607.02</v>
       </c>
       <c r="M41" t="n">
-        <v>1793.41</v>
+        <v>1703.52</v>
       </c>
       <c r="N41" t="n">
-        <v>1855.07</v>
+        <v>1800.03</v>
       </c>
       <c r="O41" t="n">
-        <v>2025.44</v>
+        <v>2043.16</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3927,79 +3935,85 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1569.99</v>
+        <v>1783</v>
       </c>
       <c r="C42" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D42" t="n">
-        <v>1549.25</v>
+        <v>1711.9</v>
       </c>
       <c r="E42" t="n">
-        <v>1783.01</v>
+        <v>1805.79</v>
       </c>
       <c r="F42" t="n">
-        <v>212.64</v>
+        <v>22.78</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.1354</v>
+        <v>0.0128</v>
       </c>
       <c r="H42" t="n">
-        <v>256.66</v>
+        <v>117.61</v>
       </c>
       <c r="I42" t="n">
-        <v>1244.18</v>
+        <v>1292.59</v>
       </c>
       <c r="J42" t="n">
-        <v>1267.38</v>
+        <v>1579.06</v>
       </c>
       <c r="K42" t="n">
-        <v>1437.2</v>
+        <v>1654.67</v>
       </c>
       <c r="L42" t="n">
-        <v>1607.02</v>
+        <v>1730.29</v>
       </c>
       <c r="M42" t="n">
-        <v>1703.52</v>
+        <v>1911.34</v>
       </c>
       <c r="N42" t="n">
-        <v>1800.03</v>
+        <v>2092.38</v>
       </c>
       <c r="O42" t="n">
-        <v>2043.16</v>
+        <v>2062.58</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4010,25 +4024,21 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4042,50 +4052,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1783</v>
+        <v>1805.76</v>
       </c>
       <c r="C43" t="n">
-        <v>1829.51</v>
+        <v>1944.16</v>
       </c>
       <c r="D43" t="n">
-        <v>1711.9</v>
+        <v>1749.35</v>
       </c>
       <c r="E43" t="n">
-        <v>1805.79</v>
+        <v>1871.51</v>
       </c>
       <c r="F43" t="n">
-        <v>22.78</v>
+        <v>65.72</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0364</v>
       </c>
       <c r="H43" t="n">
-        <v>117.61</v>
+        <v>194.81</v>
       </c>
       <c r="I43" t="n">
-        <v>1292.59</v>
+        <v>1594.29</v>
       </c>
       <c r="J43" t="n">
-        <v>1579.06</v>
+        <v>1705.72</v>
       </c>
       <c r="K43" t="n">
-        <v>1654.67</v>
+        <v>1746.98</v>
       </c>
       <c r="L43" t="n">
-        <v>1730.29</v>
+        <v>1788.25</v>
       </c>
       <c r="M43" t="n">
-        <v>1911.34</v>
+        <v>1864.59</v>
       </c>
       <c r="N43" t="n">
-        <v>2092.38</v>
+        <v>1940.94</v>
       </c>
       <c r="O43" t="n">
-        <v>2062.58</v>
+        <v>1947.13</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4096,21 +4106,25 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4124,50 +4138,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1805.76</v>
+        <v>1871.28</v>
       </c>
       <c r="C44" t="n">
-        <v>1944.16</v>
+        <v>1963.25</v>
       </c>
       <c r="D44" t="n">
-        <v>1749.35</v>
+        <v>1842.82</v>
       </c>
       <c r="E44" t="n">
-        <v>1871.51</v>
+        <v>1953.41</v>
       </c>
       <c r="F44" t="n">
-        <v>65.72</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0364</v>
+        <v>0.0438</v>
       </c>
       <c r="H44" t="n">
-        <v>194.81</v>
+        <v>120.43</v>
       </c>
       <c r="I44" t="n">
-        <v>1594.29</v>
+        <v>1554.53</v>
       </c>
       <c r="J44" t="n">
-        <v>1705.72</v>
+        <v>1689.07</v>
       </c>
       <c r="K44" t="n">
-        <v>1746.98</v>
+        <v>1774.1</v>
       </c>
       <c r="L44" t="n">
-        <v>1788.25</v>
+        <v>1859.13</v>
       </c>
       <c r="M44" t="n">
-        <v>1864.59</v>
+        <v>1968.92</v>
       </c>
       <c r="N44" t="n">
-        <v>1940.94</v>
+        <v>2078.7</v>
       </c>
       <c r="O44" t="n">
-        <v>1947.13</v>
+        <v>2138.97</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4178,7 +4192,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4188,15 +4202,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4210,69 +4222,71 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1871.28</v>
+        <v>1953.41</v>
       </c>
       <c r="C45" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D45" t="n">
-        <v>1842.82</v>
+        <v>1821.49</v>
       </c>
       <c r="E45" t="n">
-        <v>1953.41</v>
+        <v>1882.52</v>
       </c>
       <c r="F45" t="n">
-        <v>81.90000000000001</v>
+        <v>-70.89</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0363</v>
       </c>
       <c r="H45" t="n">
-        <v>120.43</v>
+        <v>154.98</v>
       </c>
       <c r="I45" t="n">
-        <v>1554.53</v>
+        <v>1722.39</v>
       </c>
       <c r="J45" t="n">
-        <v>1689.07</v>
+        <v>1858.17</v>
       </c>
       <c r="K45" t="n">
-        <v>1774.1</v>
+        <v>1893.2</v>
       </c>
       <c r="L45" t="n">
-        <v>1859.13</v>
+        <v>1928.22</v>
       </c>
       <c r="M45" t="n">
-        <v>1968.92</v>
+        <v>2013.63</v>
       </c>
       <c r="N45" t="n">
-        <v>2078.7</v>
+        <v>2099.03</v>
       </c>
       <c r="O45" t="n">
-        <v>2138.97</v>
+        <v>2083.68</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4280,81 +4294,77 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1953.41</v>
+        <v>1882.78</v>
       </c>
       <c r="C46" t="n">
-        <v>1976.46</v>
+        <v>1937.17</v>
       </c>
       <c r="D46" t="n">
-        <v>1821.49</v>
+        <v>1827.7</v>
       </c>
       <c r="E46" t="n">
-        <v>1882.52</v>
+        <v>1908.68</v>
       </c>
       <c r="F46" t="n">
-        <v>-70.89</v>
+        <v>26.16</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0363</v>
+        <v>0.0139</v>
       </c>
       <c r="H46" t="n">
-        <v>154.98</v>
+        <v>109.47</v>
       </c>
       <c r="I46" t="n">
-        <v>1722.39</v>
+        <v>1666.51</v>
       </c>
       <c r="J46" t="n">
-        <v>1858.17</v>
+        <v>1719.32</v>
       </c>
       <c r="K46" t="n">
-        <v>1893.2</v>
+        <v>1805.03</v>
       </c>
       <c r="L46" t="n">
-        <v>1928.22</v>
+        <v>1890.75</v>
       </c>
       <c r="M46" t="n">
-        <v>2013.63</v>
+        <v>1960.01</v>
       </c>
       <c r="N46" t="n">
-        <v>2099.03</v>
+        <v>2029.27</v>
       </c>
       <c r="O46" t="n">
-        <v>2083.68</v>
+        <v>2131.44</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4366,64 +4376,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1882.78</v>
+        <v>1908.72</v>
       </c>
       <c r="C47" t="n">
-        <v>1937.17</v>
+        <v>1928.99</v>
       </c>
       <c r="D47" t="n">
-        <v>1827.7</v>
+        <v>1852.84</v>
       </c>
       <c r="E47" t="n">
-        <v>1908.68</v>
+        <v>1873.94</v>
       </c>
       <c r="F47" t="n">
-        <v>26.16</v>
+        <v>-34.74</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0182</v>
       </c>
       <c r="H47" t="n">
-        <v>109.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>1666.51</v>
+        <v>1718.23</v>
       </c>
       <c r="J47" t="n">
-        <v>1719.32</v>
+        <v>1812.34</v>
       </c>
       <c r="K47" t="n">
-        <v>1805.03</v>
+        <v>1853.95</v>
       </c>
       <c r="L47" t="n">
-        <v>1890.75</v>
+        <v>1895.56</v>
       </c>
       <c r="M47" t="n">
-        <v>1960.01</v>
+        <v>1963.42</v>
       </c>
       <c r="N47" t="n">
-        <v>2029.27</v>
+        <v>2031.28</v>
       </c>
       <c r="O47" t="n">
-        <v>2131.44</v>
+        <v>2046.64</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4431,12 +4441,14 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4448,64 +4460,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1908.72</v>
+        <v>1873.97</v>
       </c>
       <c r="C48" t="n">
-        <v>1928.99</v>
+        <v>2545.88</v>
       </c>
       <c r="D48" t="n">
-        <v>1852.84</v>
+        <v>1870.75</v>
       </c>
       <c r="E48" t="n">
-        <v>1873.94</v>
+        <v>2463.82</v>
       </c>
       <c r="F48" t="n">
-        <v>-34.74</v>
+        <v>589.87</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.3148</v>
       </c>
       <c r="H48" t="n">
-        <v>76.15000000000001</v>
+        <v>675.13</v>
       </c>
       <c r="I48" t="n">
-        <v>1718.23</v>
+        <v>1776.69</v>
       </c>
       <c r="J48" t="n">
-        <v>1812.34</v>
+        <v>1789.3</v>
       </c>
       <c r="K48" t="n">
-        <v>1853.95</v>
+        <v>1835.87</v>
       </c>
       <c r="L48" t="n">
-        <v>1895.56</v>
+        <v>1882.43</v>
       </c>
       <c r="M48" t="n">
-        <v>1963.42</v>
+        <v>1912.02</v>
       </c>
       <c r="N48" t="n">
-        <v>2031.28</v>
+        <v>1941.61</v>
       </c>
       <c r="O48" t="n">
-        <v>2046.64</v>
+        <v>2005.15</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4513,83 +4525,83 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1873.97</v>
+        <v>2463.64</v>
       </c>
       <c r="C49" t="n">
-        <v>2545.88</v>
+        <v>2564.27</v>
       </c>
       <c r="D49" t="n">
-        <v>1870.75</v>
+        <v>2389.47</v>
       </c>
       <c r="E49" t="n">
-        <v>2463.82</v>
+        <v>2417.94</v>
       </c>
       <c r="F49" t="n">
-        <v>589.87</v>
+        <v>-45.88</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.3148</v>
+        <v>-0.0186</v>
       </c>
       <c r="H49" t="n">
-        <v>675.13</v>
+        <v>174.81</v>
       </c>
       <c r="I49" t="n">
-        <v>1776.69</v>
+        <v>1195.61</v>
       </c>
       <c r="J49" t="n">
-        <v>1789.3</v>
+        <v>1916.43</v>
       </c>
       <c r="K49" t="n">
-        <v>1835.87</v>
+        <v>2126.25</v>
       </c>
       <c r="L49" t="n">
-        <v>1882.43</v>
+        <v>2336.07</v>
       </c>
       <c r="M49" t="n">
-        <v>1912.02</v>
+        <v>2801.38</v>
       </c>
       <c r="N49" t="n">
-        <v>1941.61</v>
+        <v>3266.7</v>
       </c>
       <c r="O49" t="n">
-        <v>2005.15</v>
+        <v>3221.01</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4600,80 +4612,78 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2463.64</v>
+        <v>2417.9</v>
       </c>
       <c r="C50" t="n">
-        <v>2564.27</v>
+        <v>2545.62</v>
       </c>
       <c r="D50" t="n">
-        <v>2389.47</v>
+        <v>2356.19</v>
       </c>
       <c r="E50" t="n">
-        <v>2417.94</v>
+        <v>2514.55</v>
       </c>
       <c r="F50" t="n">
-        <v>-45.88</v>
+        <v>96.61</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0186</v>
+        <v>0.04</v>
       </c>
       <c r="H50" t="n">
-        <v>174.81</v>
+        <v>189.44</v>
       </c>
       <c r="I50" t="n">
-        <v>1195.61</v>
+        <v>2214.66</v>
       </c>
       <c r="J50" t="n">
-        <v>1916.43</v>
+        <v>2213.67</v>
       </c>
       <c r="K50" t="n">
-        <v>2126.25</v>
+        <v>2330.54</v>
       </c>
       <c r="L50" t="n">
-        <v>2336.07</v>
+        <v>2447.41</v>
       </c>
       <c r="M50" t="n">
-        <v>2801.38</v>
+        <v>2505.34</v>
       </c>
       <c r="N50" t="n">
-        <v>3266.7</v>
+        <v>2563.28</v>
       </c>
       <c r="O50" t="n">
-        <v>3221.01</v>
+        <v>2739.08</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4684,13 +4694,15 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4698,64 +4710,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2417.9</v>
+        <v>2514.58</v>
       </c>
       <c r="C51" t="n">
-        <v>2545.62</v>
+        <v>2663.05</v>
       </c>
       <c r="D51" t="n">
-        <v>2356.19</v>
+        <v>2406.91</v>
       </c>
       <c r="E51" t="n">
-        <v>2514.55</v>
+        <v>2477.02</v>
       </c>
       <c r="F51" t="n">
-        <v>96.61</v>
+        <v>-37.53</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.04</v>
+        <v>-0.0149</v>
       </c>
       <c r="H51" t="n">
-        <v>189.44</v>
+        <v>256.14</v>
       </c>
       <c r="I51" t="n">
-        <v>2214.66</v>
+        <v>2166.75</v>
       </c>
       <c r="J51" t="n">
-        <v>2213.67</v>
+        <v>2356.93</v>
       </c>
       <c r="K51" t="n">
-        <v>2330.54</v>
+        <v>2419.83</v>
       </c>
       <c r="L51" t="n">
-        <v>2447.41</v>
+        <v>2482.73</v>
       </c>
       <c r="M51" t="n">
-        <v>2505.34</v>
+        <v>2609.27</v>
       </c>
       <c r="N51" t="n">
-        <v>2563.28</v>
+        <v>2735.81</v>
       </c>
       <c r="O51" t="n">
-        <v>2739.08</v>
+        <v>2735.06</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4763,17 +4775,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4782,64 +4796,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2514.58</v>
+        <v>2476.6</v>
       </c>
       <c r="C52" t="n">
-        <v>2663.05</v>
+        <v>2659.72</v>
       </c>
       <c r="D52" t="n">
-        <v>2406.91</v>
+        <v>2357.96</v>
       </c>
       <c r="E52" t="n">
-        <v>2477.02</v>
+        <v>2643</v>
       </c>
       <c r="F52" t="n">
-        <v>-37.53</v>
+        <v>165.98</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.067</v>
       </c>
       <c r="H52" t="n">
-        <v>256.14</v>
+        <v>301.76</v>
       </c>
       <c r="I52" t="n">
-        <v>2166.75</v>
+        <v>2150.76</v>
       </c>
       <c r="J52" t="n">
-        <v>2356.93</v>
+        <v>2191.9</v>
       </c>
       <c r="K52" t="n">
-        <v>2419.83</v>
+        <v>2348.95</v>
       </c>
       <c r="L52" t="n">
-        <v>2482.73</v>
+        <v>2506</v>
       </c>
       <c r="M52" t="n">
-        <v>2609.27</v>
+        <v>2605.09</v>
       </c>
       <c r="N52" t="n">
-        <v>2735.81</v>
+        <v>2704.19</v>
       </c>
       <c r="O52" t="n">
-        <v>2735.06</v>
+        <v>2919.19</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4847,19 +4861,17 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4868,64 +4880,64 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2476.6</v>
+        <v>2642.78</v>
       </c>
       <c r="C53" t="n">
-        <v>2659.72</v>
+        <v>2805.5</v>
       </c>
       <c r="D53" t="n">
-        <v>2357.96</v>
+        <v>2628.69</v>
       </c>
       <c r="E53" t="n">
-        <v>2643</v>
+        <v>2686.93</v>
       </c>
       <c r="F53" t="n">
-        <v>165.98</v>
+        <v>43.93</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.067</v>
+        <v>0.0166</v>
       </c>
       <c r="H53" t="n">
-        <v>301.76</v>
+        <v>176.81</v>
       </c>
       <c r="I53" t="n">
-        <v>2150.76</v>
+        <v>2056.2</v>
       </c>
       <c r="J53" t="n">
-        <v>2191.9</v>
+        <v>2408.32</v>
       </c>
       <c r="K53" t="n">
-        <v>2348.95</v>
+        <v>2492.12</v>
       </c>
       <c r="L53" t="n">
-        <v>2506</v>
+        <v>2575.92</v>
       </c>
       <c r="M53" t="n">
-        <v>2605.09</v>
+        <v>2793.88</v>
       </c>
       <c r="N53" t="n">
-        <v>2704.19</v>
+        <v>3011.84</v>
       </c>
       <c r="O53" t="n">
-        <v>2919.19</v>
+        <v>2961.48</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4936,7 +4948,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4952,64 +4964,60 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2642.78</v>
+        <v>2687</v>
       </c>
       <c r="C54" t="n">
-        <v>2805.5</v>
+        <v>2773.52</v>
       </c>
       <c r="D54" t="n">
-        <v>2628.69</v>
+        <v>2635.48</v>
       </c>
       <c r="E54" t="n">
-        <v>2686.93</v>
+        <v>2726.51</v>
       </c>
       <c r="F54" t="n">
-        <v>43.93</v>
+        <v>39.58</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0166</v>
+        <v>0.0147</v>
       </c>
       <c r="H54" t="n">
-        <v>176.81</v>
+        <v>138.04</v>
       </c>
       <c r="I54" t="n">
-        <v>2056.2</v>
+        <v>2451.88</v>
       </c>
       <c r="J54" t="n">
-        <v>2408.32</v>
+        <v>2495.03</v>
       </c>
       <c r="K54" t="n">
-        <v>2492.12</v>
+        <v>2598.52</v>
       </c>
       <c r="L54" t="n">
-        <v>2575.92</v>
+        <v>2702.01</v>
       </c>
       <c r="M54" t="n">
-        <v>2793.88</v>
+        <v>2775.33</v>
       </c>
       <c r="N54" t="n">
-        <v>3011.84</v>
+        <v>2848.65</v>
       </c>
       <c r="O54" t="n">
-        <v>2961.48</v>
+        <v>2982.31</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5020,15 +5028,13 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5036,73 +5042,83 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2687</v>
+        <v>2726.65</v>
       </c>
       <c r="C55" t="n">
-        <v>2773.52</v>
+        <v>2736.79</v>
       </c>
       <c r="D55" t="n">
-        <v>2635.48</v>
+        <v>2406.15</v>
       </c>
       <c r="E55" t="n">
-        <v>2726.51</v>
+        <v>2534.7</v>
       </c>
       <c r="F55" t="n">
-        <v>39.58</v>
+        <v>-191.81</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0703</v>
       </c>
       <c r="H55" t="n">
-        <v>138.04</v>
+        <v>330.63</v>
       </c>
       <c r="I55" t="n">
-        <v>2451.88</v>
+        <v>2497.44</v>
       </c>
       <c r="J55" t="n">
-        <v>2495.03</v>
+        <v>2599.47</v>
       </c>
       <c r="K55" t="n">
-        <v>2598.52</v>
+        <v>2657.49</v>
       </c>
       <c r="L55" t="n">
-        <v>2702.01</v>
+        <v>2715.51</v>
       </c>
       <c r="M55" t="n">
-        <v>2775.33</v>
+        <v>2795.53</v>
       </c>
       <c r="N55" t="n">
-        <v>2848.65</v>
+        <v>2875.55</v>
       </c>
       <c r="O55" t="n">
-        <v>2982.31</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+        <v>2911.57</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5116,79 +5132,71 @@
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2726.65</v>
+        <v>2534.7</v>
       </c>
       <c r="C56" t="n">
-        <v>2736.79</v>
+        <v>2576.58</v>
       </c>
       <c r="D56" t="n">
-        <v>2406.15</v>
+        <v>2320.55</v>
       </c>
       <c r="E56" t="n">
-        <v>2534.7</v>
+        <v>2408.74</v>
       </c>
       <c r="F56" t="n">
-        <v>-191.81</v>
+        <v>-125.96</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0703</v>
+        <v>-0.0497</v>
       </c>
       <c r="H56" t="n">
-        <v>330.63</v>
+        <v>256.03</v>
       </c>
       <c r="I56" t="n">
-        <v>2497.44</v>
+        <v>2075.52</v>
       </c>
       <c r="J56" t="n">
-        <v>2599.47</v>
+        <v>2185.68</v>
       </c>
       <c r="K56" t="n">
-        <v>2657.49</v>
+        <v>2369.38</v>
       </c>
       <c r="L56" t="n">
-        <v>2715.51</v>
+        <v>2553.08</v>
       </c>
       <c r="M56" t="n">
-        <v>2795.53</v>
+        <v>2700.02</v>
       </c>
       <c r="N56" t="n">
-        <v>2875.55</v>
+        <v>2846.95</v>
       </c>
       <c r="O56" t="n">
-        <v>2911.57</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>3067.42</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5202,7 +5210,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5212,50 +5220,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2534.7</v>
+        <v>2408.74</v>
       </c>
       <c r="C57" t="n">
-        <v>2576.58</v>
+        <v>2522.84</v>
       </c>
       <c r="D57" t="n">
-        <v>2320.55</v>
+        <v>2280.55</v>
       </c>
       <c r="E57" t="n">
-        <v>2408.74</v>
+        <v>2355.95</v>
       </c>
       <c r="F57" t="n">
-        <v>-125.96</v>
+        <v>-52.79</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0497</v>
+        <v>-0.0219</v>
       </c>
       <c r="H57" t="n">
-        <v>256.03</v>
+        <v>242.29</v>
       </c>
       <c r="I57" t="n">
-        <v>2075.52</v>
+        <v>2064.52</v>
       </c>
       <c r="J57" t="n">
-        <v>2185.68</v>
+        <v>2132.8</v>
       </c>
       <c r="K57" t="n">
-        <v>2369.38</v>
+        <v>2280.73</v>
       </c>
       <c r="L57" t="n">
-        <v>2553.08</v>
+        <v>2428.65</v>
       </c>
       <c r="M57" t="n">
-        <v>2700.02</v>
+        <v>2536.76</v>
       </c>
       <c r="N57" t="n">
-        <v>2846.95</v>
+        <v>2644.86</v>
       </c>
       <c r="O57" t="n">
-        <v>3067.42</v>
+        <v>2832.61</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5265,12 +5273,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5282,7 +5290,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5292,50 +5300,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2408.74</v>
+        <v>2327.13</v>
       </c>
       <c r="C58" t="n">
-        <v>2522.84</v>
+        <v>2331.09</v>
       </c>
       <c r="D58" t="n">
-        <v>2358.75</v>
+        <v>2319.23</v>
       </c>
       <c r="E58" t="n">
-        <v>2376.32</v>
+        <v>2325.89</v>
       </c>
       <c r="F58" t="n">
-        <v>-32.42</v>
+        <v>-30.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0135</v>
+        <v>-0.0128</v>
       </c>
       <c r="H58" t="n">
-        <v>164.09</v>
+        <v>11.85</v>
       </c>
       <c r="I58" t="n">
-        <v>2064.52</v>
+        <v>2038.26</v>
       </c>
       <c r="J58" t="n">
-        <v>2132.8</v>
+        <v>2090.79</v>
       </c>
       <c r="K58" t="n">
-        <v>2280.73</v>
+        <v>2234.81</v>
       </c>
       <c r="L58" t="n">
-        <v>2428.65</v>
+        <v>2378.83</v>
       </c>
       <c r="M58" t="n">
-        <v>2536.76</v>
+        <v>2477.1</v>
       </c>
       <c r="N58" t="n">
-        <v>2644.86</v>
+        <v>2575.37</v>
       </c>
       <c r="O58" t="n">
-        <v>2832.61</v>
+        <v>2765.13</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5346,7 +5354,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5360,7 +5368,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>528.61</v>
       </c>
       <c r="I2" t="n">
-        <v>3200.94</v>
+        <v>3430.29</v>
       </c>
       <c r="J2" t="n">
-        <v>3512.62</v>
+        <v>3799.31</v>
       </c>
       <c r="K2" t="n">
-        <v>3827.44</v>
+        <v>3942.12</v>
       </c>
       <c r="L2" t="n">
-        <v>4142.26</v>
+        <v>4084.92</v>
       </c>
       <c r="M2" t="n">
-        <v>4455.51</v>
+        <v>4340.84</v>
       </c>
       <c r="N2" t="n">
-        <v>4768.76</v>
+        <v>4596.75</v>
       </c>
       <c r="O2" t="n">
-        <v>5085.15</v>
+        <v>4626.45</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +695,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5233,13 +5235,13 @@
         <v>2280.55</v>
       </c>
       <c r="E57" t="n">
-        <v>2355.95</v>
+        <v>2326.92</v>
       </c>
       <c r="F57" t="n">
-        <v>-52.79</v>
+        <v>-81.81999999999999</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0219</v>
+        <v>-0.034</v>
       </c>
       <c r="H57" t="n">
         <v>242.29</v>
@@ -5273,12 +5275,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5304,43 +5306,43 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2327.13</v>
+        <v>2320.41</v>
       </c>
       <c r="C58" t="n">
-        <v>2331.09</v>
+        <v>2327.18</v>
       </c>
       <c r="D58" t="n">
-        <v>2319.23</v>
+        <v>2316.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2325.89</v>
+        <v>2319.89</v>
       </c>
       <c r="F58" t="n">
-        <v>-30.06</v>
+        <v>-7.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0128</v>
+        <v>-0.003</v>
       </c>
       <c r="H58" t="n">
-        <v>11.85</v>
+        <v>10.47</v>
       </c>
       <c r="I58" t="n">
         <v>2038.26</v>
       </c>
       <c r="J58" t="n">
-        <v>2090.79</v>
+        <v>2047.24</v>
       </c>
       <c r="K58" t="n">
-        <v>2234.81</v>
+        <v>2205.78</v>
       </c>
       <c r="L58" t="n">
-        <v>2378.83</v>
+        <v>2364.31</v>
       </c>
       <c r="M58" t="n">
-        <v>2477.1</v>
+        <v>2448.06</v>
       </c>
       <c r="N58" t="n">
-        <v>2575.37</v>
+        <v>2531.82</v>
       </c>
       <c r="O58" t="n">
         <v>2765.13</v>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>528.61</v>
       </c>
       <c r="I2" t="n">
-        <v>3430.29</v>
+        <v>3451.12</v>
       </c>
       <c r="J2" t="n">
-        <v>3799.31</v>
+        <v>3825.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3942.12</v>
+        <v>3952.53</v>
       </c>
       <c r="L2" t="n">
-        <v>4084.92</v>
+        <v>4079.72</v>
       </c>
       <c r="M2" t="n">
-        <v>4340.84</v>
+        <v>4330.42</v>
       </c>
       <c r="N2" t="n">
-        <v>4596.75</v>
+        <v>4581.13</v>
       </c>
       <c r="O2" t="n">
-        <v>4626.45</v>
+        <v>4584.79</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -703,8 +703,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5306,25 +5308,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2320.41</v>
+        <v>2326.92</v>
       </c>
       <c r="C58" t="n">
-        <v>2327.18</v>
+        <v>2355.21</v>
       </c>
       <c r="D58" t="n">
-        <v>2316.7</v>
+        <v>2291.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2319.89</v>
+        <v>2352.18</v>
       </c>
       <c r="F58" t="n">
-        <v>-7.03</v>
+        <v>25.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0109</v>
       </c>
       <c r="H58" t="n">
-        <v>10.47</v>
+        <v>63.5</v>
       </c>
       <c r="I58" t="n">
         <v>2038.26</v>
@@ -5377,7 +5379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>528.61</v>
       </c>
       <c r="I2" t="n">
-        <v>3451.12</v>
+        <v>3495.96</v>
       </c>
       <c r="J2" t="n">
-        <v>3825.35</v>
+        <v>3881.39</v>
       </c>
       <c r="K2" t="n">
-        <v>3952.53</v>
+        <v>3974.95</v>
       </c>
       <c r="L2" t="n">
-        <v>4079.72</v>
+        <v>4068.51</v>
       </c>
       <c r="M2" t="n">
-        <v>4330.42</v>
+        <v>4308</v>
       </c>
       <c r="N2" t="n">
-        <v>4581.13</v>
+        <v>4547.5</v>
       </c>
       <c r="O2" t="n">
-        <v>4584.79</v>
+        <v>4495.11</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5311,22 +5311,22 @@
         <v>2326.92</v>
       </c>
       <c r="C58" t="n">
-        <v>2355.21</v>
+        <v>2359.88</v>
       </c>
       <c r="D58" t="n">
         <v>2291.7</v>
       </c>
       <c r="E58" t="n">
-        <v>2352.18</v>
+        <v>2304</v>
       </c>
       <c r="F58" t="n">
-        <v>25.26</v>
+        <v>-22.92</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>63.5</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="I58" t="n">
         <v>2038.26</v>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>528.61</v>
       </c>
       <c r="I2" t="n">
-        <v>3495.96</v>
+        <v>3593.86</v>
       </c>
       <c r="J2" t="n">
-        <v>3881.39</v>
+        <v>3934.79</v>
       </c>
       <c r="K2" t="n">
-        <v>3974.95</v>
+        <v>4004.19</v>
       </c>
       <c r="L2" t="n">
-        <v>4068.51</v>
+        <v>4073.6</v>
       </c>
       <c r="M2" t="n">
-        <v>4308</v>
+        <v>4278.76</v>
       </c>
       <c r="N2" t="n">
-        <v>4547.5</v>
+        <v>4483.93</v>
       </c>
       <c r="O2" t="n">
-        <v>4495.11</v>
+        <v>4417.57</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5311,22 +5311,22 @@
         <v>2326.92</v>
       </c>
       <c r="C58" t="n">
-        <v>2359.88</v>
+        <v>2388.03</v>
       </c>
       <c r="D58" t="n">
-        <v>2291.7</v>
+        <v>2181.59</v>
       </c>
       <c r="E58" t="n">
-        <v>2304</v>
+        <v>2210.01</v>
       </c>
       <c r="F58" t="n">
-        <v>-22.92</v>
+        <v>-116.91</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0502</v>
       </c>
       <c r="H58" t="n">
-        <v>68.18000000000001</v>
+        <v>206.45</v>
       </c>
       <c r="I58" t="n">
         <v>2038.26</v>
@@ -5355,12 +5355,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5377,11 +5379,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_weekly.xlsx
+++ b/three_gate/analysis/ETH_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>528.61</v>
       </c>
       <c r="I2" t="n">
-        <v>3593.86</v>
+        <v>3796.58</v>
       </c>
       <c r="J2" t="n">
-        <v>3934.79</v>
+        <v>4010.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4004.19</v>
+        <v>4054.87</v>
       </c>
       <c r="L2" t="n">
-        <v>4073.6</v>
+        <v>4098.94</v>
       </c>
       <c r="M2" t="n">
-        <v>4278.76</v>
+        <v>4228.08</v>
       </c>
       <c r="N2" t="n">
-        <v>4483.93</v>
+        <v>4357.23</v>
       </c>
       <c r="O2" t="n">
-        <v>4417.57</v>
+        <v>4316.21</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5314,19 +5314,19 @@
         <v>2388.03</v>
       </c>
       <c r="D58" t="n">
-        <v>2181.59</v>
+        <v>2233.37</v>
       </c>
       <c r="E58" t="n">
-        <v>2210.01</v>
+        <v>2239.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-116.91</v>
+        <v>-87.17</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0502</v>
+        <v>-0.0375</v>
       </c>
       <c r="H58" t="n">
-        <v>206.45</v>
+        <v>154.66</v>
       </c>
       <c r="I58" t="n">
         <v>2038.26</v>
